--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="193">
   <si>
     <t>code</t>
   </si>
@@ -109,6 +109,51 @@
     <t>7208061033000500 - UB - 2</t>
   </si>
   <si>
+    <t>7206040016002400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7202061009000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203011004200100 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271020009002300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020007000500 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271020004001901 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021005000401 - UB - 3</t>
+  </si>
+  <si>
+    <t>7202053007000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271010011002703 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210060013000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208020017000501 - UB - 2</t>
+  </si>
+  <si>
+    <t>7212020008100200 - UB - 6</t>
+  </si>
+  <si>
+    <t>7209051007000101 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210120012001800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206050001000600 - UB - 1</t>
+  </si>
+  <si>
     <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
   </si>
   <si>
@@ -181,6 +226,51 @@
     <t>BANK SULTENG</t>
   </si>
   <si>
+    <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
+  </si>
+  <si>
+    <t>BRI UNIT BUALEMO</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>ELISABET</t>
+  </si>
+  <si>
+    <t>HASRAT ABADI PT</t>
+  </si>
+  <si>
+    <t>JOYFUL KIDS</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
+  </si>
+  <si>
+    <t>UNIVERSITAS ISLAM NEGERI DATOKRAMA PALU</t>
+  </si>
+  <si>
+    <t>BANK BRI PALOLO, PT</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT PALU ANUGERAH</t>
+  </si>
+  <si>
+    <t>BRI UNIT BETELEME.PT</t>
+  </si>
+  <si>
+    <t>PAGADAIAN, PT</t>
+  </si>
+  <si>
+    <t>BANK SULTENG CAB SIGI PT</t>
+  </si>
+  <si>
+    <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
+  </si>
+  <si>
     <t>Kc.Buol@Bprmodex.com</t>
   </si>
   <si>
@@ -253,6 +343,51 @@
     <t>kaslambunu@yahoo.co.id</t>
   </si>
   <si>
+    <t>kc.tolitoli@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>nbobs@corp.brico.id</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>khenelis2@gmail.com</t>
+  </si>
+  <si>
+    <t>crc.mka@hasjrat.co.id</t>
+  </si>
+  <si>
+    <t>jk_joyfulkids@yahoo.com</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
+    <t>bca_luwuk_pajak@gmail.com</t>
+  </si>
+  <si>
+    <t>humas@iainpalu.ac.id</t>
+  </si>
+  <si>
+    <t>ferdydaud@socrpgi.co.id</t>
+  </si>
+  <si>
+    <t>paluanugerahprg@yahoo.com</t>
+  </si>
+  <si>
+    <t>n3633@co.rp.bri.co.id</t>
+  </si>
+  <si>
+    <t>cppampana@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>banksulteng_sigi@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>koperasi_maritim@yahoo.com</t>
+  </si>
+  <si>
     <t>bounced</t>
   </si>
   <si>
@@ -380,6 +515,84 @@
   </si>
   <si>
     <t>02 Jun 2026, 04:02:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:27</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:31</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:50:12</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:34:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:35:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:22:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:58:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:00</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:56</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:59</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:44:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:44:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:49:31</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:49:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:19:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:06:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:32:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:33:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:04:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:08:22</t>
   </si>
 </sst>
 </file>
@@ -737,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -768,19 +981,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -791,19 +1004,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -814,19 +1027,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -837,19 +1050,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -860,19 +1073,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -883,19 +1096,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -906,19 +1119,19 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -929,19 +1142,19 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -952,19 +1165,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -975,19 +1188,19 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -998,19 +1211,19 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F12" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1021,19 +1234,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1044,19 +1257,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F14" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1067,19 +1280,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1090,19 +1303,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1113,19 +1326,19 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1136,19 +1349,19 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1159,19 +1372,19 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1182,19 +1395,19 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1205,19 +1418,19 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1228,19 +1441,19 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1251,19 +1464,19 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1274,19 +1487,19 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1297,19 +1510,19 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1320,19 +1533,19 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1343,19 +1556,19 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E27" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1366,19 +1579,19 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F28" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1389,19 +1602,19 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1412,19 +1625,19 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1435,19 +1648,19 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1458,19 +1671,19 @@
         <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F32" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1481,19 +1694,19 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1504,19 +1717,19 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1527,19 +1740,19 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F35" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1550,19 +1763,19 @@
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -1573,19 +1786,19 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1596,19 +1809,19 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F38" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -1619,19 +1832,19 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -1642,19 +1855,19 @@
         <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -1665,19 +1878,19 @@
         <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -1688,19 +1901,19 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -1711,19 +1924,19 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F43" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -1734,19 +1947,19 @@
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F44" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -1757,19 +1970,19 @@
         <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D45" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E45" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F45" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -1780,19 +1993,19 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C46" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E46" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F46" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -1803,19 +2016,19 @@
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -1826,19 +2039,19 @@
         <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="E48" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F48" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -1849,21 +2062,711 @@
         <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>124</v>
+      </c>
+      <c r="E50" t="s">
+        <v>125</v>
+      </c>
+      <c r="F50" t="s">
+        <v>167</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" t="s">
+        <v>124</v>
+      </c>
+      <c r="E51" t="s">
+        <v>124</v>
+      </c>
+      <c r="F51" t="s">
+        <v>168</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>32</v>
+      </c>
+      <c r="B52" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" t="s">
+        <v>125</v>
+      </c>
+      <c r="E52" t="s">
+        <v>124</v>
+      </c>
+      <c r="F52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" t="s">
+        <v>169</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" t="s">
+        <v>125</v>
+      </c>
+      <c r="F54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" t="s">
+        <v>124</v>
+      </c>
+      <c r="F55" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>34</v>
+      </c>
+      <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>124</v>
+      </c>
+      <c r="E56" t="s">
+        <v>125</v>
+      </c>
+      <c r="F56" t="s">
+        <v>171</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" t="s">
+        <v>172</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" t="s">
+        <v>125</v>
+      </c>
+      <c r="E58" t="s">
+        <v>124</v>
+      </c>
+      <c r="F58" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+      <c r="D59" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" t="s">
+        <v>125</v>
+      </c>
+      <c r="F59" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" t="s">
+        <v>124</v>
+      </c>
+      <c r="E60" t="s">
+        <v>125</v>
+      </c>
+      <c r="F60" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" t="s">
+        <v>124</v>
+      </c>
+      <c r="E61" t="s">
+        <v>124</v>
+      </c>
+      <c r="F61" t="s">
+        <v>175</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" t="s">
+        <v>125</v>
+      </c>
+      <c r="F62" t="s">
+        <v>176</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" t="s">
+        <v>115</v>
+      </c>
+      <c r="D63" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" t="s">
+        <v>177</v>
+      </c>
+      <c r="G63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" t="s">
+        <v>125</v>
+      </c>
+      <c r="F64" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" t="s">
+        <v>116</v>
+      </c>
+      <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
+        <v>124</v>
+      </c>
+      <c r="F65" t="s">
+        <v>179</v>
+      </c>
+      <c r="G65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" t="s">
         <v>78</v>
       </c>
-      <c r="D49" t="s">
+      <c r="C66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" t="s">
+        <v>125</v>
+      </c>
+      <c r="F66" t="s">
+        <v>180</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67" t="s">
+        <v>117</v>
+      </c>
+      <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
+        <v>124</v>
+      </c>
+      <c r="F67" t="s">
+        <v>181</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" t="s">
         <v>79</v>
       </c>
-      <c r="E49" t="s">
+      <c r="C68" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" t="s">
+        <v>124</v>
+      </c>
+      <c r="F68" t="s">
+        <v>182</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" t="s">
         <v>79</v>
       </c>
-      <c r="F49" t="s">
+      <c r="C69" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" t="s">
+        <v>125</v>
+      </c>
+      <c r="F69" t="s">
+        <v>183</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" t="s">
+        <v>125</v>
+      </c>
+      <c r="F70" t="s">
+        <v>184</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" t="s">
+        <v>124</v>
+      </c>
+      <c r="E71" t="s">
+        <v>124</v>
+      </c>
+      <c r="F71" t="s">
+        <v>185</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>124</v>
+      </c>
+      <c r="E72" t="s">
+        <v>125</v>
+      </c>
+      <c r="F72" t="s">
+        <v>186</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" t="s">
+        <v>120</v>
+      </c>
+      <c r="D73" t="s">
+        <v>124</v>
+      </c>
+      <c r="E73" t="s">
+        <v>124</v>
+      </c>
+      <c r="F73" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" t="s">
         <v>121</v>
       </c>
-      <c r="G49">
+      <c r="D74" t="s">
+        <v>124</v>
+      </c>
+      <c r="E74" t="s">
+        <v>125</v>
+      </c>
+      <c r="F74" t="s">
+        <v>187</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>43</v>
+      </c>
+      <c r="B75" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" t="s">
+        <v>188</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" t="s">
+        <v>124</v>
+      </c>
+      <c r="E76" t="s">
+        <v>125</v>
+      </c>
+      <c r="F76" t="s">
+        <v>189</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>122</v>
+      </c>
+      <c r="D77" t="s">
+        <v>124</v>
+      </c>
+      <c r="E77" t="s">
+        <v>124</v>
+      </c>
+      <c r="F77" t="s">
+        <v>190</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>123</v>
+      </c>
+      <c r="D78" t="s">
+        <v>124</v>
+      </c>
+      <c r="E78" t="s">
+        <v>125</v>
+      </c>
+      <c r="F78" t="s">
+        <v>191</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79" t="s">
+        <v>123</v>
+      </c>
+      <c r="D79" t="s">
+        <v>124</v>
+      </c>
+      <c r="E79" t="s">
+        <v>124</v>
+      </c>
+      <c r="F79" t="s">
+        <v>192</v>
+      </c>
+      <c r="G79">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="438">
   <si>
     <t>code</t>
   </si>
@@ -154,6 +154,162 @@
     <t>7206050001000600 - UB - 1</t>
   </si>
   <si>
+    <t>7205000000000000 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271041003000901 - UB - 2</t>
+  </si>
+  <si>
+    <t>7204070011000302 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271040003000102 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204070011000100 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271041003001200 - UB - 5</t>
+  </si>
+  <si>
+    <t>7271030005002500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031001002701 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205090010000301 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206040016001300 - UB - 2</t>
+  </si>
+  <si>
+    <t>7208011001000200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021005000105 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030002000300 - UB - 2</t>
+  </si>
+  <si>
+    <t>7203030021001300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031006003901 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030004002700 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271011003000101 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030004000800 - UB - 4</t>
+  </si>
+  <si>
+    <t>7203021005000406 - UB - 10</t>
+  </si>
+  <si>
+    <t>7271030002001000 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031006001100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7209051019000800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208030015000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206010003001100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208021003000500 - UB - 2</t>
+  </si>
+  <si>
+    <t>7212020008000900 - UB - 1</t>
+  </si>
+  <si>
+    <t>7209050015000600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210121006000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031002000701 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205130008000401 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271040002000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204071001001500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271040001000102 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271031007000200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205080024000400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204032006001600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031006003901 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271040004001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030005003300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212010010000100 - UB - 8</t>
+  </si>
+  <si>
+    <t>7212040006400100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212040006000200 - UB - 2</t>
+  </si>
+  <si>
+    <t>7201040014000300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7201040016000100 - UB - 2</t>
+  </si>
+  <si>
+    <t>7212050009000200 - UB - 12</t>
+  </si>
+  <si>
+    <t>7212040009000200 - UB - 3</t>
+  </si>
+  <si>
+    <t>7212080001200100 - UB - 5</t>
+  </si>
+  <si>
+    <t>7202010020000300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203031006000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031002001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030005002800 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271020009001901 - UB - 1</t>
+  </si>
+  <si>
     <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
   </si>
   <si>
@@ -271,6 +427,159 @@
     <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
   </si>
   <si>
+    <t>PDAM KAB DONGGALA</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT TAWAELI</t>
+  </si>
+  <si>
+    <t>BANK BPD</t>
+  </si>
+  <si>
+    <t>SPBU KAYUMALUE</t>
+  </si>
+  <si>
+    <t>AKAR DAYA MANDIRI PT</t>
+  </si>
+  <si>
+    <t>BANGUN PALU SULAWESI TENGAH</t>
+  </si>
+  <si>
+    <t>ANUGERAHPERDANA</t>
+  </si>
+  <si>
+    <t>SETIA MULIA ABADI</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
+  </si>
+  <si>
+    <t>GALAXI INDO PRATAMA, CV</t>
+  </si>
+  <si>
+    <t>SAHABAT TANI, TOKO</t>
+  </si>
+  <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA, PT</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>PT VARIA KENCANA</t>
+  </si>
+  <si>
+    <t>BANK KB BUKOPIN TBK</t>
+  </si>
+  <si>
+    <t>MITRA ABADI CV</t>
+  </si>
+  <si>
+    <t>PT. KIMIA FARMA TRADING &amp; DISTRIBUTION, Kantor Cabang Palu</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>KPN ANUTAN</t>
+  </si>
+  <si>
+    <t>RSUD UNDATA PROV. SULTENG</t>
+  </si>
+  <si>
+    <t>BANK RAKYAT INDONESIA TBK, PT</t>
+  </si>
+  <si>
+    <t>SPBU AMPI BABO</t>
+  </si>
+  <si>
+    <t>BANK SULTENG UNIT SONI</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT BINARTA LUHUR</t>
+  </si>
+  <si>
+    <t>MORI DUTA MINERAL</t>
+  </si>
+  <si>
+    <t>BPR MODERN EXSPRESS, PT/BPR PALU LOKADANA UTAMA, PT</t>
+  </si>
+  <si>
+    <t>RSUD TORABELO</t>
+  </si>
+  <si>
+    <t>CITRA BARKATAMA KARYA</t>
+  </si>
+  <si>
+    <t>PT. BANK SULTENG KAS LABEAN</t>
+  </si>
+  <si>
+    <t>HAYCARB PALU MITRA PT</t>
+  </si>
+  <si>
+    <t>AMRI MARGA JAYA, PT</t>
+  </si>
+  <si>
+    <t>MANDIRI ARGO LESTARI CV</t>
+  </si>
+  <si>
+    <t>SULAWESI CENTRAL COMMODITY</t>
+  </si>
+  <si>
+    <t>ASTUN HI. ARSYAD</t>
+  </si>
+  <si>
+    <t>PLTA Poso 1</t>
+  </si>
+  <si>
+    <t>BATU HITAM JASA PERTAMBANGAN</t>
+  </si>
+  <si>
+    <t>PRIMA GELORA AGUNG LESTARI, PT</t>
+  </si>
+  <si>
+    <t>ADIPURA NOVEGA,CV</t>
+  </si>
+  <si>
+    <t>TIMUR JAYA INDO MAKMUR, PT</t>
+  </si>
+  <si>
+    <t>Toko suharman &lt;Darmiati&gt;</t>
+  </si>
+  <si>
+    <t>GENBA INDO RESOURCES</t>
+  </si>
+  <si>
+    <t>BPR Syariah &lt;Agus Supriadi&gt;</t>
+  </si>
+  <si>
+    <t>BRI UNIT SALAKAN</t>
+  </si>
+  <si>
+    <t>MULIA PACIFIC RESOURCES BHL</t>
+  </si>
+  <si>
+    <t>KEINZ VENTURA PT</t>
+  </si>
+  <si>
+    <t>FIVE STAR INDONESIA - HOFFMEN</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>PT. KIMIA FARMA APOTEK, Kantor Cabang Palu</t>
+  </si>
+  <si>
+    <t>INDOSAT OOREDOO, PT</t>
+  </si>
+  <si>
+    <t>PATRIOT BHAKTI NUSANTARA</t>
+  </si>
+  <si>
     <t>Kc.Buol@Bprmodex.com</t>
   </si>
   <si>
@@ -388,6 +697,162 @@
     <t>koperasi_maritim@yahoo.com</t>
   </si>
   <si>
+    <t>pdam_donggala@gmail.com</t>
+  </si>
+  <si>
+    <t>n3448@bricorp.co.id</t>
+  </si>
+  <si>
+    <t>bsposo@yahoo.com</t>
+  </si>
+  <si>
+    <t>spbutawaeli74943313@gmail.com</t>
+  </si>
+  <si>
+    <t>akardayamandiri49@gmail.com</t>
+  </si>
+  <si>
+    <t>hlppalu.bangunpalusulawesitengah@yahoo.com</t>
+  </si>
+  <si>
+    <t>risky.anugerahperdana@yahoo.com</t>
+  </si>
+  <si>
+    <t>pt.sma_palu@yahoo.com</t>
+  </si>
+  <si>
+    <t>bprlabuan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>galaxiindopratamatolis@gmail.com</t>
+  </si>
+  <si>
+    <t>sonnykandou80@gmail.com</t>
+  </si>
+  <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>bprpalulokadana@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>ptvariakencana@yahoo.com</t>
+  </si>
+  <si>
+    <t>idham.halid@bukopin.co.id</t>
+  </si>
+  <si>
+    <t>maol.palu@gmail.com</t>
+  </si>
+  <si>
+    <t>kftdpaly@kftd.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>kprianutan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>rsudundata@gmail.comsultengprov.co.id</t>
+  </si>
+  <si>
+    <t>n5210@copr.bri.co.id</t>
+  </si>
+  <si>
+    <t>spbu_ampibabo@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>febrialdin.rial@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>binartasumber@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>stevankristy@moridutamineral.com</t>
+  </si>
+  <si>
+    <t>kc.touna@bprpalulokadana.com</t>
+  </si>
+  <si>
+    <t>rsudsigi@gmail.com</t>
+  </si>
+  <si>
+    <t>ptcitrabarkatamakarya@yahoo.com</t>
+  </si>
+  <si>
+    <t>banksulteng_kaslabean@yahoo.com</t>
+  </si>
+  <si>
+    <t>hpm-accountr@haycarbindo.com</t>
+  </si>
+  <si>
+    <t>pt.amrimargajaya@ymail.com</t>
+  </si>
+  <si>
+    <t>cvmandiriargolestari@gmail.com</t>
+  </si>
+  <si>
+    <t>sulawesicentralcommodity@yahoo.com</t>
+  </si>
+  <si>
+    <t>astunhiarsyad28@gmail.com</t>
+  </si>
+  <si>
+    <t>pltaposo2@posoenergy.com</t>
+  </si>
+  <si>
+    <t>batuhitamjasapertambangan@yahoo.com</t>
+  </si>
+  <si>
+    <t>primagelora_palu@yahoo.com</t>
+  </si>
+  <si>
+    <t>adipuranovega@gmail.com</t>
+  </si>
+  <si>
+    <t>admin-krlm@tsanin-group.com</t>
+  </si>
+  <si>
+    <t>ktuana@asta.go.id</t>
+  </si>
+  <si>
+    <t>gir.mining2019@gmail.com</t>
+  </si>
+  <si>
+    <t>avatarcrue@gmail.com</t>
+  </si>
+  <si>
+    <t>n5164@corp.bri.com</t>
+  </si>
+  <si>
+    <t>muliapacificresources@gmail.com</t>
+  </si>
+  <si>
+    <t>keinzventura1205@gmail.com</t>
+  </si>
+  <si>
+    <t>lidychayadi@gmail.com</t>
+  </si>
+  <si>
+    <t>banksulteng.toili@yahoo.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>kimiafarmavetran93@gmail.com</t>
+  </si>
+  <si>
+    <t>ferdy@mitradm.com</t>
+  </si>
+  <si>
+    <t>pt.patriotbhaktinusantara@gmail.com</t>
+  </si>
+  <si>
     <t>bounced</t>
   </si>
   <si>
@@ -593,6 +1058,276 @@
   </si>
   <si>
     <t>02 Jun 2026, 10:08:22</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:31:35</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:35:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:02</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:17:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:12:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:21:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:22:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:08:18</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:08:36</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:29:34</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:30:02</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:01:57</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:33:19</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:34:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:34:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:34:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:39:18</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:39:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:22:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:22:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:06:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:06:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:52:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:52:54</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:01:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:45:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:46:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:59:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:00:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:50:41</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:04:03</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:57:07</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:58:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:09:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:10:04</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:12:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:06:09</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:37:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:37:42</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:11:00</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:11:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:07:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:08:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:36:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:39:45</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:23:45</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:26:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:59:12</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:59:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:10:57</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:47:26</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:47:27</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:58:46</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:02</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:36:44</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:36:45</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:21:19</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:01:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:01:31</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:00:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:00:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:11:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:12:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:59:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:44:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:44:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:39:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:39:39</t>
   </si>
 </sst>
 </file>
@@ -950,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -981,19 +1716,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F2" t="s">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1004,19 +1739,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1027,19 +1762,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F4" t="s">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1050,19 +1785,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F5" t="s">
-        <v>128</v>
+        <v>283</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1073,19 +1808,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F6" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1096,19 +1831,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F7" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1119,19 +1854,19 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1142,19 +1877,19 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>286</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1165,19 +1900,19 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>287</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1188,19 +1923,19 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>132</v>
+        <v>287</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1211,19 +1946,19 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1234,19 +1969,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F13" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1257,19 +1992,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F14" t="s">
-        <v>135</v>
+        <v>290</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1280,19 +2015,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F15" t="s">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1303,19 +2038,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>292</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1326,19 +2061,19 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F17" t="s">
-        <v>138</v>
+        <v>293</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1349,19 +2084,19 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F18" t="s">
-        <v>139</v>
+        <v>294</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1372,19 +2107,19 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>295</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1395,19 +2130,19 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E20" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F20" t="s">
-        <v>141</v>
+        <v>296</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1418,19 +2153,19 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>297</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1441,19 +2176,19 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>298</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1464,19 +2199,19 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1487,19 +2222,19 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F24" t="s">
-        <v>145</v>
+        <v>300</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1510,19 +2245,19 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F25" t="s">
-        <v>146</v>
+        <v>301</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1533,19 +2268,19 @@
         <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E26" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F26" t="s">
-        <v>147</v>
+        <v>302</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1556,19 +2291,19 @@
         <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F27" t="s">
-        <v>148</v>
+        <v>303</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1579,19 +2314,19 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E28" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>304</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1602,19 +2337,19 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F29" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="G29">
         <v>2</v>
@@ -1625,19 +2360,19 @@
         <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1648,19 +2383,19 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E31" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -1671,19 +2406,19 @@
         <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1694,19 +2429,19 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F33" t="s">
-        <v>154</v>
+        <v>309</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -1717,19 +2452,19 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1740,19 +2475,19 @@
         <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F35" t="s">
-        <v>155</v>
+        <v>310</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -1763,19 +2498,19 @@
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F36" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -1786,19 +2521,19 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E37" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F37" t="s">
-        <v>156</v>
+        <v>311</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -1809,19 +2544,19 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E38" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F38" t="s">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -1832,19 +2567,19 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F39" t="s">
-        <v>158</v>
+        <v>313</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -1855,19 +2590,19 @@
         <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F40" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -1878,19 +2613,19 @@
         <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="D41" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E41" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F41" t="s">
-        <v>159</v>
+        <v>314</v>
       </c>
       <c r="G41">
         <v>2</v>
@@ -1901,19 +2636,19 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F42" t="s">
-        <v>160</v>
+        <v>315</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -1924,19 +2659,19 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F43" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -1947,19 +2682,19 @@
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="D44" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F44" t="s">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -1970,19 +2705,19 @@
         <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="D45" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E45" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F45" t="s">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -1993,19 +2728,19 @@
         <v>29</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E46" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F46" t="s">
-        <v>163</v>
+        <v>318</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2016,19 +2751,19 @@
         <v>29</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="D47" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F47" t="s">
-        <v>164</v>
+        <v>319</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -2039,19 +2774,19 @@
         <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="D48" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E48" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F48" t="s">
-        <v>165</v>
+        <v>320</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2062,19 +2797,19 @@
         <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F49" t="s">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="G49">
         <v>2</v>
@@ -2085,19 +2820,19 @@
         <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F50" t="s">
-        <v>167</v>
+        <v>322</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2108,19 +2843,19 @@
         <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="D51" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F51" t="s">
-        <v>168</v>
+        <v>323</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -2131,19 +2866,19 @@
         <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>213</v>
       </c>
       <c r="D52" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E52" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F52" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2154,19 +2889,19 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>213</v>
       </c>
       <c r="D53" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E53" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F53" t="s">
-        <v>169</v>
+        <v>324</v>
       </c>
       <c r="G53">
         <v>2</v>
@@ -2177,19 +2912,19 @@
         <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="D54" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E54" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F54" t="s">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2200,19 +2935,19 @@
         <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="D55" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E55" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F55" t="s">
-        <v>170</v>
+        <v>325</v>
       </c>
       <c r="G55">
         <v>2</v>
@@ -2223,19 +2958,19 @@
         <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E56" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F56" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2246,19 +2981,19 @@
         <v>34</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F57" t="s">
-        <v>172</v>
+        <v>327</v>
       </c>
       <c r="G57">
         <v>2</v>
@@ -2269,19 +3004,19 @@
         <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="D58" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E58" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F58" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2292,19 +3027,19 @@
         <v>35</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="D59" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F59" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G59">
         <v>2</v>
@@ -2315,19 +3050,19 @@
         <v>36</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F60" t="s">
-        <v>174</v>
+        <v>329</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2338,19 +3073,19 @@
         <v>36</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="D61" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F61" t="s">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -2361,19 +3096,19 @@
         <v>37</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E62" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F62" t="s">
-        <v>176</v>
+        <v>331</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2384,19 +3119,19 @@
         <v>37</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F63" t="s">
-        <v>177</v>
+        <v>332</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -2407,19 +3142,19 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E64" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>333</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2430,19 +3165,19 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E65" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F65" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -2453,19 +3188,19 @@
         <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F66" t="s">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2476,19 +3211,19 @@
         <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E67" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F67" t="s">
-        <v>181</v>
+        <v>336</v>
       </c>
       <c r="G67">
         <v>2</v>
@@ -2499,19 +3234,19 @@
         <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="C68" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="D68" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E68" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F68" t="s">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2522,19 +3257,19 @@
         <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
       <c r="D69" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="E69" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F69" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="G69">
         <v>2</v>
@@ -2545,19 +3280,19 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="D70" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E70" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F70" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -2568,19 +3303,19 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="D71" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F71" t="s">
-        <v>185</v>
+        <v>340</v>
       </c>
       <c r="G71">
         <v>2</v>
@@ -2591,19 +3326,19 @@
         <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F72" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -2614,19 +3349,19 @@
         <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="D73" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E73" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F73" t="s">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2637,19 +3372,19 @@
         <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F74" t="s">
-        <v>187</v>
+        <v>342</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -2660,19 +3395,19 @@
         <v>43</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="D75" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F75" t="s">
-        <v>188</v>
+        <v>343</v>
       </c>
       <c r="G75">
         <v>2</v>
@@ -2683,19 +3418,19 @@
         <v>44</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F76" t="s">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -2706,19 +3441,19 @@
         <v>44</v>
       </c>
       <c r="B77" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C77" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E77" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="F77" t="s">
-        <v>190</v>
+        <v>345</v>
       </c>
       <c r="G77">
         <v>2</v>
@@ -2729,19 +3464,19 @@
         <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>279</v>
       </c>
       <c r="E78" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="F78" t="s">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -2752,21 +3487,2413 @@
         <v>45</v>
       </c>
       <c r="B79" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" t="s">
+        <v>226</v>
+      </c>
+      <c r="D79" t="s">
+        <v>279</v>
+      </c>
+      <c r="E79" t="s">
+        <v>279</v>
+      </c>
+      <c r="F79" t="s">
+        <v>347</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" t="s">
+        <v>137</v>
+      </c>
+      <c r="C80" t="s">
+        <v>227</v>
+      </c>
+      <c r="D80" t="s">
+        <v>280</v>
+      </c>
+      <c r="E80" t="s">
+        <v>279</v>
+      </c>
+      <c r="F80" t="s">
+        <v>348</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" t="s">
+        <v>227</v>
+      </c>
+      <c r="D81" t="s">
+        <v>280</v>
+      </c>
+      <c r="E81" t="s">
+        <v>280</v>
+      </c>
+      <c r="F81" t="s">
+        <v>348</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" t="s">
+        <v>228</v>
+      </c>
+      <c r="D82" t="s">
+        <v>279</v>
+      </c>
+      <c r="E82" t="s">
+        <v>280</v>
+      </c>
+      <c r="F82" t="s">
+        <v>349</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>47</v>
+      </c>
+      <c r="B83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" t="s">
+        <v>279</v>
+      </c>
+      <c r="E83" t="s">
+        <v>279</v>
+      </c>
+      <c r="F83" t="s">
+        <v>349</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" t="s">
+        <v>139</v>
+      </c>
+      <c r="C84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D84" t="s">
+        <v>279</v>
+      </c>
+      <c r="E84" t="s">
+        <v>280</v>
+      </c>
+      <c r="F84" t="s">
+        <v>350</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" t="s">
+        <v>139</v>
+      </c>
+      <c r="C85" t="s">
+        <v>229</v>
+      </c>
+      <c r="D85" t="s">
+        <v>279</v>
+      </c>
+      <c r="E85" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" t="s">
+        <v>351</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86" t="s">
+        <v>230</v>
+      </c>
+      <c r="D86" t="s">
+        <v>279</v>
+      </c>
+      <c r="E86" t="s">
+        <v>280</v>
+      </c>
+      <c r="F86" t="s">
+        <v>352</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s">
+        <v>140</v>
+      </c>
+      <c r="C87" t="s">
+        <v>230</v>
+      </c>
+      <c r="D87" t="s">
+        <v>279</v>
+      </c>
+      <c r="E87" t="s">
+        <v>279</v>
+      </c>
+      <c r="F87" t="s">
+        <v>353</v>
+      </c>
+      <c r="G87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" t="s">
+        <v>231</v>
+      </c>
+      <c r="D88" t="s">
+        <v>279</v>
+      </c>
+      <c r="E88" t="s">
+        <v>280</v>
+      </c>
+      <c r="F88" t="s">
+        <v>354</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" t="s">
+        <v>231</v>
+      </c>
+      <c r="D89" t="s">
+        <v>279</v>
+      </c>
+      <c r="E89" t="s">
+        <v>279</v>
+      </c>
+      <c r="F89" t="s">
+        <v>354</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" t="s">
+        <v>142</v>
+      </c>
+      <c r="C90" t="s">
+        <v>232</v>
+      </c>
+      <c r="D90" t="s">
+        <v>279</v>
+      </c>
+      <c r="E90" t="s">
+        <v>280</v>
+      </c>
+      <c r="F90" t="s">
+        <v>355</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>51</v>
+      </c>
+      <c r="B91" t="s">
+        <v>142</v>
+      </c>
+      <c r="C91" t="s">
+        <v>232</v>
+      </c>
+      <c r="D91" t="s">
+        <v>279</v>
+      </c>
+      <c r="E91" t="s">
+        <v>279</v>
+      </c>
+      <c r="F91" t="s">
+        <v>356</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>52</v>
+      </c>
+      <c r="B92" t="s">
+        <v>143</v>
+      </c>
+      <c r="C92" t="s">
+        <v>233</v>
+      </c>
+      <c r="D92" t="s">
+        <v>279</v>
+      </c>
+      <c r="E92" t="s">
+        <v>280</v>
+      </c>
+      <c r="F92" t="s">
+        <v>357</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" t="s">
+        <v>233</v>
+      </c>
+      <c r="D93" t="s">
+        <v>279</v>
+      </c>
+      <c r="E93" t="s">
+        <v>279</v>
+      </c>
+      <c r="F93" t="s">
+        <v>358</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" t="s">
+        <v>144</v>
+      </c>
+      <c r="C94" t="s">
+        <v>234</v>
+      </c>
+      <c r="D94" t="s">
+        <v>279</v>
+      </c>
+      <c r="E94" t="s">
+        <v>280</v>
+      </c>
+      <c r="F94" t="s">
+        <v>359</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" t="s">
+        <v>144</v>
+      </c>
+      <c r="C95" t="s">
+        <v>234</v>
+      </c>
+      <c r="D95" t="s">
+        <v>279</v>
+      </c>
+      <c r="E95" t="s">
+        <v>279</v>
+      </c>
+      <c r="F95" t="s">
+        <v>360</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" t="s">
+        <v>235</v>
+      </c>
+      <c r="D96" t="s">
+        <v>279</v>
+      </c>
+      <c r="E96" t="s">
+        <v>280</v>
+      </c>
+      <c r="F96" t="s">
+        <v>361</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>54</v>
+      </c>
+      <c r="B97" t="s">
+        <v>145</v>
+      </c>
+      <c r="C97" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s">
+        <v>279</v>
+      </c>
+      <c r="E97" t="s">
+        <v>279</v>
+      </c>
+      <c r="F97" t="s">
+        <v>362</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" t="s">
+        <v>146</v>
+      </c>
+      <c r="C98" t="s">
+        <v>236</v>
+      </c>
+      <c r="D98" t="s">
+        <v>280</v>
+      </c>
+      <c r="E98" t="s">
+        <v>279</v>
+      </c>
+      <c r="F98" t="s">
+        <v>363</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>146</v>
+      </c>
+      <c r="C99" t="s">
+        <v>236</v>
+      </c>
+      <c r="D99" t="s">
+        <v>280</v>
+      </c>
+      <c r="E99" t="s">
+        <v>280</v>
+      </c>
+      <c r="F99" t="s">
+        <v>364</v>
+      </c>
+      <c r="G99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>56</v>
+      </c>
+      <c r="B100" t="s">
+        <v>147</v>
+      </c>
+      <c r="C100" t="s">
+        <v>237</v>
+      </c>
+      <c r="D100" t="s">
+        <v>279</v>
+      </c>
+      <c r="E100" t="s">
+        <v>280</v>
+      </c>
+      <c r="F100" t="s">
+        <v>365</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>56</v>
+      </c>
+      <c r="B101" t="s">
+        <v>147</v>
+      </c>
+      <c r="C101" t="s">
+        <v>237</v>
+      </c>
+      <c r="D101" t="s">
+        <v>279</v>
+      </c>
+      <c r="E101" t="s">
+        <v>279</v>
+      </c>
+      <c r="F101" t="s">
+        <v>365</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" t="s">
+        <v>148</v>
+      </c>
+      <c r="C102" t="s">
+        <v>238</v>
+      </c>
+      <c r="D102" t="s">
+        <v>279</v>
+      </c>
+      <c r="E102" t="s">
+        <v>280</v>
+      </c>
+      <c r="F102" t="s">
+        <v>366</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" t="s">
+        <v>148</v>
+      </c>
+      <c r="C103" t="s">
+        <v>238</v>
+      </c>
+      <c r="D103" t="s">
+        <v>279</v>
+      </c>
+      <c r="E103" t="s">
+        <v>279</v>
+      </c>
+      <c r="F103" t="s">
+        <v>367</v>
+      </c>
+      <c r="G103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>58</v>
+      </c>
+      <c r="B104" t="s">
+        <v>149</v>
+      </c>
+      <c r="C104" t="s">
+        <v>239</v>
+      </c>
+      <c r="D104" t="s">
+        <v>279</v>
+      </c>
+      <c r="E104" t="s">
+        <v>280</v>
+      </c>
+      <c r="F104" t="s">
+        <v>368</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B105" t="s">
+        <v>149</v>
+      </c>
+      <c r="C105" t="s">
+        <v>239</v>
+      </c>
+      <c r="D105" t="s">
+        <v>279</v>
+      </c>
+      <c r="E105" t="s">
+        <v>279</v>
+      </c>
+      <c r="F105" t="s">
+        <v>369</v>
+      </c>
+      <c r="G105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>59</v>
+      </c>
+      <c r="B106" t="s">
+        <v>150</v>
+      </c>
+      <c r="C106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106" t="s">
+        <v>279</v>
+      </c>
+      <c r="E106" t="s">
+        <v>280</v>
+      </c>
+      <c r="F106" t="s">
+        <v>370</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>59</v>
+      </c>
+      <c r="B107" t="s">
+        <v>150</v>
+      </c>
+      <c r="C107" t="s">
+        <v>240</v>
+      </c>
+      <c r="D107" t="s">
+        <v>279</v>
+      </c>
+      <c r="E107" t="s">
+        <v>279</v>
+      </c>
+      <c r="F107" t="s">
+        <v>371</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>60</v>
+      </c>
+      <c r="B108" t="s">
+        <v>151</v>
+      </c>
+      <c r="C108" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" t="s">
+        <v>279</v>
+      </c>
+      <c r="E108" t="s">
+        <v>280</v>
+      </c>
+      <c r="F108" t="s">
+        <v>372</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>60</v>
+      </c>
+      <c r="B109" t="s">
+        <v>151</v>
+      </c>
+      <c r="C109" t="s">
+        <v>241</v>
+      </c>
+      <c r="D109" t="s">
+        <v>279</v>
+      </c>
+      <c r="E109" t="s">
+        <v>279</v>
+      </c>
+      <c r="F109" t="s">
+        <v>373</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" t="s">
+        <v>152</v>
+      </c>
+      <c r="C110" t="s">
+        <v>242</v>
+      </c>
+      <c r="D110" t="s">
+        <v>279</v>
+      </c>
+      <c r="E110" t="s">
+        <v>280</v>
+      </c>
+      <c r="F110" t="s">
+        <v>374</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>61</v>
+      </c>
+      <c r="B111" t="s">
+        <v>152</v>
+      </c>
+      <c r="C111" t="s">
+        <v>242</v>
+      </c>
+      <c r="D111" t="s">
+        <v>279</v>
+      </c>
+      <c r="E111" t="s">
+        <v>279</v>
+      </c>
+      <c r="F111" t="s">
+        <v>375</v>
+      </c>
+      <c r="G111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" t="s">
+        <v>243</v>
+      </c>
+      <c r="D112" t="s">
+        <v>279</v>
+      </c>
+      <c r="E112" t="s">
+        <v>280</v>
+      </c>
+      <c r="F112" t="s">
+        <v>376</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" t="s">
+        <v>153</v>
+      </c>
+      <c r="C113" t="s">
+        <v>243</v>
+      </c>
+      <c r="D113" t="s">
+        <v>279</v>
+      </c>
+      <c r="E113" t="s">
+        <v>279</v>
+      </c>
+      <c r="F113" t="s">
+        <v>377</v>
+      </c>
+      <c r="G113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" t="s">
+        <v>154</v>
+      </c>
+      <c r="C114" t="s">
+        <v>244</v>
+      </c>
+      <c r="D114" t="s">
+        <v>279</v>
+      </c>
+      <c r="E114" t="s">
+        <v>280</v>
+      </c>
+      <c r="F114" t="s">
+        <v>378</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>63</v>
+      </c>
+      <c r="B115" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" t="s">
+        <v>244</v>
+      </c>
+      <c r="D115" t="s">
+        <v>279</v>
+      </c>
+      <c r="E115" t="s">
+        <v>279</v>
+      </c>
+      <c r="F115" t="s">
+        <v>379</v>
+      </c>
+      <c r="G115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>64</v>
+      </c>
+      <c r="B116" t="s">
+        <v>155</v>
+      </c>
+      <c r="C116" t="s">
+        <v>245</v>
+      </c>
+      <c r="D116" t="s">
+        <v>279</v>
+      </c>
+      <c r="E116" t="s">
+        <v>280</v>
+      </c>
+      <c r="F116" t="s">
+        <v>380</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>64</v>
+      </c>
+      <c r="B117" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" t="s">
+        <v>245</v>
+      </c>
+      <c r="D117" t="s">
+        <v>279</v>
+      </c>
+      <c r="E117" t="s">
+        <v>279</v>
+      </c>
+      <c r="F117" t="s">
+        <v>381</v>
+      </c>
+      <c r="G117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>65</v>
+      </c>
+      <c r="B118" t="s">
+        <v>156</v>
+      </c>
+      <c r="C118" t="s">
+        <v>246</v>
+      </c>
+      <c r="D118" t="s">
+        <v>279</v>
+      </c>
+      <c r="E118" t="s">
+        <v>280</v>
+      </c>
+      <c r="F118" t="s">
+        <v>382</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>65</v>
+      </c>
+      <c r="B119" t="s">
+        <v>156</v>
+      </c>
+      <c r="C119" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+      <c r="E119" t="s">
+        <v>279</v>
+      </c>
+      <c r="F119" t="s">
+        <v>383</v>
+      </c>
+      <c r="G119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>66</v>
+      </c>
+      <c r="B120" t="s">
+        <v>157</v>
+      </c>
+      <c r="C120" t="s">
+        <v>247</v>
+      </c>
+      <c r="D120" t="s">
+        <v>279</v>
+      </c>
+      <c r="E120" t="s">
+        <v>280</v>
+      </c>
+      <c r="F120" t="s">
+        <v>290</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>157</v>
+      </c>
+      <c r="C121" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" t="s">
+        <v>279</v>
+      </c>
+      <c r="E121" t="s">
+        <v>279</v>
+      </c>
+      <c r="F121" t="s">
+        <v>290</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" t="s">
+        <v>158</v>
+      </c>
+      <c r="C122" t="s">
+        <v>248</v>
+      </c>
+      <c r="D122" t="s">
+        <v>279</v>
+      </c>
+      <c r="E122" t="s">
+        <v>280</v>
+      </c>
+      <c r="F122" t="s">
+        <v>384</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>67</v>
+      </c>
+      <c r="B123" t="s">
+        <v>158</v>
+      </c>
+      <c r="C123" t="s">
+        <v>248</v>
+      </c>
+      <c r="D123" t="s">
+        <v>279</v>
+      </c>
+      <c r="E123" t="s">
+        <v>279</v>
+      </c>
+      <c r="F123" t="s">
+        <v>384</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>68</v>
+      </c>
+      <c r="B124" t="s">
+        <v>159</v>
+      </c>
+      <c r="C124" t="s">
+        <v>249</v>
+      </c>
+      <c r="D124" t="s">
+        <v>279</v>
+      </c>
+      <c r="E124" t="s">
+        <v>280</v>
+      </c>
+      <c r="F124" t="s">
+        <v>385</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>68</v>
+      </c>
+      <c r="B125" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" t="s">
+        <v>249</v>
+      </c>
+      <c r="D125" t="s">
+        <v>279</v>
+      </c>
+      <c r="E125" t="s">
+        <v>279</v>
+      </c>
+      <c r="F125" t="s">
+        <v>386</v>
+      </c>
+      <c r="G125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>69</v>
+      </c>
+      <c r="B126" t="s">
+        <v>160</v>
+      </c>
+      <c r="C126" t="s">
+        <v>250</v>
+      </c>
+      <c r="D126" t="s">
+        <v>279</v>
+      </c>
+      <c r="E126" t="s">
+        <v>280</v>
+      </c>
+      <c r="F126" t="s">
+        <v>387</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>69</v>
+      </c>
+      <c r="B127" t="s">
+        <v>160</v>
+      </c>
+      <c r="C127" t="s">
+        <v>250</v>
+      </c>
+      <c r="D127" t="s">
+        <v>279</v>
+      </c>
+      <c r="E127" t="s">
+        <v>279</v>
+      </c>
+      <c r="F127" t="s">
+        <v>388</v>
+      </c>
+      <c r="G127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>70</v>
+      </c>
+      <c r="B128" t="s">
+        <v>161</v>
+      </c>
+      <c r="C128" t="s">
+        <v>251</v>
+      </c>
+      <c r="D128" t="s">
+        <v>279</v>
+      </c>
+      <c r="E128" t="s">
+        <v>280</v>
+      </c>
+      <c r="F128" t="s">
+        <v>389</v>
+      </c>
+      <c r="G128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>70</v>
+      </c>
+      <c r="B129" t="s">
+        <v>161</v>
+      </c>
+      <c r="C129" t="s">
+        <v>251</v>
+      </c>
+      <c r="D129" t="s">
+        <v>279</v>
+      </c>
+      <c r="E129" t="s">
+        <v>279</v>
+      </c>
+      <c r="F129" t="s">
+        <v>390</v>
+      </c>
+      <c r="G129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>71</v>
+      </c>
+      <c r="B130" t="s">
+        <v>162</v>
+      </c>
+      <c r="C130" t="s">
+        <v>252</v>
+      </c>
+      <c r="D130" t="s">
+        <v>279</v>
+      </c>
+      <c r="E130" t="s">
+        <v>280</v>
+      </c>
+      <c r="F130" t="s">
+        <v>391</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>71</v>
+      </c>
+      <c r="B131" t="s">
+        <v>162</v>
+      </c>
+      <c r="C131" t="s">
+        <v>252</v>
+      </c>
+      <c r="D131" t="s">
+        <v>279</v>
+      </c>
+      <c r="E131" t="s">
+        <v>279</v>
+      </c>
+      <c r="F131" t="s">
+        <v>391</v>
+      </c>
+      <c r="G131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>72</v>
+      </c>
+      <c r="B132" t="s">
+        <v>163</v>
+      </c>
+      <c r="C132" t="s">
+        <v>253</v>
+      </c>
+      <c r="D132" t="s">
+        <v>280</v>
+      </c>
+      <c r="E132" t="s">
+        <v>279</v>
+      </c>
+      <c r="F132" t="s">
+        <v>392</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>72</v>
+      </c>
+      <c r="B133" t="s">
+        <v>163</v>
+      </c>
+      <c r="C133" t="s">
+        <v>253</v>
+      </c>
+      <c r="D133" t="s">
+        <v>280</v>
+      </c>
+      <c r="E133" t="s">
+        <v>280</v>
+      </c>
+      <c r="F133" t="s">
+        <v>392</v>
+      </c>
+      <c r="G133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>73</v>
+      </c>
+      <c r="B134" t="s">
+        <v>164</v>
+      </c>
+      <c r="C134" t="s">
+        <v>254</v>
+      </c>
+      <c r="D134" t="s">
+        <v>279</v>
+      </c>
+      <c r="E134" t="s">
+        <v>280</v>
+      </c>
+      <c r="F134" t="s">
+        <v>393</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>73</v>
+      </c>
+      <c r="B135" t="s">
+        <v>164</v>
+      </c>
+      <c r="C135" t="s">
+        <v>254</v>
+      </c>
+      <c r="D135" t="s">
+        <v>279</v>
+      </c>
+      <c r="E135" t="s">
+        <v>279</v>
+      </c>
+      <c r="F135" t="s">
+        <v>394</v>
+      </c>
+      <c r="G135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>74</v>
+      </c>
+      <c r="B136" t="s">
+        <v>165</v>
+      </c>
+      <c r="C136" t="s">
+        <v>255</v>
+      </c>
+      <c r="D136" t="s">
+        <v>279</v>
+      </c>
+      <c r="E136" t="s">
+        <v>280</v>
+      </c>
+      <c r="F136" t="s">
+        <v>395</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>74</v>
+      </c>
+      <c r="B137" t="s">
+        <v>165</v>
+      </c>
+      <c r="C137" t="s">
+        <v>255</v>
+      </c>
+      <c r="D137" t="s">
+        <v>279</v>
+      </c>
+      <c r="E137" t="s">
+        <v>279</v>
+      </c>
+      <c r="F137" t="s">
+        <v>396</v>
+      </c>
+      <c r="G137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>75</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>256</v>
+      </c>
+      <c r="D138" t="s">
+        <v>279</v>
+      </c>
+      <c r="E138" t="s">
+        <v>280</v>
+      </c>
+      <c r="F138" t="s">
+        <v>397</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>75</v>
+      </c>
+      <c r="B139" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" t="s">
+        <v>256</v>
+      </c>
+      <c r="D139" t="s">
+        <v>279</v>
+      </c>
+      <c r="E139" t="s">
+        <v>279</v>
+      </c>
+      <c r="F139" t="s">
+        <v>398</v>
+      </c>
+      <c r="G139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>76</v>
+      </c>
+      <c r="B140" t="s">
+        <v>167</v>
+      </c>
+      <c r="C140" t="s">
+        <v>257</v>
+      </c>
+      <c r="D140" t="s">
+        <v>280</v>
+      </c>
+      <c r="E140" t="s">
+        <v>279</v>
+      </c>
+      <c r="F140" t="s">
+        <v>399</v>
+      </c>
+      <c r="G140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>76</v>
+      </c>
+      <c r="B141" t="s">
+        <v>167</v>
+      </c>
+      <c r="C141" t="s">
+        <v>257</v>
+      </c>
+      <c r="D141" t="s">
+        <v>280</v>
+      </c>
+      <c r="E141" t="s">
+        <v>280</v>
+      </c>
+      <c r="F141" t="s">
+        <v>399</v>
+      </c>
+      <c r="G141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>77</v>
+      </c>
+      <c r="B142" t="s">
+        <v>168</v>
+      </c>
+      <c r="C142" t="s">
+        <v>258</v>
+      </c>
+      <c r="D142" t="s">
+        <v>279</v>
+      </c>
+      <c r="E142" t="s">
+        <v>280</v>
+      </c>
+      <c r="F142" t="s">
+        <v>400</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>77</v>
+      </c>
+      <c r="B143" t="s">
+        <v>168</v>
+      </c>
+      <c r="C143" t="s">
+        <v>258</v>
+      </c>
+      <c r="D143" t="s">
+        <v>279</v>
+      </c>
+      <c r="E143" t="s">
+        <v>279</v>
+      </c>
+      <c r="F143" t="s">
+        <v>401</v>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>78</v>
+      </c>
+      <c r="B144" t="s">
+        <v>169</v>
+      </c>
+      <c r="C144" t="s">
+        <v>259</v>
+      </c>
+      <c r="D144" t="s">
+        <v>279</v>
+      </c>
+      <c r="E144" t="s">
+        <v>280</v>
+      </c>
+      <c r="F144" t="s">
+        <v>402</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>78</v>
+      </c>
+      <c r="B145" t="s">
+        <v>169</v>
+      </c>
+      <c r="C145" t="s">
+        <v>259</v>
+      </c>
+      <c r="D145" t="s">
+        <v>279</v>
+      </c>
+      <c r="E145" t="s">
+        <v>279</v>
+      </c>
+      <c r="F145" t="s">
+        <v>403</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>79</v>
+      </c>
+      <c r="B146" t="s">
+        <v>170</v>
+      </c>
+      <c r="C146" t="s">
+        <v>260</v>
+      </c>
+      <c r="D146" t="s">
+        <v>279</v>
+      </c>
+      <c r="E146" t="s">
+        <v>280</v>
+      </c>
+      <c r="F146" t="s">
+        <v>404</v>
+      </c>
+      <c r="G146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>79</v>
+      </c>
+      <c r="B147" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147" t="s">
+        <v>260</v>
+      </c>
+      <c r="D147" t="s">
+        <v>279</v>
+      </c>
+      <c r="E147" t="s">
+        <v>279</v>
+      </c>
+      <c r="F147" t="s">
+        <v>405</v>
+      </c>
+      <c r="G147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>80</v>
+      </c>
+      <c r="B148" t="s">
+        <v>171</v>
+      </c>
+      <c r="C148" t="s">
+        <v>261</v>
+      </c>
+      <c r="D148" t="s">
+        <v>279</v>
+      </c>
+      <c r="E148" t="s">
+        <v>280</v>
+      </c>
+      <c r="F148" t="s">
+        <v>406</v>
+      </c>
+      <c r="G148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>80</v>
+      </c>
+      <c r="B149" t="s">
+        <v>171</v>
+      </c>
+      <c r="C149" t="s">
+        <v>261</v>
+      </c>
+      <c r="D149" t="s">
+        <v>279</v>
+      </c>
+      <c r="E149" t="s">
+        <v>279</v>
+      </c>
+      <c r="F149" t="s">
+        <v>407</v>
+      </c>
+      <c r="G149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>81</v>
+      </c>
+      <c r="B150" t="s">
+        <v>172</v>
+      </c>
+      <c r="C150" t="s">
+        <v>262</v>
+      </c>
+      <c r="D150" t="s">
+        <v>279</v>
+      </c>
+      <c r="E150" t="s">
+        <v>280</v>
+      </c>
+      <c r="F150" t="s">
+        <v>408</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>81</v>
+      </c>
+      <c r="B151" t="s">
+        <v>172</v>
+      </c>
+      <c r="C151" t="s">
+        <v>262</v>
+      </c>
+      <c r="D151" t="s">
+        <v>279</v>
+      </c>
+      <c r="E151" t="s">
+        <v>279</v>
+      </c>
+      <c r="F151" t="s">
+        <v>409</v>
+      </c>
+      <c r="G151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>82</v>
+      </c>
+      <c r="B152" t="s">
+        <v>173</v>
+      </c>
+      <c r="C152" t="s">
+        <v>263</v>
+      </c>
+      <c r="D152" t="s">
+        <v>279</v>
+      </c>
+      <c r="E152" t="s">
+        <v>280</v>
+      </c>
+      <c r="F152" t="s">
+        <v>410</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>82</v>
+      </c>
+      <c r="B153" t="s">
+        <v>173</v>
+      </c>
+      <c r="C153" t="s">
+        <v>263</v>
+      </c>
+      <c r="D153" t="s">
+        <v>279</v>
+      </c>
+      <c r="E153" t="s">
+        <v>279</v>
+      </c>
+      <c r="F153" t="s">
+        <v>411</v>
+      </c>
+      <c r="G153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>83</v>
+      </c>
+      <c r="B154" t="s">
+        <v>174</v>
+      </c>
+      <c r="C154" t="s">
+        <v>264</v>
+      </c>
+      <c r="D154" t="s">
+        <v>279</v>
+      </c>
+      <c r="E154" t="s">
+        <v>280</v>
+      </c>
+      <c r="F154" t="s">
+        <v>412</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>83</v>
+      </c>
+      <c r="B155" t="s">
+        <v>174</v>
+      </c>
+      <c r="C155" t="s">
+        <v>264</v>
+      </c>
+      <c r="D155" t="s">
+        <v>279</v>
+      </c>
+      <c r="E155" t="s">
+        <v>279</v>
+      </c>
+      <c r="F155" t="s">
+        <v>413</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
         <v>84</v>
       </c>
-      <c r="C79" t="s">
-        <v>123</v>
-      </c>
-      <c r="D79" t="s">
-        <v>124</v>
-      </c>
-      <c r="E79" t="s">
-        <v>124</v>
-      </c>
-      <c r="F79" t="s">
-        <v>192</v>
-      </c>
-      <c r="G79">
+      <c r="B156" t="s">
+        <v>175</v>
+      </c>
+      <c r="C156" t="s">
+        <v>265</v>
+      </c>
+      <c r="D156" t="s">
+        <v>279</v>
+      </c>
+      <c r="E156" t="s">
+        <v>280</v>
+      </c>
+      <c r="F156" t="s">
+        <v>414</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>84</v>
+      </c>
+      <c r="B157" t="s">
+        <v>175</v>
+      </c>
+      <c r="C157" t="s">
+        <v>265</v>
+      </c>
+      <c r="D157" t="s">
+        <v>279</v>
+      </c>
+      <c r="E157" t="s">
+        <v>279</v>
+      </c>
+      <c r="F157" t="s">
+        <v>415</v>
+      </c>
+      <c r="G157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>85</v>
+      </c>
+      <c r="B158" t="s">
+        <v>176</v>
+      </c>
+      <c r="C158" t="s">
+        <v>266</v>
+      </c>
+      <c r="D158" t="s">
+        <v>279</v>
+      </c>
+      <c r="E158" t="s">
+        <v>280</v>
+      </c>
+      <c r="F158" t="s">
+        <v>416</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>85</v>
+      </c>
+      <c r="B159" t="s">
+        <v>176</v>
+      </c>
+      <c r="C159" t="s">
+        <v>266</v>
+      </c>
+      <c r="D159" t="s">
+        <v>279</v>
+      </c>
+      <c r="E159" t="s">
+        <v>279</v>
+      </c>
+      <c r="F159" t="s">
+        <v>416</v>
+      </c>
+      <c r="G159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>86</v>
+      </c>
+      <c r="B160" t="s">
+        <v>177</v>
+      </c>
+      <c r="C160" t="s">
+        <v>267</v>
+      </c>
+      <c r="D160" t="s">
+        <v>279</v>
+      </c>
+      <c r="E160" t="s">
+        <v>280</v>
+      </c>
+      <c r="F160" t="s">
+        <v>417</v>
+      </c>
+      <c r="G160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>86</v>
+      </c>
+      <c r="B161" t="s">
+        <v>177</v>
+      </c>
+      <c r="C161" t="s">
+        <v>267</v>
+      </c>
+      <c r="D161" t="s">
+        <v>279</v>
+      </c>
+      <c r="E161" t="s">
+        <v>279</v>
+      </c>
+      <c r="F161" t="s">
+        <v>418</v>
+      </c>
+      <c r="G161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>87</v>
+      </c>
+      <c r="B162" t="s">
+        <v>178</v>
+      </c>
+      <c r="C162" t="s">
+        <v>268</v>
+      </c>
+      <c r="D162" t="s">
+        <v>279</v>
+      </c>
+      <c r="E162" t="s">
+        <v>280</v>
+      </c>
+      <c r="F162" t="s">
+        <v>419</v>
+      </c>
+      <c r="G162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>87</v>
+      </c>
+      <c r="B163" t="s">
+        <v>178</v>
+      </c>
+      <c r="C163" t="s">
+        <v>268</v>
+      </c>
+      <c r="D163" t="s">
+        <v>279</v>
+      </c>
+      <c r="E163" t="s">
+        <v>279</v>
+      </c>
+      <c r="F163" t="s">
+        <v>304</v>
+      </c>
+      <c r="G163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" t="s">
+        <v>179</v>
+      </c>
+      <c r="C164" t="s">
+        <v>269</v>
+      </c>
+      <c r="D164" t="s">
+        <v>280</v>
+      </c>
+      <c r="E164" t="s">
+        <v>279</v>
+      </c>
+      <c r="F164" t="s">
+        <v>420</v>
+      </c>
+      <c r="G164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>88</v>
+      </c>
+      <c r="B165" t="s">
+        <v>179</v>
+      </c>
+      <c r="C165" t="s">
+        <v>269</v>
+      </c>
+      <c r="D165" t="s">
+        <v>280</v>
+      </c>
+      <c r="E165" t="s">
+        <v>280</v>
+      </c>
+      <c r="F165" t="s">
+        <v>421</v>
+      </c>
+      <c r="G165">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>89</v>
+      </c>
+      <c r="B166" t="s">
+        <v>180</v>
+      </c>
+      <c r="C166" t="s">
+        <v>270</v>
+      </c>
+      <c r="D166" t="s">
+        <v>279</v>
+      </c>
+      <c r="E166" t="s">
+        <v>280</v>
+      </c>
+      <c r="F166" t="s">
+        <v>422</v>
+      </c>
+      <c r="G166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>89</v>
+      </c>
+      <c r="B167" t="s">
+        <v>180</v>
+      </c>
+      <c r="C167" t="s">
+        <v>270</v>
+      </c>
+      <c r="D167" t="s">
+        <v>279</v>
+      </c>
+      <c r="E167" t="s">
+        <v>279</v>
+      </c>
+      <c r="F167" t="s">
+        <v>423</v>
+      </c>
+      <c r="G167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>90</v>
+      </c>
+      <c r="B168" t="s">
+        <v>181</v>
+      </c>
+      <c r="C168" t="s">
+        <v>271</v>
+      </c>
+      <c r="D168" t="s">
+        <v>279</v>
+      </c>
+      <c r="E168" t="s">
+        <v>280</v>
+      </c>
+      <c r="F168" t="s">
+        <v>424</v>
+      </c>
+      <c r="G168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>90</v>
+      </c>
+      <c r="B169" t="s">
+        <v>181</v>
+      </c>
+      <c r="C169" t="s">
+        <v>271</v>
+      </c>
+      <c r="D169" t="s">
+        <v>279</v>
+      </c>
+      <c r="E169" t="s">
+        <v>279</v>
+      </c>
+      <c r="F169" t="s">
+        <v>424</v>
+      </c>
+      <c r="G169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>91</v>
+      </c>
+      <c r="B170" t="s">
+        <v>182</v>
+      </c>
+      <c r="C170" t="s">
+        <v>272</v>
+      </c>
+      <c r="D170" t="s">
+        <v>279</v>
+      </c>
+      <c r="E170" t="s">
+        <v>280</v>
+      </c>
+      <c r="F170" t="s">
+        <v>425</v>
+      </c>
+      <c r="G170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>91</v>
+      </c>
+      <c r="B171" t="s">
+        <v>182</v>
+      </c>
+      <c r="C171" t="s">
+        <v>272</v>
+      </c>
+      <c r="D171" t="s">
+        <v>279</v>
+      </c>
+      <c r="E171" t="s">
+        <v>279</v>
+      </c>
+      <c r="F171" t="s">
+        <v>426</v>
+      </c>
+      <c r="G171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>92</v>
+      </c>
+      <c r="B172" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172" t="s">
+        <v>273</v>
+      </c>
+      <c r="D172" t="s">
+        <v>279</v>
+      </c>
+      <c r="E172" t="s">
+        <v>280</v>
+      </c>
+      <c r="F172" t="s">
+        <v>427</v>
+      </c>
+      <c r="G172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>92</v>
+      </c>
+      <c r="B173" t="s">
+        <v>183</v>
+      </c>
+      <c r="C173" t="s">
+        <v>273</v>
+      </c>
+      <c r="D173" t="s">
+        <v>279</v>
+      </c>
+      <c r="E173" t="s">
+        <v>279</v>
+      </c>
+      <c r="F173" t="s">
+        <v>428</v>
+      </c>
+      <c r="G173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>93</v>
+      </c>
+      <c r="B174" t="s">
+        <v>121</v>
+      </c>
+      <c r="C174" t="s">
+        <v>274</v>
+      </c>
+      <c r="D174" t="s">
+        <v>279</v>
+      </c>
+      <c r="E174" t="s">
+        <v>280</v>
+      </c>
+      <c r="F174" t="s">
+        <v>429</v>
+      </c>
+      <c r="G174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>93</v>
+      </c>
+      <c r="B175" t="s">
+        <v>121</v>
+      </c>
+      <c r="C175" t="s">
+        <v>274</v>
+      </c>
+      <c r="D175" t="s">
+        <v>279</v>
+      </c>
+      <c r="E175" t="s">
+        <v>279</v>
+      </c>
+      <c r="F175" t="s">
+        <v>430</v>
+      </c>
+      <c r="G175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>94</v>
+      </c>
+      <c r="B176" t="s">
+        <v>184</v>
+      </c>
+      <c r="C176" t="s">
+        <v>275</v>
+      </c>
+      <c r="D176" t="s">
+        <v>279</v>
+      </c>
+      <c r="E176" t="s">
+        <v>280</v>
+      </c>
+      <c r="F176" t="s">
+        <v>431</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>94</v>
+      </c>
+      <c r="B177" t="s">
+        <v>184</v>
+      </c>
+      <c r="C177" t="s">
+        <v>275</v>
+      </c>
+      <c r="D177" t="s">
+        <v>279</v>
+      </c>
+      <c r="E177" t="s">
+        <v>279</v>
+      </c>
+      <c r="F177" t="s">
+        <v>432</v>
+      </c>
+      <c r="G177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>95</v>
+      </c>
+      <c r="B178" t="s">
+        <v>185</v>
+      </c>
+      <c r="C178" t="s">
+        <v>276</v>
+      </c>
+      <c r="D178" t="s">
+        <v>279</v>
+      </c>
+      <c r="E178" t="s">
+        <v>280</v>
+      </c>
+      <c r="F178" t="s">
+        <v>433</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>95</v>
+      </c>
+      <c r="B179" t="s">
+        <v>185</v>
+      </c>
+      <c r="C179" t="s">
+        <v>276</v>
+      </c>
+      <c r="D179" t="s">
+        <v>279</v>
+      </c>
+      <c r="E179" t="s">
+        <v>279</v>
+      </c>
+      <c r="F179" t="s">
+        <v>433</v>
+      </c>
+      <c r="G179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>96</v>
+      </c>
+      <c r="B180" t="s">
+        <v>186</v>
+      </c>
+      <c r="C180" t="s">
+        <v>277</v>
+      </c>
+      <c r="D180" t="s">
+        <v>279</v>
+      </c>
+      <c r="E180" t="s">
+        <v>280</v>
+      </c>
+      <c r="F180" t="s">
+        <v>434</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>96</v>
+      </c>
+      <c r="B181" t="s">
+        <v>186</v>
+      </c>
+      <c r="C181" t="s">
+        <v>277</v>
+      </c>
+      <c r="D181" t="s">
+        <v>279</v>
+      </c>
+      <c r="E181" t="s">
+        <v>279</v>
+      </c>
+      <c r="F181" t="s">
+        <v>435</v>
+      </c>
+      <c r="G181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>97</v>
+      </c>
+      <c r="B182" t="s">
+        <v>187</v>
+      </c>
+      <c r="C182" t="s">
+        <v>278</v>
+      </c>
+      <c r="D182" t="s">
+        <v>279</v>
+      </c>
+      <c r="E182" t="s">
+        <v>280</v>
+      </c>
+      <c r="F182" t="s">
+        <v>436</v>
+      </c>
+      <c r="G182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>97</v>
+      </c>
+      <c r="B183" t="s">
+        <v>187</v>
+      </c>
+      <c r="C183" t="s">
+        <v>278</v>
+      </c>
+      <c r="D183" t="s">
+        <v>279</v>
+      </c>
+      <c r="E183" t="s">
+        <v>279</v>
+      </c>
+      <c r="F183" t="s">
+        <v>437</v>
+      </c>
+      <c r="G183">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -16,28 +16,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="501">
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>company_name</t>
-  </si>
-  <si>
-    <t>survey_status</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>global_status</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-  <si>
-    <t>order</t>
+    <t>Kode Identitas</t>
+  </si>
+  <si>
+    <t>Nama Perusahaan</t>
+  </si>
+  <si>
+    <t>Status Dokumen</t>
+  </si>
+  <si>
+    <t>Email Tujuan</t>
+  </si>
+  <si>
+    <t>Status terakhir</t>
+  </si>
+  <si>
+    <t>Status History</t>
+  </si>
+  <si>
+    <t>Timestamp History</t>
+  </si>
+  <si>
+    <t>Urutan History</t>
   </si>
   <si>
     <t>7207011006001000 - UB - 1</t>
@@ -985,538 +985,538 @@
     <t>19 Mei 2026, 11:14:37</t>
   </si>
   <si>
+    <t>19 Mei 2026, 09:51:11</t>
+  </si>
+  <si>
     <t>19 Mei 2026, 09:51:10</t>
   </si>
   <si>
-    <t>19 Mei 2026, 09:51:11</t>
-  </si>
-  <si>
     <t>19 Mei 2026, 11:14:34</t>
   </si>
   <si>
+    <t>02 Jun 2026, 07:57:37</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 07:57:15</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:57:37</t>
-  </si>
-  <si>
     <t>01 Jun 2026, 23:07:49</t>
   </si>
   <si>
+    <t>02 Jun 2026, 07:38:30</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 07:38:27</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:38:30</t>
+    <t>02 Jun 2026, 07:23:56</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:23:53</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:23:56</t>
+    <t>02 Jun 2026, 08:58:37</t>
   </si>
   <si>
     <t>02 Jun 2026, 08:56:24</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:58:37</t>
+    <t>02 Jun 2026, 03:53:26</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:51:54</t>
   </si>
   <si>
-    <t>02 Jun 2026, 03:53:26</t>
+    <t>02 Jun 2026, 01:14:20</t>
   </si>
   <si>
     <t>02 Jun 2026, 01:14:16</t>
   </si>
   <si>
-    <t>02 Jun 2026, 01:14:20</t>
+    <t>02 Jun 2026, 04:33:23</t>
   </si>
   <si>
     <t>02 Jun 2026, 04:32:41</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:33:23</t>
+    <t>01 Jun 2026, 23:17:00</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:15:52</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:17:00</t>
+    <t>02 Jun 2026, 02:09:06</t>
   </si>
   <si>
     <t>02 Jun 2026, 02:09:05</t>
   </si>
   <si>
-    <t>02 Jun 2026, 02:09:06</t>
+    <t>01 Jun 2026, 23:00:27</t>
   </si>
   <si>
     <t>01 Jun 2026, 22:59:43</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:00:27</t>
+    <t>02 Jun 2026, 01:10:45</t>
   </si>
   <si>
     <t>02 Jun 2026, 01:10:14</t>
   </si>
   <si>
-    <t>02 Jun 2026, 01:10:45</t>
+    <t>02 Jun 2026, 07:48:23</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:47:46</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:48:23</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 02:23:23</t>
   </si>
   <si>
     <t>01 Jun 2026, 22:48:15</t>
   </si>
   <si>
+    <t>02 Jun 2026, 04:39:27</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 04:39:23</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:39:27</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 08:57:51</t>
   </si>
   <si>
+    <t>02 Jun 2026, 09:04:21</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 09:04:02</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:04:21</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 00:55:50</t>
   </si>
   <si>
+    <t>02 Jun 2026, 02:30:55</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 02:29:47</t>
   </si>
   <si>
-    <t>02 Jun 2026, 02:30:55</t>
+    <t>02 Jun 2026, 04:02:15</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:59:51</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:02:15</t>
+    <t>01 Jun 2026, 23:16:31</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:16:27</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:16:31</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 06:50:12</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:47:52</t>
   </si>
   <si>
+    <t>02 Jun 2026, 08:35:20</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 08:34:32</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:35:20</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 04:22:11</t>
   </si>
   <si>
+    <t>02 Jun 2026, 06:59:00</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 06:58:39</t>
   </si>
   <si>
-    <t>02 Jun 2026, 06:59:00</t>
+    <t>02 Jun 2026, 08:55:13</t>
   </si>
   <si>
     <t>02 Jun 2026, 08:52:30</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:55:13</t>
+    <t>01 Jun 2026, 23:34:59</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:34:56</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:34:59</t>
+    <t>02 Jun 2026, 03:44:55</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:44:52</t>
   </si>
   <si>
-    <t>02 Jun 2026, 03:44:55</t>
+    <t>02 Jun 2026, 00:49:30</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:49:31</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:49:30</t>
+    <t>02 Jun 2026, 01:23:29</t>
   </si>
   <si>
     <t>02 Jun 2026, 01:23:24</t>
   </si>
   <si>
-    <t>02 Jun 2026, 01:23:29</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 06:19:08</t>
   </si>
   <si>
+    <t>02 Jun 2026, 09:06:32</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 09:04:47</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:06:32</t>
+    <t>02 Jun 2026, 06:33:41</t>
   </si>
   <si>
     <t>02 Jun 2026, 06:32:51</t>
   </si>
   <si>
-    <t>02 Jun 2026, 06:33:41</t>
+    <t>02 Jun 2026, 10:08:22</t>
   </si>
   <si>
     <t>02 Jun 2026, 10:04:58</t>
   </si>
   <si>
-    <t>02 Jun 2026, 10:08:22</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 06:31:35</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:35:32</t>
   </si>
   <si>
+    <t>02 Jun 2026, 08:52:48</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 08:52:14</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:52:48</t>
+    <t>02 Jun 2026, 00:41:02</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:41:01</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:41:02</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 09:17:21</t>
   </si>
   <si>
+    <t>02 Jun 2026, 09:12:41</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 09:11:39</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:12:41</t>
+    <t>02 Jun 2026, 05:22:20</t>
   </si>
   <si>
     <t>02 Jun 2026, 05:21:43</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:22:20</t>
+    <t>02 Jun 2026, 07:08:36</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:08:18</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:08:36</t>
+    <t>01 Jun 2026, 23:30:02</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:29:34</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:30:02</t>
+    <t>02 Jun 2026, 11:53:38</t>
   </si>
   <si>
     <t>02 Jun 2026, 11:53:36</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:53:38</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 02:01:57</t>
   </si>
   <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
     <t>01 Jun 2026, 23:06:35</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:06:38</t>
+    <t>02 Jun 2026, 10:34:01</t>
   </si>
   <si>
     <t>02 Jun 2026, 10:33:19</t>
   </si>
   <si>
-    <t>02 Jun 2026, 10:34:01</t>
+    <t>02 Jun 2026, 11:57:49</t>
   </si>
   <si>
     <t>02 Jun 2026, 11:49:47</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:57:49</t>
+    <t>02 Jun 2026, 00:34:13</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:34:08</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:34:13</t>
+    <t>02 Jun 2026, 03:39:29</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:39:18</t>
   </si>
   <si>
-    <t>02 Jun 2026, 03:39:29</t>
+    <t>02 Jun 2026, 06:22:28</t>
   </si>
   <si>
     <t>02 Jun 2026, 06:22:25</t>
   </si>
   <si>
-    <t>02 Jun 2026, 06:22:28</t>
+    <t>02 Jun 2026, 00:06:29</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:06:21</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:06:29</t>
+    <t>02 Jun 2026, 04:45:27</t>
   </si>
   <si>
     <t>02 Jun 2026, 04:43:12</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:45:27</t>
+    <t>02 Jun 2026, 05:52:54</t>
   </si>
   <si>
     <t>02 Jun 2026, 05:52:21</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:52:54</t>
-  </si>
-  <si>
     <t>01 Jun 2026, 23:01:16</t>
   </si>
   <si>
+    <t>02 Jun 2026, 05:46:05</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 05:45:34</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:46:05</t>
+    <t>02 Jun 2026, 07:00:54</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:00:24</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:00:54</t>
+    <t>02 Jun 2026, 09:00:10</t>
   </si>
   <si>
     <t>02 Jun 2026, 08:59:36</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:00:10</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 08:50:41</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:04:03</t>
   </si>
   <si>
+    <t>01 Jun 2026, 22:58:30</t>
+  </si>
+  <si>
     <t>01 Jun 2026, 22:57:07</t>
   </si>
   <si>
-    <t>01 Jun 2026, 22:58:30</t>
+    <t>02 Jun 2026, 03:10:04</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:09:36</t>
   </si>
   <si>
-    <t>02 Jun 2026, 03:10:04</t>
+    <t>02 Jun 2026, 04:12:10</t>
   </si>
   <si>
     <t>02 Jun 2026, 04:11:35</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:12:10</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 01:06:09</t>
   </si>
   <si>
+    <t>02 Jun 2026, 00:37:51</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 00:37:47</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:37:51</t>
+    <t>02 Jun 2026, 11:37:42</t>
   </si>
   <si>
     <t>02 Jun 2026, 11:37:41</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:37:42</t>
+    <t>02 Jun 2026, 07:11:36</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:11:00</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:11:36</t>
+    <t>02 Jun 2026, 09:45:54</t>
   </si>
   <si>
     <t>02 Jun 2026, 09:45:51</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:45:54</t>
+    <t>02 Jun 2026, 05:08:43</t>
   </si>
   <si>
     <t>02 Jun 2026, 05:07:16</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:08:43</t>
+    <t>02 Jun 2026, 06:39:45</t>
   </si>
   <si>
     <t>02 Jun 2026, 06:36:13</t>
   </si>
   <si>
-    <t>02 Jun 2026, 06:39:45</t>
+    <t>01 Jun 2026, 23:26:06</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:23:45</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:26:06</t>
+    <t>02 Jun 2026, 05:59:58</t>
   </si>
   <si>
     <t>02 Jun 2026, 05:59:12</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:59:58</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 07:10:57</t>
   </si>
   <si>
+    <t>02 Jun 2026, 11:47:27</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 11:47:26</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:47:27</t>
-  </si>
-  <si>
     <t>01 Jun 2026, 22:58:46</t>
   </si>
   <si>
+    <t>02 Jun 2026, 11:35:03</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 11:35:02</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:35:03</t>
+    <t>02 Jun 2026, 09:36:45</t>
   </si>
   <si>
     <t>02 Jun 2026, 09:36:44</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:36:45</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 03:21:19</t>
   </si>
   <si>
+    <t>02 Jun 2026, 07:01:31</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 07:01:30</t>
   </si>
   <si>
-    <t>02 Jun 2026, 07:01:31</t>
+    <t>01 Jun 2026, 23:00:08</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:00:04</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:00:08</t>
+    <t>02 Jun 2026, 00:12:21</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:11:48</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:12:21</t>
+    <t>02 Jun 2026, 04:58:35</t>
   </si>
   <si>
     <t>02 Jun 2026, 04:58:16</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:58:35</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 00:59:01</t>
   </si>
   <si>
+    <t>02 Jun 2026, 01:44:11</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 01:44:10</t>
   </si>
   <si>
-    <t>02 Jun 2026, 01:44:11</t>
+    <t>02 Jun 2026, 00:39:39</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:39:34</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:39:39</t>
+    <t>02 Jun 2026, 05:57:24</t>
   </si>
   <si>
     <t>02 Jun 2026, 05:57:20</t>
   </si>
   <si>
-    <t>02 Jun 2026, 05:57:24</t>
+    <t>01 Jun 2026, 23:49:00</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:48:57</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:49:00</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 07:31:06</t>
   </si>
   <si>
+    <t>02 Jun 2026, 03:12:01</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 03:11:28</t>
   </si>
   <si>
-    <t>02 Jun 2026, 03:12:01</t>
+    <t>02 Jun 2026, 08:35:38</t>
   </si>
   <si>
     <t>02 Jun 2026, 08:35:37</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:35:38</t>
+    <t>02 Jun 2026, 08:38:05</t>
   </si>
   <si>
     <t>02 Jun 2026, 08:37:43</t>
   </si>
   <si>
-    <t>02 Jun 2026, 08:38:05</t>
+    <t>02 Jun 2026, 10:28:53</t>
   </si>
   <si>
     <t>02 Jun 2026, 10:28:18</t>
   </si>
   <si>
-    <t>02 Jun 2026, 10:28:53</t>
+    <t>01 Jun 2026, 23:02:12</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:02:08</t>
   </si>
   <si>
-    <t>01 Jun 2026, 23:02:12</t>
+    <t>02 Jun 2026, 01:30:50</t>
   </si>
   <si>
     <t>02 Jun 2026, 01:29:43</t>
   </si>
   <si>
-    <t>02 Jun 2026, 01:30:50</t>
-  </si>
-  <si>
     <t>01 Jun 2026, 23:53:12</t>
   </si>
   <si>
+    <t>02 Jun 2026, 04:55:14</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 04:54:25</t>
   </si>
   <si>
-    <t>02 Jun 2026, 04:55:14</t>
+    <t>02 Jun 2026, 02:20:17</t>
   </si>
   <si>
     <t>02 Jun 2026, 02:20:10</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 02:20:17</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1920,7 @@
         <v>320</v>
       </c>
       <c r="F2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G2" t="s">
         <v>322</v>
@@ -1946,7 +1946,7 @@
         <v>320</v>
       </c>
       <c r="F3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G3" t="s">
         <v>322</v>
@@ -1969,10 +1969,10 @@
         <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
         <v>323</v>
@@ -1995,10 +1995,10 @@
         <v>218</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G5" t="s">
         <v>324</v>
@@ -2021,10 +2021,10 @@
         <v>219</v>
       </c>
       <c r="E6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G6" t="s">
         <v>325</v>
@@ -2047,10 +2047,10 @@
         <v>219</v>
       </c>
       <c r="E7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G7" t="s">
         <v>325</v>
@@ -2076,7 +2076,7 @@
         <v>320</v>
       </c>
       <c r="F8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G8" t="s">
         <v>326</v>
@@ -2102,7 +2102,7 @@
         <v>320</v>
       </c>
       <c r="F9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G9" t="s">
         <v>327</v>
@@ -2128,7 +2128,7 @@
         <v>320</v>
       </c>
       <c r="F10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G10" t="s">
         <v>328</v>
@@ -2154,7 +2154,7 @@
         <v>320</v>
       </c>
       <c r="F11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G11" t="s">
         <v>328</v>
@@ -2180,7 +2180,7 @@
         <v>320</v>
       </c>
       <c r="F12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G12" t="s">
         <v>329</v>
@@ -2206,7 +2206,7 @@
         <v>320</v>
       </c>
       <c r="F13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G13" t="s">
         <v>330</v>
@@ -2232,7 +2232,7 @@
         <v>320</v>
       </c>
       <c r="F14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G14" t="s">
         <v>331</v>
@@ -2258,7 +2258,7 @@
         <v>320</v>
       </c>
       <c r="F15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G15" t="s">
         <v>332</v>
@@ -2284,7 +2284,7 @@
         <v>320</v>
       </c>
       <c r="F16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G16" t="s">
         <v>333</v>
@@ -2310,7 +2310,7 @@
         <v>320</v>
       </c>
       <c r="F17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G17" t="s">
         <v>334</v>
@@ -2336,7 +2336,7 @@
         <v>320</v>
       </c>
       <c r="F18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G18" t="s">
         <v>335</v>
@@ -2362,7 +2362,7 @@
         <v>320</v>
       </c>
       <c r="F19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G19" t="s">
         <v>336</v>
@@ -2388,7 +2388,7 @@
         <v>320</v>
       </c>
       <c r="F20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G20" t="s">
         <v>337</v>
@@ -2414,7 +2414,7 @@
         <v>320</v>
       </c>
       <c r="F21" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G21" t="s">
         <v>338</v>
@@ -2440,7 +2440,7 @@
         <v>320</v>
       </c>
       <c r="F22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G22" t="s">
         <v>339</v>
@@ -2466,7 +2466,7 @@
         <v>320</v>
       </c>
       <c r="F23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G23" t="s">
         <v>340</v>
@@ -2492,7 +2492,7 @@
         <v>320</v>
       </c>
       <c r="F24" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G24" t="s">
         <v>341</v>
@@ -2518,7 +2518,7 @@
         <v>320</v>
       </c>
       <c r="F25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G25" t="s">
         <v>342</v>
@@ -2544,7 +2544,7 @@
         <v>320</v>
       </c>
       <c r="F26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G26" t="s">
         <v>343</v>
@@ -2570,7 +2570,7 @@
         <v>320</v>
       </c>
       <c r="F27" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G27" t="s">
         <v>344</v>
@@ -2596,7 +2596,7 @@
         <v>320</v>
       </c>
       <c r="F28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G28" t="s">
         <v>345</v>
@@ -2622,7 +2622,7 @@
         <v>320</v>
       </c>
       <c r="F29" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G29" t="s">
         <v>346</v>
@@ -2648,7 +2648,7 @@
         <v>320</v>
       </c>
       <c r="F30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G30" t="s">
         <v>347</v>
@@ -2674,7 +2674,7 @@
         <v>320</v>
       </c>
       <c r="F31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G31" t="s">
         <v>348</v>
@@ -2700,7 +2700,7 @@
         <v>320</v>
       </c>
       <c r="F32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G32" t="s">
         <v>349</v>
@@ -2726,7 +2726,7 @@
         <v>320</v>
       </c>
       <c r="F33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G33" t="s">
         <v>350</v>
@@ -2749,10 +2749,10 @@
         <v>233</v>
       </c>
       <c r="E34" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G34" t="s">
         <v>351</v>
@@ -2775,10 +2775,10 @@
         <v>233</v>
       </c>
       <c r="E35" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F35" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G35" t="s">
         <v>351</v>
@@ -2804,7 +2804,7 @@
         <v>320</v>
       </c>
       <c r="F36" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G36" t="s">
         <v>352</v>
@@ -2830,7 +2830,7 @@
         <v>320</v>
       </c>
       <c r="F37" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G37" t="s">
         <v>352</v>
@@ -2856,7 +2856,7 @@
         <v>320</v>
       </c>
       <c r="F38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G38" t="s">
         <v>353</v>
@@ -2882,7 +2882,7 @@
         <v>320</v>
       </c>
       <c r="F39" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G39" t="s">
         <v>354</v>
@@ -2905,10 +2905,10 @@
         <v>236</v>
       </c>
       <c r="E40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F40" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G40" t="s">
         <v>355</v>
@@ -2931,10 +2931,10 @@
         <v>236</v>
       </c>
       <c r="E41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F41" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G41" t="s">
         <v>355</v>
@@ -2960,7 +2960,7 @@
         <v>320</v>
       </c>
       <c r="F42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G42" t="s">
         <v>356</v>
@@ -2986,7 +2986,7 @@
         <v>320</v>
       </c>
       <c r="F43" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G43" t="s">
         <v>357</v>
@@ -3009,10 +3009,10 @@
         <v>238</v>
       </c>
       <c r="E44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F44" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G44" t="s">
         <v>358</v>
@@ -3035,10 +3035,10 @@
         <v>238</v>
       </c>
       <c r="E45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G45" t="s">
         <v>358</v>
@@ -3064,7 +3064,7 @@
         <v>320</v>
       </c>
       <c r="F46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G46" t="s">
         <v>359</v>
@@ -3090,7 +3090,7 @@
         <v>320</v>
       </c>
       <c r="F47" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G47" t="s">
         <v>360</v>
@@ -3116,7 +3116,7 @@
         <v>320</v>
       </c>
       <c r="F48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G48" t="s">
         <v>361</v>
@@ -3142,7 +3142,7 @@
         <v>320</v>
       </c>
       <c r="F49" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G49" t="s">
         <v>362</v>
@@ -3168,7 +3168,7 @@
         <v>320</v>
       </c>
       <c r="F50" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G50" t="s">
         <v>363</v>
@@ -3194,7 +3194,7 @@
         <v>320</v>
       </c>
       <c r="F51" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G51" t="s">
         <v>364</v>
@@ -3217,10 +3217,10 @@
         <v>242</v>
       </c>
       <c r="E52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G52" t="s">
         <v>365</v>
@@ -3243,10 +3243,10 @@
         <v>242</v>
       </c>
       <c r="E53" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F53" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G53" t="s">
         <v>365</v>
@@ -3272,7 +3272,7 @@
         <v>320</v>
       </c>
       <c r="F54" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G54" t="s">
         <v>366</v>
@@ -3298,7 +3298,7 @@
         <v>320</v>
       </c>
       <c r="F55" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G55" t="s">
         <v>366</v>
@@ -3324,7 +3324,7 @@
         <v>320</v>
       </c>
       <c r="F56" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G56" t="s">
         <v>367</v>
@@ -3350,7 +3350,7 @@
         <v>320</v>
       </c>
       <c r="F57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G57" t="s">
         <v>368</v>
@@ -3373,10 +3373,10 @@
         <v>245</v>
       </c>
       <c r="E58" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G58" t="s">
         <v>369</v>
@@ -3399,10 +3399,10 @@
         <v>245</v>
       </c>
       <c r="E59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F59" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G59" t="s">
         <v>369</v>
@@ -3428,7 +3428,7 @@
         <v>320</v>
       </c>
       <c r="F60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G60" t="s">
         <v>370</v>
@@ -3454,7 +3454,7 @@
         <v>320</v>
       </c>
       <c r="F61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G61" t="s">
         <v>371</v>
@@ -3480,7 +3480,7 @@
         <v>320</v>
       </c>
       <c r="F62" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G62" t="s">
         <v>372</v>
@@ -3506,7 +3506,7 @@
         <v>320</v>
       </c>
       <c r="F63" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G63" t="s">
         <v>373</v>
@@ -3532,7 +3532,7 @@
         <v>320</v>
       </c>
       <c r="F64" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G64" t="s">
         <v>374</v>
@@ -3558,7 +3558,7 @@
         <v>320</v>
       </c>
       <c r="F65" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G65" t="s">
         <v>375</v>
@@ -3584,7 +3584,7 @@
         <v>320</v>
       </c>
       <c r="F66" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G66" t="s">
         <v>376</v>
@@ -3610,7 +3610,7 @@
         <v>320</v>
       </c>
       <c r="F67" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G67" t="s">
         <v>377</v>
@@ -3633,10 +3633,10 @@
         <v>250</v>
       </c>
       <c r="E68" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F68" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G68" t="s">
         <v>378</v>
@@ -3659,10 +3659,10 @@
         <v>250</v>
       </c>
       <c r="E69" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F69" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G69" t="s">
         <v>379</v>
@@ -3688,7 +3688,7 @@
         <v>320</v>
       </c>
       <c r="F70" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G70" t="s">
         <v>380</v>
@@ -3714,7 +3714,7 @@
         <v>320</v>
       </c>
       <c r="F71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G71" t="s">
         <v>381</v>
@@ -3740,7 +3740,7 @@
         <v>320</v>
       </c>
       <c r="F72" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G72" t="s">
         <v>382</v>
@@ -3766,7 +3766,7 @@
         <v>320</v>
       </c>
       <c r="F73" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G73" t="s">
         <v>382</v>
@@ -3792,7 +3792,7 @@
         <v>320</v>
       </c>
       <c r="F74" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G74" t="s">
         <v>383</v>
@@ -3818,7 +3818,7 @@
         <v>320</v>
       </c>
       <c r="F75" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G75" t="s">
         <v>384</v>
@@ -3844,7 +3844,7 @@
         <v>320</v>
       </c>
       <c r="F76" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G76" t="s">
         <v>385</v>
@@ -3870,7 +3870,7 @@
         <v>320</v>
       </c>
       <c r="F77" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G77" t="s">
         <v>386</v>
@@ -3896,7 +3896,7 @@
         <v>320</v>
       </c>
       <c r="F78" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G78" t="s">
         <v>387</v>
@@ -3922,7 +3922,7 @@
         <v>320</v>
       </c>
       <c r="F79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G79" t="s">
         <v>388</v>
@@ -3945,10 +3945,10 @@
         <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F80" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G80" t="s">
         <v>389</v>
@@ -3971,10 +3971,10 @@
         <v>256</v>
       </c>
       <c r="E81" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F81" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G81" t="s">
         <v>389</v>
@@ -4000,7 +4000,7 @@
         <v>320</v>
       </c>
       <c r="F82" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G82" t="s">
         <v>390</v>
@@ -4026,7 +4026,7 @@
         <v>320</v>
       </c>
       <c r="F83" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G83" t="s">
         <v>390</v>
@@ -4052,7 +4052,7 @@
         <v>320</v>
       </c>
       <c r="F84" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G84" t="s">
         <v>391</v>
@@ -4078,7 +4078,7 @@
         <v>320</v>
       </c>
       <c r="F85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G85" t="s">
         <v>392</v>
@@ -4104,7 +4104,7 @@
         <v>320</v>
       </c>
       <c r="F86" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G86" t="s">
         <v>393</v>
@@ -4130,7 +4130,7 @@
         <v>320</v>
       </c>
       <c r="F87" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G87" t="s">
         <v>394</v>
@@ -4156,7 +4156,7 @@
         <v>320</v>
       </c>
       <c r="F88" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G88" t="s">
         <v>395</v>
@@ -4182,7 +4182,7 @@
         <v>320</v>
       </c>
       <c r="F89" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G89" t="s">
         <v>395</v>
@@ -4208,7 +4208,7 @@
         <v>320</v>
       </c>
       <c r="F90" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G90" t="s">
         <v>396</v>
@@ -4234,7 +4234,7 @@
         <v>320</v>
       </c>
       <c r="F91" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G91" t="s">
         <v>397</v>
@@ -4260,7 +4260,7 @@
         <v>320</v>
       </c>
       <c r="F92" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G92" t="s">
         <v>398</v>
@@ -4286,7 +4286,7 @@
         <v>320</v>
       </c>
       <c r="F93" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G93" t="s">
         <v>399</v>
@@ -4312,7 +4312,7 @@
         <v>320</v>
       </c>
       <c r="F94" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G94" t="s">
         <v>400</v>
@@ -4338,7 +4338,7 @@
         <v>320</v>
       </c>
       <c r="F95" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G95" t="s">
         <v>401</v>
@@ -4364,7 +4364,7 @@
         <v>320</v>
       </c>
       <c r="F96" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G96" t="s">
         <v>402</v>
@@ -4390,7 +4390,7 @@
         <v>320</v>
       </c>
       <c r="F97" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G97" t="s">
         <v>403</v>
@@ -4413,10 +4413,10 @@
         <v>265</v>
       </c>
       <c r="E98" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F98" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G98" t="s">
         <v>404</v>
@@ -4439,10 +4439,10 @@
         <v>265</v>
       </c>
       <c r="E99" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F99" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G99" t="s">
         <v>405</v>
@@ -4468,7 +4468,7 @@
         <v>320</v>
       </c>
       <c r="F100" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G100" t="s">
         <v>406</v>
@@ -4494,7 +4494,7 @@
         <v>320</v>
       </c>
       <c r="F101" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G101" t="s">
         <v>406</v>
@@ -4520,7 +4520,7 @@
         <v>320</v>
       </c>
       <c r="F102" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G102" t="s">
         <v>407</v>
@@ -4546,7 +4546,7 @@
         <v>320</v>
       </c>
       <c r="F103" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G103" t="s">
         <v>408</v>
@@ -4572,7 +4572,7 @@
         <v>320</v>
       </c>
       <c r="F104" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G104" t="s">
         <v>409</v>
@@ -4598,7 +4598,7 @@
         <v>320</v>
       </c>
       <c r="F105" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G105" t="s">
         <v>410</v>
@@ -4624,7 +4624,7 @@
         <v>320</v>
       </c>
       <c r="F106" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G106" t="s">
         <v>411</v>
@@ -4650,7 +4650,7 @@
         <v>320</v>
       </c>
       <c r="F107" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G107" t="s">
         <v>412</v>
@@ -4676,7 +4676,7 @@
         <v>320</v>
       </c>
       <c r="F108" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G108" t="s">
         <v>413</v>
@@ -4702,7 +4702,7 @@
         <v>320</v>
       </c>
       <c r="F109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G109" t="s">
         <v>414</v>
@@ -4728,7 +4728,7 @@
         <v>320</v>
       </c>
       <c r="F110" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G110" t="s">
         <v>415</v>
@@ -4754,7 +4754,7 @@
         <v>320</v>
       </c>
       <c r="F111" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G111" t="s">
         <v>416</v>
@@ -4780,7 +4780,7 @@
         <v>320</v>
       </c>
       <c r="F112" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G112" t="s">
         <v>417</v>
@@ -4806,7 +4806,7 @@
         <v>320</v>
       </c>
       <c r="F113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G113" t="s">
         <v>418</v>
@@ -4832,7 +4832,7 @@
         <v>320</v>
       </c>
       <c r="F114" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G114" t="s">
         <v>419</v>
@@ -4858,7 +4858,7 @@
         <v>320</v>
       </c>
       <c r="F115" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G115" t="s">
         <v>420</v>
@@ -4884,7 +4884,7 @@
         <v>320</v>
       </c>
       <c r="F116" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G116" t="s">
         <v>421</v>
@@ -4910,7 +4910,7 @@
         <v>320</v>
       </c>
       <c r="F117" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G117" t="s">
         <v>422</v>
@@ -4936,7 +4936,7 @@
         <v>320</v>
       </c>
       <c r="F118" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G118" t="s">
         <v>423</v>
@@ -4962,7 +4962,7 @@
         <v>320</v>
       </c>
       <c r="F119" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G119" t="s">
         <v>424</v>
@@ -4988,10 +4988,10 @@
         <v>320</v>
       </c>
       <c r="F120" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -5014,10 +5014,10 @@
         <v>320</v>
       </c>
       <c r="F121" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G121" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H121">
         <v>2</v>
@@ -5040,7 +5040,7 @@
         <v>320</v>
       </c>
       <c r="F122" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G122" t="s">
         <v>425</v>
@@ -5066,7 +5066,7 @@
         <v>320</v>
       </c>
       <c r="F123" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G123" t="s">
         <v>425</v>
@@ -5092,7 +5092,7 @@
         <v>320</v>
       </c>
       <c r="F124" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G124" t="s">
         <v>426</v>
@@ -5118,7 +5118,7 @@
         <v>320</v>
       </c>
       <c r="F125" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G125" t="s">
         <v>427</v>
@@ -5144,7 +5144,7 @@
         <v>320</v>
       </c>
       <c r="F126" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G126" t="s">
         <v>428</v>
@@ -5170,7 +5170,7 @@
         <v>320</v>
       </c>
       <c r="F127" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G127" t="s">
         <v>429</v>
@@ -5196,7 +5196,7 @@
         <v>320</v>
       </c>
       <c r="F128" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G128" t="s">
         <v>430</v>
@@ -5222,7 +5222,7 @@
         <v>320</v>
       </c>
       <c r="F129" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G129" t="s">
         <v>431</v>
@@ -5248,7 +5248,7 @@
         <v>320</v>
       </c>
       <c r="F130" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G130" t="s">
         <v>432</v>
@@ -5274,7 +5274,7 @@
         <v>320</v>
       </c>
       <c r="F131" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G131" t="s">
         <v>432</v>
@@ -5297,10 +5297,10 @@
         <v>282</v>
       </c>
       <c r="E132" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F132" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G132" t="s">
         <v>433</v>
@@ -5323,10 +5323,10 @@
         <v>282</v>
       </c>
       <c r="E133" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F133" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G133" t="s">
         <v>433</v>
@@ -5352,7 +5352,7 @@
         <v>320</v>
       </c>
       <c r="F134" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G134" t="s">
         <v>434</v>
@@ -5378,7 +5378,7 @@
         <v>320</v>
       </c>
       <c r="F135" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G135" t="s">
         <v>435</v>
@@ -5404,7 +5404,7 @@
         <v>320</v>
       </c>
       <c r="F136" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G136" t="s">
         <v>436</v>
@@ -5430,7 +5430,7 @@
         <v>320</v>
       </c>
       <c r="F137" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G137" t="s">
         <v>437</v>
@@ -5456,7 +5456,7 @@
         <v>320</v>
       </c>
       <c r="F138" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G138" t="s">
         <v>438</v>
@@ -5482,7 +5482,7 @@
         <v>320</v>
       </c>
       <c r="F139" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G139" t="s">
         <v>439</v>
@@ -5505,10 +5505,10 @@
         <v>286</v>
       </c>
       <c r="E140" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F140" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G140" t="s">
         <v>440</v>
@@ -5531,10 +5531,10 @@
         <v>286</v>
       </c>
       <c r="E141" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F141" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G141" t="s">
         <v>440</v>
@@ -5560,7 +5560,7 @@
         <v>320</v>
       </c>
       <c r="F142" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G142" t="s">
         <v>441</v>
@@ -5586,7 +5586,7 @@
         <v>320</v>
       </c>
       <c r="F143" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G143" t="s">
         <v>442</v>
@@ -5612,7 +5612,7 @@
         <v>320</v>
       </c>
       <c r="F144" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G144" t="s">
         <v>443</v>
@@ -5638,7 +5638,7 @@
         <v>320</v>
       </c>
       <c r="F145" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G145" t="s">
         <v>444</v>
@@ -5664,7 +5664,7 @@
         <v>320</v>
       </c>
       <c r="F146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G146" t="s">
         <v>445</v>
@@ -5690,7 +5690,7 @@
         <v>320</v>
       </c>
       <c r="F147" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G147" t="s">
         <v>446</v>
@@ -5716,7 +5716,7 @@
         <v>320</v>
       </c>
       <c r="F148" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G148" t="s">
         <v>447</v>
@@ -5742,7 +5742,7 @@
         <v>320</v>
       </c>
       <c r="F149" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G149" t="s">
         <v>448</v>
@@ -5768,7 +5768,7 @@
         <v>320</v>
       </c>
       <c r="F150" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G150" t="s">
         <v>449</v>
@@ -5794,7 +5794,7 @@
         <v>320</v>
       </c>
       <c r="F151" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G151" t="s">
         <v>450</v>
@@ -5820,7 +5820,7 @@
         <v>320</v>
       </c>
       <c r="F152" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G152" t="s">
         <v>451</v>
@@ -5846,7 +5846,7 @@
         <v>320</v>
       </c>
       <c r="F153" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G153" t="s">
         <v>452</v>
@@ -5872,7 +5872,7 @@
         <v>320</v>
       </c>
       <c r="F154" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G154" t="s">
         <v>453</v>
@@ -5898,7 +5898,7 @@
         <v>320</v>
       </c>
       <c r="F155" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G155" t="s">
         <v>454</v>
@@ -5924,7 +5924,7 @@
         <v>320</v>
       </c>
       <c r="F156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G156" t="s">
         <v>455</v>
@@ -5950,7 +5950,7 @@
         <v>320</v>
       </c>
       <c r="F157" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G157" t="s">
         <v>456</v>
@@ -5976,7 +5976,7 @@
         <v>320</v>
       </c>
       <c r="F158" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G158" t="s">
         <v>457</v>
@@ -6002,7 +6002,7 @@
         <v>320</v>
       </c>
       <c r="F159" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G159" t="s">
         <v>457</v>
@@ -6028,7 +6028,7 @@
         <v>320</v>
       </c>
       <c r="F160" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G160" t="s">
         <v>458</v>
@@ -6054,7 +6054,7 @@
         <v>320</v>
       </c>
       <c r="F161" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G161" t="s">
         <v>459</v>
@@ -6080,10 +6080,10 @@
         <v>320</v>
       </c>
       <c r="F162" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G162" t="s">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -6106,10 +6106,10 @@
         <v>320</v>
       </c>
       <c r="F163" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G163" t="s">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="H163">
         <v>2</v>
@@ -6129,10 +6129,10 @@
         <v>298</v>
       </c>
       <c r="E164" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F164" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G164" t="s">
         <v>461</v>
@@ -6155,10 +6155,10 @@
         <v>298</v>
       </c>
       <c r="E165" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F165" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G165" t="s">
         <v>462</v>
@@ -6184,7 +6184,7 @@
         <v>320</v>
       </c>
       <c r="F166" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G166" t="s">
         <v>463</v>
@@ -6210,7 +6210,7 @@
         <v>320</v>
       </c>
       <c r="F167" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G167" t="s">
         <v>464</v>
@@ -6236,7 +6236,7 @@
         <v>320</v>
       </c>
       <c r="F168" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G168" t="s">
         <v>465</v>
@@ -6262,7 +6262,7 @@
         <v>320</v>
       </c>
       <c r="F169" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G169" t="s">
         <v>465</v>
@@ -6288,7 +6288,7 @@
         <v>320</v>
       </c>
       <c r="F170" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G170" t="s">
         <v>466</v>
@@ -6314,7 +6314,7 @@
         <v>320</v>
       </c>
       <c r="F171" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G171" t="s">
         <v>467</v>
@@ -6340,7 +6340,7 @@
         <v>320</v>
       </c>
       <c r="F172" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G172" t="s">
         <v>468</v>
@@ -6366,7 +6366,7 @@
         <v>320</v>
       </c>
       <c r="F173" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G173" t="s">
         <v>469</v>
@@ -6392,7 +6392,7 @@
         <v>320</v>
       </c>
       <c r="F174" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G174" t="s">
         <v>470</v>
@@ -6418,7 +6418,7 @@
         <v>320</v>
       </c>
       <c r="F175" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G175" t="s">
         <v>471</v>
@@ -6444,7 +6444,7 @@
         <v>320</v>
       </c>
       <c r="F176" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G176" t="s">
         <v>472</v>
@@ -6470,7 +6470,7 @@
         <v>320</v>
       </c>
       <c r="F177" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G177" t="s">
         <v>473</v>
@@ -6496,7 +6496,7 @@
         <v>320</v>
       </c>
       <c r="F178" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G178" t="s">
         <v>474</v>
@@ -6522,7 +6522,7 @@
         <v>320</v>
       </c>
       <c r="F179" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G179" t="s">
         <v>474</v>
@@ -6548,7 +6548,7 @@
         <v>320</v>
       </c>
       <c r="F180" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G180" t="s">
         <v>475</v>
@@ -6574,7 +6574,7 @@
         <v>320</v>
       </c>
       <c r="F181" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G181" t="s">
         <v>476</v>
@@ -6600,7 +6600,7 @@
         <v>320</v>
       </c>
       <c r="F182" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G182" t="s">
         <v>477</v>
@@ -6626,7 +6626,7 @@
         <v>320</v>
       </c>
       <c r="F183" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G183" t="s">
         <v>478</v>
@@ -6652,7 +6652,7 @@
         <v>320</v>
       </c>
       <c r="F184" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G184" t="s">
         <v>479</v>
@@ -6678,7 +6678,7 @@
         <v>320</v>
       </c>
       <c r="F185" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G185" t="s">
         <v>480</v>
@@ -6704,7 +6704,7 @@
         <v>320</v>
       </c>
       <c r="F186" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G186" t="s">
         <v>481</v>
@@ -6730,7 +6730,7 @@
         <v>320</v>
       </c>
       <c r="F187" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G187" t="s">
         <v>482</v>
@@ -6753,10 +6753,10 @@
         <v>310</v>
       </c>
       <c r="E188" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F188" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G188" t="s">
         <v>483</v>
@@ -6779,10 +6779,10 @@
         <v>310</v>
       </c>
       <c r="E189" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F189" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G189" t="s">
         <v>483</v>
@@ -6808,7 +6808,7 @@
         <v>320</v>
       </c>
       <c r="F190" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G190" t="s">
         <v>484</v>
@@ -6834,7 +6834,7 @@
         <v>320</v>
       </c>
       <c r="F191" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G191" t="s">
         <v>485</v>
@@ -6860,7 +6860,7 @@
         <v>320</v>
       </c>
       <c r="F192" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G192" t="s">
         <v>486</v>
@@ -6886,7 +6886,7 @@
         <v>320</v>
       </c>
       <c r="F193" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G193" t="s">
         <v>487</v>
@@ -6912,7 +6912,7 @@
         <v>320</v>
       </c>
       <c r="F194" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G194" t="s">
         <v>488</v>
@@ -6938,7 +6938,7 @@
         <v>320</v>
       </c>
       <c r="F195" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G195" t="s">
         <v>489</v>
@@ -6964,7 +6964,7 @@
         <v>320</v>
       </c>
       <c r="F196" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G196" t="s">
         <v>490</v>
@@ -6990,7 +6990,7 @@
         <v>320</v>
       </c>
       <c r="F197" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G197" t="s">
         <v>491</v>
@@ -7016,7 +7016,7 @@
         <v>320</v>
       </c>
       <c r="F198" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G198" t="s">
         <v>492</v>
@@ -7042,7 +7042,7 @@
         <v>320</v>
       </c>
       <c r="F199" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G199" t="s">
         <v>493</v>
@@ -7068,7 +7068,7 @@
         <v>320</v>
       </c>
       <c r="F200" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G200" t="s">
         <v>494</v>
@@ -7094,7 +7094,7 @@
         <v>320</v>
       </c>
       <c r="F201" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G201" t="s">
         <v>495</v>
@@ -7120,7 +7120,7 @@
         <v>320</v>
       </c>
       <c r="F202" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G202" t="s">
         <v>496</v>
@@ -7146,7 +7146,7 @@
         <v>320</v>
       </c>
       <c r="F203" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G203" t="s">
         <v>496</v>
@@ -7172,7 +7172,7 @@
         <v>320</v>
       </c>
       <c r="F204" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G204" t="s">
         <v>497</v>
@@ -7198,7 +7198,7 @@
         <v>320</v>
       </c>
       <c r="F205" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G205" t="s">
         <v>498</v>
@@ -7224,7 +7224,7 @@
         <v>320</v>
       </c>
       <c r="F206" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G206" t="s">
         <v>499</v>
@@ -7250,7 +7250,7 @@
         <v>320</v>
       </c>
       <c r="F207" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G207" t="s">
         <v>500</v>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,30 +14,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="501">
-  <si>
-    <t>Kode Identitas</t>
-  </si>
-  <si>
-    <t>Nama Perusahaan</t>
-  </si>
-  <si>
-    <t>Status Dokumen</t>
-  </si>
-  <si>
-    <t>Email Tujuan</t>
-  </si>
-  <si>
-    <t>Status terakhir</t>
-  </si>
-  <si>
-    <t>Status History</t>
-  </si>
-  <si>
-    <t>Timestamp History</t>
-  </si>
-  <si>
-    <t>Urutan History</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="517">
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>survey_status</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>global_status</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+  <si>
+    <t>order</t>
   </si>
   <si>
     <t>7207011006001000 - UB - 1</t>
@@ -349,6 +349,15 @@
     <t>7271000000000000 - UB - 53</t>
   </si>
   <si>
+    <t>7207011003000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7207040002001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212040011100100 - UB - 1</t>
+  </si>
+  <si>
     <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
   </si>
   <si>
@@ -655,6 +664,15 @@
     <t>KONSUIL, PT</t>
   </si>
   <si>
+    <t>BANK MANDIRI (PERSERO) TBK KCP BUOL, PT</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT DIAPATIH</t>
+  </si>
+  <si>
+    <t>SINERGI BINTANG UTARA</t>
+  </si>
+  <si>
     <t>DRAFT</t>
   </si>
   <si>
@@ -976,12 +994,24 @@
     <t>palukonsuil@yahoo.com</t>
   </si>
   <si>
+    <t>nyoalvaro@gmail.com</t>
+  </si>
+  <si>
+    <t>yohanesyafetsulung@gmail.com</t>
+  </si>
+  <si>
+    <t>pt.sinergibintangutara@yahoo.com</t>
+  </si>
+  <si>
     <t>bounced</t>
   </si>
   <si>
     <t>queued</t>
   </si>
   <si>
+    <t>permanent_fail</t>
+  </si>
+  <si>
     <t>19 Mei 2026, 11:14:37</t>
   </si>
   <si>
@@ -1517,6 +1547,24 @@
   </si>
   <si>
     <t>02 Jun 2026, 02:20:10</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 11:14:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:32:29</t>
+  </si>
+  <si>
+    <t>21 Mei 2026, 08:24:52</t>
+  </si>
+  <si>
+    <t>21 Mei 2026, 08:24:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:45:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:44:51</t>
   </si>
 </sst>
 </file>
@@ -1874,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1908,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F2" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G2" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1934,22 +1982,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E3" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F3" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1960,22 +2008,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1986,22 +2034,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F5" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2012,22 +2060,22 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F6" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G6" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2038,22 +2086,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F7" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G7" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -2064,22 +2112,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F8" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G8" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2090,22 +2138,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F9" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G9" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -2116,22 +2164,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F10" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G10" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2142,22 +2190,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F11" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G11" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -2168,22 +2216,22 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E12" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F12" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G12" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2194,22 +2242,22 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E13" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F13" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -2220,22 +2268,22 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F14" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G14" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2246,22 +2294,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F15" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G15" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -2272,22 +2320,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E16" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F16" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G16" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2298,22 +2346,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D17" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E17" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F17" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G17" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2324,22 +2372,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E18" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F18" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G18" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2350,22 +2398,22 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E19" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F19" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G19" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -2376,22 +2424,22 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D20" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F20" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G20" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -2402,22 +2450,22 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F21" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G21" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -2428,22 +2476,22 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D22" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E22" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G22" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2454,22 +2502,22 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C23" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E23" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F23" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G23" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -2480,22 +2528,22 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E24" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F24" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G24" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2506,22 +2554,22 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D25" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F25" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G25" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="H25">
         <v>2</v>
@@ -2532,22 +2580,22 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E26" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F26" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G26" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -2558,22 +2606,22 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D27" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E27" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F27" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G27" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -2584,22 +2632,22 @@
         <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D28" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F28" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G28" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2610,22 +2658,22 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E29" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F29" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G29" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -2636,22 +2684,22 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D30" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E30" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F30" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G30" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -2662,22 +2710,22 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E31" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F31" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G31" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -2688,22 +2736,22 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D32" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E32" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F32" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G32" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2714,22 +2762,22 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D33" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E33" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F33" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G33" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -2740,22 +2788,22 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D34" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F34" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G34" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2766,22 +2814,22 @@
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D35" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E35" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F35" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G35" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -2792,22 +2840,22 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D36" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E36" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F36" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G36" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2818,22 +2866,22 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D37" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E37" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F37" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G37" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H37">
         <v>2</v>
@@ -2844,22 +2892,22 @@
         <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D38" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E38" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F38" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G38" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2870,22 +2918,22 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D39" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E39" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F39" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G39" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -2896,22 +2944,22 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D40" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F40" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G40" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2922,22 +2970,22 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D41" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E41" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F41" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G41" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="H41">
         <v>2</v>
@@ -2948,22 +2996,22 @@
         <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F42" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G42" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2974,22 +3022,22 @@
         <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F43" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G43" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="H43">
         <v>2</v>
@@ -3000,22 +3048,22 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D44" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E44" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F44" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G44" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -3026,22 +3074,22 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D45" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E45" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F45" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G45" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="H45">
         <v>2</v>
@@ -3052,22 +3100,22 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E46" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F46" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G46" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -3078,22 +3126,22 @@
         <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C47" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D47" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E47" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F47" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G47" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -3104,22 +3152,22 @@
         <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C48" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D48" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E48" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F48" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G48" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -3130,22 +3178,22 @@
         <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D49" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E49" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F49" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G49" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -3156,22 +3204,22 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D50" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E50" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F50" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G50" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -3182,22 +3230,22 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E51" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F51" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G51" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -3208,22 +3256,22 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E52" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F52" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G52" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -3234,22 +3282,22 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C53" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D53" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E53" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F53" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G53" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -3260,22 +3308,22 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E54" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F54" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G54" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -3286,22 +3334,22 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E55" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F55" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G55" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -3312,22 +3360,22 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D56" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E56" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F56" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G56" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -3338,22 +3386,22 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E57" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F57" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G57" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -3364,22 +3412,22 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D58" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F58" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G58" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -3390,22 +3438,22 @@
         <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D59" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F59" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G59" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -3416,22 +3464,22 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D60" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E60" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F60" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G60" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -3442,22 +3490,22 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D61" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E61" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F61" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G61" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -3468,22 +3516,22 @@
         <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C62" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E62" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F62" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G62" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -3494,22 +3542,22 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E63" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F63" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G63" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H63">
         <v>2</v>
@@ -3520,22 +3568,22 @@
         <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D64" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E64" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F64" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G64" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -3546,22 +3594,22 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C65" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D65" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E65" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F65" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G65" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -3572,22 +3620,22 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C66" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D66" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E66" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F66" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G66" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -3598,22 +3646,22 @@
         <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D67" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E67" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F67" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G67" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -3624,22 +3672,22 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C68" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D68" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E68" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F68" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G68" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3650,22 +3698,22 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C69" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D69" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E69" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F69" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G69" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="H69">
         <v>2</v>
@@ -3676,22 +3724,22 @@
         <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D70" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E70" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F70" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G70" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3702,22 +3750,22 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D71" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E71" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F71" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G71" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -3728,22 +3776,22 @@
         <v>43</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D72" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E72" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F72" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G72" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -3754,22 +3802,22 @@
         <v>43</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C73" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D73" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E73" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F73" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G73" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H73">
         <v>2</v>
@@ -3780,22 +3828,22 @@
         <v>44</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C74" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E74" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F74" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G74" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -3806,22 +3854,22 @@
         <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D75" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E75" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F75" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G75" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="H75">
         <v>2</v>
@@ -3832,22 +3880,22 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D76" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E76" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F76" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G76" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -3858,22 +3906,22 @@
         <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D77" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E77" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F77" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G77" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -3884,22 +3932,22 @@
         <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D78" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E78" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F78" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G78" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -3910,22 +3958,22 @@
         <v>46</v>
       </c>
       <c r="B79" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E79" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F79" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G79" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="H79">
         <v>2</v>
@@ -3936,22 +3984,22 @@
         <v>47</v>
       </c>
       <c r="B80" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D80" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E80" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F80" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G80" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -3962,22 +4010,22 @@
         <v>47</v>
       </c>
       <c r="B81" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D81" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E81" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F81" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G81" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="H81">
         <v>2</v>
@@ -3988,22 +4036,22 @@
         <v>48</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D82" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E82" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F82" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G82" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -4014,22 +4062,22 @@
         <v>48</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C83" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D83" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E83" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F83" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G83" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="H83">
         <v>2</v>
@@ -4040,22 +4088,22 @@
         <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C84" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D84" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E84" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F84" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G84" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -4066,22 +4114,22 @@
         <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C85" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D85" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E85" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F85" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G85" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="H85">
         <v>2</v>
@@ -4092,22 +4140,22 @@
         <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D86" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E86" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F86" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G86" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -4118,22 +4166,22 @@
         <v>50</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D87" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E87" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F87" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G87" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -4144,22 +4192,22 @@
         <v>51</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C88" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D88" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E88" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F88" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G88" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -4170,22 +4218,22 @@
         <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D89" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E89" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F89" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G89" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -4196,22 +4244,22 @@
         <v>52</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C90" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D90" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E90" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F90" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G90" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -4222,22 +4270,22 @@
         <v>52</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C91" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D91" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E91" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F91" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G91" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -4248,22 +4296,22 @@
         <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D92" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E92" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F92" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G92" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -4274,22 +4322,22 @@
         <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C93" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D93" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E93" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F93" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G93" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -4300,22 +4348,22 @@
         <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C94" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D94" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E94" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F94" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G94" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -4326,22 +4374,22 @@
         <v>54</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C95" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D95" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E95" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F95" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G95" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -4352,22 +4400,22 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D96" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E96" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F96" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G96" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -4378,22 +4426,22 @@
         <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C97" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D97" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E97" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F97" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G97" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="H97">
         <v>2</v>
@@ -4404,22 +4452,22 @@
         <v>56</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C98" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D98" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E98" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F98" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G98" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -4430,22 +4478,22 @@
         <v>56</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C99" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D99" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E99" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F99" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G99" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="H99">
         <v>2</v>
@@ -4456,22 +4504,22 @@
         <v>57</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D100" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E100" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F100" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G100" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -4482,22 +4530,22 @@
         <v>57</v>
       </c>
       <c r="B101" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C101" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D101" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E101" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F101" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G101" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -4508,22 +4556,22 @@
         <v>58</v>
       </c>
       <c r="B102" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C102" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D102" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E102" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F102" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G102" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -4534,22 +4582,22 @@
         <v>58</v>
       </c>
       <c r="B103" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C103" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D103" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E103" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F103" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G103" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -4560,22 +4608,22 @@
         <v>59</v>
       </c>
       <c r="B104" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C104" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E104" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F104" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G104" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -4586,22 +4634,22 @@
         <v>59</v>
       </c>
       <c r="B105" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C105" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E105" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F105" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G105" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="H105">
         <v>2</v>
@@ -4612,22 +4660,22 @@
         <v>60</v>
       </c>
       <c r="B106" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C106" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E106" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F106" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G106" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -4638,22 +4686,22 @@
         <v>60</v>
       </c>
       <c r="B107" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C107" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D107" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E107" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F107" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G107" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="H107">
         <v>2</v>
@@ -4664,22 +4712,22 @@
         <v>61</v>
       </c>
       <c r="B108" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C108" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D108" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E108" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F108" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G108" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -4690,22 +4738,22 @@
         <v>61</v>
       </c>
       <c r="B109" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C109" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D109" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E109" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F109" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G109" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="H109">
         <v>2</v>
@@ -4716,22 +4764,22 @@
         <v>62</v>
       </c>
       <c r="B110" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C110" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D110" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E110" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F110" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G110" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -4742,22 +4790,22 @@
         <v>62</v>
       </c>
       <c r="B111" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C111" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D111" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E111" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F111" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G111" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="H111">
         <v>2</v>
@@ -4768,22 +4816,22 @@
         <v>63</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C112" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D112" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E112" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F112" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G112" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -4794,22 +4842,22 @@
         <v>63</v>
       </c>
       <c r="B113" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C113" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D113" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E113" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F113" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G113" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="H113">
         <v>2</v>
@@ -4820,22 +4868,22 @@
         <v>64</v>
       </c>
       <c r="B114" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C114" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D114" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E114" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F114" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G114" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -4846,22 +4894,22 @@
         <v>64</v>
       </c>
       <c r="B115" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D115" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E115" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F115" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G115" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4872,22 +4920,22 @@
         <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D116" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E116" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F116" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G116" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -4898,22 +4946,22 @@
         <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C117" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D117" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E117" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F117" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G117" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="H117">
         <v>2</v>
@@ -4924,22 +4972,22 @@
         <v>66</v>
       </c>
       <c r="B118" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C118" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D118" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E118" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F118" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G118" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -4950,22 +4998,22 @@
         <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C119" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D119" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E119" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F119" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G119" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H119">
         <v>2</v>
@@ -4976,22 +5024,22 @@
         <v>67</v>
       </c>
       <c r="B120" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C120" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D120" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E120" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F120" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G120" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -5002,22 +5050,22 @@
         <v>67</v>
       </c>
       <c r="B121" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C121" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D121" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E121" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F121" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G121" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H121">
         <v>2</v>
@@ -5028,22 +5076,22 @@
         <v>68</v>
       </c>
       <c r="B122" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C122" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D122" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E122" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F122" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G122" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -5054,22 +5102,22 @@
         <v>68</v>
       </c>
       <c r="B123" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C123" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D123" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E123" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F123" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G123" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="H123">
         <v>2</v>
@@ -5080,22 +5128,22 @@
         <v>69</v>
       </c>
       <c r="B124" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C124" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D124" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E124" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F124" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G124" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -5106,22 +5154,22 @@
         <v>69</v>
       </c>
       <c r="B125" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C125" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D125" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E125" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F125" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G125" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="H125">
         <v>2</v>
@@ -5132,22 +5180,22 @@
         <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C126" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D126" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E126" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F126" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G126" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -5158,22 +5206,22 @@
         <v>70</v>
       </c>
       <c r="B127" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C127" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D127" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E127" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F127" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G127" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="H127">
         <v>2</v>
@@ -5184,22 +5232,22 @@
         <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C128" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D128" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E128" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F128" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G128" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -5210,22 +5258,22 @@
         <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C129" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D129" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E129" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F129" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G129" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="H129">
         <v>2</v>
@@ -5236,22 +5284,22 @@
         <v>72</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C130" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D130" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E130" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F130" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G130" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -5262,22 +5310,22 @@
         <v>72</v>
       </c>
       <c r="B131" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C131" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D131" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E131" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F131" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G131" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="H131">
         <v>2</v>
@@ -5288,22 +5336,22 @@
         <v>73</v>
       </c>
       <c r="B132" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C132" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D132" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E132" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F132" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G132" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -5314,22 +5362,22 @@
         <v>73</v>
       </c>
       <c r="B133" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C133" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D133" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E133" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F133" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G133" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="H133">
         <v>2</v>
@@ -5340,22 +5388,22 @@
         <v>74</v>
       </c>
       <c r="B134" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C134" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D134" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E134" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F134" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G134" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -5366,22 +5414,22 @@
         <v>74</v>
       </c>
       <c r="B135" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D135" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E135" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F135" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G135" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="H135">
         <v>2</v>
@@ -5392,22 +5440,22 @@
         <v>75</v>
       </c>
       <c r="B136" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C136" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D136" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E136" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F136" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G136" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="H136">
         <v>1</v>
@@ -5418,22 +5466,22 @@
         <v>75</v>
       </c>
       <c r="B137" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C137" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D137" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E137" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F137" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G137" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="H137">
         <v>2</v>
@@ -5444,22 +5492,22 @@
         <v>76</v>
       </c>
       <c r="B138" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C138" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D138" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E138" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F138" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G138" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -5470,22 +5518,22 @@
         <v>76</v>
       </c>
       <c r="B139" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D139" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E139" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F139" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G139" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="H139">
         <v>2</v>
@@ -5496,22 +5544,22 @@
         <v>77</v>
       </c>
       <c r="B140" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C140" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D140" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E140" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F140" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G140" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="H140">
         <v>1</v>
@@ -5522,22 +5570,22 @@
         <v>77</v>
       </c>
       <c r="B141" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C141" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D141" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E141" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F141" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G141" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="H141">
         <v>2</v>
@@ -5548,22 +5596,22 @@
         <v>78</v>
       </c>
       <c r="B142" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C142" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D142" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E142" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F142" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G142" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -5574,22 +5622,22 @@
         <v>78</v>
       </c>
       <c r="B143" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C143" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D143" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E143" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F143" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G143" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="H143">
         <v>2</v>
@@ -5600,22 +5648,22 @@
         <v>79</v>
       </c>
       <c r="B144" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C144" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D144" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E144" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F144" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G144" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -5626,22 +5674,22 @@
         <v>79</v>
       </c>
       <c r="B145" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C145" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D145" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E145" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F145" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G145" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="H145">
         <v>2</v>
@@ -5652,22 +5700,22 @@
         <v>80</v>
       </c>
       <c r="B146" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C146" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D146" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E146" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F146" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G146" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -5678,22 +5726,22 @@
         <v>80</v>
       </c>
       <c r="B147" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C147" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D147" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E147" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F147" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G147" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="H147">
         <v>2</v>
@@ -5704,22 +5752,22 @@
         <v>81</v>
       </c>
       <c r="B148" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C148" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D148" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E148" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F148" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G148" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -5730,22 +5778,22 @@
         <v>81</v>
       </c>
       <c r="B149" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C149" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D149" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E149" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F149" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G149" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="H149">
         <v>2</v>
@@ -5756,22 +5804,22 @@
         <v>82</v>
       </c>
       <c r="B150" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C150" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D150" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E150" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F150" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G150" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -5782,22 +5830,22 @@
         <v>82</v>
       </c>
       <c r="B151" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C151" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D151" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E151" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F151" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G151" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="H151">
         <v>2</v>
@@ -5808,22 +5856,22 @@
         <v>83</v>
       </c>
       <c r="B152" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C152" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D152" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E152" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F152" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G152" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -5834,22 +5882,22 @@
         <v>83</v>
       </c>
       <c r="B153" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C153" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D153" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E153" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F153" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G153" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="H153">
         <v>2</v>
@@ -5860,22 +5908,22 @@
         <v>84</v>
       </c>
       <c r="B154" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C154" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D154" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E154" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F154" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G154" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -5886,22 +5934,22 @@
         <v>84</v>
       </c>
       <c r="B155" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C155" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D155" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E155" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F155" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G155" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="H155">
         <v>2</v>
@@ -5912,22 +5960,22 @@
         <v>85</v>
       </c>
       <c r="B156" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C156" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D156" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E156" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F156" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G156" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -5938,22 +5986,22 @@
         <v>85</v>
       </c>
       <c r="B157" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C157" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D157" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E157" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F157" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G157" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="H157">
         <v>2</v>
@@ -5964,22 +6012,22 @@
         <v>86</v>
       </c>
       <c r="B158" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C158" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D158" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E158" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F158" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G158" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -5990,22 +6038,22 @@
         <v>86</v>
       </c>
       <c r="B159" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C159" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D159" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E159" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F159" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G159" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="H159">
         <v>2</v>
@@ -6016,22 +6064,22 @@
         <v>87</v>
       </c>
       <c r="B160" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C160" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D160" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E160" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F160" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G160" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -6042,22 +6090,22 @@
         <v>87</v>
       </c>
       <c r="B161" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C161" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D161" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E161" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F161" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G161" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="H161">
         <v>2</v>
@@ -6068,22 +6116,22 @@
         <v>88</v>
       </c>
       <c r="B162" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C162" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D162" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E162" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F162" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G162" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -6094,22 +6142,22 @@
         <v>88</v>
       </c>
       <c r="B163" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C163" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D163" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E163" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F163" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G163" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="H163">
         <v>2</v>
@@ -6120,22 +6168,22 @@
         <v>89</v>
       </c>
       <c r="B164" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C164" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D164" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E164" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F164" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G164" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -6146,22 +6194,22 @@
         <v>89</v>
       </c>
       <c r="B165" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C165" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D165" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E165" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F165" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G165" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="H165">
         <v>2</v>
@@ -6172,22 +6220,22 @@
         <v>90</v>
       </c>
       <c r="B166" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C166" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D166" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E166" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F166" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G166" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -6198,22 +6246,22 @@
         <v>90</v>
       </c>
       <c r="B167" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C167" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D167" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E167" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F167" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G167" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="H167">
         <v>2</v>
@@ -6224,22 +6272,22 @@
         <v>91</v>
       </c>
       <c r="B168" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C168" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D168" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E168" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F168" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G168" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -6250,22 +6298,22 @@
         <v>91</v>
       </c>
       <c r="B169" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C169" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D169" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E169" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F169" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G169" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="H169">
         <v>2</v>
@@ -6276,22 +6324,22 @@
         <v>92</v>
       </c>
       <c r="B170" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C170" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D170" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E170" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F170" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G170" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="H170">
         <v>1</v>
@@ -6302,22 +6350,22 @@
         <v>92</v>
       </c>
       <c r="B171" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C171" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D171" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E171" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F171" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G171" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="H171">
         <v>2</v>
@@ -6328,22 +6376,22 @@
         <v>93</v>
       </c>
       <c r="B172" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C172" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D172" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E172" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F172" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G172" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -6354,22 +6402,22 @@
         <v>93</v>
       </c>
       <c r="B173" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C173" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D173" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E173" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F173" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G173" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="H173">
         <v>2</v>
@@ -6380,22 +6428,22 @@
         <v>94</v>
       </c>
       <c r="B174" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C174" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D174" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E174" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F174" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G174" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -6406,22 +6454,22 @@
         <v>94</v>
       </c>
       <c r="B175" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C175" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D175" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E175" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F175" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G175" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="H175">
         <v>2</v>
@@ -6432,22 +6480,22 @@
         <v>95</v>
       </c>
       <c r="B176" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C176" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D176" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E176" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F176" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G176" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -6458,22 +6506,22 @@
         <v>95</v>
       </c>
       <c r="B177" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D177" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E177" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F177" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G177" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="H177">
         <v>2</v>
@@ -6484,22 +6532,22 @@
         <v>96</v>
       </c>
       <c r="B178" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D178" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E178" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F178" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G178" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -6510,22 +6558,22 @@
         <v>96</v>
       </c>
       <c r="B179" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C179" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D179" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="E179" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F179" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G179" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="H179">
         <v>2</v>
@@ -6536,22 +6584,22 @@
         <v>97</v>
       </c>
       <c r="B180" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C180" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D180" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E180" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F180" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G180" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -6562,22 +6610,22 @@
         <v>97</v>
       </c>
       <c r="B181" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C181" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D181" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E181" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F181" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G181" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="H181">
         <v>2</v>
@@ -6588,22 +6636,22 @@
         <v>98</v>
       </c>
       <c r="B182" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C182" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D182" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E182" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F182" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G182" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -6614,22 +6662,22 @@
         <v>98</v>
       </c>
       <c r="B183" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C183" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D183" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="E183" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F183" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G183" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="H183">
         <v>2</v>
@@ -6640,22 +6688,22 @@
         <v>99</v>
       </c>
       <c r="B184" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C184" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D184" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E184" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F184" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G184" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -6666,22 +6714,22 @@
         <v>99</v>
       </c>
       <c r="B185" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C185" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D185" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E185" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F185" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G185" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="H185">
         <v>2</v>
@@ -6692,22 +6740,22 @@
         <v>100</v>
       </c>
       <c r="B186" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C186" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D186" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E186" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F186" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G186" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -6718,22 +6766,22 @@
         <v>100</v>
       </c>
       <c r="B187" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C187" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D187" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E187" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F187" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G187" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="H187">
         <v>2</v>
@@ -6744,22 +6792,22 @@
         <v>101</v>
       </c>
       <c r="B188" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C188" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D188" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E188" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F188" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G188" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -6770,22 +6818,22 @@
         <v>101</v>
       </c>
       <c r="B189" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C189" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D189" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E189" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F189" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G189" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="H189">
         <v>2</v>
@@ -6796,22 +6844,22 @@
         <v>102</v>
       </c>
       <c r="B190" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C190" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D190" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E190" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F190" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G190" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -6822,22 +6870,22 @@
         <v>102</v>
       </c>
       <c r="B191" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C191" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D191" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E191" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F191" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G191" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="H191">
         <v>2</v>
@@ -6848,22 +6896,22 @@
         <v>103</v>
       </c>
       <c r="B192" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C192" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D192" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E192" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F192" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G192" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -6874,22 +6922,22 @@
         <v>103</v>
       </c>
       <c r="B193" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C193" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D193" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E193" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F193" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G193" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="H193">
         <v>2</v>
@@ -6900,22 +6948,22 @@
         <v>104</v>
       </c>
       <c r="B194" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C194" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D194" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E194" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F194" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G194" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="H194">
         <v>1</v>
@@ -6926,22 +6974,22 @@
         <v>104</v>
       </c>
       <c r="B195" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C195" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D195" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="E195" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F195" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G195" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="H195">
         <v>2</v>
@@ -6952,22 +7000,22 @@
         <v>105</v>
       </c>
       <c r="B196" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C196" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D196" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E196" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F196" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G196" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="H196">
         <v>1</v>
@@ -6978,22 +7026,22 @@
         <v>105</v>
       </c>
       <c r="B197" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C197" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D197" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E197" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F197" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G197" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="H197">
         <v>2</v>
@@ -7004,22 +7052,22 @@
         <v>106</v>
       </c>
       <c r="B198" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C198" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D198" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E198" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F198" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G198" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="H198">
         <v>1</v>
@@ -7030,22 +7078,22 @@
         <v>106</v>
       </c>
       <c r="B199" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C199" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D199" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="E199" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F199" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G199" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="H199">
         <v>2</v>
@@ -7056,22 +7104,22 @@
         <v>107</v>
       </c>
       <c r="B200" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C200" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D200" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E200" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F200" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G200" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="H200">
         <v>1</v>
@@ -7082,22 +7130,22 @@
         <v>107</v>
       </c>
       <c r="B201" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C201" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D201" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E201" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F201" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G201" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="H201">
         <v>2</v>
@@ -7108,22 +7156,22 @@
         <v>108</v>
       </c>
       <c r="B202" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C202" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D202" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E202" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F202" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G202" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="H202">
         <v>1</v>
@@ -7134,22 +7182,22 @@
         <v>108</v>
       </c>
       <c r="B203" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C203" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D203" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="E203" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F203" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G203" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="H203">
         <v>2</v>
@@ -7160,22 +7208,22 @@
         <v>109</v>
       </c>
       <c r="B204" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C204" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D204" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E204" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F204" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G204" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="H204">
         <v>1</v>
@@ -7186,22 +7234,22 @@
         <v>109</v>
       </c>
       <c r="B205" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C205" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D205" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E205" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F205" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G205" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="H205">
         <v>2</v>
@@ -7212,22 +7260,22 @@
         <v>110</v>
       </c>
       <c r="B206" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C206" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D206" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E206" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F206" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G206" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -7238,24 +7286,232 @@
         <v>110</v>
       </c>
       <c r="B207" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C207" t="s">
+        <v>222</v>
+      </c>
+      <c r="D207" t="s">
+        <v>325</v>
+      </c>
+      <c r="E207" t="s">
+        <v>329</v>
+      </c>
+      <c r="F207" t="s">
+        <v>330</v>
+      </c>
+      <c r="G207" t="s">
+        <v>510</v>
+      </c>
+      <c r="H207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>111</v>
+      </c>
+      <c r="B208" t="s">
         <v>216</v>
       </c>
-      <c r="D207" t="s">
-        <v>319</v>
-      </c>
-      <c r="E207" t="s">
-        <v>320</v>
-      </c>
-      <c r="F207" t="s">
-        <v>321</v>
-      </c>
-      <c r="G207" t="s">
-        <v>500</v>
-      </c>
-      <c r="H207">
+      <c r="C208" t="s">
+        <v>222</v>
+      </c>
+      <c r="D208" t="s">
+        <v>326</v>
+      </c>
+      <c r="E208" t="s">
+        <v>329</v>
+      </c>
+      <c r="F208" t="s">
+        <v>329</v>
+      </c>
+      <c r="G208" t="s">
+        <v>511</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>111</v>
+      </c>
+      <c r="B209" t="s">
+        <v>216</v>
+      </c>
+      <c r="C209" t="s">
+        <v>222</v>
+      </c>
+      <c r="D209" t="s">
+        <v>326</v>
+      </c>
+      <c r="E209" t="s">
+        <v>329</v>
+      </c>
+      <c r="F209" t="s">
+        <v>330</v>
+      </c>
+      <c r="G209" t="s">
+        <v>335</v>
+      </c>
+      <c r="H209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>112</v>
+      </c>
+      <c r="B210" t="s">
+        <v>217</v>
+      </c>
+      <c r="C210" t="s">
+        <v>222</v>
+      </c>
+      <c r="D210" t="s">
+        <v>327</v>
+      </c>
+      <c r="E210" t="s">
+        <v>329</v>
+      </c>
+      <c r="F210" t="s">
+        <v>331</v>
+      </c>
+      <c r="G210" t="s">
+        <v>512</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>112</v>
+      </c>
+      <c r="B211" t="s">
+        <v>217</v>
+      </c>
+      <c r="C211" t="s">
+        <v>222</v>
+      </c>
+      <c r="D211" t="s">
+        <v>327</v>
+      </c>
+      <c r="E211" t="s">
+        <v>329</v>
+      </c>
+      <c r="F211" t="s">
+        <v>329</v>
+      </c>
+      <c r="G211" t="s">
+        <v>513</v>
+      </c>
+      <c r="H211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>112</v>
+      </c>
+      <c r="B212" t="s">
+        <v>217</v>
+      </c>
+      <c r="C212" t="s">
+        <v>222</v>
+      </c>
+      <c r="D212" t="s">
+        <v>327</v>
+      </c>
+      <c r="E212" t="s">
+        <v>329</v>
+      </c>
+      <c r="F212" t="s">
+        <v>330</v>
+      </c>
+      <c r="G212" t="s">
+        <v>514</v>
+      </c>
+      <c r="H212">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>112</v>
+      </c>
+      <c r="B213" t="s">
+        <v>217</v>
+      </c>
+      <c r="C213" t="s">
+        <v>222</v>
+      </c>
+      <c r="D213" t="s">
+        <v>327</v>
+      </c>
+      <c r="E213" t="s">
+        <v>221</v>
+      </c>
+      <c r="F213" t="s">
+        <v>221</v>
+      </c>
+      <c r="G213" t="s">
+        <v>221</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>113</v>
+      </c>
+      <c r="B214" t="s">
+        <v>218</v>
+      </c>
+      <c r="C214" t="s">
+        <v>222</v>
+      </c>
+      <c r="D214" t="s">
+        <v>328</v>
+      </c>
+      <c r="E214" t="s">
+        <v>329</v>
+      </c>
+      <c r="F214" t="s">
+        <v>329</v>
+      </c>
+      <c r="G214" t="s">
+        <v>515</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>113</v>
+      </c>
+      <c r="B215" t="s">
+        <v>218</v>
+      </c>
+      <c r="C215" t="s">
+        <v>222</v>
+      </c>
+      <c r="D215" t="s">
+        <v>328</v>
+      </c>
+      <c r="E215" t="s">
+        <v>329</v>
+      </c>
+      <c r="F215" t="s">
+        <v>330</v>
+      </c>
+      <c r="G215" t="s">
+        <v>516</v>
+      </c>
+      <c r="H215">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="517">
   <si>
     <t>code</t>
   </si>
@@ -67,6 +67,297 @@
     <t>7202061009000100 - UB - 1</t>
   </si>
   <si>
+    <t>7202053007000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7202010020000300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7202054003000600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7202020019001300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021005000209 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021004200200 - UB - 4</t>
+  </si>
+  <si>
+    <t>7203011004200100 - UB - 2</t>
+  </si>
+  <si>
+    <t>7203021005000401 - UB - 3</t>
+  </si>
+  <si>
+    <t>7203021005000105 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203030021001300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021005000406 - UB - 10</t>
+  </si>
+  <si>
+    <t>7203031006000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204070011000302 - UB - 2</t>
+  </si>
+  <si>
+    <t>7204070011000100 - UB - 2</t>
+  </si>
+  <si>
+    <t>7204071001001500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204032006001600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205090009000301 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205000000000000 - UB - 2</t>
+  </si>
+  <si>
+    <t>7205090010000301 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205130008000401 - UB - 1</t>
+  </si>
+  <si>
+    <t>7205080024000400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206040014000500 - UB - 2</t>
+  </si>
+  <si>
+    <t>7206040016002400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206050001000600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7206040016001300 - UB - 2</t>
+  </si>
+  <si>
+    <t>7206010003001100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7207011006001000 - UB - 1</t>
+  </si>
+  <si>
+    <t>7207011004000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7207011003000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7207040002001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208040010000103 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208061033000500 - UB - 2</t>
+  </si>
+  <si>
+    <t>7208020017000501 - UB - 2</t>
+  </si>
+  <si>
+    <t>7208011001000200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208030015000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7208021003000500 - UB - 2</t>
+  </si>
+  <si>
+    <t>7209051007000101 - UB - 1</t>
+  </si>
+  <si>
+    <t>7209051019000800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7209050015000600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210060013000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210120012001800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7210121006000500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7211040004000800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212020008100200 - UB - 6</t>
+  </si>
+  <si>
+    <t>7212020008000900 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212010010000100 - UB - 8</t>
+  </si>
+  <si>
+    <t>7212040006400100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7212040006000200 - UB - 2</t>
+  </si>
+  <si>
+    <t>7212050009000200 - UB - 12</t>
+  </si>
+  <si>
+    <t>7212040009000200 - UB - 3</t>
+  </si>
+  <si>
+    <t>7212080001200100 - UB - 5</t>
+  </si>
+  <si>
+    <t>7212040011100100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031007000200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271041003001200 - UB - 5</t>
+  </si>
+  <si>
+    <t>7271010004001600 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271010006000103 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271011006000200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020007000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271012004000300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020007004202 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271010005000800 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271030001002000 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030001001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020009002300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020007000500 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271020004001901 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271010011002703 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271041003000901 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271040003000102 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030005002500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031001002701 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030002000300 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271031006003901 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030004002700 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271011003000101 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030004000800 - UB - 4</t>
+  </si>
+  <si>
+    <t>7271030002001000 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031006001100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031002000701 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271040002000100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271040001000102 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271031006003901 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271040004001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030005003300 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271031002001400 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271030005002800 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271020009001901 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020009001700 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271011004001500 - UB - 1</t>
+  </si>
+  <si>
+    <t>7271020008003800 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271030004001500 - UB - 5</t>
+  </si>
+  <si>
+    <t>7271030004001700 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271020008003800 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271020009001901 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271020007002901 - UB - 3</t>
+  </si>
+  <si>
+    <t>7271000000000000 - UB - 2</t>
+  </si>
+  <si>
+    <t>7271000000000000 - UB - 53</t>
+  </si>
+  <si>
     <t>BPR Syariah &lt;Agus Supriadi&gt;</t>
   </si>
   <si>
@@ -94,9 +385,303 @@
     <t>BRI UNIT BUALEMO</t>
   </si>
   <si>
+    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
+  </si>
+  <si>
+    <t>BANK SULTENG</t>
+  </si>
+  <si>
+    <t>TOTALINDO BANGGAI PERKASA</t>
+  </si>
+  <si>
+    <t>REKAYASA INDUSTRI PT</t>
+  </si>
+  <si>
+    <t>INDONESIA TSINGSHAN STAINLESS STEEL</t>
+  </si>
+  <si>
+    <t>HUA CHIN ALUMINUM INDONESIA</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>BANK BPD</t>
+  </si>
+  <si>
+    <t>AKAR DAYA MANDIRI PT</t>
+  </si>
+  <si>
+    <t>AMRI MARGA JAYA, PT</t>
+  </si>
+  <si>
+    <t>PLTA Poso 1</t>
+  </si>
+  <si>
+    <t>SEKOLAH POLISI NEGARA</t>
+  </si>
+  <si>
+    <t>PDAM KAB DONGGALA</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
+  </si>
+  <si>
+    <t>PT. BANK SULTENG KAS LABEAN</t>
+  </si>
+  <si>
+    <t>ASTUN HI. ARSYAD</t>
+  </si>
+  <si>
+    <t>BUTOL RAYA NUSANTARA, PT</t>
+  </si>
+  <si>
+    <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
+  </si>
+  <si>
+    <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
+  </si>
+  <si>
+    <t>GALAXI INDO PRATAMA, CV</t>
+  </si>
+  <si>
+    <t>BANK SULTENG UNIT SONI</t>
+  </si>
+  <si>
+    <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
+  </si>
+  <si>
+    <t>PT BANK NEGARA INDONESIA (PERSERO) TBK</t>
+  </si>
+  <si>
+    <t>BANK MANDIRI (PERSERO) TBK KCP BUOL, PT</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT DIAPATIH</t>
+  </si>
+  <si>
+    <t>BRI UNIT TINOMBO</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT PALU ANUGERAH</t>
+  </si>
+  <si>
+    <t>SAHABAT TANI, TOKO</t>
+  </si>
+  <si>
+    <t>SPBU AMPI BABO</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT BINARTA LUHUR</t>
+  </si>
+  <si>
+    <t>PAGADAIAN, PT</t>
+  </si>
+  <si>
+    <t>BANK RAKYAT INDONESIA TBK, PT</t>
+  </si>
+  <si>
+    <t>BPR MODERN EXSPRESS, PT/BPR PALU LOKADANA UTAMA, PT</t>
+  </si>
+  <si>
+    <t>BANK BRI PALOLO, PT</t>
+  </si>
+  <si>
+    <t>BANK SULTENG CAB SIGI PT</t>
+  </si>
+  <si>
+    <t>RSUD TORABELO</t>
+  </si>
+  <si>
+    <t>PERTAMINA PATRANIAGA, PT</t>
+  </si>
+  <si>
+    <t>BRI UNIT BETELEME.PT</t>
+  </si>
+  <si>
+    <t>MORI DUTA MINERAL</t>
+  </si>
+  <si>
+    <t>TIMUR JAYA INDO MAKMUR, PT</t>
+  </si>
+  <si>
+    <t>Toko suharman &lt;Darmiati&gt;</t>
+  </si>
+  <si>
+    <t>GENBA INDO RESOURCES</t>
+  </si>
+  <si>
+    <t>MULIA PACIFIC RESOURCES BHL</t>
+  </si>
+  <si>
+    <t>KEINZ VENTURA PT</t>
+  </si>
+  <si>
+    <t>FIVE STAR INDONESIA - HOFFMEN</t>
+  </si>
+  <si>
+    <t>SINERGI BINTANG UTARA</t>
+  </si>
+  <si>
+    <t>SULAWESI CENTRAL COMMODITY</t>
+  </si>
+  <si>
+    <t>BANGUN PALU SULAWESI TENGAH</t>
+  </si>
+  <si>
+    <t>ROLAND AGUNG SOPUTRA</t>
+  </si>
+  <si>
+    <t>ARBA SONS COMPANY</t>
+  </si>
+  <si>
+    <t>FAREL JAYA TRANSPORT</t>
+  </si>
+  <si>
+    <t>SETUNGGAL PERKASA</t>
+  </si>
+  <si>
+    <t>ANUGRAH JAYA PERKASA, CV</t>
+  </si>
+  <si>
+    <t>THE CLIFF TOGEAN</t>
+  </si>
+  <si>
+    <t>CV NIAGA JAYA</t>
+  </si>
+  <si>
+    <t>ANUGRAH JAYA HOUSEWARES</t>
+  </si>
+  <si>
+    <t>PT Bumi Sarana Utama, Kantor Cabang Palu</t>
+  </si>
+  <si>
+    <t>ELISABET</t>
+  </si>
+  <si>
+    <t>HASRAT ABADI PT</t>
+  </si>
+  <si>
+    <t>JOYFUL KIDS</t>
+  </si>
+  <si>
+    <t>UNIVERSITAS ISLAM NEGERI DATOKRAMA PALU</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT TAWAELI</t>
+  </si>
+  <si>
+    <t>SPBU KAYUMALUE</t>
+  </si>
+  <si>
+    <t>ANUGERAHPERDANA</t>
+  </si>
+  <si>
+    <t>SETIA MULIA ABADI</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA, PT</t>
+  </si>
+  <si>
+    <t>PT VARIA KENCANA</t>
+  </si>
+  <si>
+    <t>BANK KB BUKOPIN TBK</t>
+  </si>
+  <si>
+    <t>MITRA ABADI CV</t>
+  </si>
+  <si>
+    <t>PT. KIMIA FARMA TRADING &amp; DISTRIBUTION, Kantor Cabang Palu</t>
+  </si>
+  <si>
+    <t>KPN ANUTAN</t>
+  </si>
+  <si>
+    <t>RSUD UNDATA PROV. SULTENG</t>
+  </si>
+  <si>
+    <t>CITRA BARKATAMA KARYA</t>
+  </si>
+  <si>
+    <t>HAYCARB PALU MITRA PT</t>
+  </si>
+  <si>
+    <t>MANDIRI ARGO LESTARI CV</t>
+  </si>
+  <si>
+    <t>BATU HITAM JASA PERTAMBANGAN</t>
+  </si>
+  <si>
+    <t>PRIMA GELORA AGUNG LESTARI, PT</t>
+  </si>
+  <si>
+    <t>ADIPURA NOVEGA,CV</t>
+  </si>
+  <si>
+    <t>PT. KIMIA FARMA APOTEK, Kantor Cabang Palu</t>
+  </si>
+  <si>
+    <t>INDOSAT OOREDOO, PT</t>
+  </si>
+  <si>
+    <t>PATRIOT BHAKTI NUSANTARA</t>
+  </si>
+  <si>
+    <t>SURYA MADISTRINDO, PT</t>
+  </si>
+  <si>
+    <t>ARTHA LESTARI, CV</t>
+  </si>
+  <si>
+    <t>BANK BNI SYARIAH</t>
+  </si>
+  <si>
+    <t>MAKASAR RAYA MOTOR PT</t>
+  </si>
+  <si>
+    <t>TRIOCELEBES UTAMA, PT</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA TBK.</t>
+  </si>
+  <si>
+    <t>UNITED TRACTORS TBK, PT CAB PALU</t>
+  </si>
+  <si>
+    <t>MANDIRI MITRA USAHA</t>
+  </si>
+  <si>
+    <t>SINAR LESTARI JAYAPRIMA</t>
+  </si>
+  <si>
+    <t>KONSUIL, PT</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>SUBMITTED RESPONDENT</t>
+  </si>
+  <si>
     <t>avatarcrue@gmail.com</t>
   </si>
   <si>
@@ -124,12 +709,309 @@
     <t>nbobs@corp.brico.id</t>
   </si>
   <si>
+    <t>bca_luwuk_pajak@gmail.com</t>
+  </si>
+  <si>
+    <t>banksulteng.toili@yahoo.com</t>
+  </si>
+  <si>
+    <t>totalindobatbperkasa@gmail.com</t>
+  </si>
+  <si>
+    <t>wandysendjaja@yahoo.com</t>
+  </si>
+  <si>
+    <t>secretariat@it-stainlesssteel.com</t>
+  </si>
+  <si>
+    <t>secretariathuachinind@gmail.com</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>bsposo@yahoo.com</t>
+  </si>
+  <si>
+    <t>akardayamandiri49@gmail.com</t>
+  </si>
+  <si>
+    <t>pt.amrimargajaya@ymail.com</t>
+  </si>
+  <si>
+    <t>pltaposo2@posoenergy.com</t>
+  </si>
+  <si>
+    <t>kppnpalu651707@yahoo.com</t>
+  </si>
+  <si>
+    <t>pdam_donggala@gmail.com</t>
+  </si>
+  <si>
+    <t>bprlabuan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>banksulteng_kaslabean@yahoo.com</t>
+  </si>
+  <si>
+    <t>astunhiarsyad28@gmail.com</t>
+  </si>
+  <si>
+    <t>butolrayanusantara@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.tolitoli@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>koperasi_maritim@yahoo.com</t>
+  </si>
+  <si>
+    <t>galaxiindopratamatolis@gmail.com</t>
+  </si>
+  <si>
+    <t>febrialdin.rial@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>Kc.Buol@Bprmodex.com</t>
+  </si>
+  <si>
+    <t>cona3176@bni.co.id</t>
+  </si>
+  <si>
+    <t>nyoalvaro@gmail.com</t>
+  </si>
+  <si>
+    <t>yohanesyafetsulung@gmail.com</t>
+  </si>
+  <si>
+    <t>n5197@corpbri.co.id</t>
+  </si>
+  <si>
+    <t>kaslambunu@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>paluanugerahprg@yahoo.com</t>
+  </si>
+  <si>
+    <t>sonnykandou80@gmail.com</t>
+  </si>
+  <si>
+    <t>spbu_ampibabo@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>binartasumber@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>cppampana@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>n5210@copr.bri.co.id</t>
+  </si>
+  <si>
+    <t>kc.touna@bprpalulokadana.com</t>
+  </si>
+  <si>
+    <t>ferdydaud@socrpgi.co.id</t>
+  </si>
+  <si>
+    <t>banksulteng_sigi@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>rsudsigi@gmail.com</t>
+  </si>
+  <si>
+    <t>rezadoanker8@gmail.com</t>
+  </si>
+  <si>
+    <t>n3633@co.rp.bri.co.id</t>
+  </si>
+  <si>
+    <t>stevankristy@moridutamineral.com</t>
+  </si>
+  <si>
+    <t>admin-krlm@tsanin-group.com</t>
+  </si>
+  <si>
+    <t>ktuana@asta.go.id</t>
+  </si>
+  <si>
+    <t>gir.mining2019@gmail.com</t>
+  </si>
+  <si>
+    <t>muliapacificresources@gmail.com</t>
+  </si>
+  <si>
+    <t>keinzventura1205@gmail.com</t>
+  </si>
+  <si>
+    <t>lidychayadi@gmail.com</t>
+  </si>
+  <si>
+    <t>pt.sinergibintangutara@yahoo.com</t>
+  </si>
+  <si>
+    <t>sulawesicentralcommodity@yahoo.com</t>
+  </si>
+  <si>
+    <t>hlppalu.bangunpalusulawesitengah@yahoo.com</t>
+  </si>
+  <si>
+    <t>soputraroland@yahoo.com</t>
+  </si>
+  <si>
+    <t>arbapalu@yahoo.com</t>
+  </si>
+  <si>
+    <t>jmc_palu@yahoo.com</t>
+  </si>
+  <si>
+    <t>cv_1perkasa@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>ajptipo@gmail.com</t>
+  </si>
+  <si>
+    <t>pttct@proton.me</t>
+  </si>
+  <si>
+    <t>niagajaya52@yahoo.com</t>
+  </si>
+  <si>
+    <t>anugrahjayaperkasa@yahoo.com</t>
+  </si>
+  <si>
+    <t>palu@bsukalla.com</t>
+  </si>
+  <si>
+    <t>khenelis2@gmail.com</t>
+  </si>
+  <si>
+    <t>crc.mka@hasjrat.co.id</t>
+  </si>
+  <si>
+    <t>jk_joyfulkids@yahoo.com</t>
+  </si>
+  <si>
+    <t>humas@iainpalu.ac.id</t>
+  </si>
+  <si>
+    <t>n3448@bricorp.co.id</t>
+  </si>
+  <si>
+    <t>spbutawaeli74943313@gmail.com</t>
+  </si>
+  <si>
+    <t>risky.anugerahperdana@yahoo.com</t>
+  </si>
+  <si>
+    <t>pt.sma_palu@yahoo.com</t>
+  </si>
+  <si>
+    <t>bprpalulokadana@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>ptvariakencana@yahoo.com</t>
+  </si>
+  <si>
+    <t>idham.halid@bukopin.co.id</t>
+  </si>
+  <si>
+    <t>maol.palu@gmail.com</t>
+  </si>
+  <si>
+    <t>kftdpaly@kftd.co.id</t>
+  </si>
+  <si>
+    <t>kprianutan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>rsudundata@gmail.comsultengprov.co.id</t>
+  </si>
+  <si>
+    <t>ptcitrabarkatamakarya@yahoo.com</t>
+  </si>
+  <si>
+    <t>hpm-accountr@haycarbindo.com</t>
+  </si>
+  <si>
+    <t>cvmandiriargolestari@gmail.com</t>
+  </si>
+  <si>
+    <t>batuhitamjasapertambangan@yahoo.com</t>
+  </si>
+  <si>
+    <t>primagelora_palu@yahoo.com</t>
+  </si>
+  <si>
+    <t>adipuranovega@gmail.com</t>
+  </si>
+  <si>
+    <t>kimiafarmavetran93@gmail.com</t>
+  </si>
+  <si>
+    <t>ferdy@mitradm.com</t>
+  </si>
+  <si>
+    <t>pt.patriotbhaktinusantara@gmail.com</t>
+  </si>
+  <si>
+    <t>fero@gmail.com</t>
+  </si>
+  <si>
+    <t>arthalestari_palu@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>bnispalu@gmail.com</t>
+  </si>
+  <si>
+    <t>rrukmin@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>triocelebesutama@yahoo.com</t>
+  </si>
+  <si>
+    <t>bsikcpalu2@yahoo.com</t>
+  </si>
+  <si>
+    <t>utpalu@nadoli.com</t>
+  </si>
+  <si>
+    <t>ikapratiwi2@bankmandiri.go.id</t>
+  </si>
+  <si>
+    <t>ptsinarlestarijayaprima@yahoo.com</t>
+  </si>
+  <si>
+    <t>palukonsuil@yahoo.com</t>
+  </si>
+  <si>
     <t>bounced</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>queued</t>
   </si>
   <si>
+    <t>permanent_fail</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 11:35:03</t>
   </si>
   <si>
@@ -176,6 +1058,513 @@
   </si>
   <si>
     <t>02 Jun 2026, 06:50:12</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:59</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:12:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:11:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:20</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:49:00</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:48:57</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:23:23</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:48:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:17:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:08:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:07:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:30:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:29:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:31:35</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:30:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:29:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:12:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:31</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:08:22</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:04:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:24</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 11:14:37</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 11:14:34</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 11:14:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:32:29</t>
+  </si>
+  <si>
+    <t>21 Mei 2026, 08:24:52</t>
+  </si>
+  <si>
+    <t>21 Mei 2026, 08:24:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:55:50</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:02:15</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:59:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:01:57</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:46:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:45:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:00:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:59:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:06:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:47</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:01:16</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:04:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:49:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:49:31</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:33:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:32:51</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:58:30</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:57:07</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 09:51:11</t>
+  </si>
+  <si>
+    <t>19 Mei 2026, 09:51:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:19:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:50:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:10:57</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:47:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:47:26</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:59:43</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:58:46</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:21:19</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:01:31</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:01:30</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:00:08</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:00:04</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:45:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:44:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:11:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:11:00</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:12:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:57:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:57:15</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:58:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:56:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:14:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:14:16</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:17:00</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:15:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:09:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:09:05</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:00:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:10:45</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:10:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:48:23</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:47:46</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:57:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:35:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:34:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:22:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:00</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:58:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:44:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:44:52</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:35:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:02</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:22:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:21:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:08:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:08:18</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:34:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:33:19</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:34:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:34:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:39:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:39:18</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:22:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:22:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:06:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:06:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:52:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:52:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:10:04</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:09:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:06:09</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:37:42</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:37:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:39:45</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:36:13</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:26:06</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:23:45</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:59:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:59:12</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:59:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:44:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:44:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:39:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:39:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:31:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:12:01</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:11:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:35:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:35:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:38:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:37:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:28:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:28:18</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:02:12</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:02:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:30:50</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:29:43</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:53:12</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:55:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:54:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:20:17</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:20:10</t>
   </si>
 </sst>
 </file>
@@ -533,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -567,22 +1956,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>332</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -593,22 +1982,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -619,22 +2008,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -645,22 +2034,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>335</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -671,22 +2060,22 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>336</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -697,22 +2086,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>336</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -723,22 +2112,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -749,22 +2138,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>338</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -775,22 +2164,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>339</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -801,22 +2190,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -827,22 +2216,22 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>341</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -853,22 +2242,22 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>342</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -879,22 +2268,22 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>343</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -905,22 +2294,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>228</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>344</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -931,22 +2320,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>229</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>345</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -957,22 +2346,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>229</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>346</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -983,22 +2372,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>330</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>347</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1009,24 +2398,5120 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E19" t="s">
+        <v>328</v>
+      </c>
+      <c r="F19" t="s">
+        <v>328</v>
+      </c>
+      <c r="G19" t="s">
+        <v>347</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E20" t="s">
+        <v>328</v>
+      </c>
+      <c r="F20" t="s">
+        <v>328</v>
+      </c>
+      <c r="G20" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E21" t="s">
+        <v>328</v>
+      </c>
+      <c r="F21" t="s">
+        <v>330</v>
+      </c>
+      <c r="G21" t="s">
+        <v>349</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" t="s">
+        <v>328</v>
+      </c>
+      <c r="G22" t="s">
+        <v>350</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" t="s">
+        <v>328</v>
+      </c>
+      <c r="F23" t="s">
+        <v>330</v>
+      </c>
+      <c r="G23" t="s">
+        <v>351</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E24" t="s">
+        <v>328</v>
+      </c>
+      <c r="F24" t="s">
+        <v>328</v>
+      </c>
+      <c r="G24" t="s">
+        <v>352</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E25" t="s">
+        <v>328</v>
+      </c>
+      <c r="F25" t="s">
+        <v>330</v>
+      </c>
+      <c r="G25" t="s">
+        <v>353</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C26" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E26" t="s">
+        <v>328</v>
+      </c>
+      <c r="F26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G26" t="s">
+        <v>354</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" t="s">
+        <v>234</v>
+      </c>
+      <c r="E27" t="s">
+        <v>328</v>
+      </c>
+      <c r="F27" t="s">
+        <v>330</v>
+      </c>
+      <c r="G27" t="s">
+        <v>355</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" t="s">
+        <v>219</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" t="s">
+        <v>328</v>
+      </c>
+      <c r="F28" t="s">
+        <v>330</v>
+      </c>
+      <c r="G28" t="s">
+        <v>356</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29" t="s">
+        <v>328</v>
+      </c>
+      <c r="F29" t="s">
+        <v>328</v>
+      </c>
+      <c r="G29" t="s">
+        <v>356</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E30" t="s">
+        <v>328</v>
+      </c>
+      <c r="F30" t="s">
+        <v>328</v>
+      </c>
+      <c r="G30" t="s">
+        <v>357</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>328</v>
+      </c>
+      <c r="F31" t="s">
+        <v>330</v>
+      </c>
+      <c r="G31" t="s">
+        <v>357</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" t="s">
+        <v>237</v>
+      </c>
+      <c r="E32" t="s">
+        <v>328</v>
+      </c>
+      <c r="F32" t="s">
+        <v>328</v>
+      </c>
+      <c r="G32" t="s">
+        <v>358</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" t="s">
+        <v>237</v>
+      </c>
+      <c r="E33" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" t="s">
+        <v>330</v>
+      </c>
+      <c r="G33" t="s">
+        <v>358</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D34" t="s">
+        <v>238</v>
+      </c>
+      <c r="E34" t="s">
+        <v>328</v>
+      </c>
+      <c r="F34" t="s">
+        <v>328</v>
+      </c>
+      <c r="G34" t="s">
+        <v>359</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D35" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" t="s">
+        <v>330</v>
+      </c>
+      <c r="G35" t="s">
+        <v>360</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
         <v>25</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" t="s">
+        <v>328</v>
+      </c>
+      <c r="F36" t="s">
+        <v>328</v>
+      </c>
+      <c r="G36" t="s">
+        <v>361</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E37" t="s">
+        <v>328</v>
+      </c>
+      <c r="F37" t="s">
+        <v>330</v>
+      </c>
+      <c r="G37" t="s">
+        <v>362</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
         <v>26</v>
       </c>
-      <c r="D19" t="s">
+      <c r="B38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E38" t="s">
+        <v>328</v>
+      </c>
+      <c r="F38" t="s">
+        <v>328</v>
+      </c>
+      <c r="G38" t="s">
+        <v>363</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" t="s">
+        <v>219</v>
+      </c>
+      <c r="D39" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" t="s">
+        <v>328</v>
+      </c>
+      <c r="F39" t="s">
+        <v>330</v>
+      </c>
+      <c r="G39" t="s">
+        <v>364</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" t="s">
+        <v>328</v>
+      </c>
+      <c r="F40" t="s">
+        <v>328</v>
+      </c>
+      <c r="G40" t="s">
+        <v>365</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" t="s">
+        <v>133</v>
+      </c>
+      <c r="C41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" t="s">
+        <v>328</v>
+      </c>
+      <c r="F41" t="s">
+        <v>330</v>
+      </c>
+      <c r="G41" t="s">
+        <v>366</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" t="s">
+        <v>242</v>
+      </c>
+      <c r="E42" t="s">
+        <v>328</v>
+      </c>
+      <c r="F42" t="s">
+        <v>328</v>
+      </c>
+      <c r="G42" t="s">
+        <v>367</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E43" t="s">
+        <v>328</v>
+      </c>
+      <c r="F43" t="s">
+        <v>330</v>
+      </c>
+      <c r="G43" t="s">
+        <v>368</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s">
+        <v>219</v>
+      </c>
+      <c r="D44" t="s">
+        <v>243</v>
+      </c>
+      <c r="E44" t="s">
+        <v>328</v>
+      </c>
+      <c r="F44" t="s">
+        <v>328</v>
+      </c>
+      <c r="G44" t="s">
+        <v>369</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" t="s">
+        <v>243</v>
+      </c>
+      <c r="E45" t="s">
+        <v>328</v>
+      </c>
+      <c r="F45" t="s">
+        <v>330</v>
+      </c>
+      <c r="G45" t="s">
+        <v>370</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" t="s">
+        <v>244</v>
+      </c>
+      <c r="E46" t="s">
+        <v>328</v>
+      </c>
+      <c r="F46" t="s">
+        <v>328</v>
+      </c>
+      <c r="G46" t="s">
+        <v>371</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" t="s">
+        <v>244</v>
+      </c>
+      <c r="E47" t="s">
+        <v>328</v>
+      </c>
+      <c r="F47" t="s">
+        <v>330</v>
+      </c>
+      <c r="G47" t="s">
+        <v>371</v>
+      </c>
+      <c r="H47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" t="s">
+        <v>328</v>
+      </c>
+      <c r="G48" t="s">
+        <v>372</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" t="s">
+        <v>328</v>
+      </c>
+      <c r="F49" t="s">
+        <v>330</v>
+      </c>
+      <c r="G49" t="s">
+        <v>373</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" t="s">
+        <v>246</v>
+      </c>
+      <c r="E50" t="s">
+        <v>328</v>
+      </c>
+      <c r="F50" t="s">
+        <v>328</v>
+      </c>
+      <c r="G50" t="s">
+        <v>374</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" t="s">
+        <v>328</v>
+      </c>
+      <c r="F51" t="s">
+        <v>330</v>
+      </c>
+      <c r="G51" t="s">
+        <v>375</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" t="s">
+        <v>219</v>
+      </c>
+      <c r="D52" t="s">
+        <v>247</v>
+      </c>
+      <c r="E52" t="s">
+        <v>328</v>
+      </c>
+      <c r="F52" t="s">
+        <v>328</v>
+      </c>
+      <c r="G52" t="s">
+        <v>376</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E53" t="s">
+        <v>328</v>
+      </c>
+      <c r="F53" t="s">
+        <v>330</v>
+      </c>
+      <c r="G53" t="s">
+        <v>377</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" t="s">
+        <v>219</v>
+      </c>
+      <c r="D54" t="s">
+        <v>248</v>
+      </c>
+      <c r="E54" t="s">
+        <v>328</v>
+      </c>
+      <c r="F54" t="s">
+        <v>330</v>
+      </c>
+      <c r="G54" t="s">
+        <v>378</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" t="s">
+        <v>219</v>
+      </c>
+      <c r="D55" t="s">
+        <v>248</v>
+      </c>
+      <c r="E55" t="s">
+        <v>328</v>
+      </c>
+      <c r="F55" t="s">
+        <v>328</v>
+      </c>
+      <c r="G55" t="s">
+        <v>378</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
         <v>35</v>
       </c>
-      <c r="E19" t="s">
+      <c r="B56" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" t="s">
+        <v>249</v>
+      </c>
+      <c r="E56" t="s">
+        <v>328</v>
+      </c>
+      <c r="F56" t="s">
+        <v>328</v>
+      </c>
+      <c r="G56" t="s">
+        <v>379</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" t="s">
+        <v>249</v>
+      </c>
+      <c r="E57" t="s">
+        <v>328</v>
+      </c>
+      <c r="F57" t="s">
+        <v>330</v>
+      </c>
+      <c r="G57" t="s">
+        <v>380</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
         <v>36</v>
       </c>
-      <c r="F19" t="s">
+      <c r="B58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D58" t="s">
+        <v>250</v>
+      </c>
+      <c r="E58" t="s">
+        <v>328</v>
+      </c>
+      <c r="F58" t="s">
+        <v>328</v>
+      </c>
+      <c r="G58" t="s">
+        <v>381</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
         <v>36</v>
       </c>
-      <c r="G19" t="s">
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" t="s">
+        <v>328</v>
+      </c>
+      <c r="F59" t="s">
+        <v>330</v>
+      </c>
+      <c r="G59" t="s">
+        <v>382</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" t="s">
+        <v>251</v>
+      </c>
+      <c r="E60" t="s">
+        <v>328</v>
+      </c>
+      <c r="F60" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" t="s">
+        <v>383</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" t="s">
+        <v>219</v>
+      </c>
+      <c r="D61" t="s">
+        <v>251</v>
+      </c>
+      <c r="E61" t="s">
+        <v>328</v>
+      </c>
+      <c r="F61" t="s">
+        <v>330</v>
+      </c>
+      <c r="G61" t="s">
+        <v>384</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
+        <v>144</v>
+      </c>
+      <c r="C62" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" t="s">
+        <v>328</v>
+      </c>
+      <c r="F62" t="s">
+        <v>328</v>
+      </c>
+      <c r="G62" t="s">
+        <v>385</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s">
+        <v>144</v>
+      </c>
+      <c r="C63" t="s">
+        <v>219</v>
+      </c>
+      <c r="D63" t="s">
+        <v>252</v>
+      </c>
+      <c r="E63" t="s">
+        <v>328</v>
+      </c>
+      <c r="F63" t="s">
+        <v>330</v>
+      </c>
+      <c r="G63" t="s">
+        <v>386</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" t="s">
+        <v>145</v>
+      </c>
+      <c r="C64" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" t="s">
+        <v>253</v>
+      </c>
+      <c r="E64" t="s">
+        <v>328</v>
+      </c>
+      <c r="F64" t="s">
+        <v>328</v>
+      </c>
+      <c r="G64" t="s">
+        <v>387</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" t="s">
+        <v>219</v>
+      </c>
+      <c r="D65" t="s">
+        <v>253</v>
+      </c>
+      <c r="E65" t="s">
+        <v>328</v>
+      </c>
+      <c r="F65" t="s">
+        <v>330</v>
+      </c>
+      <c r="G65" t="s">
+        <v>388</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" t="s">
+        <v>254</v>
+      </c>
+      <c r="E66" t="s">
+        <v>328</v>
+      </c>
+      <c r="F66" t="s">
+        <v>328</v>
+      </c>
+      <c r="G66" t="s">
+        <v>389</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C67" t="s">
+        <v>219</v>
+      </c>
+      <c r="D67" t="s">
+        <v>254</v>
+      </c>
+      <c r="E67" t="s">
+        <v>328</v>
+      </c>
+      <c r="F67" t="s">
+        <v>330</v>
+      </c>
+      <c r="G67" t="s">
+        <v>390</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" t="s">
+        <v>219</v>
+      </c>
+      <c r="D68" t="s">
+        <v>255</v>
+      </c>
+      <c r="E68" t="s">
+        <v>328</v>
+      </c>
+      <c r="F68" t="s">
+        <v>330</v>
+      </c>
+      <c r="G68" t="s">
+        <v>391</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" t="s">
+        <v>147</v>
+      </c>
+      <c r="C69" t="s">
+        <v>219</v>
+      </c>
+      <c r="D69" t="s">
+        <v>255</v>
+      </c>
+      <c r="E69" t="s">
+        <v>328</v>
+      </c>
+      <c r="F69" t="s">
+        <v>328</v>
+      </c>
+      <c r="G69" t="s">
+        <v>392</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" t="s">
+        <v>219</v>
+      </c>
+      <c r="D70" t="s">
+        <v>256</v>
+      </c>
+      <c r="E70" t="s">
+        <v>328</v>
+      </c>
+      <c r="F70" t="s">
+        <v>328</v>
+      </c>
+      <c r="G70" t="s">
+        <v>393</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" t="s">
+        <v>219</v>
+      </c>
+      <c r="D71" t="s">
+        <v>256</v>
+      </c>
+      <c r="E71" t="s">
+        <v>328</v>
+      </c>
+      <c r="F71" t="s">
+        <v>330</v>
+      </c>
+      <c r="G71" t="s">
+        <v>394</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" t="s">
+        <v>149</v>
+      </c>
+      <c r="C72" t="s">
+        <v>220</v>
+      </c>
+      <c r="D72" t="s">
+        <v>257</v>
+      </c>
+      <c r="E72" t="s">
+        <v>328</v>
+      </c>
+      <c r="F72" t="s">
+        <v>328</v>
+      </c>
+      <c r="G72" t="s">
+        <v>395</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" t="s">
+        <v>328</v>
+      </c>
+      <c r="F73" t="s">
+        <v>330</v>
+      </c>
+      <c r="G73" t="s">
+        <v>395</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" t="s">
+        <v>220</v>
+      </c>
+      <c r="D74" t="s">
+        <v>258</v>
+      </c>
+      <c r="E74" t="s">
+        <v>328</v>
+      </c>
+      <c r="F74" t="s">
+        <v>330</v>
+      </c>
+      <c r="G74" t="s">
+        <v>396</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C75" t="s">
+        <v>220</v>
+      </c>
+      <c r="D75" t="s">
+        <v>258</v>
+      </c>
+      <c r="E75" t="s">
+        <v>328</v>
+      </c>
+      <c r="F75" t="s">
+        <v>328</v>
+      </c>
+      <c r="G75" t="s">
+        <v>396</v>
+      </c>
+      <c r="H75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" t="s">
+        <v>259</v>
+      </c>
+      <c r="E76" t="s">
+        <v>328</v>
+      </c>
+      <c r="F76" t="s">
+        <v>328</v>
+      </c>
+      <c r="G76" t="s">
+        <v>397</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s">
+        <v>151</v>
+      </c>
+      <c r="C77" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" t="s">
+        <v>259</v>
+      </c>
+      <c r="E77" t="s">
+        <v>328</v>
+      </c>
+      <c r="F77" t="s">
+        <v>330</v>
+      </c>
+      <c r="G77" t="s">
+        <v>396</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>46</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" t="s">
+        <v>219</v>
+      </c>
+      <c r="D78" t="s">
+        <v>260</v>
+      </c>
+      <c r="E78" t="s">
+        <v>328</v>
+      </c>
+      <c r="F78" t="s">
+        <v>331</v>
+      </c>
+      <c r="G78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" t="s">
+        <v>152</v>
+      </c>
+      <c r="C79" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" t="s">
+        <v>260</v>
+      </c>
+      <c r="E79" t="s">
+        <v>328</v>
+      </c>
+      <c r="F79" t="s">
+        <v>328</v>
+      </c>
+      <c r="G79" t="s">
+        <v>399</v>
+      </c>
+      <c r="H79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" t="s">
+        <v>152</v>
+      </c>
+      <c r="C80" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" t="s">
+        <v>260</v>
+      </c>
+      <c r="E80" t="s">
+        <v>328</v>
+      </c>
+      <c r="F80" t="s">
+        <v>330</v>
+      </c>
+      <c r="G80" t="s">
+        <v>400</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" t="s">
+        <v>219</v>
+      </c>
+      <c r="D81" t="s">
+        <v>260</v>
+      </c>
+      <c r="E81" t="s">
+        <v>329</v>
+      </c>
+      <c r="F81" t="s">
+        <v>329</v>
+      </c>
+      <c r="G81" t="s">
+        <v>329</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" t="s">
+        <v>261</v>
+      </c>
+      <c r="E82" t="s">
+        <v>328</v>
+      </c>
+      <c r="F82" t="s">
+        <v>330</v>
+      </c>
+      <c r="G82" t="s">
+        <v>401</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>47</v>
+      </c>
+      <c r="B83" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" t="s">
+        <v>219</v>
+      </c>
+      <c r="D83" t="s">
+        <v>261</v>
+      </c>
+      <c r="E83" t="s">
+        <v>328</v>
+      </c>
+      <c r="F83" t="s">
+        <v>328</v>
+      </c>
+      <c r="G83" t="s">
+        <v>401</v>
+      </c>
+      <c r="H83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>48</v>
+      </c>
+      <c r="B84" t="s">
+        <v>124</v>
+      </c>
+      <c r="C84" t="s">
+        <v>219</v>
+      </c>
+      <c r="D84" t="s">
+        <v>262</v>
+      </c>
+      <c r="E84" t="s">
+        <v>328</v>
+      </c>
+      <c r="F84" t="s">
+        <v>328</v>
+      </c>
+      <c r="G84" t="s">
+        <v>402</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" t="s">
+        <v>219</v>
+      </c>
+      <c r="D85" t="s">
+        <v>262</v>
+      </c>
+      <c r="E85" t="s">
+        <v>328</v>
+      </c>
+      <c r="F85" t="s">
+        <v>330</v>
+      </c>
+      <c r="G85" t="s">
+        <v>403</v>
+      </c>
+      <c r="H85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" t="s">
+        <v>219</v>
+      </c>
+      <c r="D86" t="s">
+        <v>263</v>
+      </c>
+      <c r="E86" t="s">
+        <v>328</v>
+      </c>
+      <c r="F86" t="s">
+        <v>328</v>
+      </c>
+      <c r="G86" t="s">
+        <v>404</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s">
+        <v>154</v>
+      </c>
+      <c r="C87" t="s">
+        <v>219</v>
+      </c>
+      <c r="D87" t="s">
+        <v>263</v>
+      </c>
+      <c r="E87" t="s">
+        <v>328</v>
+      </c>
+      <c r="F87" t="s">
+        <v>330</v>
+      </c>
+      <c r="G87" t="s">
+        <v>405</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" t="s">
+        <v>155</v>
+      </c>
+      <c r="C88" t="s">
+        <v>219</v>
+      </c>
+      <c r="D88" t="s">
+        <v>264</v>
+      </c>
+      <c r="E88" t="s">
+        <v>328</v>
+      </c>
+      <c r="F88" t="s">
+        <v>328</v>
+      </c>
+      <c r="G88" t="s">
+        <v>406</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" t="s">
+        <v>155</v>
+      </c>
+      <c r="C89" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" t="s">
+        <v>264</v>
+      </c>
+      <c r="E89" t="s">
+        <v>328</v>
+      </c>
+      <c r="F89" t="s">
+        <v>330</v>
+      </c>
+      <c r="G89" t="s">
+        <v>406</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90" t="s">
+        <v>156</v>
+      </c>
+      <c r="C90" t="s">
+        <v>219</v>
+      </c>
+      <c r="D90" t="s">
+        <v>265</v>
+      </c>
+      <c r="E90" t="s">
+        <v>328</v>
+      </c>
+      <c r="F90" t="s">
+        <v>328</v>
+      </c>
+      <c r="G90" t="s">
+        <v>407</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>51</v>
+      </c>
+      <c r="B91" t="s">
+        <v>156</v>
+      </c>
+      <c r="C91" t="s">
+        <v>219</v>
+      </c>
+      <c r="D91" t="s">
+        <v>265</v>
+      </c>
+      <c r="E91" t="s">
+        <v>328</v>
+      </c>
+      <c r="F91" t="s">
+        <v>330</v>
+      </c>
+      <c r="G91" t="s">
+        <v>408</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>52</v>
+      </c>
+      <c r="B92" t="s">
+        <v>157</v>
+      </c>
+      <c r="C92" t="s">
+        <v>219</v>
+      </c>
+      <c r="D92" t="s">
+        <v>266</v>
+      </c>
+      <c r="E92" t="s">
+        <v>328</v>
+      </c>
+      <c r="F92" t="s">
+        <v>328</v>
+      </c>
+      <c r="G92" t="s">
+        <v>409</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" t="s">
+        <v>157</v>
+      </c>
+      <c r="C93" t="s">
+        <v>219</v>
+      </c>
+      <c r="D93" t="s">
+        <v>266</v>
+      </c>
+      <c r="E93" t="s">
+        <v>328</v>
+      </c>
+      <c r="F93" t="s">
+        <v>330</v>
+      </c>
+      <c r="G93" t="s">
+        <v>410</v>
+      </c>
+      <c r="H93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
         <v>53</v>
       </c>
-      <c r="H19">
+      <c r="B94" t="s">
+        <v>158</v>
+      </c>
+      <c r="C94" t="s">
+        <v>219</v>
+      </c>
+      <c r="D94" t="s">
+        <v>267</v>
+      </c>
+      <c r="E94" t="s">
+        <v>328</v>
+      </c>
+      <c r="F94" t="s">
+        <v>328</v>
+      </c>
+      <c r="G94" t="s">
+        <v>411</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>53</v>
+      </c>
+      <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" t="s">
+        <v>219</v>
+      </c>
+      <c r="D95" t="s">
+        <v>267</v>
+      </c>
+      <c r="E95" t="s">
+        <v>328</v>
+      </c>
+      <c r="F95" t="s">
+        <v>330</v>
+      </c>
+      <c r="G95" t="s">
+        <v>412</v>
+      </c>
+      <c r="H95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>54</v>
+      </c>
+      <c r="B96" t="s">
+        <v>159</v>
+      </c>
+      <c r="C96" t="s">
+        <v>219</v>
+      </c>
+      <c r="D96" t="s">
+        <v>268</v>
+      </c>
+      <c r="E96" t="s">
+        <v>328</v>
+      </c>
+      <c r="F96" t="s">
+        <v>328</v>
+      </c>
+      <c r="G96" t="s">
+        <v>413</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>54</v>
+      </c>
+      <c r="B97" t="s">
+        <v>159</v>
+      </c>
+      <c r="C97" t="s">
+        <v>219</v>
+      </c>
+      <c r="D97" t="s">
+        <v>268</v>
+      </c>
+      <c r="E97" t="s">
+        <v>328</v>
+      </c>
+      <c r="F97" t="s">
+        <v>330</v>
+      </c>
+      <c r="G97" t="s">
+        <v>413</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>55</v>
+      </c>
+      <c r="B98" t="s">
+        <v>160</v>
+      </c>
+      <c r="C98" t="s">
+        <v>219</v>
+      </c>
+      <c r="D98" t="s">
+        <v>269</v>
+      </c>
+      <c r="E98" t="s">
+        <v>328</v>
+      </c>
+      <c r="F98" t="s">
+        <v>330</v>
+      </c>
+      <c r="G98" t="s">
+        <v>414</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>160</v>
+      </c>
+      <c r="C99" t="s">
+        <v>219</v>
+      </c>
+      <c r="D99" t="s">
+        <v>269</v>
+      </c>
+      <c r="E99" t="s">
+        <v>328</v>
+      </c>
+      <c r="F99" t="s">
+        <v>328</v>
+      </c>
+      <c r="G99" t="s">
+        <v>414</v>
+      </c>
+      <c r="H99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>56</v>
+      </c>
+      <c r="B100" t="s">
+        <v>161</v>
+      </c>
+      <c r="C100" t="s">
+        <v>219</v>
+      </c>
+      <c r="D100" t="s">
+        <v>270</v>
+      </c>
+      <c r="E100" t="s">
+        <v>328</v>
+      </c>
+      <c r="F100" t="s">
+        <v>330</v>
+      </c>
+      <c r="G100" t="s">
+        <v>415</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>56</v>
+      </c>
+      <c r="B101" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" t="s">
+        <v>219</v>
+      </c>
+      <c r="D101" t="s">
+        <v>270</v>
+      </c>
+      <c r="E101" t="s">
+        <v>328</v>
+      </c>
+      <c r="F101" t="s">
+        <v>328</v>
+      </c>
+      <c r="G101" t="s">
+        <v>416</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" t="s">
+        <v>162</v>
+      </c>
+      <c r="C102" t="s">
+        <v>219</v>
+      </c>
+      <c r="D102" t="s">
+        <v>271</v>
+      </c>
+      <c r="E102" t="s">
+        <v>328</v>
+      </c>
+      <c r="F102" t="s">
+        <v>328</v>
+      </c>
+      <c r="G102" t="s">
+        <v>417</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" t="s">
+        <v>162</v>
+      </c>
+      <c r="C103" t="s">
+        <v>219</v>
+      </c>
+      <c r="D103" t="s">
+        <v>271</v>
+      </c>
+      <c r="E103" t="s">
+        <v>328</v>
+      </c>
+      <c r="F103" t="s">
+        <v>330</v>
+      </c>
+      <c r="G103" t="s">
+        <v>418</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>58</v>
+      </c>
+      <c r="B104" t="s">
+        <v>163</v>
+      </c>
+      <c r="C104" t="s">
+        <v>219</v>
+      </c>
+      <c r="D104" t="s">
+        <v>272</v>
+      </c>
+      <c r="E104" t="s">
+        <v>328</v>
+      </c>
+      <c r="F104" t="s">
+        <v>328</v>
+      </c>
+      <c r="G104" t="s">
+        <v>419</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>58</v>
+      </c>
+      <c r="B105" t="s">
+        <v>163</v>
+      </c>
+      <c r="C105" t="s">
+        <v>219</v>
+      </c>
+      <c r="D105" t="s">
+        <v>272</v>
+      </c>
+      <c r="E105" t="s">
+        <v>328</v>
+      </c>
+      <c r="F105" t="s">
+        <v>330</v>
+      </c>
+      <c r="G105" t="s">
+        <v>420</v>
+      </c>
+      <c r="H105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>59</v>
+      </c>
+      <c r="B106" t="s">
+        <v>164</v>
+      </c>
+      <c r="C106" t="s">
+        <v>221</v>
+      </c>
+      <c r="D106" t="s">
+        <v>273</v>
+      </c>
+      <c r="E106" t="s">
+        <v>328</v>
+      </c>
+      <c r="F106" t="s">
+        <v>330</v>
+      </c>
+      <c r="G106" t="s">
+        <v>421</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>59</v>
+      </c>
+      <c r="B107" t="s">
+        <v>164</v>
+      </c>
+      <c r="C107" t="s">
+        <v>221</v>
+      </c>
+      <c r="D107" t="s">
+        <v>273</v>
+      </c>
+      <c r="E107" t="s">
+        <v>328</v>
+      </c>
+      <c r="F107" t="s">
+        <v>328</v>
+      </c>
+      <c r="G107" t="s">
+        <v>422</v>
+      </c>
+      <c r="H107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>60</v>
+      </c>
+      <c r="B108" t="s">
+        <v>165</v>
+      </c>
+      <c r="C108" t="s">
+        <v>219</v>
+      </c>
+      <c r="D108" t="s">
+        <v>274</v>
+      </c>
+      <c r="E108" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" t="s">
+        <v>328</v>
+      </c>
+      <c r="G108" t="s">
+        <v>423</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>60</v>
+      </c>
+      <c r="B109" t="s">
+        <v>165</v>
+      </c>
+      <c r="C109" t="s">
+        <v>219</v>
+      </c>
+      <c r="D109" t="s">
+        <v>274</v>
+      </c>
+      <c r="E109" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" t="s">
+        <v>330</v>
+      </c>
+      <c r="G109" t="s">
+        <v>423</v>
+      </c>
+      <c r="H109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" t="s">
+        <v>219</v>
+      </c>
+      <c r="D110" t="s">
+        <v>275</v>
+      </c>
+      <c r="E110" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" t="s">
+        <v>328</v>
+      </c>
+      <c r="G110" t="s">
+        <v>424</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>61</v>
+      </c>
+      <c r="B111" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" t="s">
+        <v>219</v>
+      </c>
+      <c r="D111" t="s">
+        <v>275</v>
+      </c>
+      <c r="E111" t="s">
+        <v>328</v>
+      </c>
+      <c r="F111" t="s">
+        <v>330</v>
+      </c>
+      <c r="G111" t="s">
+        <v>424</v>
+      </c>
+      <c r="H111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" t="s">
+        <v>219</v>
+      </c>
+      <c r="D112" t="s">
+        <v>276</v>
+      </c>
+      <c r="E112" t="s">
+        <v>328</v>
+      </c>
+      <c r="F112" t="s">
+        <v>328</v>
+      </c>
+      <c r="G112" t="s">
+        <v>425</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" t="s">
+        <v>167</v>
+      </c>
+      <c r="C113" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" t="s">
+        <v>276</v>
+      </c>
+      <c r="E113" t="s">
+        <v>328</v>
+      </c>
+      <c r="F113" t="s">
+        <v>330</v>
+      </c>
+      <c r="G113" t="s">
+        <v>425</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" t="s">
+        <v>168</v>
+      </c>
+      <c r="C114" t="s">
+        <v>219</v>
+      </c>
+      <c r="D114" t="s">
+        <v>277</v>
+      </c>
+      <c r="E114" t="s">
+        <v>328</v>
+      </c>
+      <c r="F114" t="s">
+        <v>328</v>
+      </c>
+      <c r="G114" t="s">
+        <v>426</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>63</v>
+      </c>
+      <c r="B115" t="s">
+        <v>168</v>
+      </c>
+      <c r="C115" t="s">
+        <v>219</v>
+      </c>
+      <c r="D115" t="s">
+        <v>277</v>
+      </c>
+      <c r="E115" t="s">
+        <v>328</v>
+      </c>
+      <c r="F115" t="s">
+        <v>330</v>
+      </c>
+      <c r="G115" t="s">
+        <v>427</v>
+      </c>
+      <c r="H115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>64</v>
+      </c>
+      <c r="B116" t="s">
+        <v>169</v>
+      </c>
+      <c r="C116" t="s">
+        <v>219</v>
+      </c>
+      <c r="D116" t="s">
+        <v>278</v>
+      </c>
+      <c r="E116" t="s">
+        <v>328</v>
+      </c>
+      <c r="F116" t="s">
+        <v>328</v>
+      </c>
+      <c r="G116" t="s">
+        <v>428</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>64</v>
+      </c>
+      <c r="B117" t="s">
+        <v>169</v>
+      </c>
+      <c r="C117" t="s">
+        <v>219</v>
+      </c>
+      <c r="D117" t="s">
+        <v>278</v>
+      </c>
+      <c r="E117" t="s">
+        <v>328</v>
+      </c>
+      <c r="F117" t="s">
+        <v>330</v>
+      </c>
+      <c r="G117" t="s">
+        <v>429</v>
+      </c>
+      <c r="H117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>65</v>
+      </c>
+      <c r="B118" t="s">
+        <v>170</v>
+      </c>
+      <c r="C118" t="s">
+        <v>219</v>
+      </c>
+      <c r="D118" t="s">
+        <v>279</v>
+      </c>
+      <c r="E118" t="s">
+        <v>328</v>
+      </c>
+      <c r="F118" t="s">
+        <v>328</v>
+      </c>
+      <c r="G118" t="s">
+        <v>430</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>65</v>
+      </c>
+      <c r="B119" t="s">
+        <v>170</v>
+      </c>
+      <c r="C119" t="s">
+        <v>219</v>
+      </c>
+      <c r="D119" t="s">
+        <v>279</v>
+      </c>
+      <c r="E119" t="s">
+        <v>328</v>
+      </c>
+      <c r="F119" t="s">
+        <v>330</v>
+      </c>
+      <c r="G119" t="s">
+        <v>430</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>66</v>
+      </c>
+      <c r="B120" t="s">
+        <v>171</v>
+      </c>
+      <c r="C120" t="s">
+        <v>219</v>
+      </c>
+      <c r="D120" t="s">
+        <v>280</v>
+      </c>
+      <c r="E120" t="s">
+        <v>328</v>
+      </c>
+      <c r="F120" t="s">
+        <v>328</v>
+      </c>
+      <c r="G120" t="s">
+        <v>431</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>171</v>
+      </c>
+      <c r="C121" t="s">
+        <v>219</v>
+      </c>
+      <c r="D121" t="s">
+        <v>280</v>
+      </c>
+      <c r="E121" t="s">
+        <v>328</v>
+      </c>
+      <c r="F121" t="s">
+        <v>330</v>
+      </c>
+      <c r="G121" t="s">
+        <v>432</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>67</v>
+      </c>
+      <c r="B122" t="s">
+        <v>172</v>
+      </c>
+      <c r="C122" t="s">
+        <v>219</v>
+      </c>
+      <c r="D122" t="s">
+        <v>281</v>
+      </c>
+      <c r="E122" t="s">
+        <v>328</v>
+      </c>
+      <c r="F122" t="s">
+        <v>328</v>
+      </c>
+      <c r="G122" t="s">
+        <v>433</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>67</v>
+      </c>
+      <c r="B123" t="s">
+        <v>172</v>
+      </c>
+      <c r="C123" t="s">
+        <v>219</v>
+      </c>
+      <c r="D123" t="s">
+        <v>281</v>
+      </c>
+      <c r="E123" t="s">
+        <v>328</v>
+      </c>
+      <c r="F123" t="s">
+        <v>330</v>
+      </c>
+      <c r="G123" t="s">
+        <v>434</v>
+      </c>
+      <c r="H123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>68</v>
+      </c>
+      <c r="B124" t="s">
+        <v>173</v>
+      </c>
+      <c r="C124" t="s">
+        <v>219</v>
+      </c>
+      <c r="D124" t="s">
+        <v>282</v>
+      </c>
+      <c r="E124" t="s">
+        <v>328</v>
+      </c>
+      <c r="F124" t="s">
+        <v>328</v>
+      </c>
+      <c r="G124" t="s">
+        <v>435</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>68</v>
+      </c>
+      <c r="B125" t="s">
+        <v>173</v>
+      </c>
+      <c r="C125" t="s">
+        <v>219</v>
+      </c>
+      <c r="D125" t="s">
+        <v>282</v>
+      </c>
+      <c r="E125" t="s">
+        <v>328</v>
+      </c>
+      <c r="F125" t="s">
+        <v>330</v>
+      </c>
+      <c r="G125" t="s">
+        <v>436</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>69</v>
+      </c>
+      <c r="B126" t="s">
+        <v>174</v>
+      </c>
+      <c r="C126" t="s">
+        <v>220</v>
+      </c>
+      <c r="D126" t="s">
+        <v>283</v>
+      </c>
+      <c r="E126" t="s">
+        <v>328</v>
+      </c>
+      <c r="F126" t="s">
+        <v>328</v>
+      </c>
+      <c r="G126" t="s">
+        <v>437</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>69</v>
+      </c>
+      <c r="B127" t="s">
+        <v>174</v>
+      </c>
+      <c r="C127" t="s">
+        <v>220</v>
+      </c>
+      <c r="D127" t="s">
+        <v>283</v>
+      </c>
+      <c r="E127" t="s">
+        <v>328</v>
+      </c>
+      <c r="F127" t="s">
+        <v>330</v>
+      </c>
+      <c r="G127" t="s">
+        <v>438</v>
+      </c>
+      <c r="H127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>70</v>
+      </c>
+      <c r="B128" t="s">
+        <v>175</v>
+      </c>
+      <c r="C128" t="s">
+        <v>220</v>
+      </c>
+      <c r="D128" t="s">
+        <v>284</v>
+      </c>
+      <c r="E128" t="s">
+        <v>328</v>
+      </c>
+      <c r="F128" t="s">
+        <v>328</v>
+      </c>
+      <c r="G128" t="s">
+        <v>439</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>70</v>
+      </c>
+      <c r="B129" t="s">
+        <v>175</v>
+      </c>
+      <c r="C129" t="s">
+        <v>220</v>
+      </c>
+      <c r="D129" t="s">
+        <v>284</v>
+      </c>
+      <c r="E129" t="s">
+        <v>328</v>
+      </c>
+      <c r="F129" t="s">
+        <v>330</v>
+      </c>
+      <c r="G129" t="s">
+        <v>440</v>
+      </c>
+      <c r="H129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>71</v>
+      </c>
+      <c r="B130" t="s">
+        <v>176</v>
+      </c>
+      <c r="C130" t="s">
+        <v>219</v>
+      </c>
+      <c r="D130" t="s">
+        <v>285</v>
+      </c>
+      <c r="E130" t="s">
+        <v>328</v>
+      </c>
+      <c r="F130" t="s">
+        <v>328</v>
+      </c>
+      <c r="G130" t="s">
+        <v>441</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>71</v>
+      </c>
+      <c r="B131" t="s">
+        <v>176</v>
+      </c>
+      <c r="C131" t="s">
+        <v>219</v>
+      </c>
+      <c r="D131" t="s">
+        <v>285</v>
+      </c>
+      <c r="E131" t="s">
+        <v>328</v>
+      </c>
+      <c r="F131" t="s">
+        <v>330</v>
+      </c>
+      <c r="G131" t="s">
+        <v>442</v>
+      </c>
+      <c r="H131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>72</v>
+      </c>
+      <c r="B132" t="s">
+        <v>177</v>
+      </c>
+      <c r="C132" t="s">
+        <v>219</v>
+      </c>
+      <c r="D132" t="s">
+        <v>286</v>
+      </c>
+      <c r="E132" t="s">
+        <v>328</v>
+      </c>
+      <c r="F132" t="s">
+        <v>328</v>
+      </c>
+      <c r="G132" t="s">
+        <v>443</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>72</v>
+      </c>
+      <c r="B133" t="s">
+        <v>177</v>
+      </c>
+      <c r="C133" t="s">
+        <v>219</v>
+      </c>
+      <c r="D133" t="s">
+        <v>286</v>
+      </c>
+      <c r="E133" t="s">
+        <v>328</v>
+      </c>
+      <c r="F133" t="s">
+        <v>330</v>
+      </c>
+      <c r="G133" t="s">
+        <v>444</v>
+      </c>
+      <c r="H133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>73</v>
+      </c>
+      <c r="B134" t="s">
+        <v>178</v>
+      </c>
+      <c r="C134" t="s">
+        <v>219</v>
+      </c>
+      <c r="D134" t="s">
+        <v>287</v>
+      </c>
+      <c r="E134" t="s">
+        <v>328</v>
+      </c>
+      <c r="F134" t="s">
+        <v>328</v>
+      </c>
+      <c r="G134" t="s">
+        <v>445</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>73</v>
+      </c>
+      <c r="B135" t="s">
+        <v>178</v>
+      </c>
+      <c r="C135" t="s">
+        <v>219</v>
+      </c>
+      <c r="D135" t="s">
+        <v>287</v>
+      </c>
+      <c r="E135" t="s">
+        <v>328</v>
+      </c>
+      <c r="F135" t="s">
+        <v>330</v>
+      </c>
+      <c r="G135" t="s">
+        <v>446</v>
+      </c>
+      <c r="H135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>74</v>
+      </c>
+      <c r="B136" t="s">
+        <v>179</v>
+      </c>
+      <c r="C136" t="s">
+        <v>219</v>
+      </c>
+      <c r="D136" t="s">
+        <v>288</v>
+      </c>
+      <c r="E136" t="s">
+        <v>328</v>
+      </c>
+      <c r="F136" t="s">
+        <v>328</v>
+      </c>
+      <c r="G136" t="s">
+        <v>447</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>74</v>
+      </c>
+      <c r="B137" t="s">
+        <v>179</v>
+      </c>
+      <c r="C137" t="s">
+        <v>219</v>
+      </c>
+      <c r="D137" t="s">
+        <v>288</v>
+      </c>
+      <c r="E137" t="s">
+        <v>328</v>
+      </c>
+      <c r="F137" t="s">
+        <v>330</v>
+      </c>
+      <c r="G137" t="s">
+        <v>448</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>75</v>
+      </c>
+      <c r="B138" t="s">
+        <v>180</v>
+      </c>
+      <c r="C138" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" t="s">
+        <v>328</v>
+      </c>
+      <c r="F138" t="s">
+        <v>328</v>
+      </c>
+      <c r="G138" t="s">
+        <v>449</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>75</v>
+      </c>
+      <c r="B139" t="s">
+        <v>180</v>
+      </c>
+      <c r="C139" t="s">
+        <v>219</v>
+      </c>
+      <c r="D139" t="s">
+        <v>289</v>
+      </c>
+      <c r="E139" t="s">
+        <v>328</v>
+      </c>
+      <c r="F139" t="s">
+        <v>330</v>
+      </c>
+      <c r="G139" t="s">
+        <v>450</v>
+      </c>
+      <c r="H139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>76</v>
+      </c>
+      <c r="B140" t="s">
+        <v>181</v>
+      </c>
+      <c r="C140" t="s">
+        <v>219</v>
+      </c>
+      <c r="D140" t="s">
+        <v>290</v>
+      </c>
+      <c r="E140" t="s">
+        <v>328</v>
+      </c>
+      <c r="F140" t="s">
+        <v>328</v>
+      </c>
+      <c r="G140" t="s">
+        <v>451</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>76</v>
+      </c>
+      <c r="B141" t="s">
+        <v>181</v>
+      </c>
+      <c r="C141" t="s">
+        <v>219</v>
+      </c>
+      <c r="D141" t="s">
+        <v>290</v>
+      </c>
+      <c r="E141" t="s">
+        <v>328</v>
+      </c>
+      <c r="F141" t="s">
+        <v>330</v>
+      </c>
+      <c r="G141" t="s">
+        <v>428</v>
+      </c>
+      <c r="H141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>77</v>
+      </c>
+      <c r="B142" t="s">
+        <v>182</v>
+      </c>
+      <c r="C142" t="s">
+        <v>219</v>
+      </c>
+      <c r="D142" t="s">
+        <v>291</v>
+      </c>
+      <c r="E142" t="s">
+        <v>328</v>
+      </c>
+      <c r="F142" t="s">
+        <v>328</v>
+      </c>
+      <c r="G142" t="s">
+        <v>452</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>77</v>
+      </c>
+      <c r="B143" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" t="s">
+        <v>219</v>
+      </c>
+      <c r="D143" t="s">
+        <v>291</v>
+      </c>
+      <c r="E143" t="s">
+        <v>328</v>
+      </c>
+      <c r="F143" t="s">
+        <v>330</v>
+      </c>
+      <c r="G143" t="s">
+        <v>453</v>
+      </c>
+      <c r="H143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>78</v>
+      </c>
+      <c r="B144" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" t="s">
+        <v>219</v>
+      </c>
+      <c r="D144" t="s">
+        <v>292</v>
+      </c>
+      <c r="E144" t="s">
+        <v>328</v>
+      </c>
+      <c r="F144" t="s">
+        <v>328</v>
+      </c>
+      <c r="G144" t="s">
+        <v>454</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>78</v>
+      </c>
+      <c r="B145" t="s">
+        <v>183</v>
+      </c>
+      <c r="C145" t="s">
+        <v>219</v>
+      </c>
+      <c r="D145" t="s">
+        <v>292</v>
+      </c>
+      <c r="E145" t="s">
+        <v>328</v>
+      </c>
+      <c r="F145" t="s">
+        <v>330</v>
+      </c>
+      <c r="G145" t="s">
+        <v>455</v>
+      </c>
+      <c r="H145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>79</v>
+      </c>
+      <c r="B146" t="s">
+        <v>184</v>
+      </c>
+      <c r="C146" t="s">
+        <v>219</v>
+      </c>
+      <c r="D146" t="s">
+        <v>293</v>
+      </c>
+      <c r="E146" t="s">
+        <v>328</v>
+      </c>
+      <c r="F146" t="s">
+        <v>330</v>
+      </c>
+      <c r="G146" t="s">
+        <v>456</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>79</v>
+      </c>
+      <c r="B147" t="s">
+        <v>184</v>
+      </c>
+      <c r="C147" t="s">
+        <v>219</v>
+      </c>
+      <c r="D147" t="s">
+        <v>293</v>
+      </c>
+      <c r="E147" t="s">
+        <v>328</v>
+      </c>
+      <c r="F147" t="s">
+        <v>328</v>
+      </c>
+      <c r="G147" t="s">
+        <v>456</v>
+      </c>
+      <c r="H147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>80</v>
+      </c>
+      <c r="B148" t="s">
+        <v>185</v>
+      </c>
+      <c r="C148" t="s">
+        <v>219</v>
+      </c>
+      <c r="D148" t="s">
+        <v>294</v>
+      </c>
+      <c r="E148" t="s">
+        <v>328</v>
+      </c>
+      <c r="F148" t="s">
+        <v>328</v>
+      </c>
+      <c r="G148" t="s">
+        <v>457</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>80</v>
+      </c>
+      <c r="B149" t="s">
+        <v>185</v>
+      </c>
+      <c r="C149" t="s">
+        <v>219</v>
+      </c>
+      <c r="D149" t="s">
+        <v>294</v>
+      </c>
+      <c r="E149" t="s">
+        <v>328</v>
+      </c>
+      <c r="F149" t="s">
+        <v>330</v>
+      </c>
+      <c r="G149" t="s">
+        <v>458</v>
+      </c>
+      <c r="H149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>81</v>
+      </c>
+      <c r="B150" t="s">
+        <v>186</v>
+      </c>
+      <c r="C150" t="s">
+        <v>219</v>
+      </c>
+      <c r="D150" t="s">
+        <v>295</v>
+      </c>
+      <c r="E150" t="s">
+        <v>328</v>
+      </c>
+      <c r="F150" t="s">
+        <v>330</v>
+      </c>
+      <c r="G150" t="s">
+        <v>459</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>81</v>
+      </c>
+      <c r="B151" t="s">
+        <v>186</v>
+      </c>
+      <c r="C151" t="s">
+        <v>219</v>
+      </c>
+      <c r="D151" t="s">
+        <v>295</v>
+      </c>
+      <c r="E151" t="s">
+        <v>328</v>
+      </c>
+      <c r="F151" t="s">
+        <v>328</v>
+      </c>
+      <c r="G151" t="s">
+        <v>459</v>
+      </c>
+      <c r="H151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>82</v>
+      </c>
+      <c r="B152" t="s">
+        <v>187</v>
+      </c>
+      <c r="C152" t="s">
+        <v>219</v>
+      </c>
+      <c r="D152" t="s">
+        <v>296</v>
+      </c>
+      <c r="E152" t="s">
+        <v>328</v>
+      </c>
+      <c r="F152" t="s">
+        <v>328</v>
+      </c>
+      <c r="G152" t="s">
+        <v>460</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>82</v>
+      </c>
+      <c r="B153" t="s">
+        <v>187</v>
+      </c>
+      <c r="C153" t="s">
+        <v>219</v>
+      </c>
+      <c r="D153" t="s">
+        <v>296</v>
+      </c>
+      <c r="E153" t="s">
+        <v>328</v>
+      </c>
+      <c r="F153" t="s">
+        <v>330</v>
+      </c>
+      <c r="G153" t="s">
+        <v>461</v>
+      </c>
+      <c r="H153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>83</v>
+      </c>
+      <c r="B154" t="s">
+        <v>188</v>
+      </c>
+      <c r="C154" t="s">
+        <v>219</v>
+      </c>
+      <c r="D154" t="s">
+        <v>297</v>
+      </c>
+      <c r="E154" t="s">
+        <v>328</v>
+      </c>
+      <c r="F154" t="s">
+        <v>328</v>
+      </c>
+      <c r="G154" t="s">
+        <v>462</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>83</v>
+      </c>
+      <c r="B155" t="s">
+        <v>188</v>
+      </c>
+      <c r="C155" t="s">
+        <v>219</v>
+      </c>
+      <c r="D155" t="s">
+        <v>297</v>
+      </c>
+      <c r="E155" t="s">
+        <v>328</v>
+      </c>
+      <c r="F155" t="s">
+        <v>330</v>
+      </c>
+      <c r="G155" t="s">
+        <v>463</v>
+      </c>
+      <c r="H155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>84</v>
+      </c>
+      <c r="B156" t="s">
+        <v>189</v>
+      </c>
+      <c r="C156" t="s">
+        <v>219</v>
+      </c>
+      <c r="D156" t="s">
+        <v>298</v>
+      </c>
+      <c r="E156" t="s">
+        <v>328</v>
+      </c>
+      <c r="F156" t="s">
+        <v>328</v>
+      </c>
+      <c r="G156" t="s">
+        <v>464</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>84</v>
+      </c>
+      <c r="B157" t="s">
+        <v>189</v>
+      </c>
+      <c r="C157" t="s">
+        <v>219</v>
+      </c>
+      <c r="D157" t="s">
+        <v>298</v>
+      </c>
+      <c r="E157" t="s">
+        <v>328</v>
+      </c>
+      <c r="F157" t="s">
+        <v>330</v>
+      </c>
+      <c r="G157" t="s">
+        <v>464</v>
+      </c>
+      <c r="H157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>85</v>
+      </c>
+      <c r="B158" t="s">
+        <v>190</v>
+      </c>
+      <c r="C158" t="s">
+        <v>219</v>
+      </c>
+      <c r="D158" t="s">
+        <v>299</v>
+      </c>
+      <c r="E158" t="s">
+        <v>328</v>
+      </c>
+      <c r="F158" t="s">
+        <v>328</v>
+      </c>
+      <c r="G158" t="s">
+        <v>465</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>85</v>
+      </c>
+      <c r="B159" t="s">
+        <v>190</v>
+      </c>
+      <c r="C159" t="s">
+        <v>219</v>
+      </c>
+      <c r="D159" t="s">
+        <v>299</v>
+      </c>
+      <c r="E159" t="s">
+        <v>328</v>
+      </c>
+      <c r="F159" t="s">
+        <v>330</v>
+      </c>
+      <c r="G159" t="s">
+        <v>466</v>
+      </c>
+      <c r="H159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>86</v>
+      </c>
+      <c r="B160" t="s">
+        <v>191</v>
+      </c>
+      <c r="C160" t="s">
+        <v>219</v>
+      </c>
+      <c r="D160" t="s">
+        <v>300</v>
+      </c>
+      <c r="E160" t="s">
+        <v>328</v>
+      </c>
+      <c r="F160" t="s">
+        <v>328</v>
+      </c>
+      <c r="G160" t="s">
+        <v>467</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>86</v>
+      </c>
+      <c r="B161" t="s">
+        <v>191</v>
+      </c>
+      <c r="C161" t="s">
+        <v>219</v>
+      </c>
+      <c r="D161" t="s">
+        <v>300</v>
+      </c>
+      <c r="E161" t="s">
+        <v>328</v>
+      </c>
+      <c r="F161" t="s">
+        <v>330</v>
+      </c>
+      <c r="G161" t="s">
+        <v>468</v>
+      </c>
+      <c r="H161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>87</v>
+      </c>
+      <c r="B162" t="s">
+        <v>192</v>
+      </c>
+      <c r="C162" t="s">
+        <v>219</v>
+      </c>
+      <c r="D162" t="s">
+        <v>301</v>
+      </c>
+      <c r="E162" t="s">
+        <v>328</v>
+      </c>
+      <c r="F162" t="s">
+        <v>328</v>
+      </c>
+      <c r="G162" t="s">
+        <v>469</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>87</v>
+      </c>
+      <c r="B163" t="s">
+        <v>192</v>
+      </c>
+      <c r="C163" t="s">
+        <v>219</v>
+      </c>
+      <c r="D163" t="s">
+        <v>301</v>
+      </c>
+      <c r="E163" t="s">
+        <v>328</v>
+      </c>
+      <c r="F163" t="s">
+        <v>330</v>
+      </c>
+      <c r="G163" t="s">
+        <v>470</v>
+      </c>
+      <c r="H163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" t="s">
+        <v>193</v>
+      </c>
+      <c r="C164" t="s">
+        <v>219</v>
+      </c>
+      <c r="D164" t="s">
+        <v>302</v>
+      </c>
+      <c r="E164" t="s">
+        <v>328</v>
+      </c>
+      <c r="F164" t="s">
+        <v>328</v>
+      </c>
+      <c r="G164" t="s">
+        <v>471</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>88</v>
+      </c>
+      <c r="B165" t="s">
+        <v>193</v>
+      </c>
+      <c r="C165" t="s">
+        <v>219</v>
+      </c>
+      <c r="D165" t="s">
+        <v>302</v>
+      </c>
+      <c r="E165" t="s">
+        <v>328</v>
+      </c>
+      <c r="F165" t="s">
+        <v>330</v>
+      </c>
+      <c r="G165" t="s">
+        <v>472</v>
+      </c>
+      <c r="H165">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" t="s">
+        <v>89</v>
+      </c>
+      <c r="B166" t="s">
+        <v>194</v>
+      </c>
+      <c r="C166" t="s">
+        <v>219</v>
+      </c>
+      <c r="D166" t="s">
+        <v>303</v>
+      </c>
+      <c r="E166" t="s">
+        <v>328</v>
+      </c>
+      <c r="F166" t="s">
+        <v>328</v>
+      </c>
+      <c r="G166" t="s">
+        <v>473</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
+        <v>89</v>
+      </c>
+      <c r="B167" t="s">
+        <v>194</v>
+      </c>
+      <c r="C167" t="s">
+        <v>219</v>
+      </c>
+      <c r="D167" t="s">
+        <v>303</v>
+      </c>
+      <c r="E167" t="s">
+        <v>328</v>
+      </c>
+      <c r="F167" t="s">
+        <v>330</v>
+      </c>
+      <c r="G167" t="s">
+        <v>474</v>
+      </c>
+      <c r="H167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>90</v>
+      </c>
+      <c r="B168" t="s">
+        <v>195</v>
+      </c>
+      <c r="C168" t="s">
+        <v>219</v>
+      </c>
+      <c r="D168" t="s">
+        <v>304</v>
+      </c>
+      <c r="E168" t="s">
+        <v>328</v>
+      </c>
+      <c r="F168" t="s">
+        <v>328</v>
+      </c>
+      <c r="G168" t="s">
+        <v>475</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>90</v>
+      </c>
+      <c r="B169" t="s">
+        <v>195</v>
+      </c>
+      <c r="C169" t="s">
+        <v>219</v>
+      </c>
+      <c r="D169" t="s">
+        <v>304</v>
+      </c>
+      <c r="E169" t="s">
+        <v>328</v>
+      </c>
+      <c r="F169" t="s">
+        <v>330</v>
+      </c>
+      <c r="G169" t="s">
+        <v>476</v>
+      </c>
+      <c r="H169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>91</v>
+      </c>
+      <c r="B170" t="s">
+        <v>196</v>
+      </c>
+      <c r="C170" t="s">
+        <v>219</v>
+      </c>
+      <c r="D170" t="s">
+        <v>305</v>
+      </c>
+      <c r="E170" t="s">
+        <v>328</v>
+      </c>
+      <c r="F170" t="s">
+        <v>328</v>
+      </c>
+      <c r="G170" t="s">
+        <v>477</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>91</v>
+      </c>
+      <c r="B171" t="s">
+        <v>196</v>
+      </c>
+      <c r="C171" t="s">
+        <v>219</v>
+      </c>
+      <c r="D171" t="s">
+        <v>305</v>
+      </c>
+      <c r="E171" t="s">
+        <v>328</v>
+      </c>
+      <c r="F171" t="s">
+        <v>330</v>
+      </c>
+      <c r="G171" t="s">
+        <v>478</v>
+      </c>
+      <c r="H171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>92</v>
+      </c>
+      <c r="B172" t="s">
+        <v>197</v>
+      </c>
+      <c r="C172" t="s">
+        <v>219</v>
+      </c>
+      <c r="D172" t="s">
+        <v>306</v>
+      </c>
+      <c r="E172" t="s">
+        <v>328</v>
+      </c>
+      <c r="F172" t="s">
+        <v>328</v>
+      </c>
+      <c r="G172" t="s">
+        <v>479</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>92</v>
+      </c>
+      <c r="B173" t="s">
+        <v>197</v>
+      </c>
+      <c r="C173" t="s">
+        <v>219</v>
+      </c>
+      <c r="D173" t="s">
+        <v>306</v>
+      </c>
+      <c r="E173" t="s">
+        <v>328</v>
+      </c>
+      <c r="F173" t="s">
+        <v>330</v>
+      </c>
+      <c r="G173" t="s">
+        <v>480</v>
+      </c>
+      <c r="H173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>93</v>
+      </c>
+      <c r="B174" t="s">
+        <v>198</v>
+      </c>
+      <c r="C174" t="s">
+        <v>219</v>
+      </c>
+      <c r="D174" t="s">
+        <v>307</v>
+      </c>
+      <c r="E174" t="s">
+        <v>328</v>
+      </c>
+      <c r="F174" t="s">
+        <v>328</v>
+      </c>
+      <c r="G174" t="s">
+        <v>481</v>
+      </c>
+      <c r="H174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>93</v>
+      </c>
+      <c r="B175" t="s">
+        <v>198</v>
+      </c>
+      <c r="C175" t="s">
+        <v>219</v>
+      </c>
+      <c r="D175" t="s">
+        <v>307</v>
+      </c>
+      <c r="E175" t="s">
+        <v>328</v>
+      </c>
+      <c r="F175" t="s">
+        <v>330</v>
+      </c>
+      <c r="G175" t="s">
+        <v>482</v>
+      </c>
+      <c r="H175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>94</v>
+      </c>
+      <c r="B176" t="s">
+        <v>199</v>
+      </c>
+      <c r="C176" t="s">
+        <v>219</v>
+      </c>
+      <c r="D176" t="s">
+        <v>308</v>
+      </c>
+      <c r="E176" t="s">
+        <v>328</v>
+      </c>
+      <c r="F176" t="s">
+        <v>328</v>
+      </c>
+      <c r="G176" t="s">
+        <v>340</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" t="s">
+        <v>94</v>
+      </c>
+      <c r="B177" t="s">
+        <v>199</v>
+      </c>
+      <c r="C177" t="s">
+        <v>219</v>
+      </c>
+      <c r="D177" t="s">
+        <v>308</v>
+      </c>
+      <c r="E177" t="s">
+        <v>328</v>
+      </c>
+      <c r="F177" t="s">
+        <v>330</v>
+      </c>
+      <c r="G177" t="s">
+        <v>340</v>
+      </c>
+      <c r="H177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>95</v>
+      </c>
+      <c r="B178" t="s">
+        <v>200</v>
+      </c>
+      <c r="C178" t="s">
+        <v>219</v>
+      </c>
+      <c r="D178" t="s">
+        <v>309</v>
+      </c>
+      <c r="E178" t="s">
+        <v>328</v>
+      </c>
+      <c r="F178" t="s">
+        <v>328</v>
+      </c>
+      <c r="G178" t="s">
+        <v>483</v>
+      </c>
+      <c r="H178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" t="s">
+        <v>95</v>
+      </c>
+      <c r="B179" t="s">
+        <v>200</v>
+      </c>
+      <c r="C179" t="s">
+        <v>219</v>
+      </c>
+      <c r="D179" t="s">
+        <v>309</v>
+      </c>
+      <c r="E179" t="s">
+        <v>328</v>
+      </c>
+      <c r="F179" t="s">
+        <v>330</v>
+      </c>
+      <c r="G179" t="s">
+        <v>484</v>
+      </c>
+      <c r="H179">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" t="s">
+        <v>96</v>
+      </c>
+      <c r="B180" t="s">
+        <v>201</v>
+      </c>
+      <c r="C180" t="s">
+        <v>219</v>
+      </c>
+      <c r="D180" t="s">
+        <v>310</v>
+      </c>
+      <c r="E180" t="s">
+        <v>328</v>
+      </c>
+      <c r="F180" t="s">
+        <v>330</v>
+      </c>
+      <c r="G180" t="s">
+        <v>485</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" t="s">
+        <v>96</v>
+      </c>
+      <c r="B181" t="s">
+        <v>201</v>
+      </c>
+      <c r="C181" t="s">
+        <v>219</v>
+      </c>
+      <c r="D181" t="s">
+        <v>310</v>
+      </c>
+      <c r="E181" t="s">
+        <v>328</v>
+      </c>
+      <c r="F181" t="s">
+        <v>328</v>
+      </c>
+      <c r="G181" t="s">
+        <v>485</v>
+      </c>
+      <c r="H181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>97</v>
+      </c>
+      <c r="B182" t="s">
+        <v>202</v>
+      </c>
+      <c r="C182" t="s">
+        <v>219</v>
+      </c>
+      <c r="D182" t="s">
+        <v>311</v>
+      </c>
+      <c r="E182" t="s">
+        <v>328</v>
+      </c>
+      <c r="F182" t="s">
+        <v>328</v>
+      </c>
+      <c r="G182" t="s">
+        <v>486</v>
+      </c>
+      <c r="H182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>97</v>
+      </c>
+      <c r="B183" t="s">
+        <v>202</v>
+      </c>
+      <c r="C183" t="s">
+        <v>219</v>
+      </c>
+      <c r="D183" t="s">
+        <v>311</v>
+      </c>
+      <c r="E183" t="s">
+        <v>328</v>
+      </c>
+      <c r="F183" t="s">
+        <v>330</v>
+      </c>
+      <c r="G183" t="s">
+        <v>487</v>
+      </c>
+      <c r="H183">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>98</v>
+      </c>
+      <c r="B184" t="s">
+        <v>203</v>
+      </c>
+      <c r="C184" t="s">
+        <v>219</v>
+      </c>
+      <c r="D184" t="s">
+        <v>312</v>
+      </c>
+      <c r="E184" t="s">
+        <v>328</v>
+      </c>
+      <c r="F184" t="s">
+        <v>328</v>
+      </c>
+      <c r="G184" t="s">
+        <v>488</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>98</v>
+      </c>
+      <c r="B185" t="s">
+        <v>203</v>
+      </c>
+      <c r="C185" t="s">
+        <v>219</v>
+      </c>
+      <c r="D185" t="s">
+        <v>312</v>
+      </c>
+      <c r="E185" t="s">
+        <v>328</v>
+      </c>
+      <c r="F185" t="s">
+        <v>330</v>
+      </c>
+      <c r="G185" t="s">
+        <v>489</v>
+      </c>
+      <c r="H185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>99</v>
+      </c>
+      <c r="B186" t="s">
+        <v>204</v>
+      </c>
+      <c r="C186" t="s">
+        <v>219</v>
+      </c>
+      <c r="D186" t="s">
+        <v>313</v>
+      </c>
+      <c r="E186" t="s">
+        <v>328</v>
+      </c>
+      <c r="F186" t="s">
+        <v>328</v>
+      </c>
+      <c r="G186" t="s">
+        <v>490</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" t="s">
+        <v>99</v>
+      </c>
+      <c r="B187" t="s">
+        <v>204</v>
+      </c>
+      <c r="C187" t="s">
+        <v>219</v>
+      </c>
+      <c r="D187" t="s">
+        <v>313</v>
+      </c>
+      <c r="E187" t="s">
+        <v>328</v>
+      </c>
+      <c r="F187" t="s">
+        <v>330</v>
+      </c>
+      <c r="G187" t="s">
+        <v>491</v>
+      </c>
+      <c r="H187">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B188" t="s">
+        <v>205</v>
+      </c>
+      <c r="C188" t="s">
+        <v>219</v>
+      </c>
+      <c r="D188" t="s">
+        <v>314</v>
+      </c>
+      <c r="E188" t="s">
+        <v>328</v>
+      </c>
+      <c r="F188" t="s">
+        <v>328</v>
+      </c>
+      <c r="G188" t="s">
+        <v>492</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" t="s">
+        <v>100</v>
+      </c>
+      <c r="B189" t="s">
+        <v>205</v>
+      </c>
+      <c r="C189" t="s">
+        <v>219</v>
+      </c>
+      <c r="D189" t="s">
+        <v>314</v>
+      </c>
+      <c r="E189" t="s">
+        <v>328</v>
+      </c>
+      <c r="F189" t="s">
+        <v>330</v>
+      </c>
+      <c r="G189" t="s">
+        <v>493</v>
+      </c>
+      <c r="H189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" t="s">
+        <v>101</v>
+      </c>
+      <c r="B190" t="s">
+        <v>206</v>
+      </c>
+      <c r="C190" t="s">
+        <v>219</v>
+      </c>
+      <c r="D190" t="s">
+        <v>315</v>
+      </c>
+      <c r="E190" t="s">
+        <v>328</v>
+      </c>
+      <c r="F190" t="s">
+        <v>328</v>
+      </c>
+      <c r="G190" t="s">
+        <v>494</v>
+      </c>
+      <c r="H190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" t="s">
+        <v>101</v>
+      </c>
+      <c r="B191" t="s">
+        <v>206</v>
+      </c>
+      <c r="C191" t="s">
+        <v>219</v>
+      </c>
+      <c r="D191" t="s">
+        <v>315</v>
+      </c>
+      <c r="E191" t="s">
+        <v>328</v>
+      </c>
+      <c r="F191" t="s">
+        <v>330</v>
+      </c>
+      <c r="G191" t="s">
+        <v>494</v>
+      </c>
+      <c r="H191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" t="s">
+        <v>102</v>
+      </c>
+      <c r="B192" t="s">
+        <v>207</v>
+      </c>
+      <c r="C192" t="s">
+        <v>219</v>
+      </c>
+      <c r="D192" t="s">
+        <v>316</v>
+      </c>
+      <c r="E192" t="s">
+        <v>328</v>
+      </c>
+      <c r="F192" t="s">
+        <v>328</v>
+      </c>
+      <c r="G192" t="s">
+        <v>495</v>
+      </c>
+      <c r="H192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" t="s">
+        <v>102</v>
+      </c>
+      <c r="B193" t="s">
+        <v>207</v>
+      </c>
+      <c r="C193" t="s">
+        <v>219</v>
+      </c>
+      <c r="D193" t="s">
+        <v>316</v>
+      </c>
+      <c r="E193" t="s">
+        <v>328</v>
+      </c>
+      <c r="F193" t="s">
+        <v>330</v>
+      </c>
+      <c r="G193" t="s">
+        <v>496</v>
+      </c>
+      <c r="H193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" t="s">
+        <v>103</v>
+      </c>
+      <c r="B194" t="s">
+        <v>208</v>
+      </c>
+      <c r="C194" t="s">
+        <v>219</v>
+      </c>
+      <c r="D194" t="s">
+        <v>317</v>
+      </c>
+      <c r="E194" t="s">
+        <v>328</v>
+      </c>
+      <c r="F194" t="s">
+        <v>328</v>
+      </c>
+      <c r="G194" t="s">
+        <v>497</v>
+      </c>
+      <c r="H194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" t="s">
+        <v>103</v>
+      </c>
+      <c r="B195" t="s">
+        <v>208</v>
+      </c>
+      <c r="C195" t="s">
+        <v>219</v>
+      </c>
+      <c r="D195" t="s">
+        <v>317</v>
+      </c>
+      <c r="E195" t="s">
+        <v>328</v>
+      </c>
+      <c r="F195" t="s">
+        <v>330</v>
+      </c>
+      <c r="G195" t="s">
+        <v>498</v>
+      </c>
+      <c r="H195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" t="s">
+        <v>104</v>
+      </c>
+      <c r="B196" t="s">
+        <v>209</v>
+      </c>
+      <c r="C196" t="s">
+        <v>219</v>
+      </c>
+      <c r="D196" t="s">
+        <v>318</v>
+      </c>
+      <c r="E196" t="s">
+        <v>328</v>
+      </c>
+      <c r="F196" t="s">
+        <v>330</v>
+      </c>
+      <c r="G196" t="s">
+        <v>499</v>
+      </c>
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
+        <v>104</v>
+      </c>
+      <c r="B197" t="s">
+        <v>209</v>
+      </c>
+      <c r="C197" t="s">
+        <v>219</v>
+      </c>
+      <c r="D197" t="s">
+        <v>318</v>
+      </c>
+      <c r="E197" t="s">
+        <v>328</v>
+      </c>
+      <c r="F197" t="s">
+        <v>328</v>
+      </c>
+      <c r="G197" t="s">
+        <v>499</v>
+      </c>
+      <c r="H197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>105</v>
+      </c>
+      <c r="B198" t="s">
+        <v>210</v>
+      </c>
+      <c r="C198" t="s">
+        <v>219</v>
+      </c>
+      <c r="D198" t="s">
+        <v>319</v>
+      </c>
+      <c r="E198" t="s">
+        <v>328</v>
+      </c>
+      <c r="F198" t="s">
+        <v>328</v>
+      </c>
+      <c r="G198" t="s">
+        <v>500</v>
+      </c>
+      <c r="H198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" t="s">
+        <v>105</v>
+      </c>
+      <c r="B199" t="s">
+        <v>210</v>
+      </c>
+      <c r="C199" t="s">
+        <v>219</v>
+      </c>
+      <c r="D199" t="s">
+        <v>319</v>
+      </c>
+      <c r="E199" t="s">
+        <v>328</v>
+      </c>
+      <c r="F199" t="s">
+        <v>330</v>
+      </c>
+      <c r="G199" t="s">
+        <v>501</v>
+      </c>
+      <c r="H199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" t="s">
+        <v>106</v>
+      </c>
+      <c r="B200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C200" t="s">
+        <v>219</v>
+      </c>
+      <c r="D200" t="s">
+        <v>320</v>
+      </c>
+      <c r="E200" t="s">
+        <v>328</v>
+      </c>
+      <c r="F200" t="s">
+        <v>328</v>
+      </c>
+      <c r="G200" t="s">
+        <v>502</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" t="s">
+        <v>106</v>
+      </c>
+      <c r="B201" t="s">
+        <v>211</v>
+      </c>
+      <c r="C201" t="s">
+        <v>219</v>
+      </c>
+      <c r="D201" t="s">
+        <v>320</v>
+      </c>
+      <c r="E201" t="s">
+        <v>328</v>
+      </c>
+      <c r="F201" t="s">
+        <v>330</v>
+      </c>
+      <c r="G201" t="s">
+        <v>503</v>
+      </c>
+      <c r="H201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>107</v>
+      </c>
+      <c r="B202" t="s">
+        <v>212</v>
+      </c>
+      <c r="C202" t="s">
+        <v>219</v>
+      </c>
+      <c r="D202" t="s">
+        <v>321</v>
+      </c>
+      <c r="E202" t="s">
+        <v>328</v>
+      </c>
+      <c r="F202" t="s">
+        <v>328</v>
+      </c>
+      <c r="G202" t="s">
+        <v>504</v>
+      </c>
+      <c r="H202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>107</v>
+      </c>
+      <c r="B203" t="s">
+        <v>212</v>
+      </c>
+      <c r="C203" t="s">
+        <v>219</v>
+      </c>
+      <c r="D203" t="s">
+        <v>321</v>
+      </c>
+      <c r="E203" t="s">
+        <v>328</v>
+      </c>
+      <c r="F203" t="s">
+        <v>330</v>
+      </c>
+      <c r="G203" t="s">
+        <v>505</v>
+      </c>
+      <c r="H203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
+        <v>108</v>
+      </c>
+      <c r="B204" t="s">
+        <v>213</v>
+      </c>
+      <c r="C204" t="s">
+        <v>219</v>
+      </c>
+      <c r="D204" t="s">
+        <v>322</v>
+      </c>
+      <c r="E204" t="s">
+        <v>328</v>
+      </c>
+      <c r="F204" t="s">
+        <v>328</v>
+      </c>
+      <c r="G204" t="s">
+        <v>506</v>
+      </c>
+      <c r="H204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" t="s">
+        <v>108</v>
+      </c>
+      <c r="B205" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" t="s">
+        <v>219</v>
+      </c>
+      <c r="D205" t="s">
+        <v>322</v>
+      </c>
+      <c r="E205" t="s">
+        <v>328</v>
+      </c>
+      <c r="F205" t="s">
+        <v>330</v>
+      </c>
+      <c r="G205" t="s">
+        <v>507</v>
+      </c>
+      <c r="H205">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>109</v>
+      </c>
+      <c r="B206" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" t="s">
+        <v>219</v>
+      </c>
+      <c r="D206" t="s">
+        <v>323</v>
+      </c>
+      <c r="E206" t="s">
+        <v>328</v>
+      </c>
+      <c r="F206" t="s">
+        <v>328</v>
+      </c>
+      <c r="G206" t="s">
+        <v>508</v>
+      </c>
+      <c r="H206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>109</v>
+      </c>
+      <c r="B207" t="s">
+        <v>214</v>
+      </c>
+      <c r="C207" t="s">
+        <v>219</v>
+      </c>
+      <c r="D207" t="s">
+        <v>323</v>
+      </c>
+      <c r="E207" t="s">
+        <v>328</v>
+      </c>
+      <c r="F207" t="s">
+        <v>330</v>
+      </c>
+      <c r="G207" t="s">
+        <v>509</v>
+      </c>
+      <c r="H207">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>110</v>
+      </c>
+      <c r="B208" t="s">
+        <v>215</v>
+      </c>
+      <c r="C208" t="s">
+        <v>219</v>
+      </c>
+      <c r="D208" t="s">
+        <v>324</v>
+      </c>
+      <c r="E208" t="s">
+        <v>328</v>
+      </c>
+      <c r="F208" t="s">
+        <v>328</v>
+      </c>
+      <c r="G208" t="s">
+        <v>510</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>110</v>
+      </c>
+      <c r="B209" t="s">
+        <v>215</v>
+      </c>
+      <c r="C209" t="s">
+        <v>219</v>
+      </c>
+      <c r="D209" t="s">
+        <v>324</v>
+      </c>
+      <c r="E209" t="s">
+        <v>328</v>
+      </c>
+      <c r="F209" t="s">
+        <v>330</v>
+      </c>
+      <c r="G209" t="s">
+        <v>511</v>
+      </c>
+      <c r="H209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>111</v>
+      </c>
+      <c r="B210" t="s">
+        <v>216</v>
+      </c>
+      <c r="C210" t="s">
+        <v>219</v>
+      </c>
+      <c r="D210" t="s">
+        <v>325</v>
+      </c>
+      <c r="E210" t="s">
+        <v>328</v>
+      </c>
+      <c r="F210" t="s">
+        <v>328</v>
+      </c>
+      <c r="G210" t="s">
+        <v>512</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>111</v>
+      </c>
+      <c r="B211" t="s">
+        <v>216</v>
+      </c>
+      <c r="C211" t="s">
+        <v>219</v>
+      </c>
+      <c r="D211" t="s">
+        <v>325</v>
+      </c>
+      <c r="E211" t="s">
+        <v>328</v>
+      </c>
+      <c r="F211" t="s">
+        <v>330</v>
+      </c>
+      <c r="G211" t="s">
+        <v>512</v>
+      </c>
+      <c r="H211">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>112</v>
+      </c>
+      <c r="B212" t="s">
+        <v>217</v>
+      </c>
+      <c r="C212" t="s">
+        <v>219</v>
+      </c>
+      <c r="D212" t="s">
+        <v>326</v>
+      </c>
+      <c r="E212" t="s">
+        <v>328</v>
+      </c>
+      <c r="F212" t="s">
+        <v>328</v>
+      </c>
+      <c r="G212" t="s">
+        <v>513</v>
+      </c>
+      <c r="H212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>112</v>
+      </c>
+      <c r="B213" t="s">
+        <v>217</v>
+      </c>
+      <c r="C213" t="s">
+        <v>219</v>
+      </c>
+      <c r="D213" t="s">
+        <v>326</v>
+      </c>
+      <c r="E213" t="s">
+        <v>328</v>
+      </c>
+      <c r="F213" t="s">
+        <v>330</v>
+      </c>
+      <c r="G213" t="s">
+        <v>514</v>
+      </c>
+      <c r="H213">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>113</v>
+      </c>
+      <c r="B214" t="s">
+        <v>218</v>
+      </c>
+      <c r="C214" t="s">
+        <v>219</v>
+      </c>
+      <c r="D214" t="s">
+        <v>327</v>
+      </c>
+      <c r="E214" t="s">
+        <v>328</v>
+      </c>
+      <c r="F214" t="s">
+        <v>328</v>
+      </c>
+      <c r="G214" t="s">
+        <v>515</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>113</v>
+      </c>
+      <c r="B215" t="s">
+        <v>218</v>
+      </c>
+      <c r="C215" t="s">
+        <v>219</v>
+      </c>
+      <c r="D215" t="s">
+        <v>327</v>
+      </c>
+      <c r="E215" t="s">
+        <v>328</v>
+      </c>
+      <c r="F215" t="s">
+        <v>330</v>
+      </c>
+      <c r="G215" t="s">
+        <v>516</v>
+      </c>
+      <c r="H215">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="614">
   <si>
     <t>code</t>
   </si>
@@ -103,6 +103,24 @@
     <t>7203031006000500 - UB - 1</t>
   </si>
   <si>
+    <t>7203021008000203 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021008200100 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203030025000201 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203030024000501 - UB - 1</t>
+  </si>
+  <si>
+    <t>7203021004500400 - UB - 5</t>
+  </si>
+  <si>
+    <t>7203021005200100 - UB - 3</t>
+  </si>
+  <si>
     <t>7204070011000302 - UB - 2</t>
   </si>
   <si>
@@ -115,6 +133,18 @@
     <t>7204032006001600 - UB - 1</t>
   </si>
   <si>
+    <t>7204030005000900 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204070009001200 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204070012000800 - UB - 1</t>
+  </si>
+  <si>
+    <t>7204070011000301 - UB - 3</t>
+  </si>
+  <si>
     <t>7205090009000301 - UB - 1</t>
   </si>
   <si>
@@ -178,6 +208,9 @@
     <t>7209051007000101 - UB - 1</t>
   </si>
   <si>
+    <t>7209050015000200 - UB - 1</t>
+  </si>
+  <si>
     <t>7209051019000800 - UB - 1</t>
   </si>
   <si>
@@ -331,6 +364,9 @@
     <t>7271020009001700 - UB - 1</t>
   </si>
   <si>
+    <t>7271030003002000 - UB - 5</t>
+  </si>
+  <si>
     <t>7271011004001500 - UB - 1</t>
   </si>
   <si>
@@ -421,6 +457,21 @@
     <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
   </si>
   <si>
+    <t>THE SIXTH CHEMICAL ENGINEERING CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>KENCANA BUMI MINERAL</t>
+  </si>
+  <si>
+    <t>CIPTA MANDIRI MOROWALI</t>
+  </si>
+  <si>
+    <t>INDONESIA GUANG CHING NICKEL AND STAINLESS STEEL INDUSTRY TKA</t>
+  </si>
+  <si>
+    <t>KINRUI NEW ENERGY TECHNOLOGIES  INDONESIA</t>
+  </si>
+  <si>
     <t>BANK BPD</t>
   </si>
   <si>
@@ -433,6 +484,18 @@
     <t>PLTA Poso 1</t>
   </si>
   <si>
+    <t>KCP MANDIRI MITRA USAHA TENTENA</t>
+  </si>
+  <si>
+    <t>PNM MODAL MIKRO</t>
+  </si>
+  <si>
+    <t>Balindo Manunggal Bersama, PT</t>
+  </si>
+  <si>
+    <t>FIF, PT</t>
+  </si>
+  <si>
     <t>SEKOLAH POLISI NEGARA</t>
   </si>
   <si>
@@ -493,6 +556,9 @@
     <t>PAGADAIAN, PT</t>
   </si>
   <si>
+    <t>RUMAH SAKIT UMUM AMPANA</t>
+  </si>
+  <si>
     <t>BANK RAKYAT INDONESIA TBK, PT</t>
   </si>
   <si>
@@ -631,7 +697,7 @@
     <t>PRIMA GELORA AGUNG LESTARI, PT</t>
   </si>
   <si>
-    <t>ADIPURA NOVEGA,CV</t>
+    <t>ADIPURA  NOVEGA,CV</t>
   </si>
   <si>
     <t>PT. KIMIA FARMA APOTEK, Kantor Cabang Palu</t>
@@ -646,6 +712,9 @@
     <t>SURYA MADISTRINDO, PT</t>
   </si>
   <si>
+    <t>TELKOM PALU, PT</t>
+  </si>
+  <si>
     <t>ARTHA LESTARI, CV</t>
   </si>
   <si>
@@ -745,6 +814,24 @@
     <t>smaalkhairatkolono@yahoo.co.id</t>
   </si>
   <si>
+    <t>sobeh@ppc-adulsory.com</t>
+  </si>
+  <si>
+    <t>acctaxkbm@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.morowali@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>ciptamandiri@yahoo.com</t>
+  </si>
+  <si>
+    <t>rukun@bd.em.com</t>
+  </si>
+  <si>
+    <t>secretariatkinrui@gmail.com</t>
+  </si>
+  <si>
     <t>bsposo@yahoo.com</t>
   </si>
   <si>
@@ -757,6 +844,18 @@
     <t>pltaposo2@posoenergy.com</t>
   </si>
   <si>
+    <t>kcpmandirimitrausaha@gmail.com</t>
+  </si>
+  <si>
+    <t>ulamposo@gmail.com</t>
+  </si>
+  <si>
+    <t>gracekayupa@gmail.com</t>
+  </si>
+  <si>
+    <t>dewiputrihilika90@gmail.com</t>
+  </si>
+  <si>
     <t>kppnpalu651707@yahoo.com</t>
   </si>
   <si>
@@ -787,10 +886,10 @@
     <t>febrialdin.rial@yahoo.co.id</t>
   </si>
   <si>
-    <t>Kc.Buol@Bprmodex.com</t>
-  </si>
-  <si>
-    <t>cona3176@bni.co.id</t>
+    <t>fandhymadjid96@gmail.com</t>
+  </si>
+  <si>
+    <t>ynataliaw@gmail.com</t>
   </si>
   <si>
     <t>nyoalvaro@gmail.com</t>
@@ -820,6 +919,9 @@
     <t>cppampana@yahoo.co.id</t>
   </si>
   <si>
+    <t>bludrsuampana@gmail.com</t>
+  </si>
+  <si>
     <t>n5210@copr.bri.co.id</t>
   </si>
   <si>
@@ -835,7 +937,7 @@
     <t>rsudsigi@gmail.com</t>
   </si>
   <si>
-    <t>rezadoanker8@gmail.com</t>
+    <t>razadoanker8@gmail.com</t>
   </si>
   <si>
     <t>n3633@co.rp.bri.co.id</t>
@@ -868,7 +970,7 @@
     <t>sulawesicentralcommodity@yahoo.com</t>
   </si>
   <si>
-    <t>hlppalu.bangunpalusulawesitengah@yahoo.com</t>
+    <t>sulawesitengahbangunpalu@gmail.com</t>
   </si>
   <si>
     <t>soputraroland@yahoo.com</t>
@@ -973,6 +1075,9 @@
     <t>fero@gmail.com</t>
   </si>
   <si>
+    <t>costumercare@telkom.co.id</t>
+  </si>
+  <si>
     <t>arthalestari_palu@yahoo.co.id</t>
   </si>
   <si>
@@ -1003,13 +1108,25 @@
     <t>bounced</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Bounced</t>
   </si>
   <si>
     <t>queued</t>
   </si>
   <si>
-    <t>permanent_fail</t>
+    <t>Queued</t>
+  </si>
+  <si>
+    <t>Clicked</t>
+  </si>
+  <si>
+    <t>Opened</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
+    <t>Permanent_fail</t>
   </si>
   <si>
     <t>02 Jun 2026, 11:35:03</t>
@@ -1123,6 +1240,39 @@
     <t>02 Jun 2026, 04:58:16</t>
   </si>
   <si>
+    <t>02 Jun 2026, 09:22:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:29:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:28:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:25</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 08:52:48</t>
   </si>
   <si>
@@ -1144,6 +1294,54 @@
     <t>02 Jun 2026, 05:07:16</t>
   </si>
   <si>
+    <t>01 Jun 2026, 22:47:26</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:34:35</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:38</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:35</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:58</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:55</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:51</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:40:36</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:53</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:52</t>
+  </si>
+  <si>
+    <t>26 May 2026, 09:13:56</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:30:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 13:44:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:54:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:24</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 02:30:55</t>
   </si>
   <si>
@@ -1201,24 +1399,63 @@
     <t>02 Jun 2026, 07:00:24</t>
   </si>
   <si>
-    <t>19 Mei 2026, 11:14:37</t>
-  </si>
-  <si>
-    <t>19 Mei 2026, 11:14:34</t>
-  </si>
-  <si>
-    <t>19 Mei 2026, 11:14:38</t>
+    <t>20 May 2026, 14:15:07</t>
+  </si>
+  <si>
+    <t>20 May 2026, 14:14:58</t>
+  </si>
+  <si>
+    <t>20 May 2026, 14:14:51</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:38:58</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:53</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:50</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:40</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:04</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:26</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:04</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:47</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:44</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:34</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:38</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:52</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:48</t>
   </si>
   <si>
     <t>02 Jun 2026, 00:32:29</t>
   </si>
   <si>
-    <t>21 Mei 2026, 08:24:52</t>
-  </si>
-  <si>
-    <t>21 Mei 2026, 08:24:48</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 00:55:50</t>
   </si>
   <si>
@@ -1255,18 +1492,27 @@
     <t>02 Jun 2026, 09:04:47</t>
   </si>
   <si>
+    <t>05 Jun 2026, 10:13:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:17:08</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:16:10</t>
+  </si>
+  <si>
     <t>01 Jun 2026, 23:01:16</t>
   </si>
   <si>
     <t>01 Jun 2026, 23:04:03</t>
   </si>
   <si>
+    <t>02 Jun 2026, 00:49:31</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 00:49:30</t>
   </si>
   <si>
-    <t>02 Jun 2026, 00:49:31</t>
-  </si>
-  <si>
     <t>02 Jun 2026, 06:33:41</t>
   </si>
   <si>
@@ -1279,10 +1525,49 @@
     <t>01 Jun 2026, 22:57:07</t>
   </si>
   <si>
-    <t>19 Mei 2026, 09:51:11</t>
-  </si>
-  <si>
-    <t>19 Mei 2026, 09:51:10</t>
+    <t>22 May 2026, 08:31:08</t>
+  </si>
+  <si>
+    <t>20 May 2026, 18:16:27</t>
+  </si>
+  <si>
+    <t>20 May 2026, 18:15:47</t>
+  </si>
+  <si>
+    <t>20 May 2026, 15:15:42</t>
+  </si>
+  <si>
+    <t>20 May 2026, 15:15:39</t>
+  </si>
+  <si>
+    <t>19 May 2026, 17:13:00</t>
+  </si>
+  <si>
+    <t>19 May 2026, 16:04:55</t>
+  </si>
+  <si>
+    <t>19 May 2026, 10:15:42</t>
+  </si>
+  <si>
+    <t>19 May 2026, 10:15:35</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:54:05</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:53:57</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:53:51</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:53:50</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:51:11</t>
+  </si>
+  <si>
+    <t>19 May 2026, 09:51:10</t>
   </si>
   <si>
     <t>02 Jun 2026, 06:19:08</t>
@@ -1333,6 +1618,9 @@
     <t>02 Jun 2026, 07:11:00</t>
   </si>
   <si>
+    <t>04 Jun 2026, 10:40:14</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 09:12:41</t>
   </si>
   <si>
@@ -1514,6 +1802,9 @@
   </si>
   <si>
     <t>02 Jun 2026, 07:31:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:38:19</t>
   </si>
   <si>
     <t>02 Jun 2026, 03:12:01</t>
@@ -1922,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1956,22 +2247,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E2" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F2" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G2" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1982,22 +2273,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E3" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F3" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2008,22 +2299,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F4" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G4" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -2034,22 +2325,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D5" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E5" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F5" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G5" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -2060,22 +2351,22 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E6" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F6" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G6" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2086,22 +2377,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F7" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -2112,22 +2403,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E8" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F8" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G8" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2138,22 +2429,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F9" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G9" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -2164,22 +2455,22 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F10" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G10" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2190,22 +2481,22 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F11" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G11" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -2216,22 +2507,22 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E12" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F12" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G12" t="s">
-        <v>341</v>
+        <v>380</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2242,22 +2533,22 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="E13" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F13" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G13" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -2268,22 +2559,22 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D14" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="E14" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F14" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G14" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2294,22 +2585,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="E15" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F15" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G15" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -2320,22 +2611,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E16" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F16" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G16" t="s">
-        <v>345</v>
+        <v>384</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2346,22 +2637,22 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="E17" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F17" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G17" t="s">
-        <v>346</v>
+        <v>385</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -2372,22 +2663,22 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E18" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F18" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G18" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2398,22 +2689,22 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D19" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F19" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G19" t="s">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -2424,22 +2715,22 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E20" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F20" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G20" t="s">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -2450,22 +2741,22 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D21" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E21" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F21" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G21" t="s">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -2476,22 +2767,22 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C22" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E22" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F22" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G22" t="s">
-        <v>350</v>
+        <v>389</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2502,22 +2793,22 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D23" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E23" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F23" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G23" t="s">
-        <v>351</v>
+        <v>390</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -2528,22 +2819,22 @@
         <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D24" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F24" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G24" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -2554,22 +2845,22 @@
         <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F25" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G25" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="H25">
         <v>2</v>
@@ -2580,22 +2871,22 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D26" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="E26" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F26" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G26" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -2606,22 +2897,22 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C27" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D27" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="E27" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F27" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G27" t="s">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -2632,22 +2923,22 @@
         <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F28" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G28" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -2658,22 +2949,22 @@
         <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F29" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G29" t="s">
-        <v>356</v>
+        <v>395</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -2684,22 +2975,22 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C30" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D30" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="E30" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F30" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G30" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -2710,22 +3001,22 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D31" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="E31" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F31" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G31" t="s">
-        <v>357</v>
+        <v>396</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -2736,22 +3027,22 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="E32" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F32" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G32" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -2762,22 +3053,22 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D33" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="E33" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G33" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -2788,22 +3079,22 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D34" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E34" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F34" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G34" t="s">
-        <v>359</v>
+        <v>398</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -2814,22 +3105,22 @@
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D35" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E35" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F35" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G35" t="s">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -2840,22 +3131,22 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D36" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="E36" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F36" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G36" t="s">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -2866,22 +3157,22 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D37" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F37" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G37" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="H37">
         <v>2</v>
@@ -2892,22 +3183,22 @@
         <v>26</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D38" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="E38" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F38" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G38" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -2918,22 +3209,22 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D39" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="E39" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F39" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G39" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -2944,22 +3235,22 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D40" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F40" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G40" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2970,22 +3261,22 @@
         <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D41" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E41" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F41" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G41" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="H41">
         <v>2</v>
@@ -2996,22 +3287,22 @@
         <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D42" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="E42" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F42" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G42" t="s">
-        <v>367</v>
+        <v>406</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -3022,22 +3313,22 @@
         <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D43" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="E43" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F43" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G43" t="s">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="H43">
         <v>2</v>
@@ -3048,22 +3339,22 @@
         <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="E44" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F44" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G44" t="s">
-        <v>369</v>
+        <v>408</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -3074,22 +3365,22 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D45" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="E45" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F45" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G45" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="H45">
         <v>2</v>
@@ -3100,22 +3391,22 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D46" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="E46" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F46" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G46" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -3126,22 +3417,22 @@
         <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D47" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="E47" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F47" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G47" t="s">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -3152,22 +3443,22 @@
         <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D48" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="E48" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F48" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G48" t="s">
-        <v>372</v>
+        <v>411</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -3178,22 +3469,22 @@
         <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D49" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="E49" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F49" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G49" t="s">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -3204,22 +3495,22 @@
         <v>32</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D50" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="E50" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F50" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G50" t="s">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -3230,22 +3521,22 @@
         <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D51" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="E51" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F51" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G51" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -3256,22 +3547,22 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D52" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="E52" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F52" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G52" t="s">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -3282,22 +3573,22 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D53" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="E53" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F53" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G53" t="s">
-        <v>377</v>
+        <v>416</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -3308,22 +3599,22 @@
         <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D54" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="E54" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F54" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G54" t="s">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -3334,22 +3625,22 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D55" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="E55" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F55" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G55" t="s">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -3360,22 +3651,22 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D56" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E56" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F56" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G56" t="s">
-        <v>379</v>
+        <v>419</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -3386,22 +3677,22 @@
         <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D57" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E57" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F57" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G57" t="s">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -3412,22 +3703,22 @@
         <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D58" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="E58" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F58" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G58" t="s">
-        <v>381</v>
+        <v>421</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -3438,22 +3729,22 @@
         <v>36</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D59" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="E59" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F59" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G59" t="s">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -3464,22 +3755,22 @@
         <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D60" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="E60" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F60" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G60" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -3490,22 +3781,22 @@
         <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D61" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="E61" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F61" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G61" t="s">
-        <v>384</v>
+        <v>423</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -3516,22 +3807,22 @@
         <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D62" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="E62" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F62" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="G62" t="s">
-        <v>385</v>
+        <v>424</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -3542,22 +3833,22 @@
         <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="E63" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="F63" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="G63" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
       <c r="H63">
         <v>2</v>
@@ -3568,22 +3859,22 @@
         <v>39</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D64" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="E64" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F64" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G64" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -3594,22 +3885,22 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C65" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="E65" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F65" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G65" t="s">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -3620,22 +3911,22 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D66" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="E66" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F66" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G66" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -3646,22 +3937,22 @@
         <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D67" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="E67" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F67" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G67" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -3672,22 +3963,22 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D68" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="E68" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F68" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G68" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -3698,22 +3989,22 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C69" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D69" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="E69" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G69" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="H69">
         <v>2</v>
@@ -3724,22 +4015,22 @@
         <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D70" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="E70" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F70" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G70" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -3750,22 +4041,22 @@
         <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D71" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="E71" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F71" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G71" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -3773,285 +4064,285 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D72" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="E72" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F72" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G72" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="E73" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F73" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G73" t="s">
-        <v>395</v>
+        <v>433</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="E74" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F74" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G74" t="s">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F75" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G75" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="H75">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D76" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="E76" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F76" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G76" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D77" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="E77" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F77" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G77" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D78" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="E78" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F78" t="s">
-        <v>331</v>
+        <v>368</v>
       </c>
       <c r="G78" t="s">
-        <v>398</v>
+        <v>438</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D79" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="E79" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F79" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G79" t="s">
-        <v>399</v>
+        <v>439</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B80" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D80" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="E80" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F80" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G80" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="E81" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="F81" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="G81" t="s">
-        <v>329</v>
+        <v>441</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D82" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E82" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F82" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G82" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -4059,25 +4350,25 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D83" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E83" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F83" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G83" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="H83">
         <v>2</v>
@@ -4085,25 +4376,25 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C84" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D84" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E84" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F84" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G84" t="s">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -4111,25 +4402,25 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="C85" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D85" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="E85" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F85" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G85" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="H85">
         <v>2</v>
@@ -4137,25 +4428,25 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D86" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="E86" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F86" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G86" t="s">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -4163,25 +4454,25 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D87" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="E87" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F87" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G87" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -4189,25 +4480,25 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D88" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E88" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F88" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G88" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -4215,25 +4506,25 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B89" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C89" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D89" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="E89" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F89" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G89" t="s">
-        <v>406</v>
+        <v>448</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -4241,25 +4532,25 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D90" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="E90" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F90" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G90" t="s">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -4267,25 +4558,25 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D91" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="E91" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F91" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G91" t="s">
-        <v>408</v>
+        <v>450</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -4293,25 +4584,25 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B92" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C92" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D92" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E92" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F92" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G92" t="s">
-        <v>409</v>
+        <v>451</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -4319,25 +4610,25 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D93" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E93" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F93" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G93" t="s">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="H93">
         <v>2</v>
@@ -4345,25 +4636,25 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D94" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="E94" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F94" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G94" t="s">
-        <v>411</v>
+        <v>453</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -4371,25 +4662,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C95" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D95" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="E95" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F95" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G95" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -4397,25 +4688,25 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B96" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C96" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D96" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E96" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F96" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G96" t="s">
-        <v>413</v>
+        <v>455</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -4423,25 +4714,25 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B97" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C97" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="E97" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F97" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G97" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="H97">
         <v>2</v>
@@ -4449,25 +4740,25 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B98" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C98" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="E98" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F98" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -4475,25 +4766,25 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C99" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="E99" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F99" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G99" t="s">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="H99">
         <v>2</v>
@@ -4501,25 +4792,25 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B100" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="E100" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F100" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G100" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -4527,25 +4818,25 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B101" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C101" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D101" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="E101" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F101" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G101" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="H101">
         <v>2</v>
@@ -4553,25 +4844,25 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B102" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C102" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D102" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="E102" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F102" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G102" t="s">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -4579,25 +4870,25 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B103" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C103" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D103" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="E103" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F103" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="G103" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -4605,285 +4896,285 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B104" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C104" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E104" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F104" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G104" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B105" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D105" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E105" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F105" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G105" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B106" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C106" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D106" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="E106" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F106" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="G106" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B107" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C107" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="D107" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="E107" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F107" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G107" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
       <c r="H107">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C108" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D108" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="E108" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F108" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="G108" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C109" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D109" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="E109" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F109" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G109" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C110" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D110" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E110" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F110" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G110" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B111" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D111" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E111" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F111" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G111" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C112" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D112" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E112" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F112" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="G112" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B113" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D113" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E113" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F113" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G113" t="s">
-        <v>425</v>
+        <v>470</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B114" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E114" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F114" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G114" t="s">
-        <v>426</v>
+        <v>471</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -4891,25 +5182,25 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B115" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C115" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E115" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F115" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G115" t="s">
-        <v>427</v>
+        <v>472</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4917,129 +5208,129 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B116" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D116" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E116" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F116" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="G116" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B117" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C117" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="E117" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F117" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G117" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="H117">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C118" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D118" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E118" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F118" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G118" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B119" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C119" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D119" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E119" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F119" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G119" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B120" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C120" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D120" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="E120" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F120" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G120" t="s">
-        <v>431</v>
+        <v>476</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -5047,25 +5338,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C121" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D121" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="E121" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F121" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G121" t="s">
-        <v>432</v>
+        <v>475</v>
       </c>
       <c r="H121">
         <v>2</v>
@@ -5073,25 +5364,25 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B122" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C122" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D122" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E122" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F122" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G122" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -5099,25 +5390,25 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C123" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D123" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E123" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F123" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G123" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="H123">
         <v>2</v>
@@ -5125,493 +5416,493 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B124" t="s">
         <v>173</v>
       </c>
       <c r="C124" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D124" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="E124" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F124" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="G124" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="H124">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B125" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C125" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D125" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F125" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G125" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="H125">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B126" t="s">
         <v>174</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D126" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E126" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F126" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G126" t="s">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="H126">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="C127" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D127" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="E127" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F127" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G127" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="H127">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="C128" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D128" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E128" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F128" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G128" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B129" t="s">
         <v>175</v>
       </c>
       <c r="C129" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D129" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E129" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F129" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G129" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="H129">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B130" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C130" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D130" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E130" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F130" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G130" t="s">
-        <v>441</v>
+        <v>484</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B131" t="s">
         <v>176</v>
       </c>
       <c r="C131" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D131" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E131" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F131" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G131" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="H131">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B132" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C132" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D132" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E132" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F132" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G132" t="s">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B133" t="s">
         <v>177</v>
       </c>
       <c r="C133" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D133" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="E133" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F133" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G133" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="H133">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C134" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D134" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="E134" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F134" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G134" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B135" t="s">
         <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D135" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="E135" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F135" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G135" t="s">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C136" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D136" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="E136" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F136" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G136" t="s">
-        <v>447</v>
+        <v>489</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B137" t="s">
         <v>179</v>
       </c>
       <c r="C137" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D137" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E137" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F137" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G137" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C138" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D138" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="E138" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F138" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G138" t="s">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B139" t="s">
         <v>180</v>
       </c>
       <c r="C139" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D139" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="E139" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F139" t="s">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="G139" t="s">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="H139">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C140" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D140" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E140" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F140" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G140" t="s">
-        <v>451</v>
+        <v>493</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C141" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D141" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E141" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F141" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G141" t="s">
-        <v>428</v>
+        <v>494</v>
       </c>
       <c r="H141">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B142" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C142" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D142" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E142" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F142" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G142" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -5619,25 +5910,25 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C143" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D143" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="E143" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F143" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G143" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="H143">
         <v>2</v>
@@ -5645,25 +5936,25 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B144" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C144" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D144" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="E144" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F144" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G144" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -5671,25 +5962,25 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C145" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D145" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="E145" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F145" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G145" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="H145">
         <v>2</v>
@@ -5697,25 +5988,25 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B146" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C146" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D146" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="E146" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F146" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G146" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -5723,25 +6014,25 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B147" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C147" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D147" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="E147" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F147" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G147" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="H147">
         <v>2</v>
@@ -5749,25 +6040,25 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B148" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C148" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D148" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E148" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F148" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G148" t="s">
-        <v>457</v>
+        <v>499</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -5775,25 +6066,25 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C149" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D149" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="E149" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F149" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G149" t="s">
-        <v>458</v>
+        <v>500</v>
       </c>
       <c r="H149">
         <v>2</v>
@@ -5801,25 +6092,25 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B150" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C150" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D150" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="E150" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F150" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G150" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -5827,25 +6118,25 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C151" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D151" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="E151" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F151" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G151" t="s">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="H151">
         <v>2</v>
@@ -5853,25 +6144,25 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B152" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C152" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D152" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E152" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F152" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G152" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -5879,25 +6170,25 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B153" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C153" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D153" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E153" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F153" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G153" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="H153">
         <v>2</v>
@@ -5905,961 +6196,961 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B154" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C154" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D154" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E154" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F154" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G154" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="H154">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="B155" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C155" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D155" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E155" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F155" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G155" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="H155">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C156" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D156" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E156" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F156" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G156" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="H156">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C157" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D157" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="E157" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F157" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G157" t="s">
-        <v>464</v>
+        <v>508</v>
       </c>
       <c r="H157">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C158" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D158" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E158" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F158" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G158" t="s">
-        <v>465</v>
+        <v>509</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C159" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D159" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E159" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F159" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="G159" t="s">
-        <v>466</v>
+        <v>510</v>
       </c>
       <c r="H159">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C160" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D160" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E160" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F160" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G160" t="s">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="H160">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B161" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C161" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D161" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E161" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F161" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="G161" t="s">
-        <v>468</v>
+        <v>512</v>
       </c>
       <c r="H161">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B162" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C162" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D162" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E162" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F162" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="G162" t="s">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B163" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E163" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F163" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G163" t="s">
-        <v>470</v>
+        <v>514</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B164" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C164" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D164" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E164" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F164" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G164" t="s">
-        <v>471</v>
+        <v>515</v>
       </c>
       <c r="H164">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B165" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C165" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D165" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E165" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F165" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G165" t="s">
-        <v>472</v>
+        <v>516</v>
       </c>
       <c r="H165">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="B166" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C166" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="D166" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E166" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F166" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G166" t="s">
-        <v>473</v>
+        <v>517</v>
       </c>
       <c r="H166">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B167" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C167" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D167" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E167" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F167" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G167" t="s">
-        <v>474</v>
+        <v>518</v>
       </c>
       <c r="H167">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B168" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C168" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D168" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E168" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F168" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G168" t="s">
-        <v>475</v>
+        <v>518</v>
       </c>
       <c r="H168">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B169" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C169" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D169" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E169" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F169" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G169" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
       <c r="H169">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B170" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C170" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D170" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E170" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F170" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G170" t="s">
-        <v>477</v>
+        <v>519</v>
       </c>
       <c r="H170">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C171" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D171" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E171" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F171" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G171" t="s">
-        <v>478</v>
+        <v>520</v>
       </c>
       <c r="H171">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B172" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C172" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D172" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E172" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F172" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G172" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="H172">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C173" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D173" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E173" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F173" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G173" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="H173">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B174" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C174" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D174" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E174" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F174" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G174" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B175" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C175" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D175" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E175" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F175" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G175" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="H175">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B176" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C176" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D176" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E176" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F176" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G176" t="s">
-        <v>340</v>
+        <v>524</v>
       </c>
       <c r="H176">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B177" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C177" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D177" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E177" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F177" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G177" t="s">
-        <v>340</v>
+        <v>525</v>
       </c>
       <c r="H177">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B178" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C178" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D178" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E178" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F178" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G178" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="H178">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B179" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C179" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D179" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E179" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F179" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G179" t="s">
-        <v>484</v>
+        <v>526</v>
       </c>
       <c r="H179">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B180" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C180" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D180" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E180" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F180" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G180" t="s">
-        <v>485</v>
+        <v>527</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B181" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C181" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D181" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E181" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F181" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G181" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="H181">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B182" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C182" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D182" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E182" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F182" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G182" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="H182">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B183" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C183" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D183" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E183" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F183" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G183" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="H183">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B184" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C184" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D184" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E184" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F184" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G184" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B185" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C185" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D185" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E185" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F185" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G185" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="H185">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B186" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C186" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D186" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E186" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F186" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G186" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="H186">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B187" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C187" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D187" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="E187" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F187" t="s">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="G187" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="H187">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B188" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C188" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D188" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E188" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F188" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G188" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="H188">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="B189" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C189" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="D189" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E189" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F189" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G189" t="s">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="H189">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B190" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C190" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D190" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E190" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F190" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G190" t="s">
-        <v>494</v>
+        <v>537</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -6867,25 +7158,25 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B191" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C191" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D191" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E191" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F191" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G191" t="s">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="H191">
         <v>2</v>
@@ -6893,25 +7184,25 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="B192" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C192" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D192" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E192" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F192" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G192" t="s">
-        <v>495</v>
+        <v>539</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -6919,25 +7210,25 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="B193" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C193" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D193" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E193" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F193" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G193" t="s">
-        <v>496</v>
+        <v>540</v>
       </c>
       <c r="H193">
         <v>2</v>
@@ -6945,25 +7236,25 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B194" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C194" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D194" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E194" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F194" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G194" t="s">
-        <v>497</v>
+        <v>541</v>
       </c>
       <c r="H194">
         <v>1</v>
@@ -6971,25 +7262,25 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B195" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C195" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D195" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E195" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F195" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G195" t="s">
-        <v>498</v>
+        <v>542</v>
       </c>
       <c r="H195">
         <v>2</v>
@@ -6997,25 +7288,25 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B196" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C196" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D196" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E196" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F196" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G196" t="s">
-        <v>499</v>
+        <v>543</v>
       </c>
       <c r="H196">
         <v>1</v>
@@ -7023,25 +7314,25 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B197" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D197" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E197" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F197" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G197" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="H197">
         <v>2</v>
@@ -7049,25 +7340,25 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B198" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D198" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E198" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F198" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G198" t="s">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="H198">
         <v>1</v>
@@ -7075,25 +7366,25 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B199" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C199" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D199" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E199" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F199" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G199" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="H199">
         <v>2</v>
@@ -7101,25 +7392,25 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B200" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C200" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D200" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E200" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F200" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G200" t="s">
-        <v>502</v>
+        <v>547</v>
       </c>
       <c r="H200">
         <v>1</v>
@@ -7127,25 +7418,25 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B201" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C201" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D201" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E201" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F201" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G201" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="H201">
         <v>2</v>
@@ -7153,25 +7444,25 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B202" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C202" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D202" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E202" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F202" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G202" t="s">
-        <v>504</v>
+        <v>548</v>
       </c>
       <c r="H202">
         <v>1</v>
@@ -7179,25 +7470,25 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B203" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C203" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D203" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E203" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F203" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G203" t="s">
-        <v>505</v>
+        <v>549</v>
       </c>
       <c r="H203">
         <v>2</v>
@@ -7205,25 +7496,25 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B204" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C204" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D204" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F204" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G204" t="s">
-        <v>506</v>
+        <v>550</v>
       </c>
       <c r="H204">
         <v>1</v>
@@ -7231,25 +7522,25 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B205" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C205" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D205" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F205" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G205" t="s">
-        <v>507</v>
+        <v>551</v>
       </c>
       <c r="H205">
         <v>2</v>
@@ -7257,25 +7548,25 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B206" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C206" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D206" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E206" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F206" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G206" t="s">
-        <v>508</v>
+        <v>552</v>
       </c>
       <c r="H206">
         <v>1</v>
@@ -7283,25 +7574,25 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B207" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C207" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D207" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E207" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F207" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G207" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="H207">
         <v>2</v>
@@ -7309,25 +7600,25 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C208" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D208" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E208" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F208" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G208" t="s">
-        <v>510</v>
+        <v>553</v>
       </c>
       <c r="H208">
         <v>1</v>
@@ -7335,25 +7626,25 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C209" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D209" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E209" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F209" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G209" t="s">
-        <v>511</v>
+        <v>554</v>
       </c>
       <c r="H209">
         <v>2</v>
@@ -7361,25 +7652,25 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B210" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C210" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D210" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E210" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F210" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="H210">
         <v>1</v>
@@ -7387,25 +7678,25 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B211" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C211" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D211" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E211" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F211" t="s">
-        <v>330</v>
+        <v>364</v>
       </c>
       <c r="G211" t="s">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="H211">
         <v>2</v>
@@ -7413,25 +7704,25 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C212" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D212" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E212" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F212" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G212" t="s">
-        <v>513</v>
+        <v>556</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -7439,25 +7730,25 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C213" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D213" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E213" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F213" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="H213">
         <v>2</v>
@@ -7465,25 +7756,25 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C214" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="D214" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E214" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="F214" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="G214" t="s">
-        <v>515</v>
+        <v>558</v>
       </c>
       <c r="H214">
         <v>1</v>
@@ -7491,27 +7782,1639 @@
     </row>
     <row r="215" spans="1:8">
       <c r="A215" t="s">
+        <v>94</v>
+      </c>
+      <c r="B215" t="s">
+        <v>210</v>
+      </c>
+      <c r="C215" t="s">
+        <v>242</v>
+      </c>
+      <c r="D215" t="s">
+        <v>331</v>
+      </c>
+      <c r="E215" t="s">
+        <v>364</v>
+      </c>
+      <c r="F215" t="s">
+        <v>366</v>
+      </c>
+      <c r="G215" t="s">
+        <v>559</v>
+      </c>
+      <c r="H215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>95</v>
+      </c>
+      <c r="B216" t="s">
+        <v>211</v>
+      </c>
+      <c r="C216" t="s">
+        <v>242</v>
+      </c>
+      <c r="D216" t="s">
+        <v>332</v>
+      </c>
+      <c r="E216" t="s">
+        <v>364</v>
+      </c>
+      <c r="F216" t="s">
+        <v>364</v>
+      </c>
+      <c r="G216" t="s">
+        <v>560</v>
+      </c>
+      <c r="H216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>95</v>
+      </c>
+      <c r="B217" t="s">
+        <v>211</v>
+      </c>
+      <c r="C217" t="s">
+        <v>242</v>
+      </c>
+      <c r="D217" t="s">
+        <v>332</v>
+      </c>
+      <c r="E217" t="s">
+        <v>364</v>
+      </c>
+      <c r="F217" t="s">
+        <v>366</v>
+      </c>
+      <c r="G217" t="s">
+        <v>560</v>
+      </c>
+      <c r="H217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>96</v>
+      </c>
+      <c r="B218" t="s">
+        <v>212</v>
+      </c>
+      <c r="C218" t="s">
+        <v>242</v>
+      </c>
+      <c r="D218" t="s">
+        <v>333</v>
+      </c>
+      <c r="E218" t="s">
+        <v>364</v>
+      </c>
+      <c r="F218" t="s">
+        <v>364</v>
+      </c>
+      <c r="G218" t="s">
+        <v>561</v>
+      </c>
+      <c r="H218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" t="s">
+        <v>96</v>
+      </c>
+      <c r="B219" t="s">
+        <v>212</v>
+      </c>
+      <c r="C219" t="s">
+        <v>242</v>
+      </c>
+      <c r="D219" t="s">
+        <v>333</v>
+      </c>
+      <c r="E219" t="s">
+        <v>364</v>
+      </c>
+      <c r="F219" t="s">
+        <v>366</v>
+      </c>
+      <c r="G219" t="s">
+        <v>562</v>
+      </c>
+      <c r="H219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" t="s">
+        <v>97</v>
+      </c>
+      <c r="B220" t="s">
+        <v>213</v>
+      </c>
+      <c r="C220" t="s">
+        <v>242</v>
+      </c>
+      <c r="D220" t="s">
+        <v>334</v>
+      </c>
+      <c r="E220" t="s">
+        <v>364</v>
+      </c>
+      <c r="F220" t="s">
+        <v>364</v>
+      </c>
+      <c r="G220" t="s">
+        <v>563</v>
+      </c>
+      <c r="H220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" t="s">
+        <v>97</v>
+      </c>
+      <c r="B221" t="s">
+        <v>213</v>
+      </c>
+      <c r="C221" t="s">
+        <v>242</v>
+      </c>
+      <c r="D221" t="s">
+        <v>334</v>
+      </c>
+      <c r="E221" t="s">
+        <v>364</v>
+      </c>
+      <c r="F221" t="s">
+        <v>366</v>
+      </c>
+      <c r="G221" t="s">
+        <v>564</v>
+      </c>
+      <c r="H221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" t="s">
+        <v>98</v>
+      </c>
+      <c r="B222" t="s">
+        <v>214</v>
+      </c>
+      <c r="C222" t="s">
+        <v>242</v>
+      </c>
+      <c r="D222" t="s">
+        <v>335</v>
+      </c>
+      <c r="E222" t="s">
+        <v>364</v>
+      </c>
+      <c r="F222" t="s">
+        <v>364</v>
+      </c>
+      <c r="G222" t="s">
+        <v>565</v>
+      </c>
+      <c r="H222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" t="s">
+        <v>98</v>
+      </c>
+      <c r="B223" t="s">
+        <v>214</v>
+      </c>
+      <c r="C223" t="s">
+        <v>242</v>
+      </c>
+      <c r="D223" t="s">
+        <v>335</v>
+      </c>
+      <c r="E223" t="s">
+        <v>364</v>
+      </c>
+      <c r="F223" t="s">
+        <v>366</v>
+      </c>
+      <c r="G223" t="s">
+        <v>566</v>
+      </c>
+      <c r="H223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" t="s">
+        <v>99</v>
+      </c>
+      <c r="B224" t="s">
+        <v>215</v>
+      </c>
+      <c r="C224" t="s">
+        <v>242</v>
+      </c>
+      <c r="D224" t="s">
+        <v>336</v>
+      </c>
+      <c r="E224" t="s">
+        <v>364</v>
+      </c>
+      <c r="F224" t="s">
+        <v>364</v>
+      </c>
+      <c r="G224" t="s">
+        <v>567</v>
+      </c>
+      <c r="H224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" t="s">
+        <v>99</v>
+      </c>
+      <c r="B225" t="s">
+        <v>215</v>
+      </c>
+      <c r="C225" t="s">
+        <v>242</v>
+      </c>
+      <c r="D225" t="s">
+        <v>336</v>
+      </c>
+      <c r="E225" t="s">
+        <v>364</v>
+      </c>
+      <c r="F225" t="s">
+        <v>366</v>
+      </c>
+      <c r="G225" t="s">
+        <v>568</v>
+      </c>
+      <c r="H225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" t="s">
+        <v>100</v>
+      </c>
+      <c r="B226" t="s">
+        <v>216</v>
+      </c>
+      <c r="C226" t="s">
+        <v>242</v>
+      </c>
+      <c r="D226" t="s">
+        <v>337</v>
+      </c>
+      <c r="E226" t="s">
+        <v>364</v>
+      </c>
+      <c r="F226" t="s">
+        <v>364</v>
+      </c>
+      <c r="G226" t="s">
+        <v>569</v>
+      </c>
+      <c r="H226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" t="s">
+        <v>100</v>
+      </c>
+      <c r="B227" t="s">
+        <v>216</v>
+      </c>
+      <c r="C227" t="s">
+        <v>242</v>
+      </c>
+      <c r="D227" t="s">
+        <v>337</v>
+      </c>
+      <c r="E227" t="s">
+        <v>364</v>
+      </c>
+      <c r="F227" t="s">
+        <v>366</v>
+      </c>
+      <c r="G227" t="s">
+        <v>570</v>
+      </c>
+      <c r="H227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" t="s">
+        <v>101</v>
+      </c>
+      <c r="B228" t="s">
+        <v>217</v>
+      </c>
+      <c r="C228" t="s">
+        <v>242</v>
+      </c>
+      <c r="D228" t="s">
+        <v>338</v>
+      </c>
+      <c r="E228" t="s">
+        <v>364</v>
+      </c>
+      <c r="F228" t="s">
+        <v>364</v>
+      </c>
+      <c r="G228" t="s">
+        <v>571</v>
+      </c>
+      <c r="H228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" t="s">
+        <v>101</v>
+      </c>
+      <c r="B229" t="s">
+        <v>217</v>
+      </c>
+      <c r="C229" t="s">
+        <v>242</v>
+      </c>
+      <c r="D229" t="s">
+        <v>338</v>
+      </c>
+      <c r="E229" t="s">
+        <v>364</v>
+      </c>
+      <c r="F229" t="s">
+        <v>366</v>
+      </c>
+      <c r="G229" t="s">
+        <v>572</v>
+      </c>
+      <c r="H229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" t="s">
+        <v>102</v>
+      </c>
+      <c r="B230" t="s">
+        <v>218</v>
+      </c>
+      <c r="C230" t="s">
+        <v>242</v>
+      </c>
+      <c r="D230" t="s">
+        <v>339</v>
+      </c>
+      <c r="E230" t="s">
+        <v>364</v>
+      </c>
+      <c r="F230" t="s">
+        <v>364</v>
+      </c>
+      <c r="G230" t="s">
+        <v>573</v>
+      </c>
+      <c r="H230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" t="s">
+        <v>102</v>
+      </c>
+      <c r="B231" t="s">
+        <v>218</v>
+      </c>
+      <c r="C231" t="s">
+        <v>242</v>
+      </c>
+      <c r="D231" t="s">
+        <v>339</v>
+      </c>
+      <c r="E231" t="s">
+        <v>364</v>
+      </c>
+      <c r="F231" t="s">
+        <v>366</v>
+      </c>
+      <c r="G231" t="s">
+        <v>574</v>
+      </c>
+      <c r="H231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" t="s">
+        <v>103</v>
+      </c>
+      <c r="B232" t="s">
+        <v>219</v>
+      </c>
+      <c r="C232" t="s">
+        <v>242</v>
+      </c>
+      <c r="D232" t="s">
+        <v>340</v>
+      </c>
+      <c r="E232" t="s">
+        <v>364</v>
+      </c>
+      <c r="F232" t="s">
+        <v>364</v>
+      </c>
+      <c r="G232" t="s">
+        <v>575</v>
+      </c>
+      <c r="H232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" t="s">
+        <v>103</v>
+      </c>
+      <c r="B233" t="s">
+        <v>219</v>
+      </c>
+      <c r="C233" t="s">
+        <v>242</v>
+      </c>
+      <c r="D233" t="s">
+        <v>340</v>
+      </c>
+      <c r="E233" t="s">
+        <v>364</v>
+      </c>
+      <c r="F233" t="s">
+        <v>366</v>
+      </c>
+      <c r="G233" t="s">
+        <v>576</v>
+      </c>
+      <c r="H233">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" t="s">
+        <v>104</v>
+      </c>
+      <c r="B234" t="s">
+        <v>220</v>
+      </c>
+      <c r="C234" t="s">
+        <v>242</v>
+      </c>
+      <c r="D234" t="s">
+        <v>341</v>
+      </c>
+      <c r="E234" t="s">
+        <v>364</v>
+      </c>
+      <c r="F234" t="s">
+        <v>364</v>
+      </c>
+      <c r="G234" t="s">
+        <v>577</v>
+      </c>
+      <c r="H234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" t="s">
+        <v>104</v>
+      </c>
+      <c r="B235" t="s">
+        <v>220</v>
+      </c>
+      <c r="C235" t="s">
+        <v>242</v>
+      </c>
+      <c r="D235" t="s">
+        <v>341</v>
+      </c>
+      <c r="E235" t="s">
+        <v>364</v>
+      </c>
+      <c r="F235" t="s">
+        <v>366</v>
+      </c>
+      <c r="G235" t="s">
+        <v>578</v>
+      </c>
+      <c r="H235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" t="s">
+        <v>105</v>
+      </c>
+      <c r="B236" t="s">
+        <v>221</v>
+      </c>
+      <c r="C236" t="s">
+        <v>242</v>
+      </c>
+      <c r="D236" t="s">
+        <v>342</v>
+      </c>
+      <c r="E236" t="s">
+        <v>364</v>
+      </c>
+      <c r="F236" t="s">
+        <v>364</v>
+      </c>
+      <c r="G236" t="s">
+        <v>379</v>
+      </c>
+      <c r="H236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" t="s">
+        <v>105</v>
+      </c>
+      <c r="B237" t="s">
+        <v>221</v>
+      </c>
+      <c r="C237" t="s">
+        <v>242</v>
+      </c>
+      <c r="D237" t="s">
+        <v>342</v>
+      </c>
+      <c r="E237" t="s">
+        <v>364</v>
+      </c>
+      <c r="F237" t="s">
+        <v>366</v>
+      </c>
+      <c r="G237" t="s">
+        <v>379</v>
+      </c>
+      <c r="H237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" t="s">
+        <v>106</v>
+      </c>
+      <c r="B238" t="s">
+        <v>222</v>
+      </c>
+      <c r="C238" t="s">
+        <v>242</v>
+      </c>
+      <c r="D238" t="s">
+        <v>343</v>
+      </c>
+      <c r="E238" t="s">
+        <v>364</v>
+      </c>
+      <c r="F238" t="s">
+        <v>364</v>
+      </c>
+      <c r="G238" t="s">
+        <v>579</v>
+      </c>
+      <c r="H238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" t="s">
+        <v>106</v>
+      </c>
+      <c r="B239" t="s">
+        <v>222</v>
+      </c>
+      <c r="C239" t="s">
+        <v>242</v>
+      </c>
+      <c r="D239" t="s">
+        <v>343</v>
+      </c>
+      <c r="E239" t="s">
+        <v>364</v>
+      </c>
+      <c r="F239" t="s">
+        <v>366</v>
+      </c>
+      <c r="G239" t="s">
+        <v>580</v>
+      </c>
+      <c r="H239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" t="s">
+        <v>107</v>
+      </c>
+      <c r="B240" t="s">
+        <v>223</v>
+      </c>
+      <c r="C240" t="s">
+        <v>242</v>
+      </c>
+      <c r="D240" t="s">
+        <v>344</v>
+      </c>
+      <c r="E240" t="s">
+        <v>364</v>
+      </c>
+      <c r="F240" t="s">
+        <v>366</v>
+      </c>
+      <c r="G240" t="s">
+        <v>581</v>
+      </c>
+      <c r="H240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" t="s">
+        <v>107</v>
+      </c>
+      <c r="B241" t="s">
+        <v>223</v>
+      </c>
+      <c r="C241" t="s">
+        <v>242</v>
+      </c>
+      <c r="D241" t="s">
+        <v>344</v>
+      </c>
+      <c r="E241" t="s">
+        <v>364</v>
+      </c>
+      <c r="F241" t="s">
+        <v>364</v>
+      </c>
+      <c r="G241" t="s">
+        <v>581</v>
+      </c>
+      <c r="H241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" t="s">
+        <v>108</v>
+      </c>
+      <c r="B242" t="s">
+        <v>224</v>
+      </c>
+      <c r="C242" t="s">
+        <v>242</v>
+      </c>
+      <c r="D242" t="s">
+        <v>345</v>
+      </c>
+      <c r="E242" t="s">
+        <v>364</v>
+      </c>
+      <c r="F242" t="s">
+        <v>364</v>
+      </c>
+      <c r="G242" t="s">
+        <v>582</v>
+      </c>
+      <c r="H242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" t="s">
+        <v>108</v>
+      </c>
+      <c r="B243" t="s">
+        <v>224</v>
+      </c>
+      <c r="C243" t="s">
+        <v>242</v>
+      </c>
+      <c r="D243" t="s">
+        <v>345</v>
+      </c>
+      <c r="E243" t="s">
+        <v>364</v>
+      </c>
+      <c r="F243" t="s">
+        <v>366</v>
+      </c>
+      <c r="G243" t="s">
+        <v>583</v>
+      </c>
+      <c r="H243">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" t="s">
+        <v>109</v>
+      </c>
+      <c r="B244" t="s">
+        <v>225</v>
+      </c>
+      <c r="C244" t="s">
+        <v>242</v>
+      </c>
+      <c r="D244" t="s">
+        <v>346</v>
+      </c>
+      <c r="E244" t="s">
+        <v>364</v>
+      </c>
+      <c r="F244" t="s">
+        <v>364</v>
+      </c>
+      <c r="G244" t="s">
+        <v>584</v>
+      </c>
+      <c r="H244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" t="s">
+        <v>109</v>
+      </c>
+      <c r="B245" t="s">
+        <v>225</v>
+      </c>
+      <c r="C245" t="s">
+        <v>242</v>
+      </c>
+      <c r="D245" t="s">
+        <v>346</v>
+      </c>
+      <c r="E245" t="s">
+        <v>364</v>
+      </c>
+      <c r="F245" t="s">
+        <v>366</v>
+      </c>
+      <c r="G245" t="s">
+        <v>585</v>
+      </c>
+      <c r="H245">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" t="s">
+        <v>110</v>
+      </c>
+      <c r="B246" t="s">
+        <v>226</v>
+      </c>
+      <c r="C246" t="s">
+        <v>242</v>
+      </c>
+      <c r="D246" t="s">
+        <v>347</v>
+      </c>
+      <c r="E246" t="s">
+        <v>364</v>
+      </c>
+      <c r="F246" t="s">
+        <v>364</v>
+      </c>
+      <c r="G246" t="s">
+        <v>586</v>
+      </c>
+      <c r="H246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" t="s">
+        <v>110</v>
+      </c>
+      <c r="B247" t="s">
+        <v>226</v>
+      </c>
+      <c r="C247" t="s">
+        <v>242</v>
+      </c>
+      <c r="D247" t="s">
+        <v>347</v>
+      </c>
+      <c r="E247" t="s">
+        <v>364</v>
+      </c>
+      <c r="F247" t="s">
+        <v>366</v>
+      </c>
+      <c r="G247" t="s">
+        <v>587</v>
+      </c>
+      <c r="H247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" t="s">
+        <v>111</v>
+      </c>
+      <c r="B248" t="s">
+        <v>227</v>
+      </c>
+      <c r="C248" t="s">
+        <v>242</v>
+      </c>
+      <c r="D248" t="s">
+        <v>348</v>
+      </c>
+      <c r="E248" t="s">
+        <v>364</v>
+      </c>
+      <c r="F248" t="s">
+        <v>364</v>
+      </c>
+      <c r="G248" t="s">
+        <v>588</v>
+      </c>
+      <c r="H248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" t="s">
+        <v>111</v>
+      </c>
+      <c r="B249" t="s">
+        <v>227</v>
+      </c>
+      <c r="C249" t="s">
+        <v>242</v>
+      </c>
+      <c r="D249" t="s">
+        <v>348</v>
+      </c>
+      <c r="E249" t="s">
+        <v>364</v>
+      </c>
+      <c r="F249" t="s">
+        <v>366</v>
+      </c>
+      <c r="G249" t="s">
+        <v>589</v>
+      </c>
+      <c r="H249">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" t="s">
+        <v>112</v>
+      </c>
+      <c r="B250" t="s">
+        <v>228</v>
+      </c>
+      <c r="C250" t="s">
+        <v>242</v>
+      </c>
+      <c r="D250" t="s">
+        <v>349</v>
+      </c>
+      <c r="E250" t="s">
+        <v>364</v>
+      </c>
+      <c r="F250" t="s">
+        <v>364</v>
+      </c>
+      <c r="G250" t="s">
+        <v>590</v>
+      </c>
+      <c r="H250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" t="s">
+        <v>112</v>
+      </c>
+      <c r="B251" t="s">
+        <v>228</v>
+      </c>
+      <c r="C251" t="s">
+        <v>242</v>
+      </c>
+      <c r="D251" t="s">
+        <v>349</v>
+      </c>
+      <c r="E251" t="s">
+        <v>364</v>
+      </c>
+      <c r="F251" t="s">
+        <v>366</v>
+      </c>
+      <c r="G251" t="s">
+        <v>590</v>
+      </c>
+      <c r="H251">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" t="s">
         <v>113</v>
       </c>
-      <c r="B215" t="s">
-        <v>218</v>
-      </c>
-      <c r="C215" t="s">
-        <v>219</v>
-      </c>
-      <c r="D215" t="s">
-        <v>327</v>
-      </c>
-      <c r="E215" t="s">
-        <v>328</v>
-      </c>
-      <c r="F215" t="s">
-        <v>330</v>
-      </c>
-      <c r="G215" t="s">
-        <v>516</v>
-      </c>
-      <c r="H215">
+      <c r="B252" t="s">
+        <v>229</v>
+      </c>
+      <c r="C252" t="s">
+        <v>242</v>
+      </c>
+      <c r="D252" t="s">
+        <v>350</v>
+      </c>
+      <c r="E252" t="s">
+        <v>364</v>
+      </c>
+      <c r="F252" t="s">
+        <v>364</v>
+      </c>
+      <c r="G252" t="s">
+        <v>591</v>
+      </c>
+      <c r="H252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" t="s">
+        <v>113</v>
+      </c>
+      <c r="B253" t="s">
+        <v>229</v>
+      </c>
+      <c r="C253" t="s">
+        <v>242</v>
+      </c>
+      <c r="D253" t="s">
+        <v>350</v>
+      </c>
+      <c r="E253" t="s">
+        <v>364</v>
+      </c>
+      <c r="F253" t="s">
+        <v>366</v>
+      </c>
+      <c r="G253" t="s">
+        <v>592</v>
+      </c>
+      <c r="H253">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" t="s">
+        <v>114</v>
+      </c>
+      <c r="B254" t="s">
+        <v>230</v>
+      </c>
+      <c r="C254" t="s">
+        <v>242</v>
+      </c>
+      <c r="D254" t="s">
+        <v>351</v>
+      </c>
+      <c r="E254" t="s">
+        <v>364</v>
+      </c>
+      <c r="F254" t="s">
+        <v>364</v>
+      </c>
+      <c r="G254" t="s">
+        <v>593</v>
+      </c>
+      <c r="H254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" t="s">
+        <v>114</v>
+      </c>
+      <c r="B255" t="s">
+        <v>230</v>
+      </c>
+      <c r="C255" t="s">
+        <v>242</v>
+      </c>
+      <c r="D255" t="s">
+        <v>351</v>
+      </c>
+      <c r="E255" t="s">
+        <v>364</v>
+      </c>
+      <c r="F255" t="s">
+        <v>366</v>
+      </c>
+      <c r="G255" t="s">
+        <v>594</v>
+      </c>
+      <c r="H255">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" t="s">
+        <v>115</v>
+      </c>
+      <c r="B256" t="s">
+        <v>231</v>
+      </c>
+      <c r="C256" t="s">
+        <v>242</v>
+      </c>
+      <c r="D256" t="s">
+        <v>352</v>
+      </c>
+      <c r="E256" t="s">
+        <v>364</v>
+      </c>
+      <c r="F256" t="s">
+        <v>366</v>
+      </c>
+      <c r="G256" t="s">
+        <v>595</v>
+      </c>
+      <c r="H256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" t="s">
+        <v>115</v>
+      </c>
+      <c r="B257" t="s">
+        <v>231</v>
+      </c>
+      <c r="C257" t="s">
+        <v>242</v>
+      </c>
+      <c r="D257" t="s">
+        <v>352</v>
+      </c>
+      <c r="E257" t="s">
+        <v>364</v>
+      </c>
+      <c r="F257" t="s">
+        <v>364</v>
+      </c>
+      <c r="G257" t="s">
+        <v>595</v>
+      </c>
+      <c r="H257">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" t="s">
+        <v>116</v>
+      </c>
+      <c r="B258" t="s">
+        <v>232</v>
+      </c>
+      <c r="C258" t="s">
+        <v>242</v>
+      </c>
+      <c r="D258" t="s">
+        <v>353</v>
+      </c>
+      <c r="E258" t="s">
+        <v>364</v>
+      </c>
+      <c r="F258" t="s">
+        <v>364</v>
+      </c>
+      <c r="G258" t="s">
+        <v>596</v>
+      </c>
+      <c r="H258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" t="s">
+        <v>116</v>
+      </c>
+      <c r="B259" t="s">
+        <v>232</v>
+      </c>
+      <c r="C259" t="s">
+        <v>242</v>
+      </c>
+      <c r="D259" t="s">
+        <v>353</v>
+      </c>
+      <c r="E259" t="s">
+        <v>364</v>
+      </c>
+      <c r="F259" t="s">
+        <v>366</v>
+      </c>
+      <c r="G259" t="s">
+        <v>596</v>
+      </c>
+      <c r="H259">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" t="s">
+        <v>117</v>
+      </c>
+      <c r="B260" t="s">
+        <v>233</v>
+      </c>
+      <c r="C260" t="s">
+        <v>242</v>
+      </c>
+      <c r="D260" t="s">
+        <v>354</v>
+      </c>
+      <c r="E260" t="s">
+        <v>364</v>
+      </c>
+      <c r="F260" t="s">
+        <v>364</v>
+      </c>
+      <c r="G260" t="s">
+        <v>597</v>
+      </c>
+      <c r="H260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" t="s">
+        <v>117</v>
+      </c>
+      <c r="B261" t="s">
+        <v>233</v>
+      </c>
+      <c r="C261" t="s">
+        <v>242</v>
+      </c>
+      <c r="D261" t="s">
+        <v>354</v>
+      </c>
+      <c r="E261" t="s">
+        <v>364</v>
+      </c>
+      <c r="F261" t="s">
+        <v>366</v>
+      </c>
+      <c r="G261" t="s">
+        <v>598</v>
+      </c>
+      <c r="H261">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" t="s">
+        <v>118</v>
+      </c>
+      <c r="B262" t="s">
+        <v>234</v>
+      </c>
+      <c r="C262" t="s">
+        <v>242</v>
+      </c>
+      <c r="D262" t="s">
+        <v>355</v>
+      </c>
+      <c r="E262" t="s">
+        <v>364</v>
+      </c>
+      <c r="F262" t="s">
+        <v>364</v>
+      </c>
+      <c r="G262" t="s">
+        <v>599</v>
+      </c>
+      <c r="H262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" t="s">
+        <v>118</v>
+      </c>
+      <c r="B263" t="s">
+        <v>234</v>
+      </c>
+      <c r="C263" t="s">
+        <v>242</v>
+      </c>
+      <c r="D263" t="s">
+        <v>355</v>
+      </c>
+      <c r="E263" t="s">
+        <v>364</v>
+      </c>
+      <c r="F263" t="s">
+        <v>366</v>
+      </c>
+      <c r="G263" t="s">
+        <v>600</v>
+      </c>
+      <c r="H263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" t="s">
+        <v>119</v>
+      </c>
+      <c r="B264" t="s">
+        <v>235</v>
+      </c>
+      <c r="C264" t="s">
+        <v>242</v>
+      </c>
+      <c r="D264" t="s">
+        <v>356</v>
+      </c>
+      <c r="E264" t="s">
+        <v>364</v>
+      </c>
+      <c r="F264" t="s">
+        <v>364</v>
+      </c>
+      <c r="G264" t="s">
+        <v>601</v>
+      </c>
+      <c r="H264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" t="s">
+        <v>119</v>
+      </c>
+      <c r="B265" t="s">
+        <v>235</v>
+      </c>
+      <c r="C265" t="s">
+        <v>242</v>
+      </c>
+      <c r="D265" t="s">
+        <v>356</v>
+      </c>
+      <c r="E265" t="s">
+        <v>364</v>
+      </c>
+      <c r="F265" t="s">
+        <v>366</v>
+      </c>
+      <c r="G265" t="s">
+        <v>602</v>
+      </c>
+      <c r="H265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" t="s">
+        <v>120</v>
+      </c>
+      <c r="B266" t="s">
+        <v>236</v>
+      </c>
+      <c r="C266" t="s">
+        <v>242</v>
+      </c>
+      <c r="D266" t="s">
+        <v>357</v>
+      </c>
+      <c r="E266" t="s">
+        <v>364</v>
+      </c>
+      <c r="F266" t="s">
+        <v>364</v>
+      </c>
+      <c r="G266" t="s">
+        <v>603</v>
+      </c>
+      <c r="H266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" t="s">
+        <v>120</v>
+      </c>
+      <c r="B267" t="s">
+        <v>236</v>
+      </c>
+      <c r="C267" t="s">
+        <v>242</v>
+      </c>
+      <c r="D267" t="s">
+        <v>357</v>
+      </c>
+      <c r="E267" t="s">
+        <v>364</v>
+      </c>
+      <c r="F267" t="s">
+        <v>366</v>
+      </c>
+      <c r="G267" t="s">
+        <v>604</v>
+      </c>
+      <c r="H267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" t="s">
+        <v>121</v>
+      </c>
+      <c r="B268" t="s">
+        <v>237</v>
+      </c>
+      <c r="C268" t="s">
+        <v>242</v>
+      </c>
+      <c r="D268" t="s">
+        <v>358</v>
+      </c>
+      <c r="E268" t="s">
+        <v>364</v>
+      </c>
+      <c r="F268" t="s">
+        <v>364</v>
+      </c>
+      <c r="G268" t="s">
+        <v>605</v>
+      </c>
+      <c r="H268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" t="s">
+        <v>121</v>
+      </c>
+      <c r="B269" t="s">
+        <v>237</v>
+      </c>
+      <c r="C269" t="s">
+        <v>242</v>
+      </c>
+      <c r="D269" t="s">
+        <v>358</v>
+      </c>
+      <c r="E269" t="s">
+        <v>364</v>
+      </c>
+      <c r="F269" t="s">
+        <v>366</v>
+      </c>
+      <c r="G269" t="s">
+        <v>606</v>
+      </c>
+      <c r="H269">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" t="s">
+        <v>122</v>
+      </c>
+      <c r="B270" t="s">
+        <v>238</v>
+      </c>
+      <c r="C270" t="s">
+        <v>242</v>
+      </c>
+      <c r="D270" t="s">
+        <v>359</v>
+      </c>
+      <c r="E270" t="s">
+        <v>364</v>
+      </c>
+      <c r="F270" t="s">
+        <v>364</v>
+      </c>
+      <c r="G270" t="s">
+        <v>607</v>
+      </c>
+      <c r="H270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" t="s">
+        <v>122</v>
+      </c>
+      <c r="B271" t="s">
+        <v>238</v>
+      </c>
+      <c r="C271" t="s">
+        <v>242</v>
+      </c>
+      <c r="D271" t="s">
+        <v>359</v>
+      </c>
+      <c r="E271" t="s">
+        <v>364</v>
+      </c>
+      <c r="F271" t="s">
+        <v>366</v>
+      </c>
+      <c r="G271" t="s">
+        <v>608</v>
+      </c>
+      <c r="H271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" t="s">
+        <v>123</v>
+      </c>
+      <c r="B272" t="s">
+        <v>239</v>
+      </c>
+      <c r="C272" t="s">
+        <v>242</v>
+      </c>
+      <c r="D272" t="s">
+        <v>360</v>
+      </c>
+      <c r="E272" t="s">
+        <v>364</v>
+      </c>
+      <c r="F272" t="s">
+        <v>364</v>
+      </c>
+      <c r="G272" t="s">
+        <v>609</v>
+      </c>
+      <c r="H272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" t="s">
+        <v>123</v>
+      </c>
+      <c r="B273" t="s">
+        <v>239</v>
+      </c>
+      <c r="C273" t="s">
+        <v>242</v>
+      </c>
+      <c r="D273" t="s">
+        <v>360</v>
+      </c>
+      <c r="E273" t="s">
+        <v>364</v>
+      </c>
+      <c r="F273" t="s">
+        <v>366</v>
+      </c>
+      <c r="G273" t="s">
+        <v>609</v>
+      </c>
+      <c r="H273">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" t="s">
+        <v>124</v>
+      </c>
+      <c r="B274" t="s">
+        <v>240</v>
+      </c>
+      <c r="C274" t="s">
+        <v>242</v>
+      </c>
+      <c r="D274" t="s">
+        <v>361</v>
+      </c>
+      <c r="E274" t="s">
+        <v>364</v>
+      </c>
+      <c r="F274" t="s">
+        <v>364</v>
+      </c>
+      <c r="G274" t="s">
+        <v>610</v>
+      </c>
+      <c r="H274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" t="s">
+        <v>124</v>
+      </c>
+      <c r="B275" t="s">
+        <v>240</v>
+      </c>
+      <c r="C275" t="s">
+        <v>242</v>
+      </c>
+      <c r="D275" t="s">
+        <v>361</v>
+      </c>
+      <c r="E275" t="s">
+        <v>364</v>
+      </c>
+      <c r="F275" t="s">
+        <v>366</v>
+      </c>
+      <c r="G275" t="s">
+        <v>611</v>
+      </c>
+      <c r="H275">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" t="s">
+        <v>125</v>
+      </c>
+      <c r="B276" t="s">
+        <v>241</v>
+      </c>
+      <c r="C276" t="s">
+        <v>242</v>
+      </c>
+      <c r="D276" t="s">
+        <v>362</v>
+      </c>
+      <c r="E276" t="s">
+        <v>364</v>
+      </c>
+      <c r="F276" t="s">
+        <v>364</v>
+      </c>
+      <c r="G276" t="s">
+        <v>612</v>
+      </c>
+      <c r="H276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" t="s">
+        <v>125</v>
+      </c>
+      <c r="B277" t="s">
+        <v>241</v>
+      </c>
+      <c r="C277" t="s">
+        <v>242</v>
+      </c>
+      <c r="D277" t="s">
+        <v>362</v>
+      </c>
+      <c r="E277" t="s">
+        <v>364</v>
+      </c>
+      <c r="F277" t="s">
+        <v>366</v>
+      </c>
+      <c r="G277" t="s">
+        <v>613</v>
+      </c>
+      <c r="H277">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -139,12 +139,12 @@
     <t>7204070009001200 - UB - 1</t>
   </si>
   <si>
+    <t>7204070011000301 - UB - 3</t>
+  </si>
+  <si>
     <t>7204070012000800 - UB - 1</t>
   </si>
   <si>
-    <t>7204070011000301 - UB - 3</t>
-  </si>
-  <si>
     <t>7205090009000301 - UB - 1</t>
   </si>
   <si>
@@ -490,12 +490,12 @@
     <t>PNM MODAL MIKRO</t>
   </si>
   <si>
+    <t>FIF, PT</t>
+  </si>
+  <si>
     <t>Balindo Manunggal Bersama, PT</t>
   </si>
   <si>
-    <t>FIF, PT</t>
-  </si>
-  <si>
     <t>SEKOLAH POLISI NEGARA</t>
   </si>
   <si>
@@ -850,12 +850,12 @@
     <t>ulamposo@gmail.com</t>
   </si>
   <si>
+    <t>dewiputrihilika90@gmail.com</t>
+  </si>
+  <si>
     <t>gracekayupa@gmail.com</t>
   </si>
   <si>
-    <t>dewiputrihilika90@gmail.com</t>
-  </si>
-  <si>
     <t>kppnpalu651707@yahoo.com</t>
   </si>
   <si>
@@ -1300,46 +1300,46 @@
     <t>26 May 2026, 08:34:35</t>
   </si>
   <si>
+    <t>31 May 2026, 12:04:58</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:55</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:51</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:40:36</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:53</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:52</t>
+  </si>
+  <si>
+    <t>26 May 2026, 09:13:56</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:30:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 13:44:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:54:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:24</t>
+  </si>
+  <si>
     <t>26 May 2026, 07:30:38</t>
   </si>
   <si>
     <t>26 May 2026, 07:30:35</t>
-  </si>
-  <si>
-    <t>31 May 2026, 12:04:58</t>
-  </si>
-  <si>
-    <t>31 May 2026, 12:04:55</t>
-  </si>
-  <si>
-    <t>31 May 2026, 12:04:51</t>
-  </si>
-  <si>
-    <t>26 May 2026, 11:40:36</t>
-  </si>
-  <si>
-    <t>26 May 2026, 11:27:53</t>
-  </si>
-  <si>
-    <t>26 May 2026, 11:27:52</t>
-  </si>
-  <si>
-    <t>26 May 2026, 09:13:56</t>
-  </si>
-  <si>
-    <t>26 May 2026, 08:30:14</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 13:44:06</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:54:52</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:53:32</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:53:24</t>
   </si>
   <si>
     <t>02 Jun 2026, 02:30:55</t>
@@ -3975,7 +3975,7 @@
         <v>364</v>
       </c>
       <c r="F68" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G68" t="s">
         <v>428</v>
@@ -4001,7 +4001,7 @@
         <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G69" t="s">
         <v>429</v>
@@ -4012,42 +4012,42 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E70" t="s">
         <v>364</v>
       </c>
       <c r="F70" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G70" t="s">
         <v>430</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E71" t="s">
         <v>364</v>
@@ -4059,99 +4059,99 @@
         <v>431</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E72" t="s">
         <v>364</v>
       </c>
       <c r="F72" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G72" t="s">
         <v>432</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E73" t="s">
         <v>364</v>
       </c>
       <c r="F73" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G73" t="s">
         <v>433</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E74" t="s">
         <v>364</v>
       </c>
       <c r="F74" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G74" t="s">
         <v>434</v>
       </c>
       <c r="H74">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E75" t="s">
         <v>364</v>
@@ -4163,111 +4163,111 @@
         <v>435</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E76" t="s">
         <v>364</v>
       </c>
       <c r="F76" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G76" t="s">
         <v>436</v>
       </c>
       <c r="H76">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E77" t="s">
         <v>364</v>
       </c>
       <c r="F77" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G77" t="s">
         <v>437</v>
       </c>
       <c r="H77">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E78" t="s">
         <v>364</v>
       </c>
       <c r="F78" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G78" t="s">
         <v>438</v>
       </c>
       <c r="H78">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E79" t="s">
         <v>364</v>
       </c>
       <c r="F79" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G79" t="s">
         <v>439</v>
       </c>
       <c r="H79">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -4287,13 +4287,13 @@
         <v>364</v>
       </c>
       <c r="F80" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="G80" t="s">
         <v>440</v>
       </c>
       <c r="H80">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -4319,7 +4319,7 @@
         <v>441</v>
       </c>
       <c r="H81">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:8">

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -139,12 +139,12 @@
     <t>7204070009001200 - UB - 1</t>
   </si>
   <si>
+    <t>7204070012000800 - UB - 1</t>
+  </si>
+  <si>
     <t>7204070011000301 - UB - 3</t>
   </si>
   <si>
-    <t>7204070012000800 - UB - 1</t>
-  </si>
-  <si>
     <t>7205090009000301 - UB - 1</t>
   </si>
   <si>
@@ -490,12 +490,12 @@
     <t>PNM MODAL MIKRO</t>
   </si>
   <si>
+    <t>Balindo Manunggal Bersama, PT</t>
+  </si>
+  <si>
     <t>FIF, PT</t>
   </si>
   <si>
-    <t>Balindo Manunggal Bersama, PT</t>
-  </si>
-  <si>
     <t>SEKOLAH POLISI NEGARA</t>
   </si>
   <si>
@@ -850,12 +850,12 @@
     <t>ulamposo@gmail.com</t>
   </si>
   <si>
+    <t>gracekayupa@gmail.com</t>
+  </si>
+  <si>
     <t>dewiputrihilika90@gmail.com</t>
   </si>
   <si>
-    <t>gracekayupa@gmail.com</t>
-  </si>
-  <si>
     <t>kppnpalu651707@yahoo.com</t>
   </si>
   <si>
@@ -1300,6 +1300,12 @@
     <t>26 May 2026, 08:34:35</t>
   </si>
   <si>
+    <t>26 May 2026, 07:30:38</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:35</t>
+  </si>
+  <si>
     <t>31 May 2026, 12:04:58</t>
   </si>
   <si>
@@ -1334,12 +1340,6 @@
   </si>
   <si>
     <t>02 Jun 2026, 11:53:24</t>
-  </si>
-  <si>
-    <t>26 May 2026, 07:30:38</t>
-  </si>
-  <si>
-    <t>26 May 2026, 07:30:35</t>
   </si>
   <si>
     <t>02 Jun 2026, 02:30:55</t>
@@ -3975,7 +3975,7 @@
         <v>364</v>
       </c>
       <c r="F68" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G68" t="s">
         <v>428</v>
@@ -4001,7 +4001,7 @@
         <v>364</v>
       </c>
       <c r="F69" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G69" t="s">
         <v>429</v>
@@ -4012,42 +4012,42 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E70" t="s">
         <v>364</v>
       </c>
       <c r="F70" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G70" t="s">
         <v>430</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E71" t="s">
         <v>364</v>
@@ -4059,99 +4059,99 @@
         <v>431</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E72" t="s">
         <v>364</v>
       </c>
       <c r="F72" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G72" t="s">
         <v>432</v>
       </c>
       <c r="H72">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E73" t="s">
         <v>364</v>
       </c>
       <c r="F73" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G73" t="s">
         <v>433</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E74" t="s">
         <v>364</v>
       </c>
       <c r="F74" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G74" t="s">
         <v>434</v>
       </c>
       <c r="H74">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
         <v>364</v>
@@ -4163,111 +4163,111 @@
         <v>435</v>
       </c>
       <c r="H75">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E76" t="s">
         <v>364</v>
       </c>
       <c r="F76" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G76" t="s">
         <v>436</v>
       </c>
       <c r="H76">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E77" t="s">
         <v>364</v>
       </c>
       <c r="F77" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G77" t="s">
         <v>437</v>
       </c>
       <c r="H77">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B78" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E78" t="s">
         <v>364</v>
       </c>
       <c r="F78" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G78" t="s">
         <v>438</v>
       </c>
       <c r="H78">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E79" t="s">
         <v>364</v>
       </c>
       <c r="F79" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G79" t="s">
         <v>439</v>
       </c>
       <c r="H79">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -4287,13 +4287,13 @@
         <v>364</v>
       </c>
       <c r="F80" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="G80" t="s">
         <v>440</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -4319,7 +4319,7 @@
         <v>441</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82" spans="1:8">

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="168">
   <si>
     <t>code</t>
   </si>
@@ -40,9 +40,15 @@
     <t>order</t>
   </si>
   <si>
+    <t>4b3d4210-f21f-43bc-90cb-365395f8d755</t>
+  </si>
+  <si>
     <t>ec2ea21f-b88a-400a-8f3d-a03562ff60ad</t>
   </si>
   <si>
+    <t>0d4bfa96-7cd5-47d9-b366-e133f6ea27c4</t>
+  </si>
+  <si>
     <t>ca7ed898-5339-4d22-8a89-b89adc186705</t>
   </si>
   <si>
@@ -61,9 +67,81 @@
     <t>bcd04260-5f2a-4732-99e6-e2a415b8b206</t>
   </si>
   <si>
+    <t>19131aed-4f2e-465e-a7f6-9c0d50cbf975</t>
+  </si>
+  <si>
+    <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
+  </si>
+  <si>
+    <t>2b350499-a5b6-45ce-97b3-88359725419f</t>
+  </si>
+  <si>
+    <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
+  </si>
+  <si>
+    <t>2155505c-bb3d-48ec-ba48-ac98edbdca95</t>
+  </si>
+  <si>
+    <t>abbb91f7-66fb-497f-87e0-235b843068fd</t>
+  </si>
+  <si>
+    <t>64348838-c95b-4e73-8c90-1539e49a8fa6</t>
+  </si>
+  <si>
+    <t>0219fe15-1f5c-4cd7-96f0-734727640195</t>
+  </si>
+  <si>
+    <t>208ebcc6-9881-4752-a982-5d8825476be0</t>
+  </si>
+  <si>
+    <t>df965e5e-d457-436c-a65a-af7726c7ce2b</t>
+  </si>
+  <si>
+    <t>0c6fcc80-9ea0-43b2-8775-cb18edc33d25</t>
+  </si>
+  <si>
+    <t>b2cf42e6-965c-49fa-abac-9af54426d0cc</t>
+  </si>
+  <si>
+    <t>e0e3282e-4685-4ad8-b636-6449ef659410</t>
+  </si>
+  <si>
+    <t>9818074f-7f62-4f6f-8a12-7b9ec153718e</t>
+  </si>
+  <si>
+    <t>2676b7e4-6dca-4e7f-991e-6ae27b0b0c85</t>
+  </si>
+  <si>
+    <t>9b9e29d1-fc1e-4b2d-99d7-838fde85299c</t>
+  </si>
+  <si>
+    <t>e807b2d0-c9e8-4158-bc0a-301bcc232add</t>
+  </si>
+  <si>
+    <t>22df9424-5a77-4276-ab7d-9c4bc6b29108</t>
+  </si>
+  <si>
+    <t>cfb263a1-8db1-46b4-9417-0a2e529be838</t>
+  </si>
+  <si>
+    <t>b58860b3-d502-48de-bf29-ebc5b51b0389</t>
+  </si>
+  <si>
+    <t>cf953441-4548-4748-b059-68c60a1c9312</t>
+  </si>
+  <si>
+    <t>befe39ef-4187-40aa-9e99-fef88d32baa1</t>
+  </si>
+  <si>
+    <t>BPR Syariah  &lt;Agus Supriadi&gt;</t>
+  </si>
+  <si>
     <t>BRI UNIT SALAKAN</t>
   </si>
   <si>
+    <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
+  </si>
+  <si>
     <t>BANK PERKREDITAN RAKYAT PALU LOKADANA UTAMA</t>
   </si>
   <si>
@@ -82,12 +160,81 @@
     <t>BRI UNIT BUALEMO</t>
   </si>
   <si>
+    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT MITRA NIAGA BANGGAI</t>
+  </si>
+  <si>
+    <t>BANK SULTENG</t>
+  </si>
+  <si>
+    <t>TOTALINDO BANGGAI PERKASA</t>
+  </si>
+  <si>
+    <t>REKAYASA INDUSTRI PT</t>
+  </si>
+  <si>
+    <t>JOB PERTAMINA - MEDCO E&amp;P TOMORI SULAWESI</t>
+  </si>
+  <si>
+    <t>INDONESIA TSINGSHAN STAINLESS STEEL</t>
+  </si>
+  <si>
+    <t>HUA CHIN ALUMINUM  INDONESIA</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>HADJI KALLA</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>JEMBATAN MAS ENGINEERING</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>THE SIXTH CHEMICAL ENGINEERING CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>KENCANA BUMI MINERAL</t>
+  </si>
+  <si>
+    <t>CIPTA MANDIRI MOROWALI</t>
+  </si>
+  <si>
+    <t>INDONESIA GUANG CHING NICKEL AND STAINLESS STEEL INDUSTRY TKA</t>
+  </si>
+  <si>
+    <t>KINRUI NEW ENERGY TECHNOLOGIES  INDONESIA</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
+    <t>avatarcrue@gmail.com</t>
+  </si>
+  <si>
     <t>n5164@corp.bri.com</t>
   </si>
   <si>
+    <t>bankdanamon.admin@gmail.com</t>
+  </si>
+  <si>
     <t>kc.luwuk@bprpalulokadanautama.com</t>
   </si>
   <si>
@@ -106,18 +253,102 @@
     <t>nbobs@corp.brico.id</t>
   </si>
   <si>
+    <t>bca_luwuk_pajak@gmail.com</t>
+  </si>
+  <si>
+    <t>toili@mailnesia.com</t>
+  </si>
+  <si>
+    <t>banksulteng.toili@yahoo.com</t>
+  </si>
+  <si>
+    <t>totalindobatbperkasa@gmail.com</t>
+  </si>
+  <si>
+    <t>wandysendjaja@yahoo.com</t>
+  </si>
+  <si>
+    <t>haris.ismail@job-tomori.com</t>
+  </si>
+  <si>
+    <t>secretariat@it-stainlesssteel.com</t>
+  </si>
+  <si>
+    <t>secretariathuachinind@gmail.com</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>nur.salam.coning@kallagroup.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>jembatanmas579@yahoo.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>sobeh@ppc-adulsory.com</t>
+  </si>
+  <si>
+    <t>acctaxkbm@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.morowali@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>ciptamandiri@yahoo.com</t>
+  </si>
+  <si>
+    <t>rukun@bd.em.com</t>
+  </si>
+  <si>
+    <t>secretariatkinrui@gmail.com</t>
+  </si>
+  <si>
+    <t>Permanent_fail</t>
+  </si>
+  <si>
     <t>Bounced</t>
   </si>
   <si>
     <t>Queued</t>
   </si>
   <si>
+    <t>09 Jun 2026, 11:19:15</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:02</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 09:36:45</t>
   </si>
   <si>
     <t>02 Jun 2026, 09:36:44</t>
   </si>
   <si>
+    <t>09 Jun 2026, 11:00:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:07:49</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 07:38:30</t>
   </si>
   <si>
@@ -149,6 +380,144 @@
   </si>
   <si>
     <t>02 Jun 2026, 06:50:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:02:57</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:59</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:11:11</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:10:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:12:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:11:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:20</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:05:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:49:00</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:48:57</t>
+  </si>
+  <si>
+    <t>18 May 2026, 12:37:49</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 09:53:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:51:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:23:23</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:25</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:48:15</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:04:32</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:00:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:57:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:08:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:22:02</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:06:55</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:29:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:28:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:25</t>
   </si>
 </sst>
 </file>
@@ -506,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -540,22 +909,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -566,22 +935,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -589,28 +958,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -618,51 +987,51 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -670,100 +1039,100 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -771,25 +1140,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -797,25 +1166,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -823,25 +1192,25 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -849,25 +1218,25 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -875,27 +1244,1483 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" t="s">
+        <v>103</v>
+      </c>
+      <c r="G30" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" t="s">
+        <v>101</v>
+      </c>
+      <c r="F33" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33" t="s">
+        <v>133</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
         <v>22</v>
       </c>
-      <c r="D15" t="s">
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" t="s">
+        <v>101</v>
+      </c>
+      <c r="G35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" t="s">
+        <v>137</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E38" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" t="s">
+        <v>102</v>
+      </c>
+      <c r="G38" t="s">
+        <v>137</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="F41" t="s">
+        <v>103</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>87</v>
+      </c>
+      <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>87</v>
+      </c>
+      <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" t="s">
+        <v>141</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" t="s">
+        <v>141</v>
+      </c>
+      <c r="H44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" t="s">
+        <v>102</v>
+      </c>
+      <c r="F45" t="s">
+        <v>102</v>
+      </c>
+      <c r="G45" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" t="s">
+        <v>103</v>
+      </c>
+      <c r="G46" t="s">
+        <v>143</v>
+      </c>
+      <c r="H46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
+        <v>101</v>
+      </c>
+      <c r="G47" t="s">
+        <v>144</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" t="s">
+        <v>146</v>
+      </c>
+      <c r="H49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" t="s">
+        <v>102</v>
+      </c>
+      <c r="G50" t="s">
+        <v>147</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" t="s">
+        <v>103</v>
+      </c>
+      <c r="G51" t="s">
+        <v>148</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
         <v>29</v>
       </c>
-      <c r="E15" t="s">
+      <c r="B52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" t="s">
+        <v>101</v>
+      </c>
+      <c r="F52" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" t="s">
+        <v>149</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
         <v>30</v>
       </c>
-      <c r="F15" t="s">
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" t="s">
+        <v>150</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
         <v>30</v>
       </c>
-      <c r="G15" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15">
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" t="s">
+        <v>102</v>
+      </c>
+      <c r="F54" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" t="s">
+        <v>151</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E55" t="s">
+        <v>101</v>
+      </c>
+      <c r="F55" t="s">
+        <v>101</v>
+      </c>
+      <c r="G55" t="s">
+        <v>152</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" t="s">
+        <v>101</v>
+      </c>
+      <c r="G56" t="s">
+        <v>153</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F57" t="s">
+        <v>102</v>
+      </c>
+      <c r="G57" t="s">
+        <v>154</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" t="s">
+        <v>94</v>
+      </c>
+      <c r="E58" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" t="s">
+        <v>103</v>
+      </c>
+      <c r="G58" t="s">
+        <v>155</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" t="s">
+        <v>102</v>
+      </c>
+      <c r="F59" t="s">
+        <v>103</v>
+      </c>
+      <c r="G59" t="s">
+        <v>156</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" t="s">
+        <v>102</v>
+      </c>
+      <c r="F60" t="s">
+        <v>102</v>
+      </c>
+      <c r="G60" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" t="s">
+        <v>101</v>
+      </c>
+      <c r="F61" t="s">
+        <v>101</v>
+      </c>
+      <c r="G61" t="s">
+        <v>157</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" t="s">
+        <v>101</v>
+      </c>
+      <c r="F62" t="s">
+        <v>102</v>
+      </c>
+      <c r="G62" t="s">
+        <v>158</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" t="s">
+        <v>101</v>
+      </c>
+      <c r="F63" t="s">
+        <v>103</v>
+      </c>
+      <c r="G63" t="s">
+        <v>159</v>
+      </c>
+      <c r="H63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64" t="s">
+        <v>102</v>
+      </c>
+      <c r="F64" t="s">
+        <v>102</v>
+      </c>
+      <c r="G64" t="s">
+        <v>160</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" t="s">
+        <v>103</v>
+      </c>
+      <c r="G65" t="s">
+        <v>161</v>
+      </c>
+      <c r="H65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" t="s">
+        <v>69</v>
+      </c>
+      <c r="D66" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66" t="s">
+        <v>102</v>
+      </c>
+      <c r="F66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G66" t="s">
+        <v>162</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>69</v>
+      </c>
+      <c r="D67" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67" t="s">
+        <v>102</v>
+      </c>
+      <c r="F67" t="s">
+        <v>103</v>
+      </c>
+      <c r="G67" t="s">
+        <v>163</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>69</v>
+      </c>
+      <c r="D68" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" t="s">
+        <v>102</v>
+      </c>
+      <c r="F68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G68" t="s">
+        <v>164</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" t="s">
+        <v>102</v>
+      </c>
+      <c r="F69" t="s">
+        <v>103</v>
+      </c>
+      <c r="G69" t="s">
+        <v>165</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70" t="s">
+        <v>102</v>
+      </c>
+      <c r="F70" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" t="s">
+        <v>166</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" t="s">
+        <v>69</v>
+      </c>
+      <c r="D71" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" t="s">
+        <v>102</v>
+      </c>
+      <c r="F71" t="s">
+        <v>103</v>
+      </c>
+      <c r="G71" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="146">
   <si>
     <t>code</t>
   </si>
@@ -88,7 +88,37 @@
     <t>abbb91f7-66fb-497f-87e0-235b843068fd</t>
   </si>
   <si>
-    <t>BPR SYARIAH KHAIRAN INTI  &lt;AGUS SUPRIADI&gt;</t>
+    <t>64348838-c95b-4e73-8c90-1539e49a8fa6</t>
+  </si>
+  <si>
+    <t>0219fe15-1f5c-4cd7-96f0-734727640195</t>
+  </si>
+  <si>
+    <t>208ebcc6-9881-4752-a982-5d8825476be0</t>
+  </si>
+  <si>
+    <t>df965e5e-d457-436c-a65a-af7726c7ce2b</t>
+  </si>
+  <si>
+    <t>0c6fcc80-9ea0-43b2-8775-cb18edc33d25</t>
+  </si>
+  <si>
+    <t>b2cf42e6-965c-49fa-abac-9af54426d0cc</t>
+  </si>
+  <si>
+    <t>e0e3282e-4685-4ad8-b636-6449ef659410</t>
+  </si>
+  <si>
+    <t>9818074f-7f62-4f6f-8a12-7b9ec153718e</t>
+  </si>
+  <si>
+    <t>2676b7e4-6dca-4e7f-991e-6ae27b0b0c85</t>
+  </si>
+  <si>
+    <t>9b9e29d1-fc1e-4b2d-99d7-838fde85299c</t>
+  </si>
+  <si>
+    <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
   </si>
   <si>
     <t>BPR MODERN EXPRESS PT</t>
@@ -136,12 +166,42 @@
     <t>JOB PERTAMINA - MEDCO E&amp;P TOMORI SULAWESI</t>
   </si>
   <si>
+    <t>INDONESIA TSINGSHAN STAINLESS STEEL</t>
+  </si>
+  <si>
+    <t>HUA CHIN ALUMINUM  INDONESIA</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>HADJI KALLA</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>JEMBATAN MAS ENGINEERING</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>SUBMITTED RESPONDENT</t>
+  </si>
+  <si>
     <t>DRAFT</t>
   </si>
   <si>
-    <t>SUBMITTED RESPONDENT</t>
-  </si>
-  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -193,6 +253,36 @@
     <t>haris.ismail@job-tomori.com</t>
   </si>
   <si>
+    <t>secretariat@it-stainlesssteel.com</t>
+  </si>
+  <si>
+    <t>secretariathuachinind@gmail.com</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>nur.salam.coning@kallagroup.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>jembatanmas579@yahoo.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -202,6 +292,9 @@
     <t>Queued</t>
   </si>
   <si>
+    <t>11 Jun 2026, 14:00:36</t>
+  </si>
+  <si>
     <t>09 Jun 2026, 11:19:15</t>
   </si>
   <si>
@@ -302,6 +395,63 @@
   </si>
   <si>
     <t>02 Jun 2026, 05:51:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:23:23</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:25</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:48:15</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:04:32</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:00:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:57:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:08:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
   </si>
 </sst>
 </file>
@@ -659,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -693,22 +843,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -719,22 +869,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -745,22 +895,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -768,51 +918,51 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -823,51 +973,51 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -875,25 +1025,25 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -901,51 +1051,51 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -953,51 +1103,51 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1005,51 +1155,51 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1057,51 +1207,51 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1109,51 +1259,51 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1161,51 +1311,51 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1213,51 +1363,51 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1265,25 +1415,25 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1291,74 +1441,74 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1369,25 +1519,25 @@
         <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1395,51 +1545,51 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1447,51 +1597,51 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1499,25 +1649,25 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1525,51 +1675,51 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1577,25 +1727,25 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1603,25 +1753,623 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" t="s">
+        <v>89</v>
+      </c>
+      <c r="F37" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" t="s">
+        <v>126</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" t="s">
+        <v>127</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" t="s">
+        <v>90</v>
+      </c>
+      <c r="F40" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" t="s">
+        <v>89</v>
+      </c>
+      <c r="G41" t="s">
+        <v>128</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" t="s">
+        <v>129</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
+      </c>
+      <c r="F43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F44" t="s">
+        <v>89</v>
+      </c>
+      <c r="G44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G45" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s">
+        <v>131</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" t="s">
+        <v>90</v>
+      </c>
+      <c r="F47" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47" t="s">
+        <v>132</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" t="s">
+        <v>90</v>
+      </c>
+      <c r="F48" t="s">
+        <v>91</v>
+      </c>
+      <c r="G48" t="s">
+        <v>133</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s">
+        <v>134</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" t="s">
+        <v>135</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" t="s">
+        <v>136</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" t="s">
+        <v>90</v>
+      </c>
+      <c r="F53" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" t="s">
+        <v>138</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" t="s">
+        <v>89</v>
+      </c>
+      <c r="G54" t="s">
+        <v>139</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>86</v>
+      </c>
+      <c r="E55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" t="s">
+        <v>140</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" t="s">
+        <v>91</v>
+      </c>
+      <c r="G56" t="s">
+        <v>141</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s">
         <v>58</v>
       </c>
-      <c r="E37" t="s">
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" t="s">
+        <v>87</v>
+      </c>
+      <c r="E57" t="s">
+        <v>89</v>
+      </c>
+      <c r="F57" t="s">
+        <v>89</v>
+      </c>
+      <c r="G57" t="s">
+        <v>142</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" t="s">
+        <v>89</v>
+      </c>
+      <c r="F58" t="s">
+        <v>89</v>
+      </c>
+      <c r="G58" t="s">
+        <v>143</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
         <v>59</v>
       </c>
-      <c r="F37" t="s">
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" t="s">
+        <v>88</v>
+      </c>
+      <c r="E59" t="s">
+        <v>90</v>
+      </c>
+      <c r="F59" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" t="s">
+        <v>144</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
         <v>59</v>
       </c>
-      <c r="G37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37">
-        <v>3</v>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" t="s">
+        <v>90</v>
+      </c>
+      <c r="F60" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" t="s">
+        <v>145</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="64">
   <si>
     <t>code</t>
   </si>
@@ -49,6 +49,27 @@
     <t>ec2ea21f-b88a-400a-8f3d-a03562ff60ad</t>
   </si>
   <si>
+    <t>0d4bfa96-7cd5-47d9-b366-e133f6ea27c4</t>
+  </si>
+  <si>
+    <t>ca7ed898-5339-4d22-8a89-b89adc186705</t>
+  </si>
+  <si>
+    <t>c5b60633-13fc-4352-a09f-e6b11e93fe60</t>
+  </si>
+  <si>
+    <t>87ab3e43-e1be-4b02-af1e-14720ebfb03f</t>
+  </si>
+  <si>
+    <t>941bb532-7c5e-4c33-baca-ee0b2d06fb62</t>
+  </si>
+  <si>
+    <t>96d663ec-f298-4560-9b84-996b8de92249</t>
+  </si>
+  <si>
+    <t>bcd04260-5f2a-4732-99e6-e2a415b8b206</t>
+  </si>
+  <si>
     <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
   </si>
   <si>
@@ -58,12 +79,36 @@
     <t>BRI UNIT SALAKAN</t>
   </si>
   <si>
+    <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT PALU LOKADANA UTAMA</t>
+  </si>
+  <si>
+    <t>BANK SAMPAH INDUK BERLIAN</t>
+  </si>
+  <si>
+    <t>CAHAYA BARU SENTOSA</t>
+  </si>
+  <si>
+    <t>ALL BERKEMBANG BERSAMA</t>
+  </si>
+  <si>
+    <t>TRAKINDO UTAMA, PT</t>
+  </si>
+  <si>
+    <t>BRI UNIT BUALEMO</t>
+  </si>
+  <si>
     <t>SUBMITTED RESPONDENT</t>
   </si>
   <si>
     <t>DRAFT</t>
   </si>
   <si>
+    <t>OPEN</t>
+  </si>
+  <si>
     <t>avatarcrue@gmail.com</t>
   </si>
   <si>
@@ -73,6 +118,27 @@
     <t>n5164@corp.bri.com</t>
   </si>
   <si>
+    <t>bankdanamon.admin@gmail.com</t>
+  </si>
+  <si>
+    <t>kc.luwuk@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>anasholechah6196@gmail.com</t>
+  </si>
+  <si>
+    <t>cbs_luwuk@yahoo.com</t>
+  </si>
+  <si>
+    <t>allswalayan@ymail.com</t>
+  </si>
+  <si>
+    <t>info_trakindo@gmail.com</t>
+  </si>
+  <si>
+    <t>nbobs@corp.brico.id</t>
+  </si>
+  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -101,6 +167,45 @@
   </si>
   <si>
     <t>02 Jun 2026, 09:36:44</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:00:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:07:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:38:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:38:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:23:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:23:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:53:26</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 03:51:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:33:23</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:32:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:39:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:39:23</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:50:12</t>
   </si>
 </sst>
 </file>
@@ -458,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -492,22 +597,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -518,22 +623,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -544,22 +649,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -570,22 +675,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -596,22 +701,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -622,22 +727,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -648,24 +753,414 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8">
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="286">
   <si>
     <t>code</t>
   </si>
@@ -70,6 +70,132 @@
     <t>bcd04260-5f2a-4732-99e6-e2a415b8b206</t>
   </si>
   <si>
+    <t>19131aed-4f2e-465e-a7f6-9c0d50cbf975</t>
+  </si>
+  <si>
+    <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
+  </si>
+  <si>
+    <t>2b350499-a5b6-45ce-97b3-88359725419f</t>
+  </si>
+  <si>
+    <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
+  </si>
+  <si>
+    <t>2155505c-bb3d-48ec-ba48-ac98edbdca95</t>
+  </si>
+  <si>
+    <t>abbb91f7-66fb-497f-87e0-235b843068fd</t>
+  </si>
+  <si>
+    <t>64348838-c95b-4e73-8c90-1539e49a8fa6</t>
+  </si>
+  <si>
+    <t>0219fe15-1f5c-4cd7-96f0-734727640195</t>
+  </si>
+  <si>
+    <t>208ebcc6-9881-4752-a982-5d8825476be0</t>
+  </si>
+  <si>
+    <t>df965e5e-d457-436c-a65a-af7726c7ce2b</t>
+  </si>
+  <si>
+    <t>0c6fcc80-9ea0-43b2-8775-cb18edc33d25</t>
+  </si>
+  <si>
+    <t>b2cf42e6-965c-49fa-abac-9af54426d0cc</t>
+  </si>
+  <si>
+    <t>e0e3282e-4685-4ad8-b636-6449ef659410</t>
+  </si>
+  <si>
+    <t>9818074f-7f62-4f6f-8a12-7b9ec153718e</t>
+  </si>
+  <si>
+    <t>2676b7e4-6dca-4e7f-991e-6ae27b0b0c85</t>
+  </si>
+  <si>
+    <t>9b9e29d1-fc1e-4b2d-99d7-838fde85299c</t>
+  </si>
+  <si>
+    <t>e807b2d0-c9e8-4158-bc0a-301bcc232add</t>
+  </si>
+  <si>
+    <t>22df9424-5a77-4276-ab7d-9c4bc6b29108</t>
+  </si>
+  <si>
+    <t>cfb263a1-8db1-46b4-9417-0a2e529be838</t>
+  </si>
+  <si>
+    <t>b58860b3-d502-48de-bf29-ebc5b51b0389</t>
+  </si>
+  <si>
+    <t>cf953441-4548-4748-b059-68c60a1c9312</t>
+  </si>
+  <si>
+    <t>befe39ef-4187-40aa-9e99-fef88d32baa1</t>
+  </si>
+  <si>
+    <t>df80536f-5125-46c8-aa0a-220b8d26441b</t>
+  </si>
+  <si>
+    <t>e674036e-bee0-47b7-bc94-a0c32bfa2d71</t>
+  </si>
+  <si>
+    <t>aed96e17-8337-406e-9f72-c02f709f865c</t>
+  </si>
+  <si>
+    <t>081008bc-6a02-4888-bfb2-2c1c805fa4ad</t>
+  </si>
+  <si>
+    <t>358e68c2-9ecd-47b3-85a5-e07045612b91</t>
+  </si>
+  <si>
+    <t>9e3fbec4-42cd-41c0-9b1d-f442487ed552</t>
+  </si>
+  <si>
+    <t>01b351f3-b52c-4516-a91c-00f58d08579d</t>
+  </si>
+  <si>
+    <t>7880f953-35e8-4387-aac5-b4a94b0c3c2e</t>
+  </si>
+  <si>
+    <t>74e56a04-fcd1-4332-ba6e-1bfb657dc781</t>
+  </si>
+  <si>
+    <t>d61d41d8-08d5-40a5-9a4b-ec2cda0629c1</t>
+  </si>
+  <si>
+    <t>66b93b8d-817c-4af4-9183-47792e43d54e</t>
+  </si>
+  <si>
+    <t>b6c21085-5e3c-4d3b-bcb0-1e48c3bbaca7</t>
+  </si>
+  <si>
+    <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
+  </si>
+  <si>
+    <t>8d3e9626-0215-47a7-86cd-bf85990128c8</t>
+  </si>
+  <si>
+    <t>eeee3ec7-6e8b-4ba0-86e1-e4a35de9cc96</t>
+  </si>
+  <si>
+    <t>e2d20a9c-1c32-42e2-a0cb-6567b585b199</t>
+  </si>
+  <si>
+    <t>11fd6f69-871d-4258-81f6-e2145ee9f73a</t>
+  </si>
+  <si>
+    <t>f455e248-e952-4fc6-9076-0237c90636fd</t>
+  </si>
+  <si>
+    <t>d858d260-d53e-41d2-906c-df6bbcd1d526</t>
+  </si>
+  <si>
+    <t>bf59ad9c-5369-4438-bd8a-f72ddffaa938</t>
+  </si>
+  <si>
     <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
   </si>
   <si>
@@ -100,6 +226,126 @@
     <t>BRI UNIT BUALEMO</t>
   </si>
   <si>
+    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT MITRA NIAGA BANGGAI</t>
+  </si>
+  <si>
+    <t>BANK SULTENG</t>
+  </si>
+  <si>
+    <t>TOTALINDO BANGGAI PERKASA</t>
+  </si>
+  <si>
+    <t>REKAYASA INDUSTRI PT</t>
+  </si>
+  <si>
+    <t>JOB PERTAMINA - MEDCO E&amp;P TOMORI SULAWESI</t>
+  </si>
+  <si>
+    <t>INDONESIA TSINGSHAN STAINLESS STEEL</t>
+  </si>
+  <si>
+    <t>HUA CHIN ALUMINUM  INDONESIA</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>HADJI KALLA</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>JEMBATAN MAS ENGINEERING</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>THE SIXTH CHEMICAL ENGINEERING CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>KENCANA BUMI MINERAL</t>
+  </si>
+  <si>
+    <t>CIPTA MANDIRI MOROWALI</t>
+  </si>
+  <si>
+    <t>INDONESIA GUANG CHING NICKEL AND STAINLESS STEEL INDUSTRY TKA</t>
+  </si>
+  <si>
+    <t>KINRUI NEW ENERGY TECHNOLOGIES  INDONESIA</t>
+  </si>
+  <si>
+    <t>BANK BPD</t>
+  </si>
+  <si>
+    <t>AKAR DAYA MANDIRI PT</t>
+  </si>
+  <si>
+    <t>BANK BPR PALU LOKADANA UTAMA CAB POSO, PT</t>
+  </si>
+  <si>
+    <t>AMRI MARGA JAYA, PT</t>
+  </si>
+  <si>
+    <t>PLTA Poso 1</t>
+  </si>
+  <si>
+    <t>KCP MANDIRI MITRA USAHA TENTENA</t>
+  </si>
+  <si>
+    <t>PNM MODAL MIKRO</t>
+  </si>
+  <si>
+    <t>Balindo Manunggal Bersama, PT</t>
+  </si>
+  <si>
+    <t>FIF, PT</t>
+  </si>
+  <si>
+    <t>SEKOLAH POLISI NEGARA</t>
+  </si>
+  <si>
+    <t>PDAM KAB DONGGALA</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
+  </si>
+  <si>
+    <t>PT. BANK SULTENG KAS LABEAN</t>
+  </si>
+  <si>
+    <t>ASTUN HI. ARSYAD</t>
+  </si>
+  <si>
+    <t>BUTOL RAYA NUSANTARA, PT</t>
+  </si>
+  <si>
+    <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
+  </si>
+  <si>
+    <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
+  </si>
+  <si>
+    <t>GALAXI INDO PRATAMA, CV</t>
+  </si>
+  <si>
+    <t>BANK SULTENG UNIT SONI</t>
+  </si>
+  <si>
     <t>SUBMITTED RESPONDENT</t>
   </si>
   <si>
@@ -139,6 +385,132 @@
     <t>nbobs@corp.brico.id</t>
   </si>
   <si>
+    <t>bca_luwuk_pajak@gmail.com</t>
+  </si>
+  <si>
+    <t>toili@mailnesia.com</t>
+  </si>
+  <si>
+    <t>banksulteng.toili@yahoo.com</t>
+  </si>
+  <si>
+    <t>totalindobatbperkasa@gmail.com</t>
+  </si>
+  <si>
+    <t>wandysendjaja@yahoo.com</t>
+  </si>
+  <si>
+    <t>haris.ismail@job-tomori.com</t>
+  </si>
+  <si>
+    <t>secretariat@it-stainlesssteel.com</t>
+  </si>
+  <si>
+    <t>secretariathuachinind@gmail.com</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>nur.salam.coning@kallagroup.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>jembatanmas579@yahoo.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>sobeh@ppc-adulsory.com</t>
+  </si>
+  <si>
+    <t>acctaxkbm@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.morowali@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>ciptamandiri@yahoo.com</t>
+  </si>
+  <si>
+    <t>rukun@bd.em.com</t>
+  </si>
+  <si>
+    <t>secretariatkinrui@gmail.com</t>
+  </si>
+  <si>
+    <t>bsposo@yahoo.com</t>
+  </si>
+  <si>
+    <t>akardayamandiri49@gmail.com</t>
+  </si>
+  <si>
+    <t>banksultengposo@mailnesia.com</t>
+  </si>
+  <si>
+    <t>kc.poso@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>pt.amrimargajaya@ymail.com</t>
+  </si>
+  <si>
+    <t>pltaposo2@posoenergy.com</t>
+  </si>
+  <si>
+    <t>kcpmandirimitrausaha@gmail.com</t>
+  </si>
+  <si>
+    <t>ulamposo@gmail.com</t>
+  </si>
+  <si>
+    <t>gracekayupa@gmail.com</t>
+  </si>
+  <si>
+    <t>dewiputrihilika90@gmail.com</t>
+  </si>
+  <si>
+    <t>kppnpalu651707@yahoo.com</t>
+  </si>
+  <si>
+    <t>pdam_donggala@gmail.com</t>
+  </si>
+  <si>
+    <t>bprlabuan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>banksulteng_kaslabean@yahoo.com</t>
+  </si>
+  <si>
+    <t>astunhiarsyad28@gmail.com</t>
+  </si>
+  <si>
+    <t>butolrayanusantara@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.tolitoli@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>koperasi_maritim@yahoo.com</t>
+  </si>
+  <si>
+    <t>galaxiindopratamatolis@gmail.com</t>
+  </si>
+  <si>
+    <t>febrialdin.rial@yahoo.co.id</t>
+  </si>
+  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -148,6 +520,15 @@
     <t>Queued</t>
   </si>
   <si>
+    <t>Clicked</t>
+  </si>
+  <si>
+    <t>Opened</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
     <t>11 Jun 2026, 14:00:36</t>
   </si>
   <si>
@@ -206,6 +587,291 @@
   </si>
   <si>
     <t>02 Jun 2026, 06:50:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:02:57</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:59</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:11:11</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:10:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:12:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:11:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:57:20</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:05:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:49:00</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:48:57</t>
+  </si>
+  <si>
+    <t>18 May 2026, 12:37:49</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 09:53:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:51:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:23:23</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:25</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:48:15</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:04:32</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:00:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:57:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:08:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:22:02</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:06:55</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:29:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:28:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:17:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:02:51</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:59:00</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:58:55</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:13:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:08:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:07:16</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:14</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:47:26</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:34:35</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:38</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:35</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:58</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:55</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:51</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:40:36</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:53</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:52</t>
+  </si>
+  <si>
+    <t>26 May 2026, 09:13:56</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:30:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 13:44:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:54:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:30:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:29:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:31:35</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:02:07</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:30:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:29:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:12:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:02</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:01:19</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:31</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:08:22</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:04:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:24</t>
   </si>
 </sst>
 </file>
@@ -563,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -597,22 +1263,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -623,22 +1289,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>172</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -649,22 +1315,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>173</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -675,22 +1341,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -701,22 +1367,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>175</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -727,22 +1393,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -753,22 +1419,22 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -779,22 +1445,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>178</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -805,22 +1471,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -831,22 +1497,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>179</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -857,22 +1523,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -883,22 +1549,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -909,22 +1575,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -935,22 +1601,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -961,22 +1627,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G16" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -987,22 +1653,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>185</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -1013,22 +1679,22 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1039,22 +1705,22 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -1065,22 +1731,22 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>188</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1091,22 +1757,22 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>189</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -1117,22 +1783,22 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1143,24 +1809,2702 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F23" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" t="s">
+        <v>190</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F24" t="s">
+        <v>165</v>
+      </c>
+      <c r="G24" t="s">
+        <v>191</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" t="s">
+        <v>192</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" t="s">
+        <v>194</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" t="s">
+        <v>198</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" t="s">
+        <v>199</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" t="s">
+        <v>165</v>
+      </c>
+      <c r="G33" t="s">
+        <v>200</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>112</v>
+      </c>
+      <c r="D34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" t="s">
+        <v>201</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" t="s">
+        <v>165</v>
+      </c>
+      <c r="G36" t="s">
+        <v>203</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" t="s">
+        <v>165</v>
+      </c>
+      <c r="G37" t="s">
+        <v>204</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="s">
+        <v>128</v>
+      </c>
+      <c r="E38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" t="s">
+        <v>165</v>
+      </c>
+      <c r="G38" t="s">
+        <v>205</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" t="s">
+        <v>166</v>
+      </c>
+      <c r="F39" t="s">
+        <v>167</v>
+      </c>
+      <c r="G39" t="s">
+        <v>206</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" t="s">
+        <v>166</v>
+      </c>
+      <c r="F40" t="s">
+        <v>166</v>
+      </c>
+      <c r="G40" t="s">
+        <v>206</v>
+      </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D41" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" t="s">
+        <v>165</v>
+      </c>
+      <c r="G41" t="s">
+        <v>207</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D42" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42" t="s">
+        <v>166</v>
+      </c>
+      <c r="G42" t="s">
+        <v>208</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s">
+        <v>165</v>
+      </c>
+      <c r="F43" t="s">
+        <v>167</v>
+      </c>
+      <c r="G43" t="s">
+        <v>208</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" t="s">
+        <v>165</v>
+      </c>
+      <c r="G44" t="s">
+        <v>209</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" t="s">
+        <v>165</v>
+      </c>
+      <c r="F45" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" t="s">
+        <v>210</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" t="s">
+        <v>167</v>
+      </c>
+      <c r="G46" t="s">
+        <v>210</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
         <v>27</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>132</v>
+      </c>
+      <c r="E47" t="s">
+        <v>166</v>
+      </c>
+      <c r="F47" t="s">
+        <v>166</v>
+      </c>
+      <c r="G47" t="s">
+        <v>211</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" t="s">
+        <v>132</v>
+      </c>
+      <c r="E48" t="s">
+        <v>166</v>
+      </c>
+      <c r="F48" t="s">
+        <v>167</v>
+      </c>
+      <c r="G48" t="s">
+        <v>212</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>80</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" t="s">
+        <v>165</v>
+      </c>
+      <c r="G49" t="s">
+        <v>213</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G50" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" t="s">
+        <v>165</v>
+      </c>
+      <c r="F51" t="s">
+        <v>167</v>
+      </c>
+      <c r="G51" t="s">
+        <v>215</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>29</v>
+      </c>
+      <c r="B52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" t="s">
+        <v>134</v>
+      </c>
+      <c r="E52" t="s">
+        <v>166</v>
+      </c>
+      <c r="F52" t="s">
+        <v>166</v>
+      </c>
+      <c r="G52" t="s">
+        <v>216</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" t="s">
+        <v>166</v>
+      </c>
+      <c r="F53" t="s">
+        <v>167</v>
+      </c>
+      <c r="G53" t="s">
+        <v>217</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
         <v>30</v>
       </c>
-      <c r="D23" t="s">
+      <c r="B54" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" t="s">
+        <v>165</v>
+      </c>
+      <c r="F54" t="s">
+        <v>165</v>
+      </c>
+      <c r="G54" t="s">
+        <v>218</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>136</v>
+      </c>
+      <c r="E55" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" t="s">
+        <v>219</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
+        <v>136</v>
+      </c>
+      <c r="E56" t="s">
+        <v>166</v>
+      </c>
+      <c r="F56" t="s">
+        <v>167</v>
+      </c>
+      <c r="G56" t="s">
+        <v>220</v>
+      </c>
+      <c r="H56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" t="s">
+        <v>165</v>
+      </c>
+      <c r="F57" t="s">
+        <v>165</v>
+      </c>
+      <c r="G57" t="s">
+        <v>221</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
+        <v>137</v>
+      </c>
+      <c r="E58" t="s">
+        <v>165</v>
+      </c>
+      <c r="F58" t="s">
+        <v>165</v>
+      </c>
+      <c r="G58" t="s">
+        <v>222</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
+        <v>138</v>
+      </c>
+      <c r="E59" t="s">
+        <v>166</v>
+      </c>
+      <c r="F59" t="s">
+        <v>166</v>
+      </c>
+      <c r="G59" t="s">
+        <v>223</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" t="s">
+        <v>166</v>
+      </c>
+      <c r="F60" t="s">
+        <v>167</v>
+      </c>
+      <c r="G60" t="s">
+        <v>224</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
+        <v>139</v>
+      </c>
+      <c r="E61" t="s">
+        <v>166</v>
+      </c>
+      <c r="F61" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" t="s">
+        <v>225</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" t="s">
+        <v>166</v>
+      </c>
+      <c r="G62" t="s">
+        <v>225</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
+        <v>140</v>
+      </c>
+      <c r="E63" t="s">
+        <v>165</v>
+      </c>
+      <c r="F63" t="s">
+        <v>165</v>
+      </c>
+      <c r="G63" t="s">
+        <v>226</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
+        <v>140</v>
+      </c>
+      <c r="E64" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" t="s">
+        <v>166</v>
+      </c>
+      <c r="G64" t="s">
+        <v>227</v>
+      </c>
+      <c r="H64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
+        <v>140</v>
+      </c>
+      <c r="E65" t="s">
+        <v>165</v>
+      </c>
+      <c r="F65" t="s">
+        <v>167</v>
+      </c>
+      <c r="G65" t="s">
+        <v>228</v>
+      </c>
+      <c r="H65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D66" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" t="s">
+        <v>166</v>
+      </c>
+      <c r="F66" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" t="s">
+        <v>229</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>36</v>
+      </c>
+      <c r="B67" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
+        <v>141</v>
+      </c>
+      <c r="E67" t="s">
+        <v>166</v>
+      </c>
+      <c r="F67" t="s">
+        <v>167</v>
+      </c>
+      <c r="G67" t="s">
+        <v>230</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
+        <v>142</v>
+      </c>
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68" t="s">
+        <v>166</v>
+      </c>
+      <c r="G68" t="s">
+        <v>231</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
+        <v>142</v>
+      </c>
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" t="s">
+        <v>167</v>
+      </c>
+      <c r="G69" t="s">
+        <v>232</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
+        <v>143</v>
+      </c>
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+      <c r="F70" t="s">
+        <v>166</v>
+      </c>
+      <c r="G70" t="s">
+        <v>233</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" t="s">
+        <v>166</v>
+      </c>
+      <c r="F71" t="s">
+        <v>167</v>
+      </c>
+      <c r="G71" t="s">
+        <v>234</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" t="s">
+        <v>144</v>
+      </c>
+      <c r="E72" t="s">
+        <v>166</v>
+      </c>
+      <c r="F72" t="s">
+        <v>166</v>
+      </c>
+      <c r="G72" t="s">
+        <v>235</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>144</v>
+      </c>
+      <c r="E73" t="s">
+        <v>166</v>
+      </c>
+      <c r="F73" t="s">
+        <v>167</v>
+      </c>
+      <c r="G73" t="s">
+        <v>236</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
         <v>40</v>
       </c>
-      <c r="E23" t="s">
+      <c r="B74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" t="s">
+        <v>166</v>
+      </c>
+      <c r="G74" t="s">
+        <v>237</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
+        <v>145</v>
+      </c>
+      <c r="E75" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" t="s">
+        <v>167</v>
+      </c>
+      <c r="G75" t="s">
+        <v>238</v>
+      </c>
+      <c r="H75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>146</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>166</v>
+      </c>
+      <c r="G76" t="s">
+        <v>239</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" t="s">
+        <v>92</v>
+      </c>
+      <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>146</v>
+      </c>
+      <c r="E77" t="s">
+        <v>166</v>
+      </c>
+      <c r="F77" t="s">
+        <v>167</v>
+      </c>
+      <c r="G77" t="s">
+        <v>239</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
         <v>42</v>
       </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23">
+      <c r="B78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
+        <v>147</v>
+      </c>
+      <c r="E78" t="s">
+        <v>165</v>
+      </c>
+      <c r="F78" t="s">
+        <v>165</v>
+      </c>
+      <c r="G78" t="s">
+        <v>240</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
+        <v>148</v>
+      </c>
+      <c r="E79" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79" t="s">
+        <v>241</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" t="s">
+        <v>148</v>
+      </c>
+      <c r="E80" t="s">
+        <v>166</v>
+      </c>
+      <c r="F80" t="s">
+        <v>167</v>
+      </c>
+      <c r="G80" t="s">
+        <v>242</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" t="s">
+        <v>149</v>
+      </c>
+      <c r="E81" t="s">
+        <v>165</v>
+      </c>
+      <c r="F81" t="s">
+        <v>165</v>
+      </c>
+      <c r="G81" t="s">
+        <v>243</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" t="s">
+        <v>94</v>
+      </c>
+      <c r="C82" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" t="s">
+        <v>149</v>
+      </c>
+      <c r="E82" t="s">
+        <v>165</v>
+      </c>
+      <c r="F82" t="s">
+        <v>166</v>
+      </c>
+      <c r="G82" t="s">
+        <v>244</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>44</v>
+      </c>
+      <c r="B83" t="s">
+        <v>94</v>
+      </c>
+      <c r="C83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" t="s">
+        <v>165</v>
+      </c>
+      <c r="F83" t="s">
+        <v>167</v>
+      </c>
+      <c r="G83" t="s">
+        <v>245</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
+        <v>150</v>
+      </c>
+      <c r="E84" t="s">
+        <v>166</v>
+      </c>
+      <c r="F84" t="s">
+        <v>166</v>
+      </c>
+      <c r="G84" t="s">
+        <v>246</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" t="s">
+        <v>112</v>
+      </c>
+      <c r="D85" t="s">
+        <v>150</v>
+      </c>
+      <c r="E85" t="s">
+        <v>166</v>
+      </c>
+      <c r="F85" t="s">
+        <v>167</v>
+      </c>
+      <c r="G85" t="s">
+        <v>247</v>
+      </c>
+      <c r="H85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>46</v>
+      </c>
+      <c r="B86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
+        <v>151</v>
+      </c>
+      <c r="E86" t="s">
+        <v>165</v>
+      </c>
+      <c r="F86" t="s">
+        <v>165</v>
+      </c>
+      <c r="G86" t="s">
+        <v>248</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>46</v>
+      </c>
+      <c r="B87" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" t="s">
+        <v>165</v>
+      </c>
+      <c r="F87" t="s">
+        <v>167</v>
+      </c>
+      <c r="G87" t="s">
+        <v>249</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>46</v>
+      </c>
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
+        <v>151</v>
+      </c>
+      <c r="E88" t="s">
+        <v>165</v>
+      </c>
+      <c r="F88" t="s">
+        <v>166</v>
+      </c>
+      <c r="G88" t="s">
+        <v>249</v>
+      </c>
+      <c r="H88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>47</v>
+      </c>
+      <c r="B89" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" t="s">
+        <v>166</v>
+      </c>
+      <c r="F89" t="s">
+        <v>166</v>
+      </c>
+      <c r="G89" t="s">
+        <v>250</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>47</v>
+      </c>
+      <c r="B90" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
+        <v>152</v>
+      </c>
+      <c r="E90" t="s">
+        <v>166</v>
+      </c>
+      <c r="F90" t="s">
+        <v>167</v>
+      </c>
+      <c r="G90" t="s">
+        <v>250</v>
+      </c>
+      <c r="H90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>48</v>
+      </c>
+      <c r="B91" t="s">
+        <v>98</v>
+      </c>
+      <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
+        <v>153</v>
+      </c>
+      <c r="E91" t="s">
+        <v>166</v>
+      </c>
+      <c r="F91" t="s">
+        <v>166</v>
+      </c>
+      <c r="G91" t="s">
+        <v>251</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" t="s">
+        <v>98</v>
+      </c>
+      <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
+        <v>153</v>
+      </c>
+      <c r="E92" t="s">
+        <v>166</v>
+      </c>
+      <c r="F92" t="s">
+        <v>167</v>
+      </c>
+      <c r="G92" t="s">
+        <v>252</v>
+      </c>
+      <c r="H92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
+      <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
+        <v>154</v>
+      </c>
+      <c r="E93" t="s">
+        <v>166</v>
+      </c>
+      <c r="F93" t="s">
+        <v>168</v>
+      </c>
+      <c r="G93" t="s">
+        <v>253</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" t="s">
+        <v>99</v>
+      </c>
+      <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>154</v>
+      </c>
+      <c r="E94" t="s">
+        <v>166</v>
+      </c>
+      <c r="F94" t="s">
+        <v>169</v>
+      </c>
+      <c r="G94" t="s">
+        <v>254</v>
+      </c>
+      <c r="H94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>49</v>
+      </c>
+      <c r="B95" t="s">
+        <v>99</v>
+      </c>
+      <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
+        <v>154</v>
+      </c>
+      <c r="E95" t="s">
+        <v>166</v>
+      </c>
+      <c r="F95" t="s">
+        <v>169</v>
+      </c>
+      <c r="G95" t="s">
+        <v>255</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" t="s">
+        <v>99</v>
+      </c>
+      <c r="C96" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" t="s">
+        <v>154</v>
+      </c>
+      <c r="E96" t="s">
+        <v>166</v>
+      </c>
+      <c r="F96" t="s">
+        <v>169</v>
+      </c>
+      <c r="G96" t="s">
+        <v>256</v>
+      </c>
+      <c r="H96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" t="s">
+        <v>99</v>
+      </c>
+      <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" t="s">
+        <v>154</v>
+      </c>
+      <c r="E97" t="s">
+        <v>166</v>
+      </c>
+      <c r="F97" t="s">
+        <v>170</v>
+      </c>
+      <c r="G97" t="s">
+        <v>257</v>
+      </c>
+      <c r="H97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
+        <v>154</v>
+      </c>
+      <c r="E98" t="s">
+        <v>166</v>
+      </c>
+      <c r="F98" t="s">
+        <v>167</v>
+      </c>
+      <c r="G98" t="s">
+        <v>258</v>
+      </c>
+      <c r="H98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>49</v>
+      </c>
+      <c r="B99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>154</v>
+      </c>
+      <c r="E99" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" t="s">
+        <v>166</v>
+      </c>
+      <c r="G99" t="s">
+        <v>259</v>
+      </c>
+      <c r="H99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>49</v>
+      </c>
+      <c r="B100" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
+        <v>154</v>
+      </c>
+      <c r="E100" t="s">
+        <v>166</v>
+      </c>
+      <c r="F100" t="s">
+        <v>167</v>
+      </c>
+      <c r="G100" t="s">
+        <v>260</v>
+      </c>
+      <c r="H100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>49</v>
+      </c>
+      <c r="B101" t="s">
+        <v>99</v>
+      </c>
+      <c r="C101" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" t="s">
+        <v>154</v>
+      </c>
+      <c r="E101" t="s">
+        <v>166</v>
+      </c>
+      <c r="F101" t="s">
+        <v>169</v>
+      </c>
+      <c r="G101" t="s">
+        <v>261</v>
+      </c>
+      <c r="H101">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>49</v>
+      </c>
+      <c r="B102" t="s">
+        <v>99</v>
+      </c>
+      <c r="C102" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" t="s">
+        <v>154</v>
+      </c>
+      <c r="E102" t="s">
+        <v>166</v>
+      </c>
+      <c r="F102" t="s">
+        <v>169</v>
+      </c>
+      <c r="G102" t="s">
+        <v>262</v>
+      </c>
+      <c r="H102">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>49</v>
+      </c>
+      <c r="B103" t="s">
+        <v>99</v>
+      </c>
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" t="s">
+        <v>154</v>
+      </c>
+      <c r="E103" t="s">
+        <v>166</v>
+      </c>
+      <c r="F103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G103" t="s">
+        <v>263</v>
+      </c>
+      <c r="H103">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>49</v>
+      </c>
+      <c r="B104" t="s">
+        <v>99</v>
+      </c>
+      <c r="C104" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104" t="s">
+        <v>154</v>
+      </c>
+      <c r="E104" t="s">
+        <v>166</v>
+      </c>
+      <c r="F104" t="s">
+        <v>167</v>
+      </c>
+      <c r="G104" t="s">
+        <v>264</v>
+      </c>
+      <c r="H104">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>50</v>
+      </c>
+      <c r="B105" t="s">
+        <v>100</v>
+      </c>
+      <c r="C105" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" t="s">
+        <v>155</v>
+      </c>
+      <c r="E105" t="s">
+        <v>166</v>
+      </c>
+      <c r="F105" t="s">
+        <v>166</v>
+      </c>
+      <c r="G105" t="s">
+        <v>265</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>50</v>
+      </c>
+      <c r="B106" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106" t="s">
+        <v>112</v>
+      </c>
+      <c r="D106" t="s">
+        <v>155</v>
+      </c>
+      <c r="E106" t="s">
+        <v>166</v>
+      </c>
+      <c r="F106" t="s">
+        <v>167</v>
+      </c>
+      <c r="G106" t="s">
+        <v>266</v>
+      </c>
+      <c r="H106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>51</v>
+      </c>
+      <c r="B107" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" t="s">
+        <v>156</v>
+      </c>
+      <c r="E107" t="s">
+        <v>166</v>
+      </c>
+      <c r="F107" t="s">
+        <v>167</v>
+      </c>
+      <c r="G107" t="s">
+        <v>267</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>51</v>
+      </c>
+      <c r="B108" t="s">
+        <v>101</v>
+      </c>
+      <c r="C108" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" t="s">
+        <v>156</v>
+      </c>
+      <c r="E108" t="s">
+        <v>166</v>
+      </c>
+      <c r="F108" t="s">
+        <v>166</v>
+      </c>
+      <c r="G108" t="s">
+        <v>267</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" t="s">
+        <v>102</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" t="s">
+        <v>157</v>
+      </c>
+      <c r="E109" t="s">
+        <v>165</v>
+      </c>
+      <c r="F109" t="s">
+        <v>165</v>
+      </c>
+      <c r="G109" t="s">
+        <v>268</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" t="s">
+        <v>157</v>
+      </c>
+      <c r="E110" t="s">
+        <v>165</v>
+      </c>
+      <c r="F110" t="s">
+        <v>166</v>
+      </c>
+      <c r="G110" t="s">
+        <v>269</v>
+      </c>
+      <c r="H110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>52</v>
+      </c>
+      <c r="B111" t="s">
+        <v>102</v>
+      </c>
+      <c r="C111" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" t="s">
+        <v>157</v>
+      </c>
+      <c r="E111" t="s">
+        <v>165</v>
+      </c>
+      <c r="F111" t="s">
+        <v>167</v>
+      </c>
+      <c r="G111" t="s">
+        <v>270</v>
+      </c>
+      <c r="H111">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>53</v>
+      </c>
+      <c r="B112" t="s">
+        <v>103</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" t="s">
+        <v>158</v>
+      </c>
+      <c r="E112" t="s">
+        <v>166</v>
+      </c>
+      <c r="F112" t="s">
+        <v>166</v>
+      </c>
+      <c r="G112" t="s">
+        <v>271</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>53</v>
+      </c>
+      <c r="B113" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
+        <v>158</v>
+      </c>
+      <c r="E113" t="s">
+        <v>166</v>
+      </c>
+      <c r="F113" t="s">
+        <v>167</v>
+      </c>
+      <c r="G113" t="s">
+        <v>272</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>54</v>
+      </c>
+      <c r="B114" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" t="s">
+        <v>112</v>
+      </c>
+      <c r="D114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E114" t="s">
+        <v>166</v>
+      </c>
+      <c r="F114" t="s">
+        <v>166</v>
+      </c>
+      <c r="G114" t="s">
+        <v>273</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" t="s">
+        <v>104</v>
+      </c>
+      <c r="C115" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" t="s">
+        <v>159</v>
+      </c>
+      <c r="E115" t="s">
+        <v>166</v>
+      </c>
+      <c r="F115" t="s">
+        <v>167</v>
+      </c>
+      <c r="G115" t="s">
+        <v>274</v>
+      </c>
+      <c r="H115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116" t="s">
+        <v>105</v>
+      </c>
+      <c r="C116" t="s">
+        <v>112</v>
+      </c>
+      <c r="D116" t="s">
+        <v>160</v>
+      </c>
+      <c r="E116" t="s">
+        <v>166</v>
+      </c>
+      <c r="F116" t="s">
+        <v>166</v>
+      </c>
+      <c r="G116" t="s">
+        <v>275</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117" t="s">
+        <v>105</v>
+      </c>
+      <c r="C117" t="s">
+        <v>112</v>
+      </c>
+      <c r="D117" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" t="s">
+        <v>166</v>
+      </c>
+      <c r="F117" t="s">
+        <v>167</v>
+      </c>
+      <c r="G117" t="s">
+        <v>276</v>
+      </c>
+      <c r="H117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>56</v>
+      </c>
+      <c r="B118" t="s">
+        <v>106</v>
+      </c>
+      <c r="C118" t="s">
+        <v>112</v>
+      </c>
+      <c r="D118" t="s">
+        <v>161</v>
+      </c>
+      <c r="E118" t="s">
+        <v>165</v>
+      </c>
+      <c r="F118" t="s">
+        <v>165</v>
+      </c>
+      <c r="G118" t="s">
+        <v>277</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>56</v>
+      </c>
+      <c r="B119" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" t="s">
+        <v>112</v>
+      </c>
+      <c r="D119" t="s">
+        <v>161</v>
+      </c>
+      <c r="E119" t="s">
+        <v>165</v>
+      </c>
+      <c r="F119" t="s">
+        <v>166</v>
+      </c>
+      <c r="G119" t="s">
+        <v>278</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>56</v>
+      </c>
+      <c r="B120" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" t="s">
+        <v>161</v>
+      </c>
+      <c r="E120" t="s">
+        <v>165</v>
+      </c>
+      <c r="F120" t="s">
+        <v>167</v>
+      </c>
+      <c r="G120" t="s">
+        <v>279</v>
+      </c>
+      <c r="H120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>57</v>
+      </c>
+      <c r="B121" t="s">
+        <v>107</v>
+      </c>
+      <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" t="s">
+        <v>166</v>
+      </c>
+      <c r="F121" t="s">
+        <v>166</v>
+      </c>
+      <c r="G121" t="s">
+        <v>280</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>57</v>
+      </c>
+      <c r="B122" t="s">
+        <v>107</v>
+      </c>
+      <c r="C122" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" t="s">
+        <v>162</v>
+      </c>
+      <c r="E122" t="s">
+        <v>166</v>
+      </c>
+      <c r="F122" t="s">
+        <v>167</v>
+      </c>
+      <c r="G122" t="s">
+        <v>281</v>
+      </c>
+      <c r="H122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>58</v>
+      </c>
+      <c r="B123" t="s">
+        <v>108</v>
+      </c>
+      <c r="C123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" t="s">
+        <v>163</v>
+      </c>
+      <c r="E123" t="s">
+        <v>166</v>
+      </c>
+      <c r="F123" t="s">
+        <v>167</v>
+      </c>
+      <c r="G123" t="s">
+        <v>282</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>58</v>
+      </c>
+      <c r="B124" t="s">
+        <v>108</v>
+      </c>
+      <c r="C124" t="s">
+        <v>112</v>
+      </c>
+      <c r="D124" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" t="s">
+        <v>166</v>
+      </c>
+      <c r="F124" t="s">
+        <v>166</v>
+      </c>
+      <c r="G124" t="s">
+        <v>283</v>
+      </c>
+      <c r="H124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>59</v>
+      </c>
+      <c r="B125" t="s">
+        <v>109</v>
+      </c>
+      <c r="C125" t="s">
+        <v>112</v>
+      </c>
+      <c r="D125" t="s">
+        <v>164</v>
+      </c>
+      <c r="E125" t="s">
+        <v>166</v>
+      </c>
+      <c r="F125" t="s">
+        <v>166</v>
+      </c>
+      <c r="G125" t="s">
+        <v>284</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>59</v>
+      </c>
+      <c r="B126" t="s">
+        <v>109</v>
+      </c>
+      <c r="C126" t="s">
+        <v>112</v>
+      </c>
+      <c r="D126" t="s">
+        <v>164</v>
+      </c>
+      <c r="E126" t="s">
+        <v>166</v>
+      </c>
+      <c r="F126" t="s">
+        <v>167</v>
+      </c>
+      <c r="G126" t="s">
+        <v>285</v>
+      </c>
+      <c r="H126">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="55">
   <si>
     <t>code</t>
   </si>
@@ -64,30 +64,6 @@
     <t>941bb532-7c5e-4c33-baca-ee0b2d06fb62</t>
   </si>
   <si>
-    <t>96d663ec-f298-4560-9b84-996b8de92249</t>
-  </si>
-  <si>
-    <t>bcd04260-5f2a-4732-99e6-e2a415b8b206</t>
-  </si>
-  <si>
-    <t>19131aed-4f2e-465e-a7f6-9c0d50cbf975</t>
-  </si>
-  <si>
-    <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
-  </si>
-  <si>
-    <t>2b350499-a5b6-45ce-97b3-88359725419f</t>
-  </si>
-  <si>
-    <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
-  </si>
-  <si>
-    <t>2155505c-bb3d-48ec-ba48-ac98edbdca95</t>
-  </si>
-  <si>
-    <t>abbb91f7-66fb-497f-87e0-235b843068fd</t>
-  </si>
-  <si>
     <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
   </si>
   <si>
@@ -112,30 +88,6 @@
     <t>ALL BERKEMBANG BERSAMA</t>
   </si>
   <si>
-    <t>TRAKINDO UTAMA, PT</t>
-  </si>
-  <si>
-    <t>BRI UNIT BUALEMO</t>
-  </si>
-  <si>
-    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
-  </si>
-  <si>
-    <t>BANK PERKREDITAN RAKYAT MITRA NIAGA BANGGAI</t>
-  </si>
-  <si>
-    <t>BANK SULTENG</t>
-  </si>
-  <si>
-    <t>TOTALINDO BANGGAI PERKASA</t>
-  </si>
-  <si>
-    <t>REKAYASA INDUSTRI PT</t>
-  </si>
-  <si>
-    <t>JOB PERTAMINA - MEDCO E&amp;P TOMORI SULAWESI</t>
-  </si>
-  <si>
     <t>SUBMITTED RESPONDENT</t>
   </si>
   <si>
@@ -169,30 +121,6 @@
     <t>allswalayan@ymail.com</t>
   </si>
   <si>
-    <t>info_trakindo@gmail.com</t>
-  </si>
-  <si>
-    <t>nbobs@corp.brico.id</t>
-  </si>
-  <si>
-    <t>bca_luwuk_pajak@gmail.com</t>
-  </si>
-  <si>
-    <t>toili@mailnesia.com</t>
-  </si>
-  <si>
-    <t>banksulteng.toili@yahoo.com</t>
-  </si>
-  <si>
-    <t>totalindobatbperkasa@gmail.com</t>
-  </si>
-  <si>
-    <t>wandysendjaja@yahoo.com</t>
-  </si>
-  <si>
-    <t>haris.ismail@job-tomori.com</t>
-  </si>
-  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -251,60 +179,6 @@
   </si>
   <si>
     <t>02 Jun 2026, 04:32:41</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 04:39:27</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 04:39:23</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 06:50:12</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:02:57</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:34:59</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:34:56</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 02:11:11</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:10:03</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 00:12:21</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 00:11:48</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 05:57:24</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 05:57:20</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:05:04</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:49:00</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:48:57</t>
-  </si>
-  <si>
-    <t>18 May 2026, 12:37:49</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 09:53:25</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 05:51:24</t>
   </si>
 </sst>
 </file>
@@ -662,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -696,22 +570,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>40</v>
-      </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -722,22 +596,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -748,22 +622,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
         <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" t="s">
-        <v>64</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -774,22 +648,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -800,22 +674,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -826,22 +700,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -852,22 +726,22 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -878,22 +752,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -904,22 +778,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
         <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>70</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -930,22 +804,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
         <v>46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>70</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -956,22 +830,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" t="s">
-        <v>71</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -982,22 +856,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1008,22 +882,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1034,22 +908,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -1060,22 +934,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1086,22 +960,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -1112,22 +986,22 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1138,519 +1012,25 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="H19">
         <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
-      <c r="E20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" t="s">
-        <v>79</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" t="s">
-        <v>80</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" t="s">
-        <v>59</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27" t="s">
-        <v>85</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" t="s">
-        <v>86</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" t="s">
-        <v>60</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35" t="s">
-        <v>93</v>
-      </c>
-      <c r="H35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" t="s">
-        <v>42</v>
-      </c>
-      <c r="D37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" t="s">
-        <v>59</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" t="s">
-        <v>96</v>
-      </c>
-      <c r="H38">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="74">
   <si>
     <t>code</t>
   </si>
@@ -64,6 +64,18 @@
     <t>941bb532-7c5e-4c33-baca-ee0b2d06fb62</t>
   </si>
   <si>
+    <t>96d663ec-f298-4560-9b84-996b8de92249</t>
+  </si>
+  <si>
+    <t>bcd04260-5f2a-4732-99e6-e2a415b8b206</t>
+  </si>
+  <si>
+    <t>19131aed-4f2e-465e-a7f6-9c0d50cbf975</t>
+  </si>
+  <si>
+    <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
+  </si>
+  <si>
     <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
   </si>
   <si>
@@ -88,6 +100,18 @@
     <t>ALL BERKEMBANG BERSAMA</t>
   </si>
   <si>
+    <t>TRAKINDO UTAMA, PT</t>
+  </si>
+  <si>
+    <t>BRI UNIT BUALEMO</t>
+  </si>
+  <si>
+    <t>BANK CENTRAL ASIA TBK. CABANG LUWUK</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT MITRA NIAGA BANGGAI</t>
+  </si>
+  <si>
     <t>SUBMITTED RESPONDENT</t>
   </si>
   <si>
@@ -121,6 +145,18 @@
     <t>allswalayan@ymail.com</t>
   </si>
   <si>
+    <t>info_trakindo@gmail.com</t>
+  </si>
+  <si>
+    <t>nbobs@corp.brico.id</t>
+  </si>
+  <si>
+    <t>bca_luwuk_pajak@gmail.com</t>
+  </si>
+  <si>
+    <t>toili@mailnesia.com</t>
+  </si>
+  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -179,6 +215,27 @@
   </si>
   <si>
     <t>02 Jun 2026, 04:32:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:39:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:39:23</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:50:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:02:57</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:59</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:34:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:11:11</t>
   </si>
 </sst>
 </file>
@@ -536,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -570,22 +627,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -596,22 +653,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -622,22 +679,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -648,22 +705,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -674,22 +731,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -700,22 +757,22 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -726,22 +783,22 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -752,22 +809,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -778,22 +835,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -804,22 +861,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -830,22 +887,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -856,22 +913,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -882,22 +939,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -908,22 +965,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -934,22 +991,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -960,22 +1017,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -986,22 +1043,22 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1012,25 +1069,233 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="H19">
         <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="238">
   <si>
     <t>code</t>
   </si>
@@ -67,7 +67,7 @@
     <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
   </si>
   <si>
-    <t>2b350499-a5b6-45ce-97b3-88359725419f</t>
+    <t>aed96e17-8337-406e-9f72-c02f709f865c</t>
   </si>
   <si>
     <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
@@ -127,6 +127,42 @@
     <t>df80536f-5125-46c8-aa0a-220b8d26441b</t>
   </si>
   <si>
+    <t>e674036e-bee0-47b7-bc94-a0c32bfa2d71</t>
+  </si>
+  <si>
+    <t>081008bc-6a02-4888-bfb2-2c1c805fa4ad</t>
+  </si>
+  <si>
+    <t>358e68c2-9ecd-47b3-85a5-e07045612b91</t>
+  </si>
+  <si>
+    <t>9e3fbec4-42cd-41c0-9b1d-f442487ed552</t>
+  </si>
+  <si>
+    <t>01b351f3-b52c-4516-a91c-00f58d08579d</t>
+  </si>
+  <si>
+    <t>7880f953-35e8-4387-aac5-b4a94b0c3c2e</t>
+  </si>
+  <si>
+    <t>74e56a04-fcd1-4332-ba6e-1bfb657dc781</t>
+  </si>
+  <si>
+    <t>d61d41d8-08d5-40a5-9a4b-ec2cda0629c1</t>
+  </si>
+  <si>
+    <t>66b93b8d-817c-4af4-9183-47792e43d54e</t>
+  </si>
+  <si>
+    <t>b6c21085-5e3c-4d3b-bcb0-1e48c3bbaca7</t>
+  </si>
+  <si>
+    <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
+  </si>
+  <si>
+    <t>8d3e9626-0215-47a7-86cd-bf85990128c8</t>
+  </si>
+  <si>
     <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
   </si>
   <si>
@@ -214,6 +250,42 @@
     <t>BANK BPD</t>
   </si>
   <si>
+    <t>AKAR DAYA MANDIRI PT</t>
+  </si>
+  <si>
+    <t>BANK BPR PALU LOKADANA UTAMA CAB POSO, PT</t>
+  </si>
+  <si>
+    <t>AMRI MARGA JAYA, PT</t>
+  </si>
+  <si>
+    <t>PLTA Poso 1</t>
+  </si>
+  <si>
+    <t>KCP MANDIRI MITRA USAHA TENTENA</t>
+  </si>
+  <si>
+    <t>PNM MODAL MIKRO</t>
+  </si>
+  <si>
+    <t>Balindo Manunggal Bersama, PT</t>
+  </si>
+  <si>
+    <t>FIF, PT</t>
+  </si>
+  <si>
+    <t>SEKOLAH POLISI NEGARA</t>
+  </si>
+  <si>
+    <t>PDAM KAB DONGGALA</t>
+  </si>
+  <si>
+    <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
+  </si>
+  <si>
+    <t>PT. BANK SULTENG KAS LABEAN</t>
+  </si>
+  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -313,6 +385,42 @@
     <t>bsposo@yahoo.com</t>
   </si>
   <si>
+    <t>akardayamandiri49@gmail.com</t>
+  </si>
+  <si>
+    <t>kc.poso@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>pt.amrimargajaya@ymail.com</t>
+  </si>
+  <si>
+    <t>pltaposo2@posoenergy.com</t>
+  </si>
+  <si>
+    <t>kcpmandirimitrausaha@gmail.com</t>
+  </si>
+  <si>
+    <t>ulamposo@gmail.com</t>
+  </si>
+  <si>
+    <t>gracekayupa@gmail.com</t>
+  </si>
+  <si>
+    <t>dewiputrihilika90@gmail.com</t>
+  </si>
+  <si>
+    <t>kppnpalu651707@yahoo.com</t>
+  </si>
+  <si>
+    <t>pdam_donggala@gmail.com</t>
+  </si>
+  <si>
+    <t>bprlabuan@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>banksulteng_kaslabean@yahoo.com</t>
+  </si>
+  <si>
     <t>Permanent_fail</t>
   </si>
   <si>
@@ -322,6 +430,15 @@
     <t>Queued</t>
   </si>
   <si>
+    <t>Clicked</t>
+  </si>
+  <si>
+    <t>Opened</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
     <t>09 Jun 2026, 11:00:04</t>
   </si>
   <si>
@@ -512,6 +629,105 @@
   </si>
   <si>
     <t>02 Jun 2026, 08:52:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:17:21</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:59:00</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:58:55</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:13:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:37:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:08:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:07:16</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:14</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:47:26</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:34:35</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:38</t>
+  </si>
+  <si>
+    <t>26 May 2026, 07:30:35</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:58</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:55</t>
+  </si>
+  <si>
+    <t>31 May 2026, 12:04:51</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:40:36</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:53</t>
+  </si>
+  <si>
+    <t>26 May 2026, 11:27:52</t>
+  </si>
+  <si>
+    <t>26 May 2026, 09:13:56</t>
+  </si>
+  <si>
+    <t>26 May 2026, 08:30:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 13:44:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:54:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:32</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:30:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:29:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:31:35</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:02:07</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:30:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:29:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:12:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:35</t>
   </si>
 </sst>
 </file>
@@ -869,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -903,22 +1119,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G2" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -929,22 +1145,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G3" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -955,22 +1171,22 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -981,22 +1197,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1007,22 +1223,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G6" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -1033,22 +1249,22 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G7" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1059,22 +1275,22 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G8" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1085,22 +1301,22 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G9" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1111,22 +1327,22 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1137,22 +1353,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1163,22 +1379,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1189,22 +1405,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1215,22 +1431,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G14" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -1241,22 +1457,22 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1267,22 +1483,22 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -1293,22 +1509,22 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1319,22 +1535,22 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="H18">
         <v>2</v>
@@ -1345,22 +1561,22 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1371,22 +1587,22 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G20" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="H20">
         <v>2</v>
@@ -1397,22 +1613,22 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="H21">
         <v>3</v>
@@ -1423,22 +1639,22 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G22" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1449,22 +1665,22 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1475,22 +1691,22 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H24">
         <v>2</v>
@@ -1501,22 +1717,22 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="H25">
         <v>3</v>
@@ -1527,22 +1743,22 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1553,22 +1769,22 @@
         <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1579,22 +1795,22 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="H28">
         <v>3</v>
@@ -1605,22 +1821,22 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1631,22 +1847,22 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1657,22 +1873,22 @@
         <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -1683,22 +1899,22 @@
         <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1709,22 +1925,22 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H33">
         <v>2</v>
@@ -1735,22 +1951,22 @@
         <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="H34">
         <v>3</v>
@@ -1761,22 +1977,22 @@
         <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1787,22 +2003,22 @@
         <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -1813,22 +2029,22 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E37" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="H37">
         <v>3</v>
@@ -1839,22 +2055,22 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -1865,22 +2081,22 @@
         <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -1891,22 +2107,22 @@
         <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -1917,22 +2133,22 @@
         <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G41" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="H41">
         <v>2</v>
@@ -1943,22 +2159,22 @@
         <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="H42">
         <v>3</v>
@@ -1969,22 +2185,22 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D43" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G43" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1995,22 +2211,22 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G44" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -2021,22 +2237,22 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G45" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -2047,22 +2263,22 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G46" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2073,22 +2289,22 @@
         <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>174</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -2099,22 +2315,22 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E48" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F48" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2125,22 +2341,22 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D49" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F49" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G49" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -2151,22 +2367,22 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G50" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="H50">
         <v>3</v>
@@ -2177,22 +2393,22 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G51" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2203,22 +2419,22 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G52" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -2229,22 +2445,22 @@
         <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E53" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G53" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="H53">
         <v>3</v>
@@ -2255,22 +2471,22 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G54" t="s">
-        <v>140</v>
+        <v>179</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -2281,22 +2497,22 @@
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F55" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G55" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="H55">
         <v>2</v>
@@ -2307,22 +2523,22 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E56" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F56" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G56" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2333,22 +2549,22 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D57" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F57" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
-        <v>143</v>
+        <v>182</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -2359,22 +2575,22 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F58" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G58" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="H58">
         <v>3</v>
@@ -2385,22 +2601,22 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D59" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E59" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F59" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G59" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2411,22 +2627,22 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D60" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E60" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G60" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -2437,22 +2653,22 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F61" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G61" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2463,22 +2679,22 @@
         <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G62" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2489,22 +2705,22 @@
         <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G63" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="H63">
         <v>2</v>
@@ -2515,22 +2731,22 @@
         <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D64" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E64" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F64" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G64" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2541,22 +2757,22 @@
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D65" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E65" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F65" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G65" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -2567,22 +2783,22 @@
         <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E66" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G66" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2593,22 +2809,22 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E67" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F67" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G67" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -2619,22 +2835,22 @@
         <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F68" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G68" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2645,22 +2861,22 @@
         <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E69" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F69" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G69" t="s">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="H69">
         <v>2</v>
@@ -2671,22 +2887,22 @@
         <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D70" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E70" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F70" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="G70" t="s">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2697,22 +2913,22 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D71" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G71" t="s">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="H71">
         <v>2</v>
@@ -2723,22 +2939,22 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D72" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E72" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F72" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G72" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -2749,22 +2965,22 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D73" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E73" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F73" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G73" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2775,22 +2991,22 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E74" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F74" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G74" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -2801,22 +3017,22 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D75" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E75" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F75" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G75" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -2827,22 +3043,22 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D76" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E76" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F76" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G76" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -2853,22 +3069,22 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E77" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F77" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G77" t="s">
-        <v>158</v>
+        <v>197</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -2879,22 +3095,22 @@
         <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C78" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E78" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F78" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G78" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="H78">
         <v>2</v>
@@ -2905,22 +3121,22 @@
         <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D79" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E79" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F79" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G79" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2931,22 +3147,22 @@
         <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C80" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D80" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E80" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F80" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G80" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -2957,22 +3173,22 @@
         <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D81" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E81" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F81" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G81" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2983,22 +3199,22 @@
         <v>35</v>
       </c>
       <c r="B82" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C82" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D82" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E82" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F82" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="G82" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="H82">
         <v>2</v>
@@ -3009,22 +3225,22 @@
         <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D83" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E83" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F83" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G83" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3035,24 +3251,1376 @@
         <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E84" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="F84" t="s">
+        <v>137</v>
+      </c>
+      <c r="G84" t="s">
+        <v>204</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>37</v>
+      </c>
+      <c r="B85" t="s">
+        <v>78</v>
+      </c>
+      <c r="C85" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" t="s">
+        <v>123</v>
+      </c>
+      <c r="E85" t="s">
+        <v>136</v>
+      </c>
+      <c r="F85" t="s">
+        <v>136</v>
+      </c>
+      <c r="G85" t="s">
+        <v>205</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>37</v>
+      </c>
+      <c r="B86" t="s">
+        <v>78</v>
+      </c>
+      <c r="C86" t="s">
+        <v>90</v>
+      </c>
+      <c r="D86" t="s">
+        <v>123</v>
+      </c>
+      <c r="E86" t="s">
+        <v>136</v>
+      </c>
+      <c r="F86" t="s">
+        <v>137</v>
+      </c>
+      <c r="G86" t="s">
+        <v>205</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" t="s">
         <v>101</v>
       </c>
-      <c r="G84" t="s">
+      <c r="E87" t="s">
+        <v>135</v>
+      </c>
+      <c r="F87" t="s">
+        <v>135</v>
+      </c>
+      <c r="G87" t="s">
+        <v>160</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88" t="s">
+        <v>101</v>
+      </c>
+      <c r="E88" t="s">
+        <v>135</v>
+      </c>
+      <c r="F88" t="s">
+        <v>136</v>
+      </c>
+      <c r="G88" t="s">
+        <v>161</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" t="s">
+        <v>90</v>
+      </c>
+      <c r="D89" t="s">
+        <v>101</v>
+      </c>
+      <c r="E89" t="s">
+        <v>135</v>
+      </c>
+      <c r="F89" t="s">
+        <v>137</v>
+      </c>
+      <c r="G89" t="s">
+        <v>162</v>
+      </c>
+      <c r="H89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" t="s">
+        <v>58</v>
+      </c>
+      <c r="C90" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" t="s">
+        <v>135</v>
+      </c>
+      <c r="F90" t="s">
+        <v>135</v>
+      </c>
+      <c r="G90" t="s">
+        <v>160</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C91" t="s">
+        <v>90</v>
+      </c>
+      <c r="D91" t="s">
+        <v>101</v>
+      </c>
+      <c r="E91" t="s">
+        <v>135</v>
+      </c>
+      <c r="F91" t="s">
+        <v>136</v>
+      </c>
+      <c r="G91" t="s">
+        <v>161</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>17</v>
+      </c>
+      <c r="B92" t="s">
+        <v>58</v>
+      </c>
+      <c r="C92" t="s">
+        <v>90</v>
+      </c>
+      <c r="D92" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" t="s">
+        <v>135</v>
+      </c>
+      <c r="F92" t="s">
+        <v>137</v>
+      </c>
+      <c r="G92" t="s">
+        <v>162</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>17</v>
+      </c>
+      <c r="B93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" t="s">
+        <v>90</v>
+      </c>
+      <c r="D93" t="s">
+        <v>102</v>
+      </c>
+      <c r="E93" t="s">
+        <v>135</v>
+      </c>
+      <c r="F93" t="s">
+        <v>135</v>
+      </c>
+      <c r="G93" t="s">
+        <v>163</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>17</v>
+      </c>
+      <c r="B94" t="s">
+        <v>58</v>
+      </c>
+      <c r="C94" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" t="s">
+        <v>103</v>
+      </c>
+      <c r="E94" t="s">
+        <v>136</v>
+      </c>
+      <c r="F94" t="s">
+        <v>136</v>
+      </c>
+      <c r="G94" t="s">
+        <v>164</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>17</v>
+      </c>
+      <c r="B95" t="s">
+        <v>58</v>
+      </c>
+      <c r="C95" t="s">
+        <v>90</v>
+      </c>
+      <c r="D95" t="s">
+        <v>103</v>
+      </c>
+      <c r="E95" t="s">
+        <v>136</v>
+      </c>
+      <c r="F95" t="s">
+        <v>137</v>
+      </c>
+      <c r="G95" t="s">
         <v>165</v>
       </c>
-      <c r="H84">
+      <c r="H95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" t="s">
+        <v>90</v>
+      </c>
+      <c r="D96" t="s">
+        <v>101</v>
+      </c>
+      <c r="E96" t="s">
+        <v>135</v>
+      </c>
+      <c r="F96" t="s">
+        <v>135</v>
+      </c>
+      <c r="G96" t="s">
+        <v>160</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>17</v>
+      </c>
+      <c r="B97" t="s">
+        <v>58</v>
+      </c>
+      <c r="C97" t="s">
+        <v>90</v>
+      </c>
+      <c r="D97" t="s">
+        <v>101</v>
+      </c>
+      <c r="E97" t="s">
+        <v>135</v>
+      </c>
+      <c r="F97" t="s">
+        <v>136</v>
+      </c>
+      <c r="G97" t="s">
+        <v>161</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" t="s">
+        <v>58</v>
+      </c>
+      <c r="C98" t="s">
+        <v>90</v>
+      </c>
+      <c r="D98" t="s">
+        <v>101</v>
+      </c>
+      <c r="E98" t="s">
+        <v>135</v>
+      </c>
+      <c r="F98" t="s">
+        <v>137</v>
+      </c>
+      <c r="G98" t="s">
+        <v>162</v>
+      </c>
+      <c r="H98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>17</v>
+      </c>
+      <c r="B99" t="s">
+        <v>58</v>
+      </c>
+      <c r="C99" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" t="s">
+        <v>101</v>
+      </c>
+      <c r="E99" t="s">
+        <v>135</v>
+      </c>
+      <c r="F99" t="s">
+        <v>135</v>
+      </c>
+      <c r="G99" t="s">
+        <v>160</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>17</v>
+      </c>
+      <c r="B100" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" t="s">
+        <v>90</v>
+      </c>
+      <c r="D100" t="s">
+        <v>101</v>
+      </c>
+      <c r="E100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F100" t="s">
+        <v>136</v>
+      </c>
+      <c r="G100" t="s">
+        <v>161</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" t="s">
+        <v>58</v>
+      </c>
+      <c r="C101" t="s">
+        <v>90</v>
+      </c>
+      <c r="D101" t="s">
+        <v>101</v>
+      </c>
+      <c r="E101" t="s">
+        <v>135</v>
+      </c>
+      <c r="F101" t="s">
+        <v>137</v>
+      </c>
+      <c r="G101" t="s">
+        <v>162</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" t="s">
+        <v>124</v>
+      </c>
+      <c r="E102" t="s">
+        <v>136</v>
+      </c>
+      <c r="F102" t="s">
+        <v>136</v>
+      </c>
+      <c r="G102" t="s">
+        <v>206</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" t="s">
+        <v>90</v>
+      </c>
+      <c r="D103" t="s">
+        <v>124</v>
+      </c>
+      <c r="E103" t="s">
+        <v>136</v>
+      </c>
+      <c r="F103" t="s">
+        <v>137</v>
+      </c>
+      <c r="G103" t="s">
+        <v>207</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>39</v>
+      </c>
+      <c r="B104" t="s">
+        <v>80</v>
+      </c>
+      <c r="C104" t="s">
+        <v>90</v>
+      </c>
+      <c r="D104" t="s">
+        <v>125</v>
+      </c>
+      <c r="E104" t="s">
+        <v>135</v>
+      </c>
+      <c r="F104" t="s">
+        <v>135</v>
+      </c>
+      <c r="G104" t="s">
+        <v>208</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B105" t="s">
+        <v>80</v>
+      </c>
+      <c r="C105" t="s">
+        <v>90</v>
+      </c>
+      <c r="D105" t="s">
+        <v>125</v>
+      </c>
+      <c r="E105" t="s">
+        <v>135</v>
+      </c>
+      <c r="F105" t="s">
+        <v>136</v>
+      </c>
+      <c r="G105" t="s">
+        <v>209</v>
+      </c>
+      <c r="H105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" t="s">
+        <v>80</v>
+      </c>
+      <c r="C106" t="s">
+        <v>90</v>
+      </c>
+      <c r="D106" t="s">
+        <v>125</v>
+      </c>
+      <c r="E106" t="s">
+        <v>135</v>
+      </c>
+      <c r="F106" t="s">
+        <v>137</v>
+      </c>
+      <c r="G106" t="s">
+        <v>210</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>81</v>
+      </c>
+      <c r="C107" t="s">
+        <v>90</v>
+      </c>
+      <c r="D107" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" t="s">
+        <v>136</v>
+      </c>
+      <c r="F107" t="s">
+        <v>136</v>
+      </c>
+      <c r="G107" t="s">
+        <v>211</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>81</v>
+      </c>
+      <c r="C108" t="s">
+        <v>90</v>
+      </c>
+      <c r="D108" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" t="s">
+        <v>136</v>
+      </c>
+      <c r="F108" t="s">
+        <v>137</v>
+      </c>
+      <c r="G108" t="s">
+        <v>212</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>41</v>
+      </c>
+      <c r="B109" t="s">
+        <v>82</v>
+      </c>
+      <c r="C109" t="s">
+        <v>90</v>
+      </c>
+      <c r="D109" t="s">
+        <v>127</v>
+      </c>
+      <c r="E109" t="s">
+        <v>135</v>
+      </c>
+      <c r="F109" t="s">
+        <v>135</v>
+      </c>
+      <c r="G109" t="s">
+        <v>213</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>41</v>
+      </c>
+      <c r="B110" t="s">
+        <v>82</v>
+      </c>
+      <c r="C110" t="s">
+        <v>90</v>
+      </c>
+      <c r="D110" t="s">
+        <v>127</v>
+      </c>
+      <c r="E110" t="s">
+        <v>135</v>
+      </c>
+      <c r="F110" t="s">
+        <v>137</v>
+      </c>
+      <c r="G110" t="s">
+        <v>214</v>
+      </c>
+      <c r="H110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>41</v>
+      </c>
+      <c r="B111" t="s">
+        <v>82</v>
+      </c>
+      <c r="C111" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111" t="s">
+        <v>127</v>
+      </c>
+      <c r="E111" t="s">
+        <v>135</v>
+      </c>
+      <c r="F111" t="s">
+        <v>136</v>
+      </c>
+      <c r="G111" t="s">
+        <v>214</v>
+      </c>
+      <c r="H111">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" t="s">
+        <v>83</v>
+      </c>
+      <c r="C112" t="s">
+        <v>90</v>
+      </c>
+      <c r="D112" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" t="s">
+        <v>136</v>
+      </c>
+      <c r="F112" t="s">
+        <v>136</v>
+      </c>
+      <c r="G112" t="s">
+        <v>215</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" t="s">
+        <v>83</v>
+      </c>
+      <c r="C113" t="s">
+        <v>90</v>
+      </c>
+      <c r="D113" t="s">
+        <v>128</v>
+      </c>
+      <c r="E113" t="s">
+        <v>136</v>
+      </c>
+      <c r="F113" t="s">
+        <v>137</v>
+      </c>
+      <c r="G113" t="s">
+        <v>215</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>43</v>
+      </c>
+      <c r="B114" t="s">
+        <v>84</v>
+      </c>
+      <c r="C114" t="s">
+        <v>90</v>
+      </c>
+      <c r="D114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" t="s">
+        <v>136</v>
+      </c>
+      <c r="F114" t="s">
+        <v>136</v>
+      </c>
+      <c r="G114" t="s">
+        <v>216</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>43</v>
+      </c>
+      <c r="B115" t="s">
+        <v>84</v>
+      </c>
+      <c r="C115" t="s">
+        <v>90</v>
+      </c>
+      <c r="D115" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115" t="s">
+        <v>136</v>
+      </c>
+      <c r="F115" t="s">
+        <v>137</v>
+      </c>
+      <c r="G115" t="s">
+        <v>217</v>
+      </c>
+      <c r="H115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>44</v>
+      </c>
+      <c r="B116" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" t="s">
+        <v>90</v>
+      </c>
+      <c r="D116" t="s">
+        <v>130</v>
+      </c>
+      <c r="E116" t="s">
+        <v>136</v>
+      </c>
+      <c r="F116" t="s">
+        <v>138</v>
+      </c>
+      <c r="G116" t="s">
+        <v>218</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>44</v>
+      </c>
+      <c r="B117" t="s">
+        <v>85</v>
+      </c>
+      <c r="C117" t="s">
+        <v>90</v>
+      </c>
+      <c r="D117" t="s">
+        <v>130</v>
+      </c>
+      <c r="E117" t="s">
+        <v>136</v>
+      </c>
+      <c r="F117" t="s">
+        <v>139</v>
+      </c>
+      <c r="G117" t="s">
+        <v>219</v>
+      </c>
+      <c r="H117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>44</v>
+      </c>
+      <c r="B118" t="s">
+        <v>85</v>
+      </c>
+      <c r="C118" t="s">
+        <v>90</v>
+      </c>
+      <c r="D118" t="s">
+        <v>130</v>
+      </c>
+      <c r="E118" t="s">
+        <v>136</v>
+      </c>
+      <c r="F118" t="s">
+        <v>139</v>
+      </c>
+      <c r="G118" t="s">
+        <v>220</v>
+      </c>
+      <c r="H118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>44</v>
+      </c>
+      <c r="B119" t="s">
+        <v>85</v>
+      </c>
+      <c r="C119" t="s">
+        <v>90</v>
+      </c>
+      <c r="D119" t="s">
+        <v>130</v>
+      </c>
+      <c r="E119" t="s">
+        <v>136</v>
+      </c>
+      <c r="F119" t="s">
+        <v>139</v>
+      </c>
+      <c r="G119" t="s">
+        <v>221</v>
+      </c>
+      <c r="H119">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" t="s">
+        <v>85</v>
+      </c>
+      <c r="C120" t="s">
+        <v>90</v>
+      </c>
+      <c r="D120" t="s">
+        <v>130</v>
+      </c>
+      <c r="E120" t="s">
+        <v>136</v>
+      </c>
+      <c r="F120" t="s">
+        <v>140</v>
+      </c>
+      <c r="G120" t="s">
+        <v>222</v>
+      </c>
+      <c r="H120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>44</v>
+      </c>
+      <c r="B121" t="s">
+        <v>85</v>
+      </c>
+      <c r="C121" t="s">
+        <v>90</v>
+      </c>
+      <c r="D121" t="s">
+        <v>130</v>
+      </c>
+      <c r="E121" t="s">
+        <v>136</v>
+      </c>
+      <c r="F121" t="s">
+        <v>137</v>
+      </c>
+      <c r="G121" t="s">
+        <v>223</v>
+      </c>
+      <c r="H121">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" t="s">
+        <v>85</v>
+      </c>
+      <c r="C122" t="s">
+        <v>90</v>
+      </c>
+      <c r="D122" t="s">
+        <v>130</v>
+      </c>
+      <c r="E122" t="s">
+        <v>136</v>
+      </c>
+      <c r="F122" t="s">
+        <v>136</v>
+      </c>
+      <c r="G122" t="s">
+        <v>224</v>
+      </c>
+      <c r="H122">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" t="s">
+        <v>85</v>
+      </c>
+      <c r="C123" t="s">
+        <v>90</v>
+      </c>
+      <c r="D123" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123" t="s">
+        <v>136</v>
+      </c>
+      <c r="F123" t="s">
+        <v>137</v>
+      </c>
+      <c r="G123" t="s">
+        <v>225</v>
+      </c>
+      <c r="H123">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>44</v>
+      </c>
+      <c r="B124" t="s">
+        <v>85</v>
+      </c>
+      <c r="C124" t="s">
+        <v>90</v>
+      </c>
+      <c r="D124" t="s">
+        <v>130</v>
+      </c>
+      <c r="E124" t="s">
+        <v>136</v>
+      </c>
+      <c r="F124" t="s">
+        <v>139</v>
+      </c>
+      <c r="G124" t="s">
+        <v>226</v>
+      </c>
+      <c r="H124">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>44</v>
+      </c>
+      <c r="B125" t="s">
+        <v>85</v>
+      </c>
+      <c r="C125" t="s">
+        <v>90</v>
+      </c>
+      <c r="D125" t="s">
+        <v>130</v>
+      </c>
+      <c r="E125" t="s">
+        <v>136</v>
+      </c>
+      <c r="F125" t="s">
+        <v>139</v>
+      </c>
+      <c r="G125" t="s">
+        <v>227</v>
+      </c>
+      <c r="H125">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>44</v>
+      </c>
+      <c r="B126" t="s">
+        <v>85</v>
+      </c>
+      <c r="C126" t="s">
+        <v>90</v>
+      </c>
+      <c r="D126" t="s">
+        <v>130</v>
+      </c>
+      <c r="E126" t="s">
+        <v>136</v>
+      </c>
+      <c r="F126" t="s">
+        <v>140</v>
+      </c>
+      <c r="G126" t="s">
+        <v>228</v>
+      </c>
+      <c r="H126">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>44</v>
+      </c>
+      <c r="B127" t="s">
+        <v>85</v>
+      </c>
+      <c r="C127" t="s">
+        <v>90</v>
+      </c>
+      <c r="D127" t="s">
+        <v>130</v>
+      </c>
+      <c r="E127" t="s">
+        <v>136</v>
+      </c>
+      <c r="F127" t="s">
+        <v>137</v>
+      </c>
+      <c r="G127" t="s">
+        <v>229</v>
+      </c>
+      <c r="H127">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>45</v>
+      </c>
+      <c r="B128" t="s">
+        <v>86</v>
+      </c>
+      <c r="C128" t="s">
+        <v>90</v>
+      </c>
+      <c r="D128" t="s">
+        <v>131</v>
+      </c>
+      <c r="E128" t="s">
+        <v>136</v>
+      </c>
+      <c r="F128" t="s">
+        <v>136</v>
+      </c>
+      <c r="G128" t="s">
+        <v>230</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>45</v>
+      </c>
+      <c r="B129" t="s">
+        <v>86</v>
+      </c>
+      <c r="C129" t="s">
+        <v>90</v>
+      </c>
+      <c r="D129" t="s">
+        <v>131</v>
+      </c>
+      <c r="E129" t="s">
+        <v>136</v>
+      </c>
+      <c r="F129" t="s">
+        <v>137</v>
+      </c>
+      <c r="G129" t="s">
+        <v>231</v>
+      </c>
+      <c r="H129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>46</v>
+      </c>
+      <c r="B130" t="s">
+        <v>87</v>
+      </c>
+      <c r="C130" t="s">
+        <v>90</v>
+      </c>
+      <c r="D130" t="s">
+        <v>132</v>
+      </c>
+      <c r="E130" t="s">
+        <v>136</v>
+      </c>
+      <c r="F130" t="s">
+        <v>137</v>
+      </c>
+      <c r="G130" t="s">
+        <v>232</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>46</v>
+      </c>
+      <c r="B131" t="s">
+        <v>87</v>
+      </c>
+      <c r="C131" t="s">
+        <v>90</v>
+      </c>
+      <c r="D131" t="s">
+        <v>132</v>
+      </c>
+      <c r="E131" t="s">
+        <v>136</v>
+      </c>
+      <c r="F131" t="s">
+        <v>136</v>
+      </c>
+      <c r="G131" t="s">
+        <v>232</v>
+      </c>
+      <c r="H131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>47</v>
+      </c>
+      <c r="B132" t="s">
+        <v>88</v>
+      </c>
+      <c r="C132" t="s">
+        <v>90</v>
+      </c>
+      <c r="D132" t="s">
+        <v>133</v>
+      </c>
+      <c r="E132" t="s">
+        <v>135</v>
+      </c>
+      <c r="F132" t="s">
+        <v>135</v>
+      </c>
+      <c r="G132" t="s">
+        <v>233</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>47</v>
+      </c>
+      <c r="B133" t="s">
+        <v>88</v>
+      </c>
+      <c r="C133" t="s">
+        <v>90</v>
+      </c>
+      <c r="D133" t="s">
+        <v>133</v>
+      </c>
+      <c r="E133" t="s">
+        <v>135</v>
+      </c>
+      <c r="F133" t="s">
+        <v>136</v>
+      </c>
+      <c r="G133" t="s">
+        <v>234</v>
+      </c>
+      <c r="H133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>47</v>
+      </c>
+      <c r="B134" t="s">
+        <v>88</v>
+      </c>
+      <c r="C134" t="s">
+        <v>90</v>
+      </c>
+      <c r="D134" t="s">
+        <v>133</v>
+      </c>
+      <c r="E134" t="s">
+        <v>135</v>
+      </c>
+      <c r="F134" t="s">
+        <v>137</v>
+      </c>
+      <c r="G134" t="s">
+        <v>235</v>
+      </c>
+      <c r="H134">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>48</v>
+      </c>
+      <c r="B135" t="s">
+        <v>89</v>
+      </c>
+      <c r="C135" t="s">
+        <v>90</v>
+      </c>
+      <c r="D135" t="s">
+        <v>134</v>
+      </c>
+      <c r="E135" t="s">
+        <v>136</v>
+      </c>
+      <c r="F135" t="s">
+        <v>136</v>
+      </c>
+      <c r="G135" t="s">
+        <v>236</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>48</v>
+      </c>
+      <c r="B136" t="s">
+        <v>89</v>
+      </c>
+      <c r="C136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D136" t="s">
+        <v>134</v>
+      </c>
+      <c r="E136" t="s">
+        <v>136</v>
+      </c>
+      <c r="F136" t="s">
+        <v>137</v>
+      </c>
+      <c r="G136" t="s">
+        <v>237</v>
+      </c>
+      <c r="H136">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="251">
   <si>
     <t>code</t>
   </si>
@@ -40,6 +40,15 @@
     <t>order</t>
   </si>
   <si>
+    <t>ec2ea21f-b88a-400a-8f3d-a03562ff60ad</t>
+  </si>
+  <si>
+    <t>4b3d4210-f21f-43bc-90cb-365395f8d755</t>
+  </si>
+  <si>
+    <t>81b140d6-80f9-436f-81e4-bbfc8ae820d3</t>
+  </si>
+  <si>
     <t>0d4bfa96-7cd5-47d9-b366-e133f6ea27c4</t>
   </si>
   <si>
@@ -160,7 +169,13 @@
     <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
   </si>
   <si>
-    <t>8d3e9626-0215-47a7-86cd-bf85990128c8</t>
+    <t>BRI UNIT SALAKAN</t>
+  </si>
+  <si>
+    <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
+  </si>
+  <si>
+    <t>BPR MODERN EXPRESS PT</t>
   </si>
   <si>
     <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
@@ -283,12 +298,24 @@
     <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
   </si>
   <si>
-    <t>PT. BANK SULTENG KAS LABEAN</t>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>SUBMITTED RESPONDENT</t>
   </si>
   <si>
     <t>OPEN</t>
   </si>
   <si>
+    <t>n5164@corp.bri.com</t>
+  </si>
+  <si>
+    <t>avatarcrue@gmail.com</t>
+  </si>
+  <si>
+    <t>bpr.381@lakadana.com</t>
+  </si>
+  <si>
     <t>bankdanamon.admin@gmail.com</t>
   </si>
   <si>
@@ -418,15 +445,12 @@
     <t>bprlabuan@yahoo.co.id</t>
   </si>
   <si>
-    <t>banksulteng_kaslabean@yahoo.com</t>
+    <t>Bounced</t>
   </si>
   <si>
     <t>Permanent_fail</t>
   </si>
   <si>
-    <t>Bounced</t>
-  </si>
-  <si>
     <t>Queued</t>
   </si>
   <si>
@@ -439,6 +463,27 @@
     <t>Delivered</t>
   </si>
   <si>
+    <t>02 Jun 2026, 09:36:45</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:36:44</t>
+  </si>
+  <si>
+    <t>11 Jun 2026, 14:00:36</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:19:15</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:03</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:35:02</t>
+  </si>
+  <si>
+    <t>11 Jun 2026, 10:53:00</t>
+  </si>
+  <si>
     <t>09 Jun 2026, 11:00:04</t>
   </si>
   <si>
@@ -722,12 +767,6 @@
   </si>
   <si>
     <t>01 Jun 2026, 23:29:34</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 04:12:10</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 04:11:35</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1119,22 +1158,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1145,22 +1184,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1168,28 +1207,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1197,25 +1236,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1223,25 +1262,25 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1249,74 +1288,74 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G8" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F9" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1324,25 +1363,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1353,51 +1392,51 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G11" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1405,25 +1444,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F13" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G13" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1431,51 +1470,51 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G14" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G15" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1483,51 +1522,51 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F16" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1535,51 +1574,51 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F18" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G18" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1587,25 +1626,25 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G20" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1613,25 +1652,25 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G21" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1639,22 +1678,22 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F22" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1662,28 +1701,28 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G23" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1691,25 +1730,25 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F24" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G24" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1717,48 +1756,48 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F25" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G25" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F26" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1766,25 +1805,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F27" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G27" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1792,25 +1831,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H28">
         <v>3</v>
@@ -1818,25 +1857,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G29" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1844,25 +1883,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F30" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1870,25 +1909,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G31" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -1896,288 +1935,288 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F32" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G32" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G33" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G34" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F35" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G35" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G36" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F37" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F38" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G38" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E39" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F40" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G40" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D41" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F41" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F42" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G42" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H42">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2185,25 +2224,25 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2211,51 +2250,51 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F44" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G44" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2263,51 +2302,51 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E46" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F46" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2315,25 +2354,25 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G48" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2341,51 +2380,51 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G49" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E50" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G50" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="H50">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2393,25 +2432,25 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E51" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F51" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2419,51 +2458,51 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E52" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D53" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2471,51 +2510,51 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F54" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E55" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2523,25 +2562,25 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E56" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F56" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G56" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2549,51 +2588,51 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E57" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F57" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G57" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G58" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2601,25 +2640,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F59" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G59" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2627,25 +2666,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G60" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2653,22 +2692,22 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F61" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G61" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2676,28 +2715,28 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F62" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G62" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2705,100 +2744,100 @@
         <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C63" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D63" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E63" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G63" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F64" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G64" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D65" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E65" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F65" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G65" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D66" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E66" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F66" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G66" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2806,25 +2845,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D67" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E67" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G67" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -2832,25 +2871,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D68" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E68" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F68" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2861,51 +2900,51 @@
         <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C69" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D69" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E69" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="H69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D70" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E70" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F70" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G70" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2913,25 +2952,25 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D71" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E71" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F71" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G71" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2939,48 +2978,48 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D72" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E72" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F72" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G72" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D73" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="E73" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F73" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G73" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2988,25 +3027,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="E74" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F74" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G74" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -3014,25 +3053,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E75" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F75" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G75" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3040,25 +3079,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D76" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E76" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F76" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G76" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -3066,25 +3105,25 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D77" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G77" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3092,25 +3131,25 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D78" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E78" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F78" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G78" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="H78">
         <v>2</v>
@@ -3118,132 +3157,132 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C79" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E79" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F79" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G79" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="E80" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F80" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G80" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="H80">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D81" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E81" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F81" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G81" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D82" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E82" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F82" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G82" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="H82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D83" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E83" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F83" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G83" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3251,51 +3290,51 @@
         <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D84" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E84" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F84" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G84" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D85" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E85" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F85" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G85" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3303,126 +3342,126 @@
         <v>37</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C86" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D86" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E86" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F86" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G86" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="H86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B87" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C87" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D87" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E87" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F87" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G87" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B88" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D88" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E88" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F88" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G88" t="s">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="H88">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D89" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E89" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F89" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G89" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D90" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E90" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F90" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G90" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -3430,25 +3469,25 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E91" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F91" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G91" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3456,77 +3495,77 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D92" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E92" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F92" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G92" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B93" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D93" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E93" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F93" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G93" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C94" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F94" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G94" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3534,25 +3573,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E95" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F95" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G95" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3560,340 +3599,340 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C96" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D96" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E96" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F96" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G96" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C97" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D97" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E97" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F97" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G97" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H97">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C98" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D98" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E98" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F98" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G98" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H98">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C99" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D99" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E99" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F99" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G99" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C100" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D100" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E100" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F100" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G100" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="H100">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C101" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D101" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E101" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F101" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G101" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D102" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E102" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F102" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G102" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C103" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D103" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E103" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F103" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G103" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C104" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D104" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E104" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F104" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G104" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C105" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D105" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E105" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F105" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="H105">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B106" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C106" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D106" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E106" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F106" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G106" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="H106">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B107" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C107" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D107" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E107" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F107" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G107" t="s">
-        <v>211</v>
+        <v>176</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B108" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C108" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E108" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F108" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G108" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3901,22 +3940,22 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C109" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E109" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F109" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G109" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -3927,22 +3966,22 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C110" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D110" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E110" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F110" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G110" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H110">
         <v>2</v>
@@ -3950,28 +3989,28 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B111" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C111" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E111" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F111" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G111" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="H111">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3979,25 +4018,25 @@
         <v>42</v>
       </c>
       <c r="B112" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D112" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E112" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F112" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G112" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H112">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4005,25 +4044,25 @@
         <v>42</v>
       </c>
       <c r="B113" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D113" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E113" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F113" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G113" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4031,22 +4070,22 @@
         <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C114" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D114" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E114" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F114" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G114" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -4057,22 +4096,22 @@
         <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D115" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E115" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F115" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G115" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4083,22 +4122,22 @@
         <v>44</v>
       </c>
       <c r="B116" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C116" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D116" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E116" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F116" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G116" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -4109,22 +4148,22 @@
         <v>44</v>
       </c>
       <c r="B117" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C117" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D117" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E117" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F117" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G117" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H117">
         <v>2</v>
@@ -4135,22 +4174,22 @@
         <v>44</v>
       </c>
       <c r="B118" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C118" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D118" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E118" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F118" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G118" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H118">
         <v>3</v>
@@ -4158,340 +4197,340 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C119" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D119" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E119" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F119" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G119" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H119">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C120" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D120" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E120" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F120" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G120" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="H120">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B121" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C121" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D121" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E121" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F121" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G121" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H121">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B122" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C122" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D122" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F122" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G122" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H122">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C123" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D123" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E123" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F123" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G123" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H123">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B124" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C124" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D124" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E124" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F124" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G124" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H124">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B125" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C125" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D125" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E125" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F125" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G125" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H125">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B126" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C126" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D126" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E126" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F126" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G126" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H126">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B127" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C127" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D127" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E127" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F127" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G127" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H127">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C128" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D128" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E128" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F128" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G128" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B129" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C129" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D129" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E129" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F129" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G129" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="H129">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B130" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C130" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D130" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E130" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F130" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G130" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B131" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C131" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D131" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E131" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F131" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G131" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H131">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4499,25 +4538,25 @@
         <v>47</v>
       </c>
       <c r="B132" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C132" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D132" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E132" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F132" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="G132" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4525,25 +4564,25 @@
         <v>47</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C133" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D133" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E133" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F133" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G133" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="H133">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4551,25 +4590,25 @@
         <v>47</v>
       </c>
       <c r="B134" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C134" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D134" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E134" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F134" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G134" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="H134">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4577,22 +4616,22 @@
         <v>48</v>
       </c>
       <c r="B135" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C135" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D135" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E135" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F135" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G135" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -4603,25 +4642,155 @@
         <v>48</v>
       </c>
       <c r="B136" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C136" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E136" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F136" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G136" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H136">
         <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>49</v>
+      </c>
+      <c r="B137" t="s">
+        <v>92</v>
+      </c>
+      <c r="C137" t="s">
+        <v>96</v>
+      </c>
+      <c r="D137" t="s">
+        <v>141</v>
+      </c>
+      <c r="E137" t="s">
+        <v>143</v>
+      </c>
+      <c r="F137" t="s">
+        <v>145</v>
+      </c>
+      <c r="G137" t="s">
+        <v>247</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>49</v>
+      </c>
+      <c r="B138" t="s">
+        <v>92</v>
+      </c>
+      <c r="C138" t="s">
+        <v>96</v>
+      </c>
+      <c r="D138" t="s">
+        <v>141</v>
+      </c>
+      <c r="E138" t="s">
+        <v>143</v>
+      </c>
+      <c r="F138" t="s">
+        <v>143</v>
+      </c>
+      <c r="G138" t="s">
+        <v>247</v>
+      </c>
+      <c r="H138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>50</v>
+      </c>
+      <c r="B139" t="s">
+        <v>93</v>
+      </c>
+      <c r="C139" t="s">
+        <v>96</v>
+      </c>
+      <c r="D139" t="s">
+        <v>142</v>
+      </c>
+      <c r="E139" t="s">
+        <v>144</v>
+      </c>
+      <c r="F139" t="s">
+        <v>144</v>
+      </c>
+      <c r="G139" t="s">
+        <v>248</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" t="s">
+        <v>93</v>
+      </c>
+      <c r="C140" t="s">
+        <v>96</v>
+      </c>
+      <c r="D140" t="s">
+        <v>142</v>
+      </c>
+      <c r="E140" t="s">
+        <v>144</v>
+      </c>
+      <c r="F140" t="s">
+        <v>143</v>
+      </c>
+      <c r="G140" t="s">
+        <v>249</v>
+      </c>
+      <c r="H140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" t="s">
+        <v>93</v>
+      </c>
+      <c r="C141" t="s">
+        <v>96</v>
+      </c>
+      <c r="D141" t="s">
+        <v>142</v>
+      </c>
+      <c r="E141" t="s">
+        <v>144</v>
+      </c>
+      <c r="F141" t="s">
+        <v>145</v>
+      </c>
+      <c r="G141" t="s">
+        <v>250</v>
+      </c>
+      <c r="H141">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="319">
   <si>
     <t>code</t>
   </si>
@@ -40,15 +40,6 @@
     <t>order</t>
   </si>
   <si>
-    <t>ec2ea21f-b88a-400a-8f3d-a03562ff60ad</t>
-  </si>
-  <si>
-    <t>4b3d4210-f21f-43bc-90cb-365395f8d755</t>
-  </si>
-  <si>
-    <t>81b140d6-80f9-436f-81e4-bbfc8ae820d3</t>
-  </si>
-  <si>
     <t>0d4bfa96-7cd5-47d9-b366-e133f6ea27c4</t>
   </si>
   <si>
@@ -76,7 +67,7 @@
     <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
   </si>
   <si>
-    <t>aed96e17-8337-406e-9f72-c02f709f865c</t>
+    <t>8a32e430-23b2-46ff-8b68-7dd7afb33862</t>
   </si>
   <si>
     <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
@@ -169,13 +160,46 @@
     <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
   </si>
   <si>
-    <t>BRI UNIT SALAKAN</t>
-  </si>
-  <si>
-    <t>PTBPRSYARIAHKHAIRANINTIAMANAH</t>
-  </si>
-  <si>
-    <t>BPR MODERN EXPRESS PT</t>
+    <t>8d3e9626-0215-47a7-86cd-bf85990128c8</t>
+  </si>
+  <si>
+    <t>eeee3ec7-6e8b-4ba0-86e1-e4a35de9cc96</t>
+  </si>
+  <si>
+    <t>e2d20a9c-1c32-42e2-a0cb-6567b585b199</t>
+  </si>
+  <si>
+    <t>11fd6f69-871d-4258-81f6-e2145ee9f73a</t>
+  </si>
+  <si>
+    <t>f455e248-e952-4fc6-9076-0237c90636fd</t>
+  </si>
+  <si>
+    <t>d858d260-d53e-41d2-906c-df6bbcd1d526</t>
+  </si>
+  <si>
+    <t>bf59ad9c-5369-4438-bd8a-f72ddffaa938</t>
+  </si>
+  <si>
+    <t>a9979a0c-403c-4acf-bb30-3023bbfba8b5</t>
+  </si>
+  <si>
+    <t>75b6fc99-ef00-42bd-8f54-fcab0ac2a238</t>
+  </si>
+  <si>
+    <t>7caf507f-ded1-4591-bf6a-60996f83c71b</t>
+  </si>
+  <si>
+    <t>3266144a-e1e8-481f-a863-d9ee0ed1a652</t>
+  </si>
+  <si>
+    <t>3f7e067e-eee9-4f79-957c-920de5e4f72f</t>
+  </si>
+  <si>
+    <t>5aac7959-5c27-489b-a9dc-ffa53a25291b</t>
+  </si>
+  <si>
+    <t>487d79ac-cb64-4668-9531-ebc3f866653e</t>
   </si>
   <si>
     <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
@@ -298,24 +322,54 @@
     <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
   </si>
   <si>
+    <t>PT. BANK SULTENG KAS LABEAN</t>
+  </si>
+  <si>
+    <t>ASTUN HI. ARSYAD</t>
+  </si>
+  <si>
+    <t>BUTOL RAYA NUSANTARA, PT</t>
+  </si>
+  <si>
+    <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
+  </si>
+  <si>
+    <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
+  </si>
+  <si>
+    <t>GALAXI INDO PRATAMA, CV</t>
+  </si>
+  <si>
+    <t>BANK SULTENG UNIT SONI</t>
+  </si>
+  <si>
+    <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
+  </si>
+  <si>
+    <t>PT BANK NEGARA INDONESIA (PERSERO) TBK</t>
+  </si>
+  <si>
+    <t>BANK MANDIRI (PERSERO) TBK KCP BUOL, PT</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT DIAPATIH</t>
+  </si>
+  <si>
+    <t>BRI UNIT TINOMBO</t>
+  </si>
+  <si>
+    <t>SAHABAT TANI, TOKO</t>
+  </si>
+  <si>
+    <t>BANK PERKREDITAN RAKYAT PALU ANUGERAH</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
     <t>DRAFT</t>
   </si>
   <si>
-    <t>SUBMITTED RESPONDENT</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>n5164@corp.bri.com</t>
-  </si>
-  <si>
-    <t>avatarcrue@gmail.com</t>
-  </si>
-  <si>
-    <t>bpr.381@lakadana.com</t>
-  </si>
-  <si>
     <t>bankdanamon.admin@gmail.com</t>
   </si>
   <si>
@@ -445,12 +499,54 @@
     <t>bprlabuan@yahoo.co.id</t>
   </si>
   <si>
+    <t>banksulteng_kaslabean@yahoo.com</t>
+  </si>
+  <si>
+    <t>astunhiarsyad28@gmail.com</t>
+  </si>
+  <si>
+    <t>butolrayanusantara@yahoo.com</t>
+  </si>
+  <si>
+    <t>kc.tolitoli@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>koperasi_maritim@yahoo.com</t>
+  </si>
+  <si>
+    <t>galaxiindopratamatolis@gmail.com</t>
+  </si>
+  <si>
+    <t>febrialdin.rial@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>fandhymadjid96@gmail.com</t>
+  </si>
+  <si>
+    <t>ynataliaw@gmail.com</t>
+  </si>
+  <si>
+    <t>nyoalvaro@gmail.com</t>
+  </si>
+  <si>
+    <t>yohanesyafetsulung@gmail.com</t>
+  </si>
+  <si>
+    <t>n5197@corpbri.co.id</t>
+  </si>
+  <si>
+    <t>sonnykandou80@gmail.com</t>
+  </si>
+  <si>
+    <t>paluanugerahprg@yahoo.com</t>
+  </si>
+  <si>
+    <t>Permanent_fail</t>
+  </si>
+  <si>
     <t>Bounced</t>
   </si>
   <si>
-    <t>Permanent_fail</t>
-  </si>
-  <si>
     <t>Queued</t>
   </si>
   <si>
@@ -463,27 +559,6 @@
     <t>Delivered</t>
   </si>
   <si>
-    <t>02 Jun 2026, 09:36:45</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 09:36:44</t>
-  </si>
-  <si>
-    <t>11 Jun 2026, 14:00:36</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:19:15</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:35:03</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:35:02</t>
-  </si>
-  <si>
-    <t>11 Jun 2026, 10:53:00</t>
-  </si>
-  <si>
     <t>09 Jun 2026, 11:00:04</t>
   </si>
   <si>
@@ -767,6 +842,135 @@
   </si>
   <si>
     <t>01 Jun 2026, 23:29:34</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:12:10</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:51</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:21</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:04:02</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:01:19</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:31</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:16:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:08:22</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 10:04:58</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:38</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:53:36</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:00:24</t>
+  </si>
+  <si>
+    <t>20 May 2026, 14:15:07</t>
+  </si>
+  <si>
+    <t>20 May 2026, 14:14:58</t>
+  </si>
+  <si>
+    <t>20 May 2026, 14:14:51</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:38:58</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:53</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:50</t>
+  </si>
+  <si>
+    <t>20 May 2026, 10:34:40</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:37</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:04</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:26</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:04</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:47</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:44</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:34</t>
+  </si>
+  <si>
+    <t>10 Jun 2026, 15:04:30</t>
+  </si>
+  <si>
+    <t>10 Jun 2026, 14:33:40</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:38</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:52</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:48</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:12:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:32:29</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:16:05</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:55:50</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:01:57</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:18:28</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 01:23:24</t>
   </si>
 </sst>
 </file>
@@ -1124,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1158,22 +1362,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -1184,22 +1388,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -1207,28 +1411,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G4" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1236,25 +1440,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G5" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1262,25 +1466,25 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G6" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1288,74 +1492,74 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F7" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1363,25 +1567,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1392,51 +1596,51 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F11" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G12" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1444,25 +1648,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G13" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1470,51 +1674,51 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F14" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F15" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G15" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1522,51 +1726,51 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G16" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F17" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1574,51 +1778,51 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G18" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G19" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1626,25 +1830,25 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G20" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1652,25 +1856,25 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G21" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1678,22 +1882,22 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G22" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1701,28 +1905,28 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="E23" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G23" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1730,25 +1934,25 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G24" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1756,48 +1960,48 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F25" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G25" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="G26" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1805,25 +2009,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F27" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G27" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1831,25 +2035,25 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G28" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="H28">
         <v>3</v>
@@ -1857,25 +2061,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1883,25 +2087,25 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1909,25 +2113,25 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F31" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G31" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -1935,288 +2139,288 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F33" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G33" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E34" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G34" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E35" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G36" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F38" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F39" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G39" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F40" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G41" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="H41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G42" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2224,25 +2428,25 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F43" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G43" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2250,51 +2454,51 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G44" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="H44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F45" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G45" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -2302,51 +2506,51 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="E46" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F46" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G46" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E47" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F47" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G47" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -2354,25 +2558,25 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F48" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G48" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2380,51 +2584,51 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D49" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G49" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E50" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F50" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G50" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2432,25 +2636,25 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E51" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F51" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="G51" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2458,51 +2662,51 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E52" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G52" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F53" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G53" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -2510,51 +2714,51 @@
         <v>24</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F54" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G54" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F55" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G55" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2562,25 +2766,25 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F56" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G56" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -2588,51 +2792,51 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F57" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G57" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F58" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G58" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2640,25 +2844,25 @@
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F59" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2666,25 +2870,25 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F60" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G60" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2692,22 +2896,22 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F61" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G61" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2715,28 +2919,28 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="E62" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F62" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G62" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2744,100 +2948,100 @@
         <v>28</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="E63" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F63" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G63" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="E64" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F64" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G64" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="E65" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G65" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E66" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F66" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G66" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2845,25 +3049,25 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D67" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E67" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G67" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -2871,25 +3075,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D68" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G68" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2900,51 +3104,51 @@
         <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D69" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G69" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D70" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F70" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G70" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2952,25 +3156,25 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F71" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G71" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2978,48 +3182,48 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E72" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G72" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E73" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F73" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G73" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -3027,25 +3231,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D74" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E74" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F74" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G74" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -3053,25 +3257,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E75" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F75" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G75" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3079,25 +3283,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D76" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E76" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F76" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G76" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="H76">
         <v>2</v>
@@ -3105,25 +3309,25 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E77" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F77" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G77" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3131,25 +3335,25 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G78" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="H78">
         <v>2</v>
@@ -3157,132 +3361,132 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D79" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F79" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G79" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="H79">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F80" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G80" t="s">
-        <v>158</v>
+        <v>240</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D81" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="E81" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F81" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G81" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D82" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F82" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G82" t="s">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="H82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B83" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F83" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G83" t="s">
-        <v>161</v>
+        <v>243</v>
       </c>
       <c r="H83">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -3290,51 +3494,51 @@
         <v>36</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="E84" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F84" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G84" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="E85" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F85" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G85" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -3342,126 +3546,126 @@
         <v>37</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="E86" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G86" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G87" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E88" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F88" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G88" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E89" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F89" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G89" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="H89">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D90" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E90" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F90" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G90" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -3469,25 +3673,25 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C91" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E91" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F91" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G91" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="H91">
         <v>2</v>
@@ -3495,77 +3699,77 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F92" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G92" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D93" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F93" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G93" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="H93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E94" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F94" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G94" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3573,25 +3777,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E95" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F95" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G95" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3599,340 +3803,340 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C96" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E96" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F96" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G96" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="H96">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E97" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F97" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G97" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C98" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D98" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E98" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F98" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G98" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C99" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E99" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F99" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G99" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="H99">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C100" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="E100" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F100" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G100" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F101" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G101" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C102" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="E102" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F102" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G102" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C103" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="E103" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F103" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G103" t="s">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C104" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="E104" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F104" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G104" t="s">
-        <v>176</v>
+        <v>248</v>
       </c>
       <c r="H104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B105" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C105" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="E105" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F105" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G105" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B106" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C106" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="E106" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F106" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="G106" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="H106">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B107" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C107" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D107" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E107" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F107" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G107" t="s">
-        <v>176</v>
+        <v>251</v>
       </c>
       <c r="H107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C108" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D108" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="E108" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F108" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G108" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="H108">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3940,22 +4144,22 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C109" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D109" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E109" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F109" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="G109" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -3966,22 +4170,22 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D110" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E110" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F110" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G110" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="H110">
         <v>2</v>
@@ -3989,28 +4193,28 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C111" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D111" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E111" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F111" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G111" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -4018,25 +4222,25 @@
         <v>42</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C112" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D112" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="E112" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F112" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G112" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -4044,25 +4248,25 @@
         <v>42</v>
       </c>
       <c r="B113" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C113" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D113" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="E113" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F113" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G113" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -4070,22 +4274,22 @@
         <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C114" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D114" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E114" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F114" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G114" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -4096,22 +4300,22 @@
         <v>43</v>
       </c>
       <c r="B115" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C115" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D115" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E115" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F115" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G115" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -4122,22 +4326,22 @@
         <v>44</v>
       </c>
       <c r="B116" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C116" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E116" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F116" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="G116" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -4148,22 +4352,22 @@
         <v>44</v>
       </c>
       <c r="B117" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D117" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E117" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F117" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="G117" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="H117">
         <v>2</v>
@@ -4174,22 +4378,22 @@
         <v>44</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E118" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F118" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="G118" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="H118">
         <v>3</v>
@@ -4197,340 +4401,340 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E119" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F119" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="G119" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E120" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F120" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="G120" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="H120">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B121" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="E121" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F121" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G121" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B122" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C122" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="E122" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F122" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G122" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="H122">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C123" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D123" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E123" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F123" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="G123" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C124" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E124" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F124" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="G124" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="H124">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C125" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E125" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F125" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="G125" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="H125">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B126" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C126" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E126" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F126" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="G126" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="H126">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C127" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D127" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E127" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F127" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="G127" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="H127">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C128" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D128" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="E128" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F128" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G128" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="H128">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C129" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D129" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="E129" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F129" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G129" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="H129">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B130" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D130" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E130" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F130" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G130" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H130">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B131" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C131" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D131" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E131" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F131" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="G131" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H131">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4538,25 +4742,25 @@
         <v>47</v>
       </c>
       <c r="B132" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C132" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D132" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E132" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F132" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="G132" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="H132">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4564,25 +4768,25 @@
         <v>47</v>
       </c>
       <c r="B133" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C133" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D133" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E133" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F133" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="G133" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="H133">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4590,25 +4794,25 @@
         <v>47</v>
       </c>
       <c r="B134" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C134" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D134" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E134" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="F134" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G134" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="H134">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4616,22 +4820,22 @@
         <v>48</v>
       </c>
       <c r="B135" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C135" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D135" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E135" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F135" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="G135" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -4642,22 +4846,22 @@
         <v>48</v>
       </c>
       <c r="B136" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C136" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D136" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E136" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F136" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="G136" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="H136">
         <v>2</v>
@@ -4668,22 +4872,22 @@
         <v>49</v>
       </c>
       <c r="B137" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C137" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D137" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E137" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F137" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -4694,22 +4898,22 @@
         <v>49</v>
       </c>
       <c r="B138" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C138" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D138" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E138" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F138" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G138" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="H138">
         <v>2</v>
@@ -4720,22 +4924,22 @@
         <v>50</v>
       </c>
       <c r="B139" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C139" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D139" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="E139" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F139" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="G139" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -4746,22 +4950,22 @@
         <v>50</v>
       </c>
       <c r="B140" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C140" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D140" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="E140" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F140" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="G140" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="H140">
         <v>2</v>
@@ -4769,27 +4973,1509 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B141" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C141" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D141" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="E141" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="F141" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G141" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>51</v>
+      </c>
+      <c r="B142" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" t="s">
+        <v>116</v>
+      </c>
+      <c r="D142" t="s">
+        <v>164</v>
+      </c>
+      <c r="E142" t="s">
+        <v>175</v>
+      </c>
+      <c r="F142" t="s">
+        <v>176</v>
+      </c>
+      <c r="G142" t="s">
+        <v>283</v>
+      </c>
+      <c r="H142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>51</v>
+      </c>
+      <c r="B143" t="s">
+        <v>105</v>
+      </c>
+      <c r="C143" t="s">
+        <v>116</v>
+      </c>
+      <c r="D143" t="s">
+        <v>164</v>
+      </c>
+      <c r="E143" t="s">
+        <v>175</v>
+      </c>
+      <c r="F143" t="s">
+        <v>177</v>
+      </c>
+      <c r="G143" t="s">
+        <v>284</v>
+      </c>
+      <c r="H143">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>52</v>
+      </c>
+      <c r="B144" t="s">
+        <v>106</v>
+      </c>
+      <c r="C144" t="s">
+        <v>116</v>
+      </c>
+      <c r="D144" t="s">
+        <v>165</v>
+      </c>
+      <c r="E144" t="s">
+        <v>176</v>
+      </c>
+      <c r="F144" t="s">
+        <v>176</v>
+      </c>
+      <c r="G144" t="s">
+        <v>285</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>52</v>
+      </c>
+      <c r="B145" t="s">
+        <v>106</v>
+      </c>
+      <c r="C145" t="s">
+        <v>116</v>
+      </c>
+      <c r="D145" t="s">
+        <v>165</v>
+      </c>
+      <c r="E145" t="s">
+        <v>176</v>
+      </c>
+      <c r="F145" t="s">
+        <v>177</v>
+      </c>
+      <c r="G145" t="s">
+        <v>286</v>
+      </c>
+      <c r="H145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>53</v>
+      </c>
+      <c r="B146" t="s">
+        <v>107</v>
+      </c>
+      <c r="C146" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" t="s">
+        <v>166</v>
+      </c>
+      <c r="E146" t="s">
+        <v>176</v>
+      </c>
+      <c r="F146" t="s">
+        <v>177</v>
+      </c>
+      <c r="G146" t="s">
+        <v>287</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" t="s">
+        <v>107</v>
+      </c>
+      <c r="C147" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" t="s">
+        <v>166</v>
+      </c>
+      <c r="E147" t="s">
+        <v>176</v>
+      </c>
+      <c r="F147" t="s">
+        <v>176</v>
+      </c>
+      <c r="G147" t="s">
+        <v>288</v>
+      </c>
+      <c r="H147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>54</v>
+      </c>
+      <c r="B148" t="s">
+        <v>108</v>
+      </c>
+      <c r="C148" t="s">
+        <v>116</v>
+      </c>
+      <c r="D148" t="s">
+        <v>167</v>
+      </c>
+      <c r="E148" t="s">
+        <v>176</v>
+      </c>
+      <c r="F148" t="s">
+        <v>176</v>
+      </c>
+      <c r="G148" t="s">
+        <v>289</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>54</v>
+      </c>
+      <c r="B149" t="s">
+        <v>108</v>
+      </c>
+      <c r="C149" t="s">
+        <v>116</v>
+      </c>
+      <c r="D149" t="s">
+        <v>167</v>
+      </c>
+      <c r="E149" t="s">
+        <v>176</v>
+      </c>
+      <c r="F149" t="s">
+        <v>177</v>
+      </c>
+      <c r="G149" t="s">
+        <v>290</v>
+      </c>
+      <c r="H149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>55</v>
+      </c>
+      <c r="B150" t="s">
+        <v>109</v>
+      </c>
+      <c r="C150" t="s">
+        <v>117</v>
+      </c>
+      <c r="D150" t="s">
+        <v>168</v>
+      </c>
+      <c r="E150" t="s">
+        <v>176</v>
+      </c>
+      <c r="F150" t="s">
+        <v>178</v>
+      </c>
+      <c r="G150" t="s">
+        <v>291</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>55</v>
+      </c>
+      <c r="B151" t="s">
+        <v>109</v>
+      </c>
+      <c r="C151" t="s">
+        <v>117</v>
+      </c>
+      <c r="D151" t="s">
+        <v>168</v>
+      </c>
+      <c r="E151" t="s">
+        <v>176</v>
+      </c>
+      <c r="F151" t="s">
+        <v>178</v>
+      </c>
+      <c r="G151" t="s">
+        <v>292</v>
+      </c>
+      <c r="H151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>55</v>
+      </c>
+      <c r="B152" t="s">
+        <v>109</v>
+      </c>
+      <c r="C152" t="s">
+        <v>117</v>
+      </c>
+      <c r="D152" t="s">
+        <v>168</v>
+      </c>
+      <c r="E152" t="s">
+        <v>176</v>
+      </c>
+      <c r="F152" t="s">
+        <v>179</v>
+      </c>
+      <c r="G152" t="s">
+        <v>293</v>
+      </c>
+      <c r="H152">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>55</v>
+      </c>
+      <c r="B153" t="s">
+        <v>109</v>
+      </c>
+      <c r="C153" t="s">
+        <v>117</v>
+      </c>
+      <c r="D153" t="s">
+        <v>168</v>
+      </c>
+      <c r="E153" t="s">
+        <v>176</v>
+      </c>
+      <c r="F153" t="s">
+        <v>179</v>
+      </c>
+      <c r="G153" t="s">
+        <v>294</v>
+      </c>
+      <c r="H153">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>55</v>
+      </c>
+      <c r="B154" t="s">
+        <v>109</v>
+      </c>
+      <c r="C154" t="s">
+        <v>117</v>
+      </c>
+      <c r="D154" t="s">
+        <v>168</v>
+      </c>
+      <c r="E154" t="s">
+        <v>176</v>
+      </c>
+      <c r="F154" t="s">
+        <v>178</v>
+      </c>
+      <c r="G154" t="s">
+        <v>295</v>
+      </c>
+      <c r="H154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>55</v>
+      </c>
+      <c r="B155" t="s">
+        <v>109</v>
+      </c>
+      <c r="C155" t="s">
+        <v>117</v>
+      </c>
+      <c r="D155" t="s">
+        <v>168</v>
+      </c>
+      <c r="E155" t="s">
+        <v>176</v>
+      </c>
+      <c r="F155" t="s">
+        <v>179</v>
+      </c>
+      <c r="G155" t="s">
+        <v>296</v>
+      </c>
+      <c r="H155">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>55</v>
+      </c>
+      <c r="B156" t="s">
+        <v>109</v>
+      </c>
+      <c r="C156" t="s">
+        <v>117</v>
+      </c>
+      <c r="D156" t="s">
+        <v>168</v>
+      </c>
+      <c r="E156" t="s">
+        <v>176</v>
+      </c>
+      <c r="F156" t="s">
+        <v>180</v>
+      </c>
+      <c r="G156" t="s">
+        <v>297</v>
+      </c>
+      <c r="H156">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>55</v>
+      </c>
+      <c r="B157" t="s">
+        <v>109</v>
+      </c>
+      <c r="C157" t="s">
+        <v>117</v>
+      </c>
+      <c r="D157" t="s">
+        <v>168</v>
+      </c>
+      <c r="E157" t="s">
+        <v>176</v>
+      </c>
+      <c r="F157" t="s">
+        <v>177</v>
+      </c>
+      <c r="G157" t="s">
+        <v>297</v>
+      </c>
+      <c r="H157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>55</v>
+      </c>
+      <c r="B158" t="s">
+        <v>109</v>
+      </c>
+      <c r="C158" t="s">
+        <v>117</v>
+      </c>
+      <c r="D158" t="s">
+        <v>168</v>
+      </c>
+      <c r="E158" t="s">
+        <v>176</v>
+      </c>
+      <c r="F158" t="s">
+        <v>176</v>
+      </c>
+      <c r="G158" t="s">
+        <v>298</v>
+      </c>
+      <c r="H158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>55</v>
+      </c>
+      <c r="B159" t="s">
+        <v>109</v>
+      </c>
+      <c r="C159" t="s">
+        <v>117</v>
+      </c>
+      <c r="D159" t="s">
+        <v>168</v>
+      </c>
+      <c r="E159" t="s">
+        <v>176</v>
+      </c>
+      <c r="F159" t="s">
+        <v>177</v>
+      </c>
+      <c r="G159" t="s">
+        <v>298</v>
+      </c>
+      <c r="H159">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" t="s">
+        <v>55</v>
+      </c>
+      <c r="B160" t="s">
+        <v>109</v>
+      </c>
+      <c r="C160" t="s">
+        <v>117</v>
+      </c>
+      <c r="D160" t="s">
+        <v>168</v>
+      </c>
+      <c r="E160" t="s">
+        <v>176</v>
+      </c>
+      <c r="F160" t="s">
+        <v>180</v>
+      </c>
+      <c r="G160" t="s">
+        <v>299</v>
+      </c>
+      <c r="H160">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>55</v>
+      </c>
+      <c r="B161" t="s">
+        <v>109</v>
+      </c>
+      <c r="C161" t="s">
+        <v>117</v>
+      </c>
+      <c r="D161" t="s">
+        <v>168</v>
+      </c>
+      <c r="E161" t="s">
+        <v>176</v>
+      </c>
+      <c r="F161" t="s">
+        <v>177</v>
+      </c>
+      <c r="G161" t="s">
+        <v>300</v>
+      </c>
+      <c r="H161">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>56</v>
+      </c>
+      <c r="B162" t="s">
+        <v>110</v>
+      </c>
+      <c r="C162" t="s">
+        <v>117</v>
+      </c>
+      <c r="D162" t="s">
+        <v>169</v>
+      </c>
+      <c r="E162" t="s">
+        <v>176</v>
+      </c>
+      <c r="F162" t="s">
+        <v>178</v>
+      </c>
+      <c r="G162" t="s">
+        <v>301</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" t="s">
+        <v>56</v>
+      </c>
+      <c r="B163" t="s">
+        <v>110</v>
+      </c>
+      <c r="C163" t="s">
+        <v>117</v>
+      </c>
+      <c r="D163" t="s">
+        <v>169</v>
+      </c>
+      <c r="E163" t="s">
+        <v>176</v>
+      </c>
+      <c r="F163" t="s">
+        <v>179</v>
+      </c>
+      <c r="G163" t="s">
+        <v>302</v>
+      </c>
+      <c r="H163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" t="s">
+        <v>56</v>
+      </c>
+      <c r="B164" t="s">
+        <v>110</v>
+      </c>
+      <c r="C164" t="s">
+        <v>117</v>
+      </c>
+      <c r="D164" t="s">
+        <v>169</v>
+      </c>
+      <c r="E164" t="s">
+        <v>176</v>
+      </c>
+      <c r="F164" t="s">
+        <v>180</v>
+      </c>
+      <c r="G164" t="s">
+        <v>303</v>
+      </c>
+      <c r="H164">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" t="s">
+        <v>56</v>
+      </c>
+      <c r="B165" t="s">
+        <v>110</v>
+      </c>
+      <c r="C165" t="s">
+        <v>117</v>
+      </c>
+      <c r="D165" t="s">
+        <v>169</v>
+      </c>
+      <c r="E165" t="s">
+        <v>176</v>
+      </c>
+      <c r="F165" t="s">
+        <v>177</v>
+      </c>
+      <c r="G165" t="s">
+        <v>304</v>
+      </c>
+      <c r="H165">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" t="s">
+        <v>56</v>
+      </c>
+      <c r="B166" t="s">
+        <v>110</v>
+      </c>
+      <c r="C166" t="s">
+        <v>117</v>
+      </c>
+      <c r="D166" t="s">
+        <v>169</v>
+      </c>
+      <c r="E166" t="s">
+        <v>176</v>
+      </c>
+      <c r="F166" t="s">
+        <v>177</v>
+      </c>
+      <c r="G166" t="s">
+        <v>305</v>
+      </c>
+      <c r="H166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" t="s">
+        <v>56</v>
+      </c>
+      <c r="B167" t="s">
+        <v>110</v>
+      </c>
+      <c r="C167" t="s">
+        <v>117</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+      <c r="E167" t="s">
+        <v>176</v>
+      </c>
+      <c r="F167" t="s">
+        <v>176</v>
+      </c>
+      <c r="G167" t="s">
+        <v>305</v>
+      </c>
+      <c r="H167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" t="s">
+        <v>56</v>
+      </c>
+      <c r="B168" t="s">
+        <v>110</v>
+      </c>
+      <c r="C168" t="s">
+        <v>117</v>
+      </c>
+      <c r="D168" t="s">
+        <v>169</v>
+      </c>
+      <c r="E168" t="s">
+        <v>176</v>
+      </c>
+      <c r="F168" t="s">
+        <v>179</v>
+      </c>
+      <c r="G168" t="s">
+        <v>306</v>
+      </c>
+      <c r="H168">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>56</v>
+      </c>
+      <c r="B169" t="s">
+        <v>110</v>
+      </c>
+      <c r="C169" t="s">
+        <v>117</v>
+      </c>
+      <c r="D169" t="s">
+        <v>169</v>
+      </c>
+      <c r="E169" t="s">
+        <v>176</v>
+      </c>
+      <c r="F169" t="s">
+        <v>179</v>
+      </c>
+      <c r="G169" t="s">
+        <v>307</v>
+      </c>
+      <c r="H169">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" t="s">
+        <v>57</v>
+      </c>
+      <c r="B170" t="s">
+        <v>111</v>
+      </c>
+      <c r="C170" t="s">
+        <v>116</v>
+      </c>
+      <c r="D170" t="s">
+        <v>170</v>
+      </c>
+      <c r="E170" t="s">
+        <v>176</v>
+      </c>
+      <c r="F170" t="s">
+        <v>176</v>
+      </c>
+      <c r="G170" t="s">
+        <v>308</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" t="s">
+        <v>57</v>
+      </c>
+      <c r="B171" t="s">
+        <v>111</v>
+      </c>
+      <c r="C171" t="s">
+        <v>116</v>
+      </c>
+      <c r="D171" t="s">
+        <v>170</v>
+      </c>
+      <c r="E171" t="s">
+        <v>176</v>
+      </c>
+      <c r="F171" t="s">
+        <v>177</v>
+      </c>
+      <c r="G171" t="s">
+        <v>305</v>
+      </c>
+      <c r="H171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" t="s">
+        <v>58</v>
+      </c>
+      <c r="B172" t="s">
+        <v>112</v>
+      </c>
+      <c r="C172" t="s">
+        <v>116</v>
+      </c>
+      <c r="D172" t="s">
+        <v>171</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+      <c r="F172" t="s">
+        <v>176</v>
+      </c>
+      <c r="G172" t="s">
+        <v>309</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" t="s">
+        <v>58</v>
+      </c>
+      <c r="B173" t="s">
+        <v>112</v>
+      </c>
+      <c r="C173" t="s">
+        <v>116</v>
+      </c>
+      <c r="D173" t="s">
+        <v>171</v>
+      </c>
+      <c r="E173" t="s">
+        <v>175</v>
+      </c>
+      <c r="F173" t="s">
+        <v>177</v>
+      </c>
+      <c r="G173" t="s">
+        <v>310</v>
+      </c>
+      <c r="H173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" t="s">
+        <v>58</v>
+      </c>
+      <c r="B174" t="s">
+        <v>112</v>
+      </c>
+      <c r="C174" t="s">
+        <v>116</v>
+      </c>
+      <c r="D174" t="s">
+        <v>171</v>
+      </c>
+      <c r="E174" t="s">
+        <v>175</v>
+      </c>
+      <c r="F174" t="s">
+        <v>175</v>
+      </c>
+      <c r="G174" t="s">
+        <v>311</v>
+      </c>
+      <c r="H174">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>58</v>
+      </c>
+      <c r="B175" t="s">
+        <v>112</v>
+      </c>
+      <c r="C175" t="s">
+        <v>116</v>
+      </c>
+      <c r="D175" t="s">
+        <v>171</v>
+      </c>
+      <c r="E175" t="s">
+        <v>175</v>
+      </c>
+      <c r="F175" t="s">
+        <v>175</v>
+      </c>
+      <c r="G175" t="s">
+        <v>312</v>
+      </c>
+      <c r="H175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>59</v>
+      </c>
+      <c r="B176" t="s">
+        <v>113</v>
+      </c>
+      <c r="C176" t="s">
+        <v>116</v>
+      </c>
+      <c r="D176" t="s">
+        <v>172</v>
+      </c>
+      <c r="E176" t="s">
+        <v>175</v>
+      </c>
+      <c r="F176" t="s">
+        <v>175</v>
+      </c>
+      <c r="G176" t="s">
+        <v>313</v>
+      </c>
+      <c r="H176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" t="s">
+        <v>59</v>
+      </c>
+      <c r="B177" t="s">
+        <v>113</v>
+      </c>
+      <c r="C177" t="s">
+        <v>116</v>
+      </c>
+      <c r="D177" t="s">
+        <v>172</v>
+      </c>
+      <c r="E177" t="s">
+        <v>175</v>
+      </c>
+      <c r="F177" t="s">
+        <v>177</v>
+      </c>
+      <c r="G177" t="s">
+        <v>314</v>
+      </c>
+      <c r="H177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>59</v>
+      </c>
+      <c r="B178" t="s">
+        <v>113</v>
+      </c>
+      <c r="C178" t="s">
+        <v>116</v>
+      </c>
+      <c r="D178" t="s">
+        <v>172</v>
+      </c>
+      <c r="E178" t="s">
+        <v>175</v>
+      </c>
+      <c r="F178" t="s">
+        <v>176</v>
+      </c>
+      <c r="G178" t="s">
+        <v>314</v>
+      </c>
+      <c r="H178">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" t="s">
+        <v>60</v>
+      </c>
+      <c r="B179" t="s">
+        <v>114</v>
+      </c>
+      <c r="C179" t="s">
+        <v>116</v>
+      </c>
+      <c r="D179" t="s">
+        <v>173</v>
+      </c>
+      <c r="E179" t="s">
+        <v>176</v>
+      </c>
+      <c r="F179" t="s">
+        <v>176</v>
+      </c>
+      <c r="G179" t="s">
+        <v>315</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" t="s">
+        <v>60</v>
+      </c>
+      <c r="B180" t="s">
+        <v>114</v>
+      </c>
+      <c r="C180" t="s">
+        <v>116</v>
+      </c>
+      <c r="D180" t="s">
+        <v>173</v>
+      </c>
+      <c r="E180" t="s">
+        <v>176</v>
+      </c>
+      <c r="F180" t="s">
+        <v>177</v>
+      </c>
+      <c r="G180" t="s">
+        <v>315</v>
+      </c>
+      <c r="H180">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" t="s">
+        <v>17</v>
+      </c>
+      <c r="B181" t="s">
+        <v>71</v>
+      </c>
+      <c r="C181" t="s">
+        <v>116</v>
+      </c>
+      <c r="D181" t="s">
+        <v>128</v>
+      </c>
+      <c r="E181" t="s">
+        <v>175</v>
+      </c>
+      <c r="F181" t="s">
+        <v>175</v>
+      </c>
+      <c r="G181" t="s">
+        <v>200</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" t="s">
+        <v>17</v>
+      </c>
+      <c r="B182" t="s">
+        <v>71</v>
+      </c>
+      <c r="C182" t="s">
+        <v>116</v>
+      </c>
+      <c r="D182" t="s">
+        <v>128</v>
+      </c>
+      <c r="E182" t="s">
+        <v>175</v>
+      </c>
+      <c r="F182" t="s">
+        <v>176</v>
+      </c>
+      <c r="G182" t="s">
+        <v>201</v>
+      </c>
+      <c r="H182">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" t="s">
+        <v>71</v>
+      </c>
+      <c r="C183" t="s">
+        <v>116</v>
+      </c>
+      <c r="D183" t="s">
+        <v>128</v>
+      </c>
+      <c r="E183" t="s">
+        <v>175</v>
+      </c>
+      <c r="F183" t="s">
+        <v>177</v>
+      </c>
+      <c r="G183" t="s">
+        <v>202</v>
+      </c>
+      <c r="H183">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B184" t="s">
+        <v>71</v>
+      </c>
+      <c r="C184" t="s">
+        <v>116</v>
+      </c>
+      <c r="D184" t="s">
+        <v>128</v>
+      </c>
+      <c r="E184" t="s">
+        <v>175</v>
+      </c>
+      <c r="F184" t="s">
+        <v>175</v>
+      </c>
+      <c r="G184" t="s">
+        <v>200</v>
+      </c>
+      <c r="H184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>17</v>
+      </c>
+      <c r="B185" t="s">
+        <v>71</v>
+      </c>
+      <c r="C185" t="s">
+        <v>116</v>
+      </c>
+      <c r="D185" t="s">
+        <v>128</v>
+      </c>
+      <c r="E185" t="s">
+        <v>175</v>
+      </c>
+      <c r="F185" t="s">
+        <v>176</v>
+      </c>
+      <c r="G185" t="s">
+        <v>201</v>
+      </c>
+      <c r="H185">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>17</v>
+      </c>
+      <c r="B186" t="s">
+        <v>71</v>
+      </c>
+      <c r="C186" t="s">
+        <v>116</v>
+      </c>
+      <c r="D186" t="s">
+        <v>128</v>
+      </c>
+      <c r="E186" t="s">
+        <v>175</v>
+      </c>
+      <c r="F186" t="s">
+        <v>177</v>
+      </c>
+      <c r="G186" t="s">
+        <v>202</v>
+      </c>
+      <c r="H186">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" t="s">
+        <v>17</v>
+      </c>
+      <c r="B187" t="s">
+        <v>71</v>
+      </c>
+      <c r="C187" t="s">
+        <v>116</v>
+      </c>
+      <c r="D187" t="s">
+        <v>129</v>
+      </c>
+      <c r="E187" t="s">
+        <v>175</v>
+      </c>
+      <c r="F187" t="s">
+        <v>175</v>
+      </c>
+      <c r="G187" t="s">
+        <v>203</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>17</v>
+      </c>
+      <c r="B188" t="s">
+        <v>71</v>
+      </c>
+      <c r="C188" t="s">
+        <v>116</v>
+      </c>
+      <c r="D188" t="s">
+        <v>130</v>
+      </c>
+      <c r="E188" t="s">
+        <v>176</v>
+      </c>
+      <c r="F188" t="s">
+        <v>176</v>
+      </c>
+      <c r="G188" t="s">
+        <v>204</v>
+      </c>
+      <c r="H188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" t="s">
+        <v>17</v>
+      </c>
+      <c r="B189" t="s">
+        <v>71</v>
+      </c>
+      <c r="C189" t="s">
+        <v>116</v>
+      </c>
+      <c r="D189" t="s">
+        <v>130</v>
+      </c>
+      <c r="E189" t="s">
+        <v>176</v>
+      </c>
+      <c r="F189" t="s">
+        <v>177</v>
+      </c>
+      <c r="G189" t="s">
+        <v>205</v>
+      </c>
+      <c r="H189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" t="s">
+        <v>17</v>
+      </c>
+      <c r="B190" t="s">
+        <v>71</v>
+      </c>
+      <c r="C190" t="s">
+        <v>116</v>
+      </c>
+      <c r="D190" t="s">
+        <v>128</v>
+      </c>
+      <c r="E190" t="s">
+        <v>175</v>
+      </c>
+      <c r="F190" t="s">
+        <v>175</v>
+      </c>
+      <c r="G190" t="s">
+        <v>200</v>
+      </c>
+      <c r="H190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" t="s">
+        <v>17</v>
+      </c>
+      <c r="B191" t="s">
+        <v>71</v>
+      </c>
+      <c r="C191" t="s">
+        <v>116</v>
+      </c>
+      <c r="D191" t="s">
+        <v>128</v>
+      </c>
+      <c r="E191" t="s">
+        <v>175</v>
+      </c>
+      <c r="F191" t="s">
+        <v>176</v>
+      </c>
+      <c r="G191" t="s">
+        <v>201</v>
+      </c>
+      <c r="H191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" t="s">
+        <v>17</v>
+      </c>
+      <c r="B192" t="s">
+        <v>71</v>
+      </c>
+      <c r="C192" t="s">
+        <v>116</v>
+      </c>
+      <c r="D192" t="s">
+        <v>128</v>
+      </c>
+      <c r="E192" t="s">
+        <v>175</v>
+      </c>
+      <c r="F192" t="s">
+        <v>177</v>
+      </c>
+      <c r="G192" t="s">
+        <v>202</v>
+      </c>
+      <c r="H192">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" t="s">
+        <v>17</v>
+      </c>
+      <c r="B193" t="s">
+        <v>71</v>
+      </c>
+      <c r="C193" t="s">
+        <v>116</v>
+      </c>
+      <c r="D193" t="s">
+        <v>128</v>
+      </c>
+      <c r="E193" t="s">
+        <v>175</v>
+      </c>
+      <c r="F193" t="s">
+        <v>175</v>
+      </c>
+      <c r="G193" t="s">
+        <v>200</v>
+      </c>
+      <c r="H193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" t="s">
+        <v>17</v>
+      </c>
+      <c r="B194" t="s">
+        <v>71</v>
+      </c>
+      <c r="C194" t="s">
+        <v>116</v>
+      </c>
+      <c r="D194" t="s">
+        <v>128</v>
+      </c>
+      <c r="E194" t="s">
+        <v>175</v>
+      </c>
+      <c r="F194" t="s">
+        <v>176</v>
+      </c>
+      <c r="G194" t="s">
+        <v>201</v>
+      </c>
+      <c r="H194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" t="s">
+        <v>17</v>
+      </c>
+      <c r="B195" t="s">
+        <v>71</v>
+      </c>
+      <c r="C195" t="s">
+        <v>116</v>
+      </c>
+      <c r="D195" t="s">
+        <v>128</v>
+      </c>
+      <c r="E195" t="s">
+        <v>175</v>
+      </c>
+      <c r="F195" t="s">
+        <v>177</v>
+      </c>
+      <c r="G195" t="s">
+        <v>202</v>
+      </c>
+      <c r="H195">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" t="s">
+        <v>61</v>
+      </c>
+      <c r="B196" t="s">
+        <v>115</v>
+      </c>
+      <c r="C196" t="s">
+        <v>116</v>
+      </c>
+      <c r="D196" t="s">
+        <v>174</v>
+      </c>
+      <c r="E196" t="s">
+        <v>175</v>
+      </c>
+      <c r="F196" t="s">
+        <v>175</v>
+      </c>
+      <c r="G196" t="s">
+        <v>316</v>
+      </c>
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
+        <v>61</v>
+      </c>
+      <c r="B197" t="s">
+        <v>115</v>
+      </c>
+      <c r="C197" t="s">
+        <v>116</v>
+      </c>
+      <c r="D197" t="s">
+        <v>174</v>
+      </c>
+      <c r="E197" t="s">
+        <v>175</v>
+      </c>
+      <c r="F197" t="s">
+        <v>176</v>
+      </c>
+      <c r="G197" t="s">
+        <v>317</v>
+      </c>
+      <c r="H197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>61</v>
+      </c>
+      <c r="B198" t="s">
+        <v>115</v>
+      </c>
+      <c r="C198" t="s">
+        <v>116</v>
+      </c>
+      <c r="D198" t="s">
+        <v>174</v>
+      </c>
+      <c r="E198" t="s">
+        <v>175</v>
+      </c>
+      <c r="F198" t="s">
+        <v>177</v>
+      </c>
+      <c r="G198" t="s">
+        <v>318</v>
+      </c>
+      <c r="H198">
         <v>3</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="124">
   <si>
     <t>code</t>
   </si>
@@ -82,6 +82,24 @@
     <t>ad55d177-41a1-444e-ae54-8c6807aee095</t>
   </si>
   <si>
+    <t>2155505c-bb3d-48ec-ba48-ac98edbdca95</t>
+  </si>
+  <si>
+    <t>abbb91f7-66fb-497f-87e0-235b843068fd</t>
+  </si>
+  <si>
+    <t>64348838-c95b-4e73-8c90-1539e49a8fa6</t>
+  </si>
+  <si>
+    <t>0219fe15-1f5c-4cd7-96f0-734727640195</t>
+  </si>
+  <si>
+    <t>208ebcc6-9881-4752-a982-5d8825476be0</t>
+  </si>
+  <si>
+    <t>df965e5e-d457-436c-a65a-af7726c7ce2b</t>
+  </si>
+  <si>
     <t>BRI UNIT SALAKAN</t>
   </si>
   <si>
@@ -124,6 +142,24 @@
     <t>TOTALINDO BANGGAI PERKASA</t>
   </si>
   <si>
+    <t>REKAYASA INDUSTRI PT</t>
+  </si>
+  <si>
+    <t>JOB PERTAMINA - MEDCO E&amp;P TOMORI SULAWESI</t>
+  </si>
+  <si>
+    <t>INDONESIA TSINGSHAN STAINLESS STEEL</t>
+  </si>
+  <si>
+    <t>HUA CHIN ALUMINUM  INDONESIA</t>
+  </si>
+  <si>
+    <t>TIGA BAJI, PT</t>
+  </si>
+  <si>
+    <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
+  </si>
+  <si>
     <t>DRAFT</t>
   </si>
   <si>
@@ -184,6 +220,24 @@
     <t>totalindobatbperkasa@gmail.com</t>
   </si>
   <si>
+    <t>wandysendjaja@yahoo.com</t>
+  </si>
+  <si>
+    <t>haris.ismail@job-tomori.com</t>
+  </si>
+  <si>
+    <t>secretariat@it-stainlesssteel.com</t>
+  </si>
+  <si>
+    <t>secretariathuachinind@gmail.com</t>
+  </si>
+  <si>
+    <t>aka-hamsah@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>mccmorowali@yahoo.com</t>
+  </si>
+  <si>
     <t>Bounced</t>
   </si>
   <si>
@@ -293,6 +347,45 @@
   </si>
   <si>
     <t>02 Jun 2026, 05:57:20</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:05:04</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:49:00</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:48:57</t>
+  </si>
+  <si>
+    <t>18 May 2026, 12:37:49</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 09:53:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 05:51:24</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:23:23</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 10:57:25</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 22:48:15</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:04:32</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:47:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:55:13</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:30</t>
   </si>
 </sst>
 </file>
@@ -650,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -684,22 +777,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -710,22 +803,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -736,22 +829,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -762,22 +855,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -788,22 +881,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -814,22 +907,22 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -840,22 +933,22 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -866,22 +959,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -892,22 +985,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -918,22 +1011,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -944,22 +1037,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -970,22 +1063,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -996,22 +1089,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1022,22 +1115,22 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -1048,22 +1141,22 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1074,22 +1167,22 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -1100,22 +1193,22 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1126,22 +1219,22 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -1152,22 +1245,22 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1178,22 +1271,22 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -1204,22 +1297,22 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1230,22 +1323,22 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -1256,22 +1349,22 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1282,22 +1375,22 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H25">
         <v>2</v>
@@ -1308,22 +1401,22 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1334,22 +1427,22 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E27" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1360,22 +1453,22 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1386,22 +1479,22 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1412,22 +1505,22 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1438,22 +1531,22 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -1464,22 +1557,22 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -1490,22 +1583,22 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1516,22 +1609,22 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1542,22 +1635,22 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -1568,22 +1661,22 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H36">
         <v>3</v>
@@ -1594,22 +1687,22 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -1620,22 +1713,22 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -1646,22 +1739,22 @@
         <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H39">
         <v>3</v>
@@ -1672,22 +1765,22 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D40" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -1698,22 +1791,22 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F41" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -1724,22 +1817,22 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F42" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H42">
         <v>2</v>
@@ -1750,22 +1843,22 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1776,22 +1869,22 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G44" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -1802,22 +1895,22 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F45" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1828,22 +1921,22 @@
         <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1854,22 +1947,22 @@
         <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -1880,22 +1973,22 @@
         <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H48">
         <v>3</v>
@@ -1906,22 +1999,22 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F49" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1932,22 +2025,22 @@
         <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F50" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -1958,22 +2051,22 @@
         <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -1984,22 +2077,22 @@
         <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G52" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2010,22 +2103,22 @@
         <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -2036,22 +2129,22 @@
         <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -2062,22 +2155,22 @@
         <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2088,22 +2181,22 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D56" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E56" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G56" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2114,22 +2207,22 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -2140,22 +2233,22 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2166,22 +2259,22 @@
         <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G59" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -2192,22 +2285,22 @@
         <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F60" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H60">
         <v>3</v>
@@ -2218,22 +2311,22 @@
         <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2244,22 +2337,22 @@
         <v>20</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H62">
         <v>2</v>
@@ -2270,22 +2363,22 @@
         <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -2296,22 +2389,22 @@
         <v>20</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C64" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F64" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2322,22 +2415,22 @@
         <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C65" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F65" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -2348,22 +2441,22 @@
         <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F66" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -2374,22 +2467,22 @@
         <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2400,22 +2493,22 @@
         <v>20</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C68" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H68">
         <v>2</v>
@@ -2426,22 +2519,22 @@
         <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F69" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2452,22 +2545,22 @@
         <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F70" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2478,22 +2571,22 @@
         <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E71" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F71" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G71" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2504,22 +2597,22 @@
         <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D72" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G72" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H72">
         <v>2</v>
@@ -2530,22 +2623,22 @@
         <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C73" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F73" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2556,22 +2649,22 @@
         <v>20</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D74" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E74" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F74" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G74" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -2582,22 +2675,22 @@
         <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D75" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F75" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2608,22 +2701,22 @@
         <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -2634,22 +2727,22 @@
         <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C77" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D77" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E77" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F77" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G77" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -2660,22 +2753,22 @@
         <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E78" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F78" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H78">
         <v>3</v>
@@ -2686,22 +2779,22 @@
         <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D79" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E79" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F79" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2712,22 +2805,22 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E80" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F80" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G80" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -2738,22 +2831,22 @@
         <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E81" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F81" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2764,22 +2857,22 @@
         <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E82" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F82" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2790,22 +2883,22 @@
         <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D83" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E83" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F83" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G83" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H83">
         <v>2</v>
@@ -2816,22 +2909,22 @@
         <v>20</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C84" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E84" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F84" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -2842,22 +2935,22 @@
         <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C85" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E85" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2868,22 +2961,22 @@
         <v>20</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C86" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D86" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E86" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F86" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G86" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2894,22 +2987,22 @@
         <v>20</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C87" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D87" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F87" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -2920,22 +3013,22 @@
         <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C88" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D88" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E88" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G88" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -2946,22 +3039,22 @@
         <v>20</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D89" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E89" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G89" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -2972,22 +3065,22 @@
         <v>20</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C90" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D90" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E90" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -2998,22 +3091,22 @@
         <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C91" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E91" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F91" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="G91" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -3024,22 +3117,22 @@
         <v>20</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C92" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D92" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E92" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F92" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G92" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H92">
         <v>2</v>
@@ -3050,22 +3143,22 @@
         <v>20</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D93" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E93" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="H93">
         <v>3</v>
@@ -3076,22 +3169,22 @@
         <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C94" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D94" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F94" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G94" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3102,24 +3195,440 @@
         <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C95" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D95" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F95" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" t="s">
+        <v>42</v>
+      </c>
+      <c r="C96" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" t="s">
+        <v>68</v>
+      </c>
+      <c r="E96" t="s">
+        <v>75</v>
+      </c>
+      <c r="F96" t="s">
+        <v>75</v>
+      </c>
+      <c r="G96" t="s">
+        <v>111</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97" t="s">
+        <v>50</v>
+      </c>
+      <c r="D97" t="s">
+        <v>68</v>
+      </c>
+      <c r="E97" t="s">
+        <v>75</v>
+      </c>
+      <c r="F97" t="s">
+        <v>74</v>
+      </c>
+      <c r="G97" t="s">
+        <v>112</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C98" t="s">
+        <v>50</v>
+      </c>
+      <c r="D98" t="s">
+        <v>68</v>
+      </c>
+      <c r="E98" t="s">
+        <v>75</v>
+      </c>
+      <c r="F98" t="s">
+        <v>76</v>
+      </c>
+      <c r="G98" t="s">
+        <v>113</v>
+      </c>
+      <c r="H98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>50</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" t="s">
+        <v>75</v>
+      </c>
+      <c r="F99" t="s">
+        <v>75</v>
+      </c>
+      <c r="G99" t="s">
+        <v>114</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" t="s">
+        <v>75</v>
+      </c>
+      <c r="F100" t="s">
+        <v>75</v>
+      </c>
+      <c r="G100" t="s">
+        <v>115</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" t="s">
+        <v>43</v>
+      </c>
+      <c r="C101" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" t="s">
+        <v>75</v>
+      </c>
+      <c r="F101" t="s">
+        <v>75</v>
+      </c>
+      <c r="G101" t="s">
+        <v>116</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102" t="s">
+        <v>70</v>
+      </c>
+      <c r="E102" t="s">
+        <v>74</v>
+      </c>
+      <c r="F102" t="s">
+        <v>76</v>
+      </c>
+      <c r="G102" t="s">
+        <v>117</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103" t="s">
+        <v>70</v>
+      </c>
+      <c r="E103" t="s">
+        <v>74</v>
+      </c>
+      <c r="F103" t="s">
+        <v>74</v>
+      </c>
+      <c r="G103" t="s">
+        <v>117</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>45</v>
+      </c>
+      <c r="C104" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" t="s">
+        <v>71</v>
+      </c>
+      <c r="E104" t="s">
+        <v>75</v>
+      </c>
+      <c r="F104" t="s">
+        <v>75</v>
+      </c>
+      <c r="G104" t="s">
+        <v>118</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>45</v>
+      </c>
+      <c r="C105" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" t="s">
+        <v>74</v>
+      </c>
+      <c r="G105" t="s">
+        <v>119</v>
+      </c>
+      <c r="H105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>45</v>
+      </c>
+      <c r="C106" t="s">
+        <v>50</v>
+      </c>
+      <c r="D106" t="s">
+        <v>71</v>
+      </c>
+      <c r="E106" t="s">
+        <v>75</v>
+      </c>
+      <c r="F106" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" t="s">
+        <v>119</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>26</v>
+      </c>
+      <c r="B107" t="s">
+        <v>46</v>
+      </c>
+      <c r="C107" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" t="s">
+        <v>72</v>
+      </c>
+      <c r="E107" t="s">
+        <v>75</v>
+      </c>
+      <c r="F107" t="s">
+        <v>75</v>
+      </c>
+      <c r="G107" t="s">
+        <v>120</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" t="s">
+        <v>26</v>
+      </c>
+      <c r="B108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" t="s">
+        <v>72</v>
+      </c>
+      <c r="E108" t="s">
+        <v>75</v>
+      </c>
+      <c r="F108" t="s">
+        <v>74</v>
+      </c>
+      <c r="G108" t="s">
+        <v>121</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" t="s">
+        <v>26</v>
+      </c>
+      <c r="B109" t="s">
+        <v>46</v>
+      </c>
+      <c r="C109" t="s">
+        <v>50</v>
+      </c>
+      <c r="D109" t="s">
+        <v>72</v>
+      </c>
+      <c r="E109" t="s">
+        <v>75</v>
+      </c>
+      <c r="F109" t="s">
+        <v>76</v>
+      </c>
+      <c r="G109" t="s">
+        <v>121</v>
+      </c>
+      <c r="H109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B110" t="s">
+        <v>47</v>
+      </c>
+      <c r="C110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" t="s">
+        <v>73</v>
+      </c>
+      <c r="E110" t="s">
+        <v>74</v>
+      </c>
+      <c r="F110" t="s">
+        <v>74</v>
+      </c>
+      <c r="G110" t="s">
+        <v>122</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
+      <c r="B111" t="s">
+        <v>47</v>
+      </c>
+      <c r="C111" t="s">
+        <v>50</v>
+      </c>
+      <c r="D111" t="s">
+        <v>73</v>
+      </c>
+      <c r="E111" t="s">
+        <v>74</v>
+      </c>
+      <c r="F111" t="s">
+        <v>76</v>
+      </c>
+      <c r="G111" t="s">
+        <v>123</v>
+      </c>
+      <c r="H111">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="188">
   <si>
     <t>code</t>
   </si>
@@ -100,6 +100,45 @@
     <t>df965e5e-d457-436c-a65a-af7726c7ce2b</t>
   </si>
   <si>
+    <t>0c6fcc80-9ea0-43b2-8775-cb18edc33d25</t>
+  </si>
+  <si>
+    <t>b2cf42e6-965c-49fa-abac-9af54426d0cc</t>
+  </si>
+  <si>
+    <t>e0e3282e-4685-4ad8-b636-6449ef659410</t>
+  </si>
+  <si>
+    <t>9818074f-7f62-4f6f-8a12-7b9ec153718e</t>
+  </si>
+  <si>
+    <t>2676b7e4-6dca-4e7f-991e-6ae27b0b0c85</t>
+  </si>
+  <si>
+    <t>9b9e29d1-fc1e-4b2d-99d7-838fde85299c</t>
+  </si>
+  <si>
+    <t>e807b2d0-c9e8-4158-bc0a-301bcc232add</t>
+  </si>
+  <si>
+    <t>22df9424-5a77-4276-ab7d-9c4bc6b29108</t>
+  </si>
+  <si>
+    <t>b58860b3-d502-48de-bf29-ebc5b51b0389</t>
+  </si>
+  <si>
+    <t>cf953441-4548-4748-b059-68c60a1c9312</t>
+  </si>
+  <si>
+    <t>befe39ef-4187-40aa-9e99-fef88d32baa1</t>
+  </si>
+  <si>
+    <t>df80536f-5125-46c8-aa0a-220b8d26441b</t>
+  </si>
+  <si>
+    <t>e674036e-bee0-47b7-bc94-a0c32bfa2d71</t>
+  </si>
+  <si>
     <t>BRI UNIT SALAKAN</t>
   </si>
   <si>
@@ -160,6 +199,45 @@
     <t>MCC15 ENGINEERING AND CONSTRUCTION</t>
   </si>
   <si>
+    <t>BROLY NICKEL INDUSTRY</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA, PT</t>
+  </si>
+  <si>
+    <t>HADJI KALLA</t>
+  </si>
+  <si>
+    <t>Detian Coking Indonesia</t>
+  </si>
+  <si>
+    <t>JEMBATAN MAS ENGINEERING</t>
+  </si>
+  <si>
+    <t>INDONESIA RUIPU NICKEL AND CROME ALLOY, PT</t>
+  </si>
+  <si>
+    <t>THE SIXTH CHEMICAL ENGINEERING CONSTRUCTION</t>
+  </si>
+  <si>
+    <t>KENCANA BUMI MINERAL</t>
+  </si>
+  <si>
+    <t>CIPTA MANDIRI MOROWALI</t>
+  </si>
+  <si>
+    <t>INDONESIA GUANG CHING NICKEL AND STAINLESS STEEL INDUSTRY TKA</t>
+  </si>
+  <si>
+    <t>KINRUI NEW ENERGY TECHNOLOGIES  INDONESIA</t>
+  </si>
+  <si>
+    <t>BANK BPD</t>
+  </si>
+  <si>
+    <t>AKAR DAYA MANDIRI PT</t>
+  </si>
+  <si>
     <t>DRAFT</t>
   </si>
   <si>
@@ -238,6 +316,45 @@
     <t>mccmorowali@yahoo.com</t>
   </si>
   <si>
+    <t>hengjayasite@yahoo.com</t>
+  </si>
+  <si>
+    <t>sapriliya@bsm.co.id</t>
+  </si>
+  <si>
+    <t>nur.salam.coning@kallagroup.co.id</t>
+  </si>
+  <si>
+    <t>secretariat@detiancoking-ind.com</t>
+  </si>
+  <si>
+    <t>jembatanmas579@yahoo.com</t>
+  </si>
+  <si>
+    <t>smaalkhairatkolono@yahoo.co.id</t>
+  </si>
+  <si>
+    <t>sobeh@ppc-adulsory.com</t>
+  </si>
+  <si>
+    <t>acctaxkbm@yahoo.com</t>
+  </si>
+  <si>
+    <t>ciptamandiri@yahoo.com</t>
+  </si>
+  <si>
+    <t>rukun@bd.em.com</t>
+  </si>
+  <si>
+    <t>secretariatkinrui@gmail.com</t>
+  </si>
+  <si>
+    <t>bsposo@yahoo.com</t>
+  </si>
+  <si>
+    <t>akardayamandiri49@gmail.com</t>
+  </si>
+  <si>
     <t>Bounced</t>
   </si>
   <si>
@@ -386,6 +503,81 @@
   </si>
   <si>
     <t>02 Jun 2026, 08:52:30</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:00:02</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:06:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:57:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:49:47</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:57:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:45:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:43:12</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:08:56</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:11:39</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 04:58:16</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:22:02</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:06:55</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:15</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:52:11</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:29:20</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:28:43</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:53</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:54:49</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:29</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 06:59:25</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:48</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 08:52:14</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:17:21</t>
   </si>
 </sst>
 </file>
@@ -743,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -777,22 +969,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -803,22 +995,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -829,22 +1021,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -855,22 +1047,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -881,22 +1073,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -907,22 +1099,22 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -933,22 +1125,22 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -959,22 +1151,22 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -985,22 +1177,22 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1011,22 +1203,22 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -1037,22 +1229,22 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1063,22 +1255,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1089,22 +1281,22 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1115,22 +1307,22 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -1141,22 +1333,22 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1167,22 +1359,22 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -1193,22 +1385,22 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1219,22 +1411,22 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -1245,22 +1437,22 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1271,22 +1463,22 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G21" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="H21">
         <v>2</v>
@@ -1297,22 +1489,22 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1323,22 +1515,22 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="H23">
         <v>2</v>
@@ -1349,22 +1541,22 @@
         <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F24" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1375,22 +1567,22 @@
         <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H25">
         <v>2</v>
@@ -1401,22 +1593,22 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1427,22 +1619,22 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="H27">
         <v>2</v>
@@ -1453,22 +1645,22 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1479,22 +1671,22 @@
         <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="H29">
         <v>2</v>
@@ -1505,22 +1697,22 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E30" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1531,22 +1723,22 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="H31">
         <v>2</v>
@@ -1557,22 +1749,22 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="E32" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="H32">
         <v>3</v>
@@ -1583,22 +1775,22 @@
         <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1609,22 +1801,22 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G34" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1635,22 +1827,22 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H35">
         <v>2</v>
@@ -1661,22 +1853,22 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H36">
         <v>3</v>
@@ -1687,22 +1879,22 @@
         <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G37" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -1713,22 +1905,22 @@
         <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G38" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -1739,22 +1931,22 @@
         <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H39">
         <v>3</v>
@@ -1765,22 +1957,22 @@
         <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G40" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -1791,22 +1983,22 @@
         <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D41" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G41" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -1817,22 +2009,22 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D42" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H42">
         <v>2</v>
@@ -1843,22 +2035,22 @@
         <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1869,22 +2061,22 @@
         <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F44" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G44" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -1895,22 +2087,22 @@
         <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H45">
         <v>3</v>
@@ -1921,22 +2113,22 @@
         <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G46" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1947,22 +2139,22 @@
         <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F47" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H47">
         <v>2</v>
@@ -1973,22 +2165,22 @@
         <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G48" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H48">
         <v>3</v>
@@ -1999,22 +2191,22 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G49" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2025,22 +2217,22 @@
         <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E50" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G50" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -2051,22 +2243,22 @@
         <v>20</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G51" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H51">
         <v>3</v>
@@ -2077,22 +2269,22 @@
         <v>20</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F52" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G52" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2103,22 +2295,22 @@
         <v>20</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F53" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -2129,22 +2321,22 @@
         <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F54" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G54" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H54">
         <v>3</v>
@@ -2155,22 +2347,22 @@
         <v>20</v>
       </c>
       <c r="B55" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2181,22 +2373,22 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E56" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F56" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G56" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2207,22 +2399,22 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E57" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -2233,22 +2425,22 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G58" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2259,22 +2451,22 @@
         <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C59" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E59" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G59" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -2285,22 +2477,22 @@
         <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H60">
         <v>3</v>
@@ -2311,22 +2503,22 @@
         <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2337,22 +2529,22 @@
         <v>20</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C62" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D62" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G62" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H62">
         <v>2</v>
@@ -2363,22 +2555,22 @@
         <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H63">
         <v>3</v>
@@ -2389,22 +2581,22 @@
         <v>20</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E64" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G64" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2415,22 +2607,22 @@
         <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G65" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H65">
         <v>2</v>
@@ -2441,22 +2633,22 @@
         <v>20</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E66" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F66" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G66" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -2467,22 +2659,22 @@
         <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G67" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2493,22 +2685,22 @@
         <v>20</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E68" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G68" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H68">
         <v>2</v>
@@ -2519,22 +2711,22 @@
         <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D69" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H69">
         <v>3</v>
@@ -2545,22 +2737,22 @@
         <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D70" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E70" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G70" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2571,22 +2763,22 @@
         <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E71" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F71" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G71" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2597,22 +2789,22 @@
         <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D72" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E72" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G72" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H72">
         <v>2</v>
@@ -2623,22 +2815,22 @@
         <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E73" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G73" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2649,22 +2841,22 @@
         <v>20</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D74" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E74" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G74" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -2675,22 +2867,22 @@
         <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F75" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H75">
         <v>3</v>
@@ -2701,22 +2893,22 @@
         <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E76" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F76" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G76" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -2727,22 +2919,22 @@
         <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D77" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G77" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H77">
         <v>2</v>
@@ -2753,22 +2945,22 @@
         <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H78">
         <v>3</v>
@@ -2779,22 +2971,22 @@
         <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D79" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E79" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G79" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2805,22 +2997,22 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D80" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G80" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H80">
         <v>2</v>
@@ -2831,22 +3023,22 @@
         <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -2857,22 +3049,22 @@
         <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D82" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2883,22 +3075,22 @@
         <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C83" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D83" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E83" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G83" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H83">
         <v>2</v>
@@ -2909,22 +3101,22 @@
         <v>20</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C84" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D84" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E84" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -2935,22 +3127,22 @@
         <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D85" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G85" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2961,22 +3153,22 @@
         <v>20</v>
       </c>
       <c r="B86" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D86" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E86" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F86" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G86" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2987,22 +3179,22 @@
         <v>20</v>
       </c>
       <c r="B87" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D87" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="E87" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F87" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="H87">
         <v>2</v>
@@ -3013,22 +3205,22 @@
         <v>20</v>
       </c>
       <c r="B88" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C88" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D88" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G88" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -3039,22 +3231,22 @@
         <v>20</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C89" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D89" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G89" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -3065,22 +3257,22 @@
         <v>20</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C90" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E90" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H90">
         <v>3</v>
@@ -3091,22 +3283,22 @@
         <v>20</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C91" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D91" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E91" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G91" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -3117,22 +3309,22 @@
         <v>20</v>
       </c>
       <c r="B92" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C92" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D92" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E92" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G92" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="H92">
         <v>2</v>
@@ -3143,22 +3335,22 @@
         <v>20</v>
       </c>
       <c r="B93" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D93" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="E93" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="H93">
         <v>3</v>
@@ -3169,22 +3361,22 @@
         <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D94" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E94" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F94" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G94" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3195,22 +3387,22 @@
         <v>21</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C95" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D95" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="E95" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F95" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="H95">
         <v>2</v>
@@ -3221,22 +3413,22 @@
         <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D96" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F96" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G96" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3247,22 +3439,22 @@
         <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D97" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G97" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="H97">
         <v>2</v>
@@ -3273,22 +3465,22 @@
         <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C98" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D98" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="E98" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G98" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="H98">
         <v>3</v>
@@ -3299,22 +3491,22 @@
         <v>23</v>
       </c>
       <c r="B99" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D99" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E99" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G99" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3325,22 +3517,22 @@
         <v>23</v>
       </c>
       <c r="B100" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C100" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D100" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E100" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G100" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="H100">
         <v>2</v>
@@ -3351,22 +3543,22 @@
         <v>23</v>
       </c>
       <c r="B101" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C101" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D101" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="H101">
         <v>3</v>
@@ -3377,22 +3569,22 @@
         <v>24</v>
       </c>
       <c r="B102" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C102" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D102" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E102" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F102" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G102" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3403,22 +3595,22 @@
         <v>24</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C103" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D103" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E103" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F103" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G103" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="H103">
         <v>2</v>
@@ -3429,22 +3621,22 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C104" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F104" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G104" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3455,22 +3647,22 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C105" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D105" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E105" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F105" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G105" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="H105">
         <v>2</v>
@@ -3481,22 +3673,22 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D106" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E106" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F106" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G106" t="s">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="H106">
         <v>3</v>
@@ -3507,22 +3699,22 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D107" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E107" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F107" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="G107" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -3533,22 +3725,22 @@
         <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C108" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D108" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E108" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F108" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G108" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H108">
         <v>2</v>
@@ -3559,22 +3751,22 @@
         <v>26</v>
       </c>
       <c r="B109" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D109" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="E109" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F109" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G109" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="H109">
         <v>3</v>
@@ -3585,22 +3777,22 @@
         <v>27</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C110" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D110" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E110" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="F110" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="G110" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -3611,24 +3803,934 @@
         <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C111" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D111" t="s">
+        <v>99</v>
+      </c>
+      <c r="E111" t="s">
+        <v>113</v>
+      </c>
+      <c r="F111" t="s">
+        <v>115</v>
+      </c>
+      <c r="G111" t="s">
+        <v>162</v>
+      </c>
+      <c r="H111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C112" t="s">
+        <v>76</v>
+      </c>
+      <c r="D112" t="s">
+        <v>100</v>
+      </c>
+      <c r="E112" t="s">
+        <v>114</v>
+      </c>
+      <c r="F112" t="s">
+        <v>114</v>
+      </c>
+      <c r="G112" t="s">
+        <v>163</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" t="s">
+        <v>61</v>
+      </c>
+      <c r="C113" t="s">
+        <v>76</v>
+      </c>
+      <c r="D113" t="s">
+        <v>100</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" t="s">
+        <v>113</v>
+      </c>
+      <c r="G113" t="s">
+        <v>164</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>61</v>
+      </c>
+      <c r="C114" t="s">
+        <v>76</v>
+      </c>
+      <c r="D114" t="s">
+        <v>100</v>
+      </c>
+      <c r="E114" t="s">
+        <v>114</v>
+      </c>
+      <c r="F114" t="s">
+        <v>115</v>
+      </c>
+      <c r="G114" t="s">
+        <v>165</v>
+      </c>
+      <c r="H114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" t="s">
+        <v>29</v>
+      </c>
+      <c r="B115" t="s">
+        <v>62</v>
+      </c>
+      <c r="C115" t="s">
+        <v>76</v>
+      </c>
+      <c r="D115" t="s">
+        <v>101</v>
+      </c>
+      <c r="E115" t="s">
+        <v>113</v>
+      </c>
+      <c r="F115" t="s">
+        <v>113</v>
+      </c>
+      <c r="G115" t="s">
+        <v>166</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" t="s">
+        <v>29</v>
+      </c>
+      <c r="B116" t="s">
+        <v>62</v>
+      </c>
+      <c r="C116" t="s">
+        <v>76</v>
+      </c>
+      <c r="D116" t="s">
+        <v>101</v>
+      </c>
+      <c r="E116" t="s">
+        <v>113</v>
+      </c>
+      <c r="F116" t="s">
+        <v>115</v>
+      </c>
+      <c r="G116" t="s">
+        <v>167</v>
+      </c>
+      <c r="H116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" t="s">
+        <v>30</v>
+      </c>
+      <c r="B117" t="s">
+        <v>63</v>
+      </c>
+      <c r="C117" t="s">
+        <v>76</v>
+      </c>
+      <c r="D117" t="s">
+        <v>102</v>
+      </c>
+      <c r="E117" t="s">
+        <v>114</v>
+      </c>
+      <c r="F117" t="s">
+        <v>114</v>
+      </c>
+      <c r="G117" t="s">
+        <v>168</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" t="s">
+        <v>31</v>
+      </c>
+      <c r="B118" t="s">
+        <v>64</v>
+      </c>
+      <c r="C118" t="s">
+        <v>76</v>
+      </c>
+      <c r="D118" t="s">
+        <v>103</v>
+      </c>
+      <c r="E118" t="s">
+        <v>113</v>
+      </c>
+      <c r="F118" t="s">
+        <v>113</v>
+      </c>
+      <c r="G118" t="s">
+        <v>169</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" t="s">
+        <v>31</v>
+      </c>
+      <c r="B119" t="s">
+        <v>64</v>
+      </c>
+      <c r="C119" t="s">
+        <v>76</v>
+      </c>
+      <c r="D119" t="s">
+        <v>103</v>
+      </c>
+      <c r="E119" t="s">
+        <v>113</v>
+      </c>
+      <c r="F119" t="s">
+        <v>115</v>
+      </c>
+      <c r="G119" t="s">
+        <v>170</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" t="s">
+        <v>32</v>
+      </c>
+      <c r="B120" t="s">
+        <v>65</v>
+      </c>
+      <c r="C120" t="s">
+        <v>76</v>
+      </c>
+      <c r="D120" t="s">
+        <v>104</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="F120" t="s">
+        <v>114</v>
+      </c>
+      <c r="G120" t="s">
+        <v>171</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" t="s">
+        <v>32</v>
+      </c>
+      <c r="B121" t="s">
+        <v>65</v>
+      </c>
+      <c r="C121" t="s">
+        <v>76</v>
+      </c>
+      <c r="D121" t="s">
+        <v>104</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
+        <v>114</v>
+      </c>
+      <c r="G121" t="s">
+        <v>172</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" t="s">
+        <v>66</v>
+      </c>
+      <c r="C122" t="s">
+        <v>76</v>
+      </c>
+      <c r="D122" t="s">
+        <v>105</v>
+      </c>
+      <c r="E122" t="s">
+        <v>113</v>
+      </c>
+      <c r="F122" t="s">
+        <v>113</v>
+      </c>
+      <c r="G122" t="s">
+        <v>173</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" t="s">
+        <v>66</v>
+      </c>
+      <c r="C123" t="s">
+        <v>76</v>
+      </c>
+      <c r="D123" t="s">
+        <v>105</v>
+      </c>
+      <c r="E123" t="s">
+        <v>113</v>
+      </c>
+      <c r="F123" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" t="s">
+        <v>174</v>
+      </c>
+      <c r="H123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" t="s">
+        <v>67</v>
+      </c>
+      <c r="C124" t="s">
+        <v>76</v>
+      </c>
+      <c r="D124" t="s">
+        <v>106</v>
+      </c>
+      <c r="E124" t="s">
+        <v>113</v>
+      </c>
+      <c r="F124" t="s">
+        <v>115</v>
+      </c>
+      <c r="G124" t="s">
+        <v>175</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" t="s">
+        <v>34</v>
+      </c>
+      <c r="B125" t="s">
+        <v>67</v>
+      </c>
+      <c r="C125" t="s">
+        <v>76</v>
+      </c>
+      <c r="D125" t="s">
+        <v>106</v>
+      </c>
+      <c r="E125" t="s">
+        <v>113</v>
+      </c>
+      <c r="F125" t="s">
+        <v>113</v>
+      </c>
+      <c r="G125" t="s">
+        <v>175</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" t="s">
+        <v>35</v>
+      </c>
+      <c r="B126" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" t="s">
+        <v>76</v>
+      </c>
+      <c r="D126" t="s">
+        <v>107</v>
+      </c>
+      <c r="E126" t="s">
+        <v>114</v>
+      </c>
+      <c r="F126" t="s">
+        <v>114</v>
+      </c>
+      <c r="G126" t="s">
+        <v>176</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127" t="s">
+        <v>68</v>
+      </c>
+      <c r="C127" t="s">
+        <v>76</v>
+      </c>
+      <c r="D127" t="s">
+        <v>107</v>
+      </c>
+      <c r="E127" t="s">
+        <v>114</v>
+      </c>
+      <c r="F127" t="s">
+        <v>113</v>
+      </c>
+      <c r="G127" t="s">
+        <v>177</v>
+      </c>
+      <c r="H127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
+        <v>35</v>
+      </c>
+      <c r="B128" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" t="s">
+        <v>76</v>
+      </c>
+      <c r="D128" t="s">
+        <v>107</v>
+      </c>
+      <c r="E128" t="s">
+        <v>114</v>
+      </c>
+      <c r="F128" t="s">
+        <v>115</v>
+      </c>
+      <c r="G128" t="s">
+        <v>178</v>
+      </c>
+      <c r="H128">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
+        <v>12</v>
+      </c>
+      <c r="B129" t="s">
+        <v>45</v>
+      </c>
+      <c r="C129" t="s">
+        <v>76</v>
+      </c>
+      <c r="D129" t="s">
+        <v>81</v>
+      </c>
+      <c r="E129" t="s">
+        <v>113</v>
+      </c>
+      <c r="F129" t="s">
+        <v>113</v>
+      </c>
+      <c r="G129" t="s">
+        <v>125</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" t="s">
+        <v>45</v>
+      </c>
+      <c r="C130" t="s">
+        <v>76</v>
+      </c>
+      <c r="D130" t="s">
+        <v>81</v>
+      </c>
+      <c r="E130" t="s">
+        <v>113</v>
+      </c>
+      <c r="F130" t="s">
+        <v>115</v>
+      </c>
+      <c r="G130" t="s">
+        <v>126</v>
+      </c>
+      <c r="H130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>45</v>
+      </c>
+      <c r="C131" t="s">
+        <v>76</v>
+      </c>
+      <c r="D131" t="s">
+        <v>82</v>
+      </c>
+      <c r="E131" t="s">
+        <v>113</v>
+      </c>
+      <c r="F131" t="s">
+        <v>113</v>
+      </c>
+      <c r="G131" t="s">
+        <v>127</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132" t="s">
+        <v>45</v>
+      </c>
+      <c r="C132" t="s">
+        <v>76</v>
+      </c>
+      <c r="D132" t="s">
+        <v>82</v>
+      </c>
+      <c r="E132" t="s">
+        <v>113</v>
+      </c>
+      <c r="F132" t="s">
+        <v>115</v>
+      </c>
+      <c r="G132" t="s">
+        <v>128</v>
+      </c>
+      <c r="H132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133" t="s">
+        <v>45</v>
+      </c>
+      <c r="C133" t="s">
+        <v>76</v>
+      </c>
+      <c r="D133" t="s">
+        <v>81</v>
+      </c>
+      <c r="E133" t="s">
+        <v>113</v>
+      </c>
+      <c r="F133" t="s">
+        <v>113</v>
+      </c>
+      <c r="G133" t="s">
+        <v>125</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" t="s">
+        <v>45</v>
+      </c>
+      <c r="C134" t="s">
+        <v>76</v>
+      </c>
+      <c r="D134" t="s">
+        <v>81</v>
+      </c>
+      <c r="E134" t="s">
+        <v>113</v>
+      </c>
+      <c r="F134" t="s">
+        <v>115</v>
+      </c>
+      <c r="G134" t="s">
+        <v>126</v>
+      </c>
+      <c r="H134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" t="s">
+        <v>45</v>
+      </c>
+      <c r="C135" t="s">
+        <v>76</v>
+      </c>
+      <c r="D135" t="s">
+        <v>82</v>
+      </c>
+      <c r="E135" t="s">
+        <v>113</v>
+      </c>
+      <c r="F135" t="s">
+        <v>113</v>
+      </c>
+      <c r="G135" t="s">
+        <v>127</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" t="s">
+        <v>45</v>
+      </c>
+      <c r="C136" t="s">
+        <v>76</v>
+      </c>
+      <c r="D136" t="s">
+        <v>82</v>
+      </c>
+      <c r="E136" t="s">
+        <v>113</v>
+      </c>
+      <c r="F136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G136" t="s">
+        <v>128</v>
+      </c>
+      <c r="H136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" t="s">
+        <v>69</v>
+      </c>
+      <c r="C137" t="s">
+        <v>76</v>
+      </c>
+      <c r="D137" t="s">
+        <v>108</v>
+      </c>
+      <c r="E137" t="s">
+        <v>113</v>
+      </c>
+      <c r="F137" t="s">
+        <v>113</v>
+      </c>
+      <c r="G137" t="s">
+        <v>179</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" t="s">
+        <v>69</v>
+      </c>
+      <c r="C138" t="s">
+        <v>76</v>
+      </c>
+      <c r="D138" t="s">
+        <v>108</v>
+      </c>
+      <c r="E138" t="s">
+        <v>113</v>
+      </c>
+      <c r="F138" t="s">
+        <v>115</v>
+      </c>
+      <c r="G138" t="s">
+        <v>180</v>
+      </c>
+      <c r="H138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>37</v>
+      </c>
+      <c r="B139" t="s">
+        <v>70</v>
+      </c>
+      <c r="C139" t="s">
+        <v>76</v>
+      </c>
+      <c r="D139" t="s">
+        <v>109</v>
+      </c>
+      <c r="E139" t="s">
+        <v>113</v>
+      </c>
+      <c r="F139" t="s">
+        <v>113</v>
+      </c>
+      <c r="G139" t="s">
+        <v>181</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" t="s">
+        <v>70</v>
+      </c>
+      <c r="C140" t="s">
+        <v>76</v>
+      </c>
+      <c r="D140" t="s">
+        <v>109</v>
+      </c>
+      <c r="E140" t="s">
+        <v>113</v>
+      </c>
+      <c r="F140" t="s">
+        <v>115</v>
+      </c>
+      <c r="G140" t="s">
+        <v>182</v>
+      </c>
+      <c r="H140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>38</v>
+      </c>
+      <c r="B141" t="s">
+        <v>71</v>
+      </c>
+      <c r="C141" t="s">
+        <v>76</v>
+      </c>
+      <c r="D141" t="s">
+        <v>110</v>
+      </c>
+      <c r="E141" t="s">
+        <v>113</v>
+      </c>
+      <c r="F141" t="s">
+        <v>113</v>
+      </c>
+      <c r="G141" t="s">
+        <v>183</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>38</v>
+      </c>
+      <c r="B142" t="s">
+        <v>71</v>
+      </c>
+      <c r="C142" t="s">
+        <v>76</v>
+      </c>
+      <c r="D142" t="s">
+        <v>110</v>
+      </c>
+      <c r="E142" t="s">
+        <v>113</v>
+      </c>
+      <c r="F142" t="s">
+        <v>115</v>
+      </c>
+      <c r="G142" t="s">
+        <v>184</v>
+      </c>
+      <c r="H142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>39</v>
+      </c>
+      <c r="B143" t="s">
+        <v>72</v>
+      </c>
+      <c r="C143" t="s">
+        <v>76</v>
+      </c>
+      <c r="D143" t="s">
+        <v>111</v>
+      </c>
+      <c r="E143" t="s">
+        <v>113</v>
+      </c>
+      <c r="F143" t="s">
+        <v>113</v>
+      </c>
+      <c r="G143" t="s">
+        <v>185</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>39</v>
+      </c>
+      <c r="B144" t="s">
+        <v>72</v>
+      </c>
+      <c r="C144" t="s">
+        <v>76</v>
+      </c>
+      <c r="D144" t="s">
+        <v>111</v>
+      </c>
+      <c r="E144" t="s">
+        <v>113</v>
+      </c>
+      <c r="F144" t="s">
+        <v>115</v>
+      </c>
+      <c r="G144" t="s">
+        <v>186</v>
+      </c>
+      <c r="H144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>40</v>
+      </c>
+      <c r="B145" t="s">
         <v>73</v>
       </c>
-      <c r="E111" t="s">
-        <v>74</v>
-      </c>
-      <c r="F111" t="s">
-        <v>76</v>
-      </c>
-      <c r="G111" t="s">
-        <v>123</v>
-      </c>
-      <c r="H111">
+      <c r="C145" t="s">
+        <v>76</v>
+      </c>
+      <c r="D145" t="s">
+        <v>112</v>
+      </c>
+      <c r="E145" t="s">
+        <v>113</v>
+      </c>
+      <c r="F145" t="s">
+        <v>113</v>
+      </c>
+      <c r="G145" t="s">
+        <v>187</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>40</v>
+      </c>
+      <c r="B146" t="s">
+        <v>73</v>
+      </c>
+      <c r="C146" t="s">
+        <v>76</v>
+      </c>
+      <c r="D146" t="s">
+        <v>112</v>
+      </c>
+      <c r="E146" t="s">
+        <v>113</v>
+      </c>
+      <c r="F146" t="s">
+        <v>115</v>
+      </c>
+      <c r="G146" t="s">
+        <v>187</v>
+      </c>
+      <c r="H146">
         <v>2</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -169,6 +169,12 @@
     <t>01b351f3-b52c-4516-a91c-00f58d08579d</t>
   </si>
   <si>
+    <t>b6c21085-5e3c-4d3b-bcb0-1e48c3bbaca7</t>
+  </si>
+  <si>
+    <t>eeee3ec7-6e8b-4ba0-86e1-e4a35de9cc96</t>
+  </si>
+  <si>
     <t>66b93b8d-817c-4af4-9183-47792e43d54e</t>
   </si>
   <si>
@@ -178,12 +184,6 @@
     <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
   </si>
   <si>
-    <t>eeee3ec7-6e8b-4ba0-86e1-e4a35de9cc96</t>
-  </si>
-  <si>
-    <t>b6c21085-5e3c-4d3b-bcb0-1e48c3bbaca7</t>
-  </si>
-  <si>
     <t>f455e248-e952-4fc6-9076-0237c90636fd</t>
   </si>
   <si>
@@ -550,6 +550,12 @@
     <t>KCP MANDIRI MITRA USAHA TENTENA</t>
   </si>
   <si>
+    <t>PDAM KAB DONGGALA</t>
+  </si>
+  <si>
+    <t>ASTUN HI. ARSYAD</t>
+  </si>
+  <si>
     <t>SEKOLAH POLISI NEGARA</t>
   </si>
   <si>
@@ -559,12 +565,6 @@
     <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
   </si>
   <si>
-    <t>ASTUN HI. ARSYAD</t>
-  </si>
-  <si>
-    <t>PDAM KAB DONGGALA</t>
-  </si>
-  <si>
     <t>KOPERASI KONSUMEN DHARMA MARITIM TOLITOLI</t>
   </si>
   <si>
@@ -931,6 +931,12 @@
     <t>kcpmandirimitrausaha@gmail.com</t>
   </si>
   <si>
+    <t>pdam_donggala@gmail.com</t>
+  </si>
+  <si>
+    <t>astunhiarsyad28@gmail.com</t>
+  </si>
+  <si>
     <t>kppnpalu651707@yahoo.com</t>
   </si>
   <si>
@@ -940,12 +946,6 @@
     <t>bprlabuan@yahoo.co.id</t>
   </si>
   <si>
-    <t>astunhiarsyad28@gmail.com</t>
-  </si>
-  <si>
-    <t>pdam_donggala@gmail.com</t>
-  </si>
-  <si>
     <t>koperasi_maritim@yahoo.com</t>
   </si>
   <si>
@@ -1480,6 +1480,15 @@
     <t>01 Jun 2026, 22:47:26</t>
   </si>
   <si>
+    <t>02 Jun 2026, 06:31:35</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:54</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 09:45:51</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 02:30:55</t>
   </si>
   <si>
@@ -1499,15 +1508,6 @@
   </si>
   <si>
     <t>01 Jun 2026, 23:29:34</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 09:45:54</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 09:45:51</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 06:31:35</t>
   </si>
   <si>
     <t>02 Jun 2026, 10:08:22</t>
@@ -5810,7 +5810,7 @@
         <v>388</v>
       </c>
       <c r="F114" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G114" t="s">
         <v>488</v>
@@ -5839,10 +5839,10 @@
         <v>388</v>
       </c>
       <c r="F115" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G115" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H115">
         <v>2</v>
@@ -5871,7 +5871,7 @@
         <v>388</v>
       </c>
       <c r="G116" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -5900,7 +5900,7 @@
         <v>390</v>
       </c>
       <c r="G117" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H117">
         <v>2</v>
@@ -5923,13 +5923,13 @@
         <v>307</v>
       </c>
       <c r="E118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F118" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G118" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -5952,13 +5952,13 @@
         <v>307</v>
       </c>
       <c r="E119" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F119" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G119" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H119">
         <v>2</v>
@@ -5969,28 +5969,28 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B120" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C120" t="s">
         <v>262</v>
       </c>
       <c r="D120" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E120" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F120" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G120" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I120" t="s">
         <v>705</v>
@@ -6013,13 +6013,13 @@
         <v>388</v>
       </c>
       <c r="F121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G121" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="s">
         <v>705</v>
@@ -6027,28 +6027,28 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B122" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C122" t="s">
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E122" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F122" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G122" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I122" t="s">
         <v>705</v>
@@ -6068,16 +6068,16 @@
         <v>309</v>
       </c>
       <c r="E123" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F123" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G123" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123" t="s">
         <v>705</v>
@@ -6097,16 +6097,16 @@
         <v>309</v>
       </c>
       <c r="E124" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G124" t="s">
         <v>497</v>
       </c>
       <c r="H124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I124" t="s">
         <v>705</v>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3121" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="714">
   <si>
     <t>code</t>
   </si>
@@ -265,12 +265,12 @@
     <t>ccb05db1-4c75-48a4-af8d-3afec698c2b0</t>
   </si>
   <si>
+    <t>964afb29-6bd2-4eed-80a6-cad68ec6908c</t>
+  </si>
+  <si>
     <t>bf80de69-7b3b-490c-8124-38ba829bd928</t>
   </si>
   <si>
-    <t>964afb29-6bd2-4eed-80a6-cad68ec6908c</t>
-  </si>
-  <si>
     <t>0829529d-cd5a-4edf-83d1-af18106eaef1</t>
   </si>
   <si>
@@ -295,18 +295,18 @@
     <t>d0165086-104a-4500-b00b-2fc5d6b40f95</t>
   </si>
   <si>
+    <t>13d6fcb9-8ce0-4a1e-95f1-aec964383baa</t>
+  </si>
+  <si>
     <t>196883ff-6fac-4215-82ad-2eca8c1fe974</t>
   </si>
   <si>
-    <t>13d6fcb9-8ce0-4a1e-95f1-aec964383baa</t>
+    <t>378ebc19-fd46-4557-91f9-cb71ad58fe6d</t>
   </si>
   <si>
     <t>435c8c27-de5c-4a97-a672-5bd16e36f2a1</t>
   </si>
   <si>
-    <t>378ebc19-fd46-4557-91f9-cb71ad58fe6d</t>
-  </si>
-  <si>
     <t>56f75602-d43a-4bec-81d8-cd5eace22450</t>
   </si>
   <si>
@@ -643,12 +643,12 @@
     <t>SINERGI BINTANG UTARA</t>
   </si>
   <si>
+    <t>Toko suharman &lt;Darmiati&gt;</t>
+  </si>
+  <si>
     <t>KEINZ VENTURA PT</t>
   </si>
   <si>
-    <t>Toko suharman &lt;Darmiati&gt;</t>
-  </si>
-  <si>
     <t>GENBA INDO RESOURCES</t>
   </si>
   <si>
@@ -673,18 +673,18 @@
     <t>MANADO MOTOR, CV</t>
   </si>
   <si>
+    <t>PRIMA GELORA AGUNG LESTARI, PT</t>
+  </si>
+  <si>
     <t>BANK BRI UNIT TAWAELI</t>
   </si>
   <si>
-    <t>PRIMA GELORA AGUNG LESTARI, PT</t>
+    <t>SPBU KAYUMALUE</t>
   </si>
   <si>
     <t>HAYCARB PALU MITRA PT</t>
   </si>
   <si>
-    <t>SPBU KAYUMALUE</t>
-  </si>
-  <si>
     <t>MANDIRI ARGO LESTARI CV</t>
   </si>
   <si>
@@ -1027,12 +1027,12 @@
     <t>pt.sinergibintangutara@yahoo.com</t>
   </si>
   <si>
+    <t>ktuana@asta.go.id</t>
+  </si>
+  <si>
     <t>keinzventura1205@gmail.com</t>
   </si>
   <si>
-    <t>ktuana@asta.go.id</t>
-  </si>
-  <si>
     <t>gir.mining2019@gmail.com</t>
   </si>
   <si>
@@ -1057,18 +1057,18 @@
     <t>soputraroland@yahoo.com</t>
   </si>
   <si>
+    <t>primagelora_palu@yahoo.com</t>
+  </si>
+  <si>
     <t>n3448@bricorp.co.id</t>
   </si>
   <si>
-    <t>primagelora_palu@yahoo.com</t>
+    <t>spbutawaeli74943313@gmail.com</t>
   </si>
   <si>
     <t>hpm-accountr@haycarbindo.com</t>
   </si>
   <si>
-    <t>spbutawaeli74943313@gmail.com</t>
-  </si>
-  <si>
     <t>cvmandiriargolestari@gmail.com</t>
   </si>
   <si>
@@ -1762,18 +1762,18 @@
     <t>02 Jun 2026, 07:44:51</t>
   </si>
   <si>
+    <t>02 Jun 2026, 11:47:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 11:47:26</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 07:01:31</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:01:30</t>
   </si>
   <si>
-    <t>02 Jun 2026, 11:47:27</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 11:47:26</t>
-  </si>
-  <si>
     <t>09 Jun 2026, 10:59:03</t>
   </si>
   <si>
@@ -1837,31 +1837,31 @@
     <t>02 Jun 2026, 07:57:15</t>
   </si>
   <si>
+    <t>09 Jun 2026, 11:01:38</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:26:06</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:23:45</t>
+  </si>
+  <si>
     <t>01 Jun 2026, 23:35:32</t>
   </si>
   <si>
-    <t>09 Jun 2026, 11:01:38</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:26:06</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:23:45</t>
+    <t>09 Jun 2026, 11:13:52</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:02</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:41:01</t>
   </si>
   <si>
     <t>09 Jun 2026, 11:17:18</t>
   </si>
   <si>
     <t>02 Jun 2026, 01:06:09</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:13:52</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 00:41:02</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 00:41:01</t>
   </si>
   <si>
     <t>02 Jun 2026, 11:37:42</t>
@@ -2513,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I387"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -10279,7 +10279,7 @@
         <v>389</v>
       </c>
       <c r="G268" t="s">
-        <v>404</v>
+        <v>607</v>
       </c>
       <c r="H268">
         <v>1</v>
@@ -10308,7 +10308,7 @@
         <v>388</v>
       </c>
       <c r="G269" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H269">
         <v>2</v>
@@ -10337,7 +10337,7 @@
         <v>390</v>
       </c>
       <c r="G270" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H270">
         <v>3</v>
@@ -10366,7 +10366,7 @@
         <v>389</v>
       </c>
       <c r="G271" t="s">
-        <v>608</v>
+        <v>404</v>
       </c>
       <c r="H271">
         <v>1</v>
@@ -10395,7 +10395,7 @@
         <v>388</v>
       </c>
       <c r="G272" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H272">
         <v>2</v>
@@ -10479,7 +10479,7 @@
         <v>389</v>
       </c>
       <c r="F275" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G275" t="s">
         <v>612</v>
@@ -10508,10 +10508,10 @@
         <v>389</v>
       </c>
       <c r="F276" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G276" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H276">
         <v>3</v>
@@ -10540,7 +10540,7 @@
         <v>389</v>
       </c>
       <c r="G277" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H277">
         <v>1</v>
@@ -10566,10 +10566,10 @@
         <v>389</v>
       </c>
       <c r="F278" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G278" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H278">
         <v>2</v>
@@ -10595,7 +10595,7 @@
         <v>389</v>
       </c>
       <c r="F279" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G279" t="s">
         <v>615</v>
@@ -13736,93 +13736,6 @@
         <v>2</v>
       </c>
       <c r="I387" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9">
-      <c r="A388" t="s">
-        <v>92</v>
-      </c>
-      <c r="B388" t="s">
-        <v>218</v>
-      </c>
-      <c r="C388" t="s">
-        <v>261</v>
-      </c>
-      <c r="D388" t="s">
-        <v>346</v>
-      </c>
-      <c r="E388" t="s">
-        <v>389</v>
-      </c>
-      <c r="F388" t="s">
-        <v>389</v>
-      </c>
-      <c r="G388" t="s">
-        <v>604</v>
-      </c>
-      <c r="H388">
-        <v>1</v>
-      </c>
-      <c r="I388" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9">
-      <c r="A389" t="s">
-        <v>92</v>
-      </c>
-      <c r="B389" t="s">
-        <v>218</v>
-      </c>
-      <c r="C389" t="s">
-        <v>261</v>
-      </c>
-      <c r="D389" t="s">
-        <v>346</v>
-      </c>
-      <c r="E389" t="s">
-        <v>389</v>
-      </c>
-      <c r="F389" t="s">
-        <v>388</v>
-      </c>
-      <c r="G389" t="s">
-        <v>605</v>
-      </c>
-      <c r="H389">
-        <v>2</v>
-      </c>
-      <c r="I389" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9">
-      <c r="A390" t="s">
-        <v>92</v>
-      </c>
-      <c r="B390" t="s">
-        <v>218</v>
-      </c>
-      <c r="C390" t="s">
-        <v>261</v>
-      </c>
-      <c r="D390" t="s">
-        <v>346</v>
-      </c>
-      <c r="E390" t="s">
-        <v>389</v>
-      </c>
-      <c r="F390" t="s">
-        <v>390</v>
-      </c>
-      <c r="G390" t="s">
-        <v>606</v>
-      </c>
-      <c r="H390">
-        <v>3</v>
-      </c>
-      <c r="I390" t="s">
         <v>713</v>
       </c>
     </row>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3121" uniqueCount="714">
   <si>
     <t>code</t>
   </si>
@@ -2513,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I387"/>
+  <dimension ref="A1:I390"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -13739,6 +13739,93 @@
         <v>713</v>
       </c>
     </row>
+    <row r="388" spans="1:9">
+      <c r="A388" t="s">
+        <v>92</v>
+      </c>
+      <c r="B388" t="s">
+        <v>218</v>
+      </c>
+      <c r="C388" t="s">
+        <v>261</v>
+      </c>
+      <c r="D388" t="s">
+        <v>346</v>
+      </c>
+      <c r="E388" t="s">
+        <v>389</v>
+      </c>
+      <c r="F388" t="s">
+        <v>389</v>
+      </c>
+      <c r="G388" t="s">
+        <v>604</v>
+      </c>
+      <c r="H388">
+        <v>1</v>
+      </c>
+      <c r="I388" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" t="s">
+        <v>92</v>
+      </c>
+      <c r="B389" t="s">
+        <v>218</v>
+      </c>
+      <c r="C389" t="s">
+        <v>261</v>
+      </c>
+      <c r="D389" t="s">
+        <v>346</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
+      </c>
+      <c r="F389" t="s">
+        <v>388</v>
+      </c>
+      <c r="G389" t="s">
+        <v>605</v>
+      </c>
+      <c r="H389">
+        <v>2</v>
+      </c>
+      <c r="I389" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" t="s">
+        <v>92</v>
+      </c>
+      <c r="B390" t="s">
+        <v>218</v>
+      </c>
+      <c r="C390" t="s">
+        <v>261</v>
+      </c>
+      <c r="D390" t="s">
+        <v>346</v>
+      </c>
+      <c r="E390" t="s">
+        <v>389</v>
+      </c>
+      <c r="F390" t="s">
+        <v>390</v>
+      </c>
+      <c r="G390" t="s">
+        <v>606</v>
+      </c>
+      <c r="H390">
+        <v>3</v>
+      </c>
+      <c r="I390" t="s">
+        <v>713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -52,6 +52,9 @@
     <t>81b140d6-80f9-436f-81e4-bbfc8ae820d3</t>
   </si>
   <si>
+    <t>ca7ed898-5339-4d22-8a89-b89adc186705</t>
+  </si>
+  <si>
     <t>5ed2770d-9be6-4fc1-bf70-0d4e10c482c8</t>
   </si>
   <si>
@@ -85,9 +88,6 @@
     <t>87ab3e43-e1be-4b02-af1e-14720ebfb03f</t>
   </si>
   <si>
-    <t>ca7ed898-5339-4d22-8a89-b89adc186705</t>
-  </si>
-  <si>
     <t>0d4bfa96-7cd5-47d9-b366-e133f6ea27c4</t>
   </si>
   <si>
@@ -439,6 +439,9 @@
     <t>BPR MODERN EXPRESS PT</t>
   </si>
   <si>
+    <t>BANK PERKREDITAN RAKYAT PALU LOKADANA UTAMA</t>
+  </si>
+  <si>
     <t>BANK PERKREDITAN RAKYAT MITRA NIAGA BANGGAI</t>
   </si>
   <si>
@@ -472,9 +475,6 @@
     <t>CAHAYA BARU SENTOSA</t>
   </si>
   <si>
-    <t>BANK PERKREDITAN RAKYAT PALU LOKADANA UTAMA</t>
-  </si>
-  <si>
     <t>BANK DANAMON INDONESIA, PT TBK KCP LUWUK</t>
   </si>
   <si>
@@ -814,6 +814,12 @@
     <t>bpr.381@lakadana.com</t>
   </si>
   <si>
+    <t>kc.luwuk@bprpalulokadanautama.com</t>
+  </si>
+  <si>
+    <t>kc.morowali@bprpalulokadanautama.com</t>
+  </si>
+  <si>
     <t>toili@mailnesia.com</t>
   </si>
   <si>
@@ -847,12 +853,6 @@
     <t>cbs_luwuk@yahoo.com</t>
   </si>
   <si>
-    <t>kc.luwuk@bprpalulokadanautama.com</t>
-  </si>
-  <si>
-    <t>kc.morowali@bprpalulokadanautama.com</t>
-  </si>
-  <si>
     <t>bankdanamon.admin@gmail.com</t>
   </si>
   <si>
@@ -1219,6 +1219,18 @@
     <t>11 Jun 2026, 10:53:00</t>
   </si>
   <si>
+    <t>02 Jun 2026, 07:38:30</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:38:27</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:41</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 07:55:37</t>
+  </si>
+  <si>
     <t>02 Jun 2026, 02:11:11</t>
   </si>
   <si>
@@ -1289,18 +1301,6 @@
   </si>
   <si>
     <t>02 Jun 2026, 03:51:54</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 07:38:30</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 07:38:27</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 07:55:41</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 07:55:37</t>
   </si>
   <si>
     <t>09 Jun 2026, 11:00:04</t>
@@ -2965,10 +2965,10 @@
         <v>266</v>
       </c>
       <c r="E16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G16" t="s">
         <v>401</v>
@@ -2982,28 +2982,28 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F17" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G17" t="s">
         <v>402</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
         <v>702</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" t="s">
         <v>261</v>
@@ -3023,7 +3023,7 @@
         <v>267</v>
       </c>
       <c r="E18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F18" t="s">
         <v>388</v>
@@ -3032,7 +3032,7 @@
         <v>403</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
         <v>702</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" t="s">
         <v>261</v>
@@ -3052,7 +3052,7 @@
         <v>267</v>
       </c>
       <c r="E19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F19" t="s">
         <v>390</v>
@@ -3061,7 +3061,7 @@
         <v>404</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="s">
         <v>702</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
         <v>261</v>
@@ -3107,19 +3107,19 @@
         <v>261</v>
       </c>
       <c r="D21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" t="s">
         <v>389</v>
       </c>
       <c r="F21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G21" t="s">
         <v>406</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
         <v>702</v>
@@ -3136,19 +3136,19 @@
         <v>261</v>
       </c>
       <c r="D22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E22" t="s">
         <v>389</v>
       </c>
       <c r="F22" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G22" t="s">
         <v>407</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="s">
         <v>702</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
         <v>261</v>
@@ -3168,16 +3168,16 @@
         <v>269</v>
       </c>
       <c r="E23" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F23" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G23" t="s">
         <v>408</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="s">
         <v>702</v>
@@ -3194,19 +3194,19 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G24" t="s">
         <v>409</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
         <v>702</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
         <v>261</v>
@@ -3226,16 +3226,16 @@
         <v>270</v>
       </c>
       <c r="E25" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F25" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G25" t="s">
         <v>410</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="s">
         <v>702</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C26" t="s">
         <v>261</v>
@@ -3255,16 +3255,16 @@
         <v>270</v>
       </c>
       <c r="E26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F26" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G26" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="s">
         <v>702</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
         <v>261</v>
@@ -3284,13 +3284,13 @@
         <v>271</v>
       </c>
       <c r="E27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G27" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
         <v>261</v>
@@ -3313,13 +3313,13 @@
         <v>271</v>
       </c>
       <c r="E28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F28" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G28" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H28">
         <v>2</v>
@@ -3339,19 +3339,19 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E29" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F29" t="s">
         <v>390</v>
       </c>
       <c r="G29" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
         <v>702</v>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
         <v>261</v>
@@ -3380,7 +3380,7 @@
         <v>414</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="s">
         <v>702</v>
@@ -3397,19 +3397,19 @@
         <v>261</v>
       </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E31" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F31" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G31" t="s">
         <v>415</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
         <v>702</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
         <v>261</v>
@@ -3432,13 +3432,13 @@
         <v>389</v>
       </c>
       <c r="F32" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G32" t="s">
         <v>416</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" t="s">
         <v>702</v>
@@ -3446,10 +3446,10 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
         <v>261</v>
@@ -3461,13 +3461,13 @@
         <v>389</v>
       </c>
       <c r="F33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G33" t="s">
         <v>417</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
         <v>702</v>
@@ -3484,19 +3484,19 @@
         <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E34" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F34" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G34" t="s">
         <v>418</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" t="s">
         <v>702</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
         <v>261</v>
@@ -3519,13 +3519,13 @@
         <v>388</v>
       </c>
       <c r="F35" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G35" t="s">
         <v>419</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="s">
         <v>702</v>
@@ -3542,19 +3542,19 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E36" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G36" t="s">
         <v>420</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I36" t="s">
         <v>702</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
         <v>261</v>
@@ -3574,16 +3574,16 @@
         <v>275</v>
       </c>
       <c r="E37" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F37" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G37" t="s">
         <v>421</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I37" t="s">
         <v>702</v>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
         <v>261</v>
@@ -3603,16 +3603,16 @@
         <v>275</v>
       </c>
       <c r="E38" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G38" t="s">
         <v>422</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" t="s">
         <v>702</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
         <v>261</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
         <v>261</v>
@@ -3678,10 +3678,10 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
         <v>261</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
         <v>261</v>
@@ -3942,13 +3942,13 @@
         <v>26</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E50" t="s">
         <v>388</v>
@@ -3957,7 +3957,7 @@
         <v>390</v>
       </c>
       <c r="G50" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -3971,13 +3971,13 @@
         <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E51" t="s">
         <v>388</v>
@@ -3986,7 +3986,7 @@
         <v>388</v>
       </c>
       <c r="G51" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -4000,13 +4000,13 @@
         <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C52" t="s">
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E52" t="s">
         <v>388</v>
@@ -4015,7 +4015,7 @@
         <v>390</v>
       </c>
       <c r="G52" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -4029,13 +4029,13 @@
         <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="E53" t="s">
         <v>388</v>
@@ -4044,7 +4044,7 @@
         <v>388</v>
       </c>
       <c r="G53" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -5160,7 +5160,7 @@
         <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C92" t="s">
         <v>261</v>
@@ -7248,7 +7248,7 @@
         <v>65</v>
       </c>
       <c r="B164" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C164" t="s">
         <v>261</v>
@@ -7277,7 +7277,7 @@
         <v>65</v>
       </c>
       <c r="B165" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C165" t="s">
         <v>261</v>
@@ -7306,7 +7306,7 @@
         <v>65</v>
       </c>
       <c r="B166" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C166" t="s">
         <v>261</v>
@@ -7335,13 +7335,13 @@
         <v>65</v>
       </c>
       <c r="B167" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C167" t="s">
         <v>261</v>
       </c>
       <c r="D167" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E167" t="s">
         <v>389</v>
@@ -7350,7 +7350,7 @@
         <v>388</v>
       </c>
       <c r="G167" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H167">
         <v>2</v>
@@ -7364,13 +7364,13 @@
         <v>65</v>
       </c>
       <c r="B168" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C168" t="s">
         <v>261</v>
       </c>
       <c r="D168" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E168" t="s">
         <v>389</v>
@@ -7379,7 +7379,7 @@
         <v>390</v>
       </c>
       <c r="G168" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H168">
         <v>3</v>
@@ -7393,13 +7393,13 @@
         <v>65</v>
       </c>
       <c r="B169" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C169" t="s">
         <v>261</v>
       </c>
       <c r="D169" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E169" t="s">
         <v>389</v>
@@ -7408,7 +7408,7 @@
         <v>389</v>
       </c>
       <c r="G169" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -10424,7 +10424,7 @@
         <v>389</v>
       </c>
       <c r="G273" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H273">
         <v>1</v>
@@ -10888,7 +10888,7 @@
         <v>388</v>
       </c>
       <c r="G289" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H289">
         <v>1</v>
@@ -10917,7 +10917,7 @@
         <v>390</v>
       </c>
       <c r="G290" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H290">
         <v>2</v>
@@ -13222,7 +13222,7 @@
         <v>131</v>
       </c>
       <c r="B370" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C370" t="s">
         <v>261</v>
@@ -13251,7 +13251,7 @@
         <v>131</v>
       </c>
       <c r="B371" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C371" t="s">
         <v>261</v>
@@ -13280,7 +13280,7 @@
         <v>131</v>
       </c>
       <c r="B372" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C372" t="s">
         <v>261</v>
@@ -13309,13 +13309,13 @@
         <v>131</v>
       </c>
       <c r="B373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C373" t="s">
         <v>261</v>
       </c>
       <c r="D373" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E373" t="s">
         <v>389</v>
@@ -13324,7 +13324,7 @@
         <v>389</v>
       </c>
       <c r="G373" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H373">
         <v>1</v>
@@ -13338,13 +13338,13 @@
         <v>131</v>
       </c>
       <c r="B374" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C374" t="s">
         <v>261</v>
       </c>
       <c r="D374" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E374" t="s">
         <v>389</v>
@@ -13353,7 +13353,7 @@
         <v>388</v>
       </c>
       <c r="G374" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H374">
         <v>2</v>
@@ -13367,13 +13367,13 @@
         <v>131</v>
       </c>
       <c r="B375" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C375" t="s">
         <v>261</v>
       </c>
       <c r="D375" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E375" t="s">
         <v>389</v>
@@ -13382,7 +13382,7 @@
         <v>390</v>
       </c>
       <c r="G375" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H375">
         <v>3</v>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -199,18 +199,18 @@
     <t>11fd6f69-871d-4258-81f6-e2145ee9f73a</t>
   </si>
   <si>
+    <t>7caf507f-ded1-4591-bf6a-60996f83c71b</t>
+  </si>
+  <si>
+    <t>3266144a-e1e8-481f-a863-d9ee0ed1a652</t>
+  </si>
+  <si>
+    <t>75b6fc99-ef00-42bd-8f54-fcab0ac2a238</t>
+  </si>
+  <si>
     <t>a9979a0c-403c-4acf-bb30-3023bbfba8b5</t>
   </si>
   <si>
-    <t>75b6fc99-ef00-42bd-8f54-fcab0ac2a238</t>
-  </si>
-  <si>
-    <t>3266144a-e1e8-481f-a863-d9ee0ed1a652</t>
-  </si>
-  <si>
-    <t>7caf507f-ded1-4591-bf6a-60996f83c71b</t>
-  </si>
-  <si>
     <t>8a32e430-23b2-46ff-8b68-7dd7afb33862</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
   </si>
   <si>
+    <t>BANK MANDIRI (PERSERO) TBK KCP BUOL, PT</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT DIAPATIH</t>
+  </si>
+  <si>
+    <t>PT BANK NEGARA INDONESIA (PERSERO) TBK</t>
+  </si>
+  <si>
     <t>BANK PEREKONOMIAN RAKYAT MODERN EXPRESS</t>
   </si>
   <si>
-    <t>PT BANK NEGARA INDONESIA (PERSERO) TBK</t>
-  </si>
-  <si>
-    <t>BANK BRI UNIT DIAPATIH</t>
-  </si>
-  <si>
-    <t>BANK MANDIRI (PERSERO) TBK KCP BUOL, PT</t>
-  </si>
-  <si>
     <t>BRI UNIT TINOMBO</t>
   </si>
   <si>
@@ -961,18 +961,18 @@
     <t>kc.tolitoli@bprpalulokadanautama.com</t>
   </si>
   <si>
+    <t>nyoalvaro@gmail.com</t>
+  </si>
+  <si>
+    <t>yohanesyafetsulung@gmail.com</t>
+  </si>
+  <si>
+    <t>ynataliaw@gmail.com</t>
+  </si>
+  <si>
     <t>fandhymadjid96@gmail.com</t>
   </si>
   <si>
-    <t>ynataliaw@gmail.com</t>
-  </si>
-  <si>
-    <t>yohanesyafetsulung@gmail.com</t>
-  </si>
-  <si>
-    <t>nyoalvaro@gmail.com</t>
-  </si>
-  <si>
     <t>kaslambunu@yahoo.co.id</t>
   </si>
   <si>
@@ -1543,6 +1543,42 @@
     <t>01 Jun 2026, 23:16:27</t>
   </si>
   <si>
+    <t>19 May 2026, 11:14:38</t>
+  </si>
+  <si>
+    <t>19 May 2026, 11:14:34</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:52</t>
+  </si>
+  <si>
+    <t>21 May 2026, 08:24:48</t>
+  </si>
+  <si>
+    <t>09 Jun 2026, 11:12:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 00:32:29</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:26</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:03:04</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:47</t>
+  </si>
+  <si>
+    <t>20 May 2026, 11:02:44</t>
+  </si>
+  <si>
+    <t>10 Jun 2026, 15:04:30</t>
+  </si>
+  <si>
+    <t>10 Jun 2026, 14:33:40</t>
+  </si>
+  <si>
     <t>20 May 2026, 14:15:07</t>
   </si>
   <si>
@@ -1571,42 +1607,6 @@
   </si>
   <si>
     <t>02 Jun 2026, 11:49:04</t>
-  </si>
-  <si>
-    <t>20 May 2026, 11:03:26</t>
-  </si>
-  <si>
-    <t>20 May 2026, 11:03:04</t>
-  </si>
-  <si>
-    <t>20 May 2026, 11:02:47</t>
-  </si>
-  <si>
-    <t>20 May 2026, 11:02:44</t>
-  </si>
-  <si>
-    <t>19 May 2026, 11:14:34</t>
-  </si>
-  <si>
-    <t>10 Jun 2026, 15:04:30</t>
-  </si>
-  <si>
-    <t>10 Jun 2026, 14:33:40</t>
-  </si>
-  <si>
-    <t>21 May 2026, 08:24:52</t>
-  </si>
-  <si>
-    <t>21 May 2026, 08:24:48</t>
-  </si>
-  <si>
-    <t>09 Jun 2026, 11:12:55</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 00:32:29</t>
-  </si>
-  <si>
-    <t>19 May 2026, 11:14:38</t>
   </si>
   <si>
     <t>02 Jun 2026, 04:02:15</t>
@@ -6497,7 +6497,7 @@
         <v>188</v>
       </c>
       <c r="C138" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>315</v>
@@ -6506,7 +6506,7 @@
         <v>388</v>
       </c>
       <c r="F138" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G138" t="s">
         <v>509</v>
@@ -6526,7 +6526,7 @@
         <v>188</v>
       </c>
       <c r="C139" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>315</v>
@@ -6535,7 +6535,7 @@
         <v>388</v>
       </c>
       <c r="F139" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G139" t="s">
         <v>510</v>
@@ -6549,28 +6549,28 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B140" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D140" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E140" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F140" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G140" t="s">
         <v>511</v>
       </c>
       <c r="H140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I140" t="s">
         <v>707</v>
@@ -6578,28 +6578,28 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B141" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E141" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F141" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G141" t="s">
         <v>512</v>
       </c>
       <c r="H141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I141" t="s">
         <v>707</v>
@@ -6607,28 +6607,28 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B142" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C142" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F142" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G142" t="s">
         <v>513</v>
       </c>
       <c r="H142">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I142" t="s">
         <v>707</v>
@@ -6636,28 +6636,28 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B143" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E143" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F143" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G143" t="s">
         <v>514</v>
       </c>
       <c r="H143">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I143" t="s">
         <v>707</v>
@@ -6665,28 +6665,28 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B144" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C144" t="s">
         <v>262</v>
       </c>
       <c r="D144" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E144" t="s">
         <v>388</v>
       </c>
       <c r="F144" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G144" t="s">
         <v>515</v>
       </c>
       <c r="H144">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I144" t="s">
         <v>707</v>
@@ -6694,28 +6694,28 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B145" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C145" t="s">
         <v>262</v>
       </c>
       <c r="D145" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E145" t="s">
         <v>388</v>
       </c>
       <c r="F145" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G145" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H145">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I145" t="s">
         <v>707</v>
@@ -6723,28 +6723,28 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B146" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C146" t="s">
         <v>262</v>
       </c>
       <c r="D146" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E146" t="s">
         <v>388</v>
       </c>
       <c r="F146" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G146" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H146">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I146" t="s">
         <v>707</v>
@@ -6752,16 +6752,16 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B147" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C147" t="s">
         <v>262</v>
       </c>
       <c r="D147" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E147" t="s">
         <v>388</v>
@@ -6770,10 +6770,10 @@
         <v>390</v>
       </c>
       <c r="G147" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H147">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I147" t="s">
         <v>707</v>
@@ -6781,28 +6781,28 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B148" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C148" t="s">
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E148" t="s">
         <v>388</v>
       </c>
       <c r="F148" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G148" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="H148">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I148" t="s">
         <v>707</v>
@@ -6810,28 +6810,28 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B149" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C149" t="s">
         <v>262</v>
       </c>
       <c r="D149" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E149" t="s">
         <v>388</v>
       </c>
       <c r="F149" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G149" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="H149">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I149" t="s">
         <v>707</v>
@@ -6839,28 +6839,28 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B150" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C150" t="s">
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E150" t="s">
         <v>388</v>
       </c>
       <c r="F150" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G150" t="s">
         <v>519</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I150" t="s">
         <v>707</v>
@@ -6868,16 +6868,16 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B151" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C151" t="s">
         <v>262</v>
       </c>
       <c r="D151" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E151" t="s">
         <v>388</v>
@@ -6889,7 +6889,7 @@
         <v>520</v>
       </c>
       <c r="H151">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I151" t="s">
         <v>707</v>
@@ -6897,28 +6897,28 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B152" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C152" t="s">
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E152" t="s">
         <v>388</v>
       </c>
       <c r="F152" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G152" t="s">
         <v>521</v>
       </c>
       <c r="H152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I152" t="s">
         <v>707</v>
@@ -6926,28 +6926,28 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B153" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C153" t="s">
         <v>262</v>
       </c>
       <c r="D153" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E153" t="s">
         <v>388</v>
       </c>
       <c r="F153" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G153" t="s">
         <v>522</v>
       </c>
       <c r="H153">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I153" t="s">
         <v>707</v>
@@ -6955,28 +6955,28 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B154" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C154" t="s">
         <v>262</v>
       </c>
       <c r="D154" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E154" t="s">
         <v>388</v>
       </c>
       <c r="F154" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G154" t="s">
         <v>523</v>
       </c>
       <c r="H154">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I154" t="s">
         <v>707</v>
@@ -6984,28 +6984,28 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B155" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C155" t="s">
         <v>262</v>
       </c>
       <c r="D155" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E155" t="s">
         <v>388</v>
       </c>
       <c r="F155" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G155" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I155" t="s">
         <v>707</v>
@@ -7013,28 +7013,28 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B156" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C156" t="s">
         <v>262</v>
       </c>
       <c r="D156" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E156" t="s">
         <v>388</v>
       </c>
       <c r="F156" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G156" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H156">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I156" t="s">
         <v>707</v>
@@ -7042,16 +7042,16 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B157" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C157" t="s">
         <v>262</v>
       </c>
       <c r="D157" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E157" t="s">
         <v>388</v>
@@ -7060,10 +7060,10 @@
         <v>392</v>
       </c>
       <c r="G157" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H157">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I157" t="s">
         <v>707</v>
@@ -7071,28 +7071,28 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B158" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C158" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D158" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E158" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F158" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G158" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I158" t="s">
         <v>707</v>
@@ -7100,19 +7100,19 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B159" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C159" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E159" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F159" t="s">
         <v>390</v>
@@ -7121,7 +7121,7 @@
         <v>527</v>
       </c>
       <c r="H159">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I159" t="s">
         <v>707</v>
@@ -7129,28 +7129,28 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B160" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C160" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D160" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E160" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F160" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G160" t="s">
         <v>528</v>
       </c>
       <c r="H160">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I160" t="s">
         <v>707</v>
@@ -7158,28 +7158,28 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B161" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C161" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E161" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F161" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G161" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H161">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I161" t="s">
         <v>707</v>
@@ -7193,7 +7193,7 @@
         <v>191</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>318</v>
@@ -7202,13 +7202,13 @@
         <v>388</v>
       </c>
       <c r="F162" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G162" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I162" t="s">
         <v>707</v>
@@ -7222,7 +7222,7 @@
         <v>191</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>318</v>
@@ -7234,10 +7234,10 @@
         <v>390</v>
       </c>
       <c r="G163" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I163" t="s">
         <v>707</v>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="714">
   <si>
     <t>code</t>
   </si>
@@ -2513,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I392"/>
+  <dimension ref="A1:I389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -13797,93 +13797,6 @@
         <v>713</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
-      <c r="A390" t="s">
-        <v>92</v>
-      </c>
-      <c r="B390" t="s">
-        <v>218</v>
-      </c>
-      <c r="C390" t="s">
-        <v>260</v>
-      </c>
-      <c r="D390" t="s">
-        <v>346</v>
-      </c>
-      <c r="E390" t="s">
-        <v>389</v>
-      </c>
-      <c r="F390" t="s">
-        <v>389</v>
-      </c>
-      <c r="G390" t="s">
-        <v>604</v>
-      </c>
-      <c r="H390">
-        <v>1</v>
-      </c>
-      <c r="I390" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9">
-      <c r="A391" t="s">
-        <v>92</v>
-      </c>
-      <c r="B391" t="s">
-        <v>218</v>
-      </c>
-      <c r="C391" t="s">
-        <v>260</v>
-      </c>
-      <c r="D391" t="s">
-        <v>346</v>
-      </c>
-      <c r="E391" t="s">
-        <v>389</v>
-      </c>
-      <c r="F391" t="s">
-        <v>388</v>
-      </c>
-      <c r="G391" t="s">
-        <v>605</v>
-      </c>
-      <c r="H391">
-        <v>2</v>
-      </c>
-      <c r="I391" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9">
-      <c r="A392" t="s">
-        <v>92</v>
-      </c>
-      <c r="B392" t="s">
-        <v>218</v>
-      </c>
-      <c r="C392" t="s">
-        <v>260</v>
-      </c>
-      <c r="D392" t="s">
-        <v>346</v>
-      </c>
-      <c r="E392" t="s">
-        <v>389</v>
-      </c>
-      <c r="F392" t="s">
-        <v>390</v>
-      </c>
-      <c r="G392" t="s">
-        <v>606</v>
-      </c>
-      <c r="H392">
-        <v>3</v>
-      </c>
-      <c r="I392" t="s">
-        <v>713</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="714">
   <si>
     <t>code</t>
   </si>
@@ -2513,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I389"/>
+  <dimension ref="A1:I392"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -13797,6 +13797,93 @@
         <v>713</v>
       </c>
     </row>
+    <row r="390" spans="1:9">
+      <c r="A390" t="s">
+        <v>92</v>
+      </c>
+      <c r="B390" t="s">
+        <v>218</v>
+      </c>
+      <c r="C390" t="s">
+        <v>260</v>
+      </c>
+      <c r="D390" t="s">
+        <v>346</v>
+      </c>
+      <c r="E390" t="s">
+        <v>389</v>
+      </c>
+      <c r="F390" t="s">
+        <v>389</v>
+      </c>
+      <c r="G390" t="s">
+        <v>604</v>
+      </c>
+      <c r="H390">
+        <v>1</v>
+      </c>
+      <c r="I390" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" t="s">
+        <v>92</v>
+      </c>
+      <c r="B391" t="s">
+        <v>218</v>
+      </c>
+      <c r="C391" t="s">
+        <v>260</v>
+      </c>
+      <c r="D391" t="s">
+        <v>346</v>
+      </c>
+      <c r="E391" t="s">
+        <v>389</v>
+      </c>
+      <c r="F391" t="s">
+        <v>388</v>
+      </c>
+      <c r="G391" t="s">
+        <v>605</v>
+      </c>
+      <c r="H391">
+        <v>2</v>
+      </c>
+      <c r="I391" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392" t="s">
+        <v>92</v>
+      </c>
+      <c r="B392" t="s">
+        <v>218</v>
+      </c>
+      <c r="C392" t="s">
+        <v>260</v>
+      </c>
+      <c r="D392" t="s">
+        <v>346</v>
+      </c>
+      <c r="E392" t="s">
+        <v>389</v>
+      </c>
+      <c r="F392" t="s">
+        <v>390</v>
+      </c>
+      <c r="G392" t="s">
+        <v>606</v>
+      </c>
+      <c r="H392">
+        <v>3</v>
+      </c>
+      <c r="I392" t="s">
+        <v>713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="721">
   <si>
     <t>code</t>
   </si>
@@ -2534,7 +2534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I385"/>
+  <dimension ref="A1:I391"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -13702,6 +13702,180 @@
         <v>720</v>
       </c>
     </row>
+    <row r="386" spans="1:9">
+      <c r="A386" t="s">
+        <v>88</v>
+      </c>
+      <c r="B386" t="s">
+        <v>212</v>
+      </c>
+      <c r="C386" t="s">
+        <v>258</v>
+      </c>
+      <c r="D386" t="s">
+        <v>340</v>
+      </c>
+      <c r="E386" t="s">
+        <v>387</v>
+      </c>
+      <c r="F386" t="s">
+        <v>390</v>
+      </c>
+      <c r="G386" t="s">
+        <v>595</v>
+      </c>
+      <c r="H386">
+        <v>1</v>
+      </c>
+      <c r="I386" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387" t="s">
+        <v>88</v>
+      </c>
+      <c r="B387" t="s">
+        <v>212</v>
+      </c>
+      <c r="C387" t="s">
+        <v>258</v>
+      </c>
+      <c r="D387" t="s">
+        <v>340</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+      <c r="F387" t="s">
+        <v>387</v>
+      </c>
+      <c r="G387" t="s">
+        <v>596</v>
+      </c>
+      <c r="H387">
+        <v>2</v>
+      </c>
+      <c r="I387" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388" t="s">
+        <v>88</v>
+      </c>
+      <c r="B388" t="s">
+        <v>212</v>
+      </c>
+      <c r="C388" t="s">
+        <v>258</v>
+      </c>
+      <c r="D388" t="s">
+        <v>340</v>
+      </c>
+      <c r="E388" t="s">
+        <v>387</v>
+      </c>
+      <c r="F388" t="s">
+        <v>388</v>
+      </c>
+      <c r="G388" t="s">
+        <v>597</v>
+      </c>
+      <c r="H388">
+        <v>3</v>
+      </c>
+      <c r="I388" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389" t="s">
+        <v>91</v>
+      </c>
+      <c r="B389" t="s">
+        <v>215</v>
+      </c>
+      <c r="C389" t="s">
+        <v>258</v>
+      </c>
+      <c r="D389" t="s">
+        <v>343</v>
+      </c>
+      <c r="E389" t="s">
+        <v>386</v>
+      </c>
+      <c r="F389" t="s">
+        <v>386</v>
+      </c>
+      <c r="G389" t="s">
+        <v>607</v>
+      </c>
+      <c r="H389">
+        <v>1</v>
+      </c>
+      <c r="I389" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390" t="s">
+        <v>91</v>
+      </c>
+      <c r="B390" t="s">
+        <v>215</v>
+      </c>
+      <c r="C390" t="s">
+        <v>258</v>
+      </c>
+      <c r="D390" t="s">
+        <v>343</v>
+      </c>
+      <c r="E390" t="s">
+        <v>386</v>
+      </c>
+      <c r="F390" t="s">
+        <v>387</v>
+      </c>
+      <c r="G390" t="s">
+        <v>608</v>
+      </c>
+      <c r="H390">
+        <v>2</v>
+      </c>
+      <c r="I390" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391" t="s">
+        <v>91</v>
+      </c>
+      <c r="B391" t="s">
+        <v>215</v>
+      </c>
+      <c r="C391" t="s">
+        <v>258</v>
+      </c>
+      <c r="D391" t="s">
+        <v>343</v>
+      </c>
+      <c r="E391" t="s">
+        <v>386</v>
+      </c>
+      <c r="F391" t="s">
+        <v>388</v>
+      </c>
+      <c r="G391" t="s">
+        <v>609</v>
+      </c>
+      <c r="H391">
+        <v>3</v>
+      </c>
+      <c r="I391" t="s">
+        <v>720</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/bounced_emails.xlsx
+++ b/bounced_emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3737" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3769" uniqueCount="722">
   <si>
     <t>code</t>
   </si>
@@ -169,6 +169,9 @@
     <t>9e3fbec4-42cd-41c0-9b1d-f442487ed552</t>
   </si>
   <si>
+    <t>66b93b8d-817c-4af4-9183-47792e43d54e</t>
+  </si>
+  <si>
     <t>15f31e98-1701-4d23-8de8-7493899a44db</t>
   </si>
   <si>
@@ -181,9 +184,6 @@
     <t>b6c21085-5e3c-4d3b-bcb0-1e48c3bbaca7</t>
   </si>
   <si>
-    <t>66b93b8d-817c-4af4-9183-47792e43d54e</t>
-  </si>
-  <si>
     <t>11fd6f69-871d-4258-81f6-e2145ee9f73a</t>
   </si>
   <si>
@@ -280,6 +280,12 @@
     <t>df3046b4-68b5-434c-9531-b1f4e4bb005a</t>
   </si>
   <si>
+    <t>5d84f0dd-76e2-48bc-a62a-853bf1b56063</t>
+  </si>
+  <si>
+    <t>196883ff-6fac-4215-82ad-2eca8c1fe974</t>
+  </si>
+  <si>
     <t>4ffe0701-f2c0-4d6c-bf99-f0544e854791</t>
   </si>
   <si>
@@ -289,12 +295,6 @@
     <t>378ebc19-fd46-4557-91f9-cb71ad58fe6d</t>
   </si>
   <si>
-    <t>196883ff-6fac-4215-82ad-2eca8c1fe974</t>
-  </si>
-  <si>
-    <t>5d84f0dd-76e2-48bc-a62a-853bf1b56063</t>
-  </si>
-  <si>
     <t>c84daca6-6da0-4820-934d-ff61ff8b866b</t>
   </si>
   <si>
@@ -544,6 +544,9 @@
     <t>PLTA Poso 1</t>
   </si>
   <si>
+    <t>SEKOLAH POLISI NEGARA</t>
+  </si>
+  <si>
     <t>BPR PALU LOKADANA UTAMA KAS LABUAN</t>
   </si>
   <si>
@@ -556,9 +559,6 @@
     <t>PDAM KAB DONGGALA</t>
   </si>
   <si>
-    <t>SEKOLAH POLISI NEGARA</t>
-  </si>
-  <si>
     <t>BANK PEREKONOMIAN RAKYAT (BPR) MODERN EXPRESS CABANG TOLTIOLI</t>
   </si>
   <si>
@@ -652,6 +652,12 @@
     <t>MORI DUTA MINERAL</t>
   </si>
   <si>
+    <t>ANUGRAH JAYA PERKASA, CV</t>
+  </si>
+  <si>
+    <t>BANK BRI UNIT TAWAELI</t>
+  </si>
+  <si>
     <t>TELKOM PALU, PT</t>
   </si>
   <si>
@@ -661,12 +667,6 @@
     <t>SPBU KAYUMALUE</t>
   </si>
   <si>
-    <t>BANK BRI UNIT TAWAELI</t>
-  </si>
-  <si>
-    <t>ANUGRAH JAYA PERKASA, CV</t>
-  </si>
-  <si>
     <t>SURYA MADISTRINDO, PT</t>
   </si>
   <si>
@@ -928,6 +928,9 @@
     <t>pltaposo2@posoenergy.com</t>
   </si>
   <si>
+    <t>kppnpalu651707@yahoo.com</t>
+  </si>
+  <si>
     <t>bprlabuan@yahoo.co.id</t>
   </si>
   <si>
@@ -940,9 +943,6 @@
     <t>pdam_donggala@gmail.com</t>
   </si>
   <si>
-    <t>kppnpalu651707@yahoo.com</t>
-  </si>
-  <si>
     <t>kc.tolitoli@bprpalulokadanautama.com</t>
   </si>
   <si>
@@ -1039,6 +1039,12 @@
     <t>stevankristy@moridutamineral.com</t>
   </si>
   <si>
+    <t>ajptipo@gmail.com</t>
+  </si>
+  <si>
+    <t>n3448@bricorp.co.id</t>
+  </si>
+  <si>
     <t>costumercare@telkom.co.id</t>
   </si>
   <si>
@@ -1048,12 +1054,6 @@
     <t>spbutawaeli74943313@gmail.com</t>
   </si>
   <si>
-    <t>n3448@bricorp.co.id</t>
-  </si>
-  <si>
-    <t>ajptipo@gmail.com</t>
-  </si>
-  <si>
     <t>fero@gmail.com</t>
   </si>
   <si>
@@ -1486,6 +1486,12 @@
     <t>02 Jun 2026, 05:07:16</t>
   </si>
   <si>
+    <t>02 Jun 2026, 02:30:55</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:29:47</t>
+  </si>
+  <si>
     <t>09 Jun 2026, 11:02:07</t>
   </si>
   <si>
@@ -1510,12 +1516,6 @@
     <t>02 Jun 2026, 06:31:35</t>
   </si>
   <si>
-    <t>02 Jun 2026, 02:30:55</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 02:29:47</t>
-  </si>
-  <si>
     <t>09 Jun 2026, 11:01:19</t>
   </si>
   <si>
@@ -1804,6 +1804,15 @@
     <t>02 Jun 2026, 08:50:41</t>
   </si>
   <si>
+    <t>02 Jun 2026, 02:09:06</t>
+  </si>
+  <si>
+    <t>02 Jun 2026, 02:09:05</t>
+  </si>
+  <si>
+    <t>01 Jun 2026, 23:35:32</t>
+  </si>
+  <si>
     <t>09 Jun 2026, 11:20:25</t>
   </si>
   <si>
@@ -1823,15 +1832,6 @@
   </si>
   <si>
     <t>02 Jun 2026, 00:41:01</t>
-  </si>
-  <si>
-    <t>01 Jun 2026, 23:35:32</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 02:09:06</t>
-  </si>
-  <si>
-    <t>02 Jun 2026, 02:09:05</t>
   </si>
   <si>
     <t>02 Jun 2026, 07:31:06</t>
@@ -2537,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I467"/>
+  <dimension ref="A1:I471"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6289,16 +6289,16 @@
         <v>176</v>
       </c>
       <c r="C130" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D130" t="s">
         <v>304</v>
       </c>
       <c r="E130" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F130" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G130" t="s">
         <v>490</v>
@@ -6318,16 +6318,16 @@
         <v>176</v>
       </c>
       <c r="C131" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D131" t="s">
         <v>304</v>
       </c>
       <c r="E131" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F131" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G131" t="s">
         <v>491</v>
@@ -6341,28 +6341,28 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B132" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C132" t="s">
         <v>260</v>
       </c>
       <c r="D132" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E132" t="s">
         <v>387</v>
       </c>
       <c r="F132" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G132" t="s">
         <v>492</v>
       </c>
       <c r="H132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I132" t="s">
         <v>713</v>
@@ -6382,7 +6382,7 @@
         <v>305</v>
       </c>
       <c r="E133" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F133" t="s">
         <v>388</v>
@@ -6391,7 +6391,7 @@
         <v>493</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I133" t="s">
         <v>713</v>
@@ -6411,7 +6411,7 @@
         <v>305</v>
       </c>
       <c r="E134" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F134" t="s">
         <v>389</v>
@@ -6420,7 +6420,7 @@
         <v>494</v>
       </c>
       <c r="H134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I134" t="s">
         <v>713</v>
@@ -6434,7 +6434,7 @@
         <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
         <v>306</v>
@@ -6463,7 +6463,7 @@
         <v>178</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D136" t="s">
         <v>306</v>
@@ -6492,7 +6492,7 @@
         <v>179</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D137" t="s">
         <v>307</v>
@@ -6501,7 +6501,7 @@
         <v>388</v>
       </c>
       <c r="F137" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G137" t="s">
         <v>497</v>
@@ -6521,7 +6521,7 @@
         <v>179</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D138" t="s">
         <v>307</v>
@@ -6530,10 +6530,10 @@
         <v>388</v>
       </c>
       <c r="F138" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G138" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H138">
         <v>2</v>
@@ -6559,10 +6559,10 @@
         <v>388</v>
       </c>
       <c r="F139" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G139" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -6588,7 +6588,7 @@
         <v>388</v>
       </c>
       <c r="F140" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G140" t="s">
         <v>499</v>
@@ -6608,16 +6608,16 @@
         <v>176</v>
       </c>
       <c r="C141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>304</v>
       </c>
       <c r="E141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G141" t="s">
         <v>490</v>
@@ -6637,16 +6637,16 @@
         <v>176</v>
       </c>
       <c r="C142" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>304</v>
       </c>
       <c r="E142" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G142" t="s">
         <v>491</v>
@@ -6660,28 +6660,28 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B143" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C143" t="s">
         <v>260</v>
       </c>
       <c r="D143" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E143" t="s">
         <v>387</v>
       </c>
       <c r="F143" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G143" t="s">
         <v>492</v>
       </c>
       <c r="H143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I143" t="s">
         <v>713</v>
@@ -6689,28 +6689,28 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E144" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F144" t="s">
         <v>388</v>
       </c>
       <c r="G144" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I144" t="s">
         <v>713</v>
@@ -6718,28 +6718,28 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B145" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E145" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F145" t="s">
         <v>389</v>
       </c>
       <c r="G145" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I145" t="s">
         <v>713</v>
@@ -6747,60 +6747,60 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B146" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C146" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D146" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F146" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G146" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H146">
         <v>1</v>
       </c>
       <c r="I146" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B147" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C147" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E147" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F147" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G147" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H147">
         <v>2</v>
       </c>
       <c r="I147" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -6820,13 +6820,13 @@
         <v>387</v>
       </c>
       <c r="F148" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G148" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I148" t="s">
         <v>714</v>
@@ -6834,28 +6834,28 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B149" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C149" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E149" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F149" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G149" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I149" t="s">
         <v>714</v>
@@ -6863,28 +6863,28 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B150" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C150" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D150" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E150" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F150" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G150" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I150" t="s">
         <v>714</v>
@@ -6892,25 +6892,25 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C151" t="s">
         <v>261</v>
       </c>
       <c r="D151" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E151" t="s">
         <v>388</v>
       </c>
       <c r="F151" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G151" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -6921,25 +6921,25 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C152" t="s">
         <v>261</v>
       </c>
       <c r="D152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E152" t="s">
         <v>388</v>
       </c>
       <c r="F152" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G152" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H152">
         <v>2</v>
@@ -6950,16 +6950,16 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B153" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C153" t="s">
         <v>261</v>
       </c>
       <c r="D153" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E153" t="s">
         <v>388</v>
@@ -6968,7 +6968,7 @@
         <v>388</v>
       </c>
       <c r="G153" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -6979,16 +6979,16 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B154" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C154" t="s">
         <v>261</v>
       </c>
       <c r="D154" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E154" t="s">
         <v>388</v>
@@ -6997,7 +6997,7 @@
         <v>389</v>
       </c>
       <c r="G154" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H154">
         <v>2</v>
@@ -7008,16 +7008,16 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B155" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C155" t="s">
         <v>261</v>
       </c>
       <c r="D155" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E155" t="s">
         <v>388</v>
@@ -7026,7 +7026,7 @@
         <v>388</v>
       </c>
       <c r="G155" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -7037,16 +7037,16 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B156" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C156" t="s">
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E156" t="s">
         <v>388</v>
@@ -7055,7 +7055,7 @@
         <v>389</v>
       </c>
       <c r="G156" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H156">
         <v>2</v>
@@ -7066,60 +7066,60 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B157" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D157" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E157" t="s">
         <v>388</v>
       </c>
       <c r="F157" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G157" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H157">
         <v>1</v>
       </c>
       <c r="I157" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B158" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D158" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E158" t="s">
         <v>388</v>
       </c>
       <c r="F158" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G158" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H158">
         <v>2</v>
       </c>
       <c r="I158" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -7139,13 +7139,13 @@
         <v>388</v>
       </c>
       <c r="F159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G159" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I159" t="s">
         <v>715</v>
@@ -7168,13 +7168,13 @@
         <v>388</v>
       </c>
       <c r="F160" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G160" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I160" t="s">
         <v>715</v>
@@ -7197,13 +7197,13 @@
         <v>388</v>
       </c>
       <c r="F161" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G161" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H161">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I161" t="s">
         <v>715</v>
@@ -7226,13 +7226,13 @@
         <v>388</v>
       </c>
       <c r="F162" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G162" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H162">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I162" t="s">
         <v>715</v>
@@ -7255,13 +7255,13 @@
         <v>388</v>
       </c>
       <c r="F163" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G163" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H163">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I163" t="s">
         <v>715</v>
@@ -7284,13 +7284,13 @@
         <v>388</v>
       </c>
       <c r="F164" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G164" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H164">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I164" t="s">
         <v>715</v>
@@ -7298,28 +7298,28 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B165" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C165" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D165" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E165" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F165" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G165" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I165" t="s">
         <v>715</v>
@@ -7327,28 +7327,28 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B166" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C166" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D166" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E166" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F166" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G166" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H166">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I166" t="s">
         <v>715</v>
@@ -7371,13 +7371,13 @@
         <v>387</v>
       </c>
       <c r="F167" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G167" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H167">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I167" t="s">
         <v>715</v>
@@ -7400,13 +7400,13 @@
         <v>387</v>
       </c>
       <c r="F168" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G168" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H168">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I168" t="s">
         <v>715</v>
@@ -7414,28 +7414,28 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C169" t="s">
         <v>261</v>
       </c>
       <c r="D169" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G169" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H169">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I169" t="s">
         <v>715</v>
@@ -7443,28 +7443,28 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B170" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C170" t="s">
         <v>261</v>
       </c>
       <c r="D170" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E170" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F170" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G170" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="H170">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I170" t="s">
         <v>715</v>
@@ -7472,25 +7472,25 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B171" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C171" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D171" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E171" t="s">
         <v>388</v>
       </c>
       <c r="F171" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G171" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -7501,25 +7501,25 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B172" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C172" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D172" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E172" t="s">
         <v>388</v>
       </c>
       <c r="F172" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G172" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="H172">
         <v>2</v>
@@ -7545,13 +7545,13 @@
         <v>388</v>
       </c>
       <c r="F173" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G173" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H173">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I173" t="s">
         <v>715</v>
@@ -7574,13 +7574,13 @@
         <v>388</v>
       </c>
       <c r="F174" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G174" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H174">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I174" t="s">
         <v>715</v>
@@ -7603,13 +7603,13 @@
         <v>388</v>
       </c>
       <c r="F175" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G175" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H175">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I175" t="s">
         <v>715</v>
@@ -7635,10 +7635,10 @@
         <v>392</v>
       </c>
       <c r="G176" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H176">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I176" t="s">
         <v>715</v>
@@ -7661,13 +7661,13 @@
         <v>388</v>
       </c>
       <c r="F177" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G177" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H177">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I177" t="s">
         <v>715</v>
@@ -7690,13 +7690,13 @@
         <v>388</v>
       </c>
       <c r="F178" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G178" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H178">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I178" t="s">
         <v>715</v>
@@ -7719,13 +7719,13 @@
         <v>388</v>
       </c>
       <c r="F179" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G179" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H179">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I179" t="s">
         <v>715</v>
@@ -7751,10 +7751,10 @@
         <v>389</v>
       </c>
       <c r="G180" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H180">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I180" t="s">
         <v>715</v>
@@ -7777,13 +7777,13 @@
         <v>388</v>
       </c>
       <c r="F181" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G181" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H181">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I181" t="s">
         <v>715</v>
@@ -7809,10 +7809,10 @@
         <v>389</v>
       </c>
       <c r="G182" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H182">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I182" t="s">
         <v>715</v>
@@ -7820,28 +7820,28 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B183" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C183" t="s">
         <v>260</v>
       </c>
       <c r="D183" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E183" t="s">
         <v>388</v>
       </c>
       <c r="F183" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G183" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="H183">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I183" t="s">
         <v>715</v>
@@ -7849,28 +7849,28 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B184" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C184" t="s">
         <v>260</v>
       </c>
       <c r="D184" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E184" t="s">
         <v>388</v>
       </c>
       <c r="F184" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G184" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="H184">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I184" t="s">
         <v>715</v>
@@ -7893,13 +7893,13 @@
         <v>388</v>
       </c>
       <c r="F185" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G185" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I185" t="s">
         <v>715</v>
@@ -7922,13 +7922,13 @@
         <v>388</v>
       </c>
       <c r="F186" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G186" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H186">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I186" t="s">
         <v>715</v>
@@ -7951,13 +7951,13 @@
         <v>388</v>
       </c>
       <c r="F187" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G187" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H187">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I187" t="s">
         <v>715</v>
@@ -7980,13 +7980,13 @@
         <v>388</v>
       </c>
       <c r="F188" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G188" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H188">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I188" t="s">
         <v>715</v>
@@ -8009,13 +8009,13 @@
         <v>388</v>
       </c>
       <c r="F189" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G189" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H189">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I189" t="s">
         <v>715</v>
@@ -8038,13 +8038,13 @@
         <v>388</v>
       </c>
       <c r="F190" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G190" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I190" t="s">
         <v>715</v>
@@ -8052,28 +8052,28 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B191" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D191" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E191" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F191" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G191" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I191" t="s">
         <v>715</v>
@@ -8081,28 +8081,28 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D192" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E192" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F192" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G192" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H192">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I192" t="s">
         <v>715</v>
@@ -8125,13 +8125,13 @@
         <v>387</v>
       </c>
       <c r="F193" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G193" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I193" t="s">
         <v>715</v>
@@ -8154,13 +8154,13 @@
         <v>387</v>
       </c>
       <c r="F194" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G194" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H194">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I194" t="s">
         <v>715</v>
@@ -8168,28 +8168,28 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B195" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C195" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E195" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F195" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G195" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I195" t="s">
         <v>715</v>
@@ -8197,28 +8197,28 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B196" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C196" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E196" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F196" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G196" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H196">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I196" t="s">
         <v>715</v>
@@ -8241,13 +8241,13 @@
         <v>388</v>
       </c>
       <c r="F197" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G197" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I197" t="s">
         <v>715</v>
@@ -8270,13 +8270,13 @@
         <v>388</v>
       </c>
       <c r="F198" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G198" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I198" t="s">
         <v>715</v>
@@ -8299,13 +8299,13 @@
         <v>388</v>
       </c>
       <c r="F199" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G199" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H199">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I199" t="s">
         <v>715</v>
@@ -8331,10 +8331,10 @@
         <v>392</v>
       </c>
       <c r="G200" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H200">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I200" t="s">
         <v>715</v>
@@ -8357,13 +8357,13 @@
         <v>388</v>
       </c>
       <c r="F201" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G201" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H201">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I201" t="s">
         <v>715</v>
@@ -8386,13 +8386,13 @@
         <v>388</v>
       </c>
       <c r="F202" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G202" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H202">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I202" t="s">
         <v>715</v>
@@ -8415,13 +8415,13 @@
         <v>388</v>
       </c>
       <c r="F203" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G203" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H203">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I203" t="s">
         <v>715</v>
@@ -8447,10 +8447,10 @@
         <v>389</v>
       </c>
       <c r="G204" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H204">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I204" t="s">
         <v>715</v>
@@ -8473,13 +8473,13 @@
         <v>388</v>
       </c>
       <c r="F205" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G205" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H205">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I205" t="s">
         <v>715</v>
@@ -8505,10 +8505,10 @@
         <v>389</v>
       </c>
       <c r="G206" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H206">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I206" t="s">
         <v>715</v>
@@ -8516,60 +8516,60 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B207" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D207" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E207" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F207" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G207" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H207">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I207" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B208" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D208" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E208" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F208" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G208" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H208">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I208" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -8589,13 +8589,13 @@
         <v>387</v>
       </c>
       <c r="F209" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G209" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H209">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I209" t="s">
         <v>716</v>
@@ -8603,28 +8603,28 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B210" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="C210" t="s">
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E210" t="s">
         <v>387</v>
       </c>
       <c r="F210" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G210" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I210" t="s">
         <v>716</v>
@@ -8632,28 +8632,28 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B211" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="C211" t="s">
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E211" t="s">
         <v>387</v>
       </c>
       <c r="F211" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G211" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="H211">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I211" t="s">
         <v>716</v>
@@ -8676,13 +8676,13 @@
         <v>387</v>
       </c>
       <c r="F212" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G212" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="H212">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I212" t="s">
         <v>716</v>
@@ -8690,28 +8690,28 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B213" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C213" t="s">
         <v>261</v>
       </c>
       <c r="D213" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E213" t="s">
         <v>387</v>
       </c>
       <c r="F213" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G213" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I213" t="s">
         <v>716</v>
@@ -8719,28 +8719,28 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B214" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C214" t="s">
         <v>261</v>
       </c>
       <c r="D214" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E214" t="s">
         <v>387</v>
       </c>
       <c r="F214" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G214" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I214" t="s">
         <v>716</v>
@@ -8763,13 +8763,13 @@
         <v>387</v>
       </c>
       <c r="F215" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G215" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="H215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I215" t="s">
         <v>716</v>
@@ -8792,13 +8792,13 @@
         <v>387</v>
       </c>
       <c r="F216" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G216" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H216">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I216" t="s">
         <v>716</v>
@@ -8806,28 +8806,28 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B217" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C217" t="s">
         <v>261</v>
       </c>
       <c r="D217" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E217" t="s">
         <v>387</v>
       </c>
       <c r="F217" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G217" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="H217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I217" t="s">
         <v>716</v>
@@ -8835,28 +8835,28 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B218" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C218" t="s">
         <v>261</v>
       </c>
       <c r="D218" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E218" t="s">
         <v>387</v>
       </c>
       <c r="F218" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G218" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H218">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I218" t="s">
         <v>716</v>
@@ -8879,13 +8879,13 @@
         <v>387</v>
       </c>
       <c r="F219" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G219" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="H219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I219" t="s">
         <v>716</v>
@@ -8893,28 +8893,28 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B220" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C220" t="s">
         <v>261</v>
       </c>
       <c r="D220" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E220" t="s">
         <v>387</v>
       </c>
       <c r="F220" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G220" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H220">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I220" t="s">
         <v>716</v>
@@ -8922,28 +8922,28 @@
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C221" t="s">
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E221" t="s">
         <v>387</v>
       </c>
       <c r="F221" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G221" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I221" t="s">
         <v>716</v>
@@ -8966,13 +8966,13 @@
         <v>387</v>
       </c>
       <c r="F222" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G222" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="H222">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I222" t="s">
         <v>716</v>
@@ -8995,13 +8995,13 @@
         <v>387</v>
       </c>
       <c r="F223" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G223" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H223">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I223" t="s">
         <v>716</v>
@@ -9009,28 +9009,28 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B224" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C224" t="s">
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E224" t="s">
         <v>387</v>
       </c>
       <c r="F224" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G224" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I224" t="s">
         <v>716</v>
@@ -9038,16 +9038,16 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B225" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C225" t="s">
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E225" t="s">
         <v>387</v>
@@ -9056,10 +9056,10 @@
         <v>388</v>
       </c>
       <c r="G225" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H225">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I225" t="s">
         <v>716</v>
@@ -9082,13 +9082,13 @@
         <v>387</v>
       </c>
       <c r="F226" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G226" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H226">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I226" t="s">
         <v>716</v>
@@ -9096,83 +9096,83 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C227" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E227" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F227" t="s">
         <v>388</v>
       </c>
       <c r="G227" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="H227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I227" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B228" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C228" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E228" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F228" t="s">
         <v>389</v>
       </c>
       <c r="G228" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H228">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I228" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B229" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C229" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D229" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E229" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F229" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G229" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H229">
         <v>1</v>
@@ -9183,25 +9183,25 @@
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C230" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D230" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E230" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F230" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G230" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H230">
         <v>2</v>
@@ -9227,13 +9227,13 @@
         <v>387</v>
       </c>
       <c r="F231" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I231" t="s">
         <v>717</v>
@@ -9241,28 +9241,28 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B232" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D232" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E232" t="s">
         <v>387</v>
       </c>
       <c r="F232" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G232" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H232">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I232" t="s">
         <v>717</v>
@@ -9270,28 +9270,28 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B233" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D233" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E233" t="s">
         <v>387</v>
       </c>
       <c r="F233" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G233" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I233" t="s">
         <v>717</v>
@@ -9314,13 +9314,13 @@
         <v>387</v>
       </c>
       <c r="F234" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I234" t="s">
         <v>717</v>
@@ -9328,28 +9328,28 @@
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B235" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C235" t="s">
         <v>261</v>
       </c>
       <c r="D235" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E235" t="s">
         <v>387</v>
       </c>
       <c r="F235" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G235" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" t="s">
         <v>717</v>
@@ -9357,16 +9357,16 @@
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B236" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C236" t="s">
         <v>261</v>
       </c>
       <c r="D236" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E236" t="s">
         <v>387</v>
@@ -9375,10 +9375,10 @@
         <v>389</v>
       </c>
       <c r="G236" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H236">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I236" t="s">
         <v>717</v>
@@ -9401,13 +9401,13 @@
         <v>387</v>
       </c>
       <c r="F237" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H237">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I237" t="s">
         <v>717</v>
@@ -9415,28 +9415,28 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B238" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C238" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D238" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E238" t="s">
         <v>387</v>
       </c>
       <c r="F238" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G238" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="H238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I238" t="s">
         <v>717</v>
@@ -9444,16 +9444,16 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B239" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C239" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D239" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E239" t="s">
         <v>387</v>
@@ -9462,10 +9462,10 @@
         <v>388</v>
       </c>
       <c r="G239" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="H239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I239" t="s">
         <v>717</v>
@@ -9488,13 +9488,13 @@
         <v>387</v>
       </c>
       <c r="F240" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G240" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H240">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I240" t="s">
         <v>717</v>
@@ -9502,60 +9502,60 @@
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B241" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C241" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D241" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E241" t="s">
         <v>387</v>
       </c>
       <c r="F241" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G241" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="H241">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I241" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B242" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C242" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D242" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E242" t="s">
         <v>387</v>
       </c>
       <c r="F242" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G242" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="H242">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I242" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -9575,13 +9575,13 @@
         <v>387</v>
       </c>
       <c r="F243" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G243" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I243" t="s">
         <v>718</v>
@@ -9589,28 +9589,28 @@
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B244" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C244" t="s">
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E244" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F244" t="s">
         <v>388</v>
       </c>
       <c r="G244" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I244" t="s">
         <v>718</v>
@@ -9618,28 +9618,28 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B245" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C245" t="s">
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E245" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F245" t="s">
         <v>389</v>
       </c>
       <c r="G245" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I245" t="s">
         <v>718</v>
@@ -9647,25 +9647,25 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B246" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C246" t="s">
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E246" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F246" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G246" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H246">
         <v>1</v>
@@ -9676,25 +9676,25 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B247" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C247" t="s">
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E247" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F247" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G247" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H247">
         <v>2</v>
@@ -9720,13 +9720,13 @@
         <v>387</v>
       </c>
       <c r="F248" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G248" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H248">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I248" t="s">
         <v>718</v>
@@ -9734,60 +9734,60 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B249" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C249" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E249" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F249" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G249" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I249" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B250" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C250" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E250" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F250" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G250" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I250" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -9810,10 +9810,10 @@
         <v>392</v>
       </c>
       <c r="G251" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H251">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I251" t="s">
         <v>719</v>
@@ -9836,13 +9836,13 @@
         <v>388</v>
       </c>
       <c r="F252" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G252" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I252" t="s">
         <v>719</v>
@@ -9865,13 +9865,13 @@
         <v>388</v>
       </c>
       <c r="F253" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G253" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H253">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I253" t="s">
         <v>719</v>
@@ -9894,13 +9894,13 @@
         <v>388</v>
       </c>
       <c r="F254" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G254" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H254">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I254" t="s">
         <v>719</v>
@@ -9923,13 +9923,13 @@
         <v>388</v>
       </c>
       <c r="F255" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G255" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H255">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I255" t="s">
         <v>719</v>
@@ -9955,10 +9955,10 @@
         <v>392</v>
       </c>
       <c r="G256" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H256">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I256" t="s">
         <v>719</v>
@@ -9984,10 +9984,10 @@
         <v>392</v>
       </c>
       <c r="G257" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H257">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I257" t="s">
         <v>719</v>
@@ -10010,13 +10010,13 @@
         <v>388</v>
       </c>
       <c r="F258" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G258" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H258">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I258" t="s">
         <v>719</v>
@@ -10042,10 +10042,10 @@
         <v>392</v>
       </c>
       <c r="G259" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H259">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I259" t="s">
         <v>719</v>
@@ -10068,13 +10068,13 @@
         <v>388</v>
       </c>
       <c r="F260" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G260" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H260">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I260" t="s">
         <v>719</v>
@@ -10097,13 +10097,13 @@
         <v>388</v>
       </c>
       <c r="F261" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G261" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H261">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I261" t="s">
         <v>719</v>
@@ -10126,13 +10126,13 @@
         <v>388</v>
       </c>
       <c r="F262" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G262" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H262">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I262" t="s">
         <v>719</v>
@@ -10155,13 +10155,13 @@
         <v>388</v>
       </c>
       <c r="F263" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G263" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H263">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I263" t="s">
         <v>719</v>
@@ -10184,13 +10184,13 @@
         <v>388</v>
       </c>
       <c r="F264" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G264" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="H264">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I264" t="s">
         <v>719</v>
@@ -10213,13 +10213,13 @@
         <v>388</v>
       </c>
       <c r="F265" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G265" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I265" t="s">
         <v>719</v>
@@ -10245,10 +10245,10 @@
         <v>392</v>
       </c>
       <c r="G266" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H266">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I266" t="s">
         <v>719</v>
@@ -10271,13 +10271,13 @@
         <v>388</v>
       </c>
       <c r="F267" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G267" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H267">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I267" t="s">
         <v>719</v>
@@ -10300,13 +10300,13 @@
         <v>388</v>
       </c>
       <c r="F268" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G268" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H268">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I268" t="s">
         <v>719</v>
@@ -10329,13 +10329,13 @@
         <v>388</v>
       </c>
       <c r="F269" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G269" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H269">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I269" t="s">
         <v>719</v>
@@ -10358,13 +10358,13 @@
         <v>388</v>
       </c>
       <c r="F270" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G270" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H270">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I270" t="s">
         <v>719</v>
@@ -10390,10 +10390,10 @@
         <v>392</v>
       </c>
       <c r="G271" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H271">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I271" t="s">
         <v>719</v>
@@ -10419,10 +10419,10 @@
         <v>392</v>
       </c>
       <c r="G272" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H272">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I272" t="s">
         <v>719</v>
@@ -10445,13 +10445,13 @@
         <v>388</v>
       </c>
       <c r="F273" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G273" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H273">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I273" t="s">
         <v>719</v>
@@ -10477,10 +10477,10 @@
         <v>392</v>
       </c>
       <c r="G274" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H274">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I274" t="s">
         <v>719</v>
@@ -10503,13 +10503,13 @@
         <v>388</v>
       </c>
       <c r="F275" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G275" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H275">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I275" t="s">
         <v>719</v>
@@ -10532,13 +10532,13 @@
         <v>388</v>
       </c>
       <c r="F276" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G276" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H276">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I276" t="s">
         <v>719</v>
@@ -10561,13 +10561,13 @@
         <v>388</v>
       </c>
       <c r="F277" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G277" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H277">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I277" t="s">
         <v>719</v>
@@ -10590,13 +10590,13 @@
         <v>388</v>
       </c>
       <c r="F278" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G278" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H278">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I278" t="s">
         <v>719</v>
@@ -10604,74 +10604,74 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B279" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C279" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D279" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E279" t="s">
         <v>388</v>
       </c>
       <c r="F279" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G279" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H279">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I279" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B280" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C280" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D280" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E280" t="s">
         <v>388</v>
       </c>
       <c r="F280" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G280" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H280">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I280" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B281" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C281" t="s">
         <v>261</v>
       </c>
       <c r="D281" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E281" t="s">
         <v>388</v>
@@ -10680,7 +10680,7 @@
         <v>388</v>
       </c>
       <c r="G281" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H281">
         <v>1</v>
@@ -10691,16 +10691,16 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B282" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C282" t="s">
         <v>261</v>
       </c>
       <c r="D282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E282" t="s">
         <v>388</v>
@@ -10709,7 +10709,7 @@
         <v>389</v>
       </c>
       <c r="G282" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H282">
         <v>2</v>
@@ -10720,16 +10720,16 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B283" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C283" t="s">
         <v>261</v>
       </c>
       <c r="D283" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E283" t="s">
         <v>388</v>
@@ -10738,7 +10738,7 @@
         <v>388</v>
       </c>
       <c r="G283" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H283">
         <v>1</v>
@@ -10749,16 +10749,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B284" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C284" t="s">
         <v>261</v>
       </c>
       <c r="D284" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E284" t="s">
         <v>388</v>
@@ -10767,7 +10767,7 @@
         <v>389</v>
       </c>
       <c r="G284" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H284">
         <v>2</v>
@@ -10778,16 +10778,16 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B285" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C285" t="s">
         <v>261</v>
       </c>
       <c r="D285" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E285" t="s">
         <v>388</v>
@@ -10796,7 +10796,7 @@
         <v>388</v>
       </c>
       <c r="G285" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H285">
         <v>1</v>
@@ -10807,16 +10807,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B286" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C286" t="s">
         <v>261</v>
       </c>
       <c r="D286" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E286" t="s">
         <v>388</v>
@@ -10825,7 +10825,7 @@
         <v>389</v>
       </c>
       <c r="G286" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H286">
         <v>2</v>
@@ -10836,16 +10836,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B287" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C287" t="s">
         <v>261</v>
       </c>
       <c r="D287" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E287" t="s">
         <v>388</v>
@@ -10854,7 +10854,7 @@
         <v>388</v>
       </c>
       <c r="G287" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H287">
         <v>1</v>
@@ -10865,16 +10865,16 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B288" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C288" t="s">
         <v>261</v>
       </c>
       <c r="D288" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E288" t="s">
         <v>388</v>
@@ -10883,7 +10883,7 @@
         <v>389</v>
       </c>
       <c r="G288" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H288">
         <v>2</v>
@@ -10894,25 +10894,25 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B289" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C289" t="s">
         <v>261</v>
       </c>
       <c r="D289" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E289" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F289" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G289" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H289">
         <v>1</v>
@@ -10923,25 +10923,25 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B290" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C290" t="s">
         <v>261</v>
       </c>
       <c r="D290" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E290" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F290" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G290" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H290">
         <v>2</v>
@@ -10967,13 +10967,13 @@
         <v>387</v>
       </c>
       <c r="F291" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G291" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H291">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I291" t="s">
         <v>720</v>
@@ -10981,28 +10981,28 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B292" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C292" t="s">
         <v>261</v>
       </c>
       <c r="D292" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E292" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F292" t="s">
         <v>388</v>
       </c>
       <c r="G292" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I292" t="s">
         <v>720</v>
@@ -11010,28 +11010,28 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B293" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C293" t="s">
         <v>261</v>
       </c>
       <c r="D293" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E293" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F293" t="s">
         <v>389</v>
       </c>
       <c r="G293" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H293">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I293" t="s">
         <v>720</v>
@@ -11039,16 +11039,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B294" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C294" t="s">
         <v>261</v>
       </c>
       <c r="D294" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E294" t="s">
         <v>388</v>
@@ -11057,7 +11057,7 @@
         <v>388</v>
       </c>
       <c r="G294" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H294">
         <v>1</v>
@@ -11068,16 +11068,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B295" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C295" t="s">
         <v>261</v>
       </c>
       <c r="D295" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E295" t="s">
         <v>388</v>
@@ -11086,7 +11086,7 @@
         <v>389</v>
       </c>
       <c r="G295" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H295">
         <v>2</v>
@@ -11097,16 +11097,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B296" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C296" t="s">
         <v>261</v>
       </c>
       <c r="D296" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E296" t="s">
         <v>388</v>
@@ -11115,7 +11115,7 @@
         <v>388</v>
       </c>
       <c r="G296" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H296">
         <v>1</v>
@@ -11126,16 +11126,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B297" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C297" t="s">
         <v>261</v>
       </c>
       <c r="D297" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E297" t="s">
         <v>388</v>
@@ -11144,7 +11144,7 @@
         <v>389</v>
       </c>
       <c r="G297" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H297">
         <v>2</v>
@@ -11155,60 +11155,60 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B298" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C298" t="s">
         <v>261</v>
       </c>
       <c r="D298" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E298" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F298" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G298" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H298">
         <v>1</v>
       </c>
       <c r="I298" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B299" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C299" t="s">
         <v>261</v>
       </c>
       <c r="D299" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E299" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F299" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G299" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H299">
         <v>2</v>
       </c>
       <c r="I299" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11225,16 +11225,16 @@
         <v>341</v>
       </c>
       <c r="E300" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F300" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G300" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H300">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I300" t="s">
         <v>721</v>
@@ -11242,28 +11242,28 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B301" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C301" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D301" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E301" t="s">
         <v>388</v>
       </c>
       <c r="F301" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G301" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I301" t="s">
         <v>721</v>
@@ -11277,22 +11277,22 @@
         <v>213</v>
       </c>
       <c r="C302" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D302" t="s">
         <v>342</v>
       </c>
       <c r="E302" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F302" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G302" t="s">
-        <v>599</v>
+        <v>428</v>
       </c>
       <c r="H302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I302" t="s">
         <v>721</v>
@@ -11300,28 +11300,28 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B303" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C303" t="s">
         <v>261</v>
       </c>
       <c r="D303" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E303" t="s">
         <v>387</v>
       </c>
       <c r="F303" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G303" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I303" t="s">
         <v>721</v>
@@ -11329,28 +11329,28 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B304" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C304" t="s">
         <v>261</v>
       </c>
       <c r="D304" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E304" t="s">
         <v>387</v>
       </c>
       <c r="F304" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G304" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="H304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I304" t="s">
         <v>721</v>
@@ -11373,13 +11373,13 @@
         <v>387</v>
       </c>
       <c r="F305" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G305" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="H305">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I305" t="s">
         <v>721</v>
@@ -11387,28 +11387,28 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B306" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C306" t="s">
         <v>261</v>
       </c>
       <c r="D306" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E306" t="s">
         <v>387</v>
       </c>
       <c r="F306" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G306" t="s">
-        <v>428</v>
+        <v>600</v>
       </c>
       <c r="H306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I306" t="s">
         <v>721</v>
@@ -11416,28 +11416,28 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B307" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C307" t="s">
         <v>261</v>
       </c>
       <c r="D307" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E307" t="s">
         <v>387</v>
       </c>
       <c r="F307" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G307" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H307">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I307" t="s">
         <v>721</v>
@@ -11451,22 +11451,22 @@
         <v>215</v>
       </c>
       <c r="C308" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D308" t="s">
         <v>344</v>
       </c>
       <c r="E308" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F308" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G308" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H308">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I308" t="s">
         <v>721</v>
@@ -11474,28 +11474,28 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B309" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C309" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D309" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E309" t="s">
         <v>388</v>
       </c>
       <c r="F309" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G309" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I309" t="s">
         <v>721</v>
@@ -11515,16 +11515,16 @@
         <v>345</v>
       </c>
       <c r="E310" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F310" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G310" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I310" t="s">
         <v>721</v>
@@ -11532,28 +11532,28 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B311" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C311" t="s">
         <v>261</v>
       </c>
       <c r="D311" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E311" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F311" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G311" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I311" t="s">
         <v>721</v>
@@ -11561,28 +11561,28 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B312" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C312" t="s">
         <v>261</v>
       </c>
       <c r="D312" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E312" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F312" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G312" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I312" t="s">
         <v>721</v>
@@ -11590,25 +11590,25 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B313" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C313" t="s">
         <v>261</v>
       </c>
       <c r="D313" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E313" t="s">
         <v>388</v>
       </c>
       <c r="F313" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G313" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H313">
         <v>1</v>
@@ -11619,25 +11619,25 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B314" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C314" t="s">
         <v>261</v>
       </c>
       <c r="D314" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E314" t="s">
         <v>388</v>
       </c>
       <c r="F314" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G314" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H314">
         <v>2</v>
@@ -11648,16 +11648,16 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B315" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C315" t="s">
         <v>261</v>
       </c>
       <c r="D315" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E315" t="s">
         <v>388</v>
@@ -11666,7 +11666,7 @@
         <v>388</v>
       </c>
       <c r="G315" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H315">
         <v>1</v>
@@ -11677,16 +11677,16 @@
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B316" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C316" t="s">
         <v>261</v>
       </c>
       <c r="D316" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E316" t="s">
         <v>388</v>
@@ -11695,7 +11695,7 @@
         <v>389</v>
       </c>
       <c r="G316" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H316">
         <v>2</v>
@@ -11706,25 +11706,25 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B317" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C317" t="s">
         <v>261</v>
       </c>
       <c r="D317" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E317" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F317" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G317" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H317">
         <v>1</v>
@@ -11735,25 +11735,25 @@
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B318" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C318" t="s">
         <v>261</v>
       </c>
       <c r="D318" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E318" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F318" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G318" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H318">
         <v>2</v>
@@ -11779,13 +11779,13 @@
         <v>387</v>
       </c>
       <c r="F319" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G319" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H319">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I319" t="s">
         <v>721</v>
@@ -11793,28 +11793,28 @@
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B320" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C320" t="s">
         <v>261</v>
       </c>
       <c r="D320" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E320" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F320" t="s">
         <v>388</v>
       </c>
       <c r="G320" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I320" t="s">
         <v>721</v>
@@ -11822,28 +11822,28 @@
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B321" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C321" t="s">
         <v>261</v>
       </c>
       <c r="D321" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E321" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F321" t="s">
         <v>389</v>
       </c>
       <c r="G321" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H321">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I321" t="s">
         <v>721</v>
@@ -11851,16 +11851,16 @@
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B322" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C322" t="s">
         <v>261</v>
       </c>
       <c r="D322" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E322" t="s">
         <v>388</v>
@@ -11869,7 +11869,7 @@
         <v>388</v>
       </c>
       <c r="G322" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H322">
         <v>1</v>
@@ -11880,16 +11880,16 @@
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B323" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C323" t="s">
         <v>261</v>
       </c>
       <c r="D323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E323" t="s">
         <v>388</v>
@@ -11898,7 +11898,7 @@
         <v>389</v>
       </c>
       <c r="G323" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H323">
         <v>2</v>
@@ -11909,16 +11909,16 @@
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B324" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C324" t="s">
         <v>261</v>
       </c>
       <c r="D324" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E324" t="s">
         <v>388</v>
@@ -11927,7 +11927,7 @@
         <v>388</v>
       </c>
       <c r="G324" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H324">
         <v>1</v>
@@ -11938,16 +11938,16 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B325" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C325" t="s">
         <v>261</v>
       </c>
       <c r="D325" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E325" t="s">
         <v>388</v>
@@ -11956,7 +11956,7 @@
         <v>389</v>
       </c>
       <c r="G325" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H325">
         <v>2</v>
@@ -11967,16 +11967,16 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B326" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C326" t="s">
         <v>261</v>
       </c>
       <c r="D326" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E326" t="s">
         <v>388</v>
@@ -11985,7 +11985,7 @@
         <v>388</v>
       </c>
       <c r="G326" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H326">
         <v>1</v>
@@ -11996,16 +11996,16 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B327" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C327" t="s">
         <v>261</v>
       </c>
       <c r="D327" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E327" t="s">
         <v>388</v>
@@ -12014,7 +12014,7 @@
         <v>389</v>
       </c>
       <c r="G327" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H327">
         <v>2</v>
@@ -12025,16 +12025,16 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B328" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C328" t="s">
         <v>261</v>
       </c>
       <c r="D328" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E328" t="s">
         <v>388</v>
@@ -12043,7 +12043,7 @@
         <v>388</v>
       </c>
       <c r="G328" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H328">
         <v>1</v>
@@ -12054,16 +12054,16 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B329" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C329" t="s">
         <v>261</v>
       </c>
       <c r="D329" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E329" t="s">
         <v>388</v>
@@ -12072,7 +12072,7 @@
         <v>389</v>
       </c>
       <c r="G329" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H329">
         <v>2</v>
@@ -12083,16 +12083,16 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B330" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C330" t="s">
         <v>261</v>
       </c>
       <c r="D330" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E330" t="s">
         <v>388</v>
@@ -12101,7 +12101,7 @@
         <v>388</v>
       </c>
       <c r="G330" t="s">
-        <v>410</v>
+        <v>621</v>
       </c>
       <c r="H330">
         <v>1</v>
@@ -12112,16 +12112,16 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B331" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C331" t="s">
         <v>261</v>
       </c>
       <c r="D331" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E331" t="s">
         <v>388</v>
@@ -12130,7 +12130,7 @@
         <v>389</v>
       </c>
       <c r="G331" t="s">
-        <v>410</v>
+        <v>622</v>
       </c>
       <c r="H331">
         <v>2</v>
@@ -12141,16 +12141,16 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B332" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C332" t="s">
         <v>261</v>
       </c>
       <c r="D332" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E332" t="s">
         <v>388</v>
@@ -12159,7 +12159,7 @@
         <v>388</v>
       </c>
       <c r="G332" t="s">
-        <v>623</v>
+        <v>410</v>
       </c>
       <c r="H332">
         <v>1</v>
@@ -12170,16 +12170,16 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B333" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C333" t="s">
         <v>261</v>
       </c>
       <c r="D333" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E333" t="s">
         <v>388</v>
@@ -12188,7 +12188,7 @@
         <v>389</v>
       </c>
       <c r="G333" t="s">
-        <v>624</v>
+        <v>410</v>
       </c>
       <c r="H333">
         <v>2</v>
@@ -12199,16 +12199,16 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B334" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C334" t="s">
         <v>261</v>
       </c>
       <c r="D334" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E334" t="s">
         <v>388</v>
@@ -12217,7 +12217,7 @@
         <v>388</v>
       </c>
       <c r="G334" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H334">
         <v>1</v>
@@ -12228,16 +12228,16 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B335" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C335" t="s">
         <v>261</v>
       </c>
       <c r="D335" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E335" t="s">
         <v>388</v>
@@ -12246,7 +12246,7 @@
         <v>389</v>
       </c>
       <c r="G335" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H335">
         <v>2</v>
@@ -12257,25 +12257,25 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B336" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C336" t="s">
         <v>261</v>
       </c>
       <c r="D336" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E336" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F336" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G336" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H336">
         <v>1</v>
@@ -12286,25 +12286,25 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B337" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C337" t="s">
         <v>261</v>
       </c>
       <c r="D337" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E337" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F337" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G337" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="H337">
         <v>2</v>
@@ -12330,13 +12330,13 @@
         <v>387</v>
       </c>
       <c r="F338" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G338" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H338">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I338" t="s">
         <v>721</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B339" t="s">
         <v>229</v>
@@ -12359,13 +12359,13 @@
         <v>387</v>
       </c>
       <c r="F339" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G339" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H339">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I339" t="s">
         <v>721</v>
@@ -12373,7 +12373,7 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B340" t="s">
         <v>229</v>
@@ -12388,13 +12388,13 @@
         <v>387</v>
       </c>
       <c r="F340" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G340" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H340">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I340" t="s">
         <v>721</v>
@@ -12417,13 +12417,13 @@
         <v>387</v>
       </c>
       <c r="F341" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G341" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H341">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I341" t="s">
         <v>721</v>
@@ -12431,28 +12431,28 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B342" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C342" t="s">
         <v>261</v>
       </c>
       <c r="D342" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E342" t="s">
         <v>387</v>
       </c>
       <c r="F342" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G342" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H342">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I342" t="s">
         <v>721</v>
@@ -12460,28 +12460,28 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B343" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C343" t="s">
         <v>261</v>
       </c>
       <c r="D343" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E343" t="s">
         <v>387</v>
       </c>
       <c r="F343" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G343" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H343">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I343" t="s">
         <v>721</v>
@@ -12504,13 +12504,13 @@
         <v>387</v>
       </c>
       <c r="F344" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G344" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H344">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I344" t="s">
         <v>721</v>
@@ -12518,28 +12518,28 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B345" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C345" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D345" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E345" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F345" t="s">
         <v>388</v>
       </c>
       <c r="G345" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I345" t="s">
         <v>721</v>
@@ -12547,28 +12547,28 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B346" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C346" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D346" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E346" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F346" t="s">
         <v>389</v>
       </c>
       <c r="G346" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H346">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I346" t="s">
         <v>721</v>
@@ -12576,25 +12576,25 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B347" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C347" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D347" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E347" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F347" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G347" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H347">
         <v>1</v>
@@ -12605,25 +12605,25 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B348" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C348" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D348" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E348" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F348" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G348" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H348">
         <v>2</v>
@@ -12649,13 +12649,13 @@
         <v>387</v>
       </c>
       <c r="F349" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G349" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H349">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I349" t="s">
         <v>721</v>
@@ -12663,28 +12663,28 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B350" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C350" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D350" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E350" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F350" t="s">
         <v>388</v>
       </c>
       <c r="G350" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I350" t="s">
         <v>721</v>
@@ -12692,28 +12692,28 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B351" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C351" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D351" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E351" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F351" t="s">
         <v>389</v>
       </c>
       <c r="G351" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I351" t="s">
         <v>721</v>
@@ -12721,25 +12721,25 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B352" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C352" t="s">
         <v>261</v>
       </c>
       <c r="D352" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E352" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F352" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G352" t="s">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="H352">
         <v>1</v>
@@ -12750,25 +12750,25 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B353" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C353" t="s">
         <v>261</v>
       </c>
       <c r="D353" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E353" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F353" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G353" t="s">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="H353">
         <v>2</v>
@@ -12794,13 +12794,13 @@
         <v>387</v>
       </c>
       <c r="F354" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G354" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H354">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I354" t="s">
         <v>721</v>
@@ -12808,28 +12808,28 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B355" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C355" t="s">
         <v>261</v>
       </c>
       <c r="D355" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="E355" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F355" t="s">
         <v>388</v>
       </c>
       <c r="G355" t="s">
-        <v>639</v>
+        <v>612</v>
       </c>
       <c r="H355">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I355" t="s">
         <v>721</v>
@@ -12837,28 +12837,28 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B356" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C356" t="s">
         <v>261</v>
       </c>
       <c r="D356" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="E356" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F356" t="s">
         <v>389</v>
       </c>
       <c r="G356" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="H356">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I356" t="s">
         <v>721</v>
@@ -12866,25 +12866,25 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B357" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C357" t="s">
         <v>261</v>
       </c>
       <c r="D357" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E357" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F357" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G357" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H357">
         <v>1</v>
@@ -12895,25 +12895,25 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B358" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C358" t="s">
         <v>261</v>
       </c>
       <c r="D358" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E358" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F358" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G358" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H358">
         <v>2</v>
@@ -12939,13 +12939,13 @@
         <v>387</v>
       </c>
       <c r="F359" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G359" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H359">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I359" t="s">
         <v>721</v>
@@ -12953,28 +12953,28 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B360" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C360" t="s">
         <v>261</v>
       </c>
       <c r="D360" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E360" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F360" t="s">
         <v>388</v>
       </c>
       <c r="G360" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I360" t="s">
         <v>721</v>
@@ -12982,28 +12982,28 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B361" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C361" t="s">
         <v>261</v>
       </c>
       <c r="D361" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E361" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F361" t="s">
         <v>389</v>
       </c>
       <c r="G361" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I361" t="s">
         <v>721</v>
@@ -13011,16 +13011,16 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B362" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C362" t="s">
         <v>261</v>
       </c>
       <c r="D362" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E362" t="s">
         <v>388</v>
@@ -13029,7 +13029,7 @@
         <v>388</v>
       </c>
       <c r="G362" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="H362">
         <v>1</v>
@@ -13040,16 +13040,16 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B363" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C363" t="s">
         <v>261</v>
       </c>
       <c r="D363" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E363" t="s">
         <v>388</v>
@@ -13058,7 +13058,7 @@
         <v>389</v>
       </c>
       <c r="G363" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H363">
         <v>2</v>
@@ -13069,25 +13069,25 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B364" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C364" t="s">
         <v>261</v>
       </c>
       <c r="D364" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E364" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F364" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G364" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H364">
         <v>1</v>
@@ -13098,25 +13098,25 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B365" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C365" t="s">
         <v>261</v>
       </c>
       <c r="D365" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E365" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F365" t="s">
         <v>389</v>
       </c>
       <c r="G365" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H365">
         <v>2</v>
@@ -13142,13 +13142,13 @@
         <v>387</v>
       </c>
       <c r="F366" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G366" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H366">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I366" t="s">
         <v>721</v>
@@ -13156,28 +13156,28 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B367" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C367" t="s">
         <v>261</v>
       </c>
       <c r="D367" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E367" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F367" t="s">
         <v>389</v>
       </c>
       <c r="G367" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H367">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I367" t="s">
         <v>721</v>
@@ -13185,28 +13185,28 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B368" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C368" t="s">
         <v>261</v>
       </c>
       <c r="D368" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E368" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F368" t="s">
         <v>388</v>
       </c>
       <c r="G368" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I368" t="s">
         <v>721</v>
@@ -13214,25 +13214,25 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B369" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C369" t="s">
         <v>261</v>
       </c>
       <c r="D369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E369" t="s">
         <v>388</v>
       </c>
       <c r="F369" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G369" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H369">
         <v>1</v>
@@ -13243,25 +13243,25 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B370" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C370" t="s">
         <v>261</v>
       </c>
       <c r="D370" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E370" t="s">
         <v>388</v>
       </c>
       <c r="F370" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G370" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H370">
         <v>2</v>
@@ -13287,13 +13287,13 @@
         <v>388</v>
       </c>
       <c r="F371" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G371" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H371">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I371" t="s">
         <v>721</v>
@@ -13319,10 +13319,10 @@
         <v>389</v>
       </c>
       <c r="G372" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H372">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I372" t="s">
         <v>721</v>
@@ -13345,13 +13345,13 @@
         <v>388</v>
       </c>
       <c r="F373" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G373" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H373">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I373" t="s">
         <v>721</v>
@@ -13377,10 +13377,10 @@
         <v>389</v>
       </c>
       <c r="G374" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H374">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I374" t="s">
         <v>721</v>
@@ -13388,16 +13388,16 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B375" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C375" t="s">
         <v>261</v>
       </c>
       <c r="D375" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E375" t="s">
         <v>388</v>
@@ -13406,10 +13406,10 @@
         <v>388</v>
       </c>
       <c r="G375" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H375">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I375" t="s">
         <v>721</v>
@@ -13417,16 +13417,16 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B376" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C376" t="s">
         <v>261</v>
       </c>
       <c r="D376" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E376" t="s">
         <v>388</v>
@@ -13435,10 +13435,10 @@
         <v>389</v>
       </c>
       <c r="G376" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H376">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I376" t="s">
         <v>721</v>
@@ -13446,25 +13446,25 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B377" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C377" t="s">
         <v>261</v>
       </c>
       <c r="D377" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E377" t="s">
         <v>388</v>
       </c>
       <c r="F377" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G377" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H377">
         <v>1</v>
@@ -13475,16 +13475,16 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B378" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C378" t="s">
         <v>261</v>
       </c>
       <c r="D378" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E378" t="s">
         <v>388</v>
@@ -13493,7 +13493,7 @@
         <v>389</v>
       </c>
       <c r="G378" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H378">
         <v>2</v>
@@ -13519,13 +13519,13 @@
         <v>388</v>
       </c>
       <c r="F379" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G379" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H379">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I379" t="s">
         <v>721</v>
@@ -13548,13 +13548,13 @@
         <v>388</v>
       </c>
       <c r="F380" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G380" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H380">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I380" t="s">
         <v>721</v>
@@ -13562,28 +13562,28 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B381" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C381" t="s">
         <v>261</v>
       </c>
       <c r="D381" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E381" t="s">
         <v>388</v>
       </c>
       <c r="F381" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G381" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H381">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I381" t="s">
         <v>721</v>
@@ -13591,28 +13591,28 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B382" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C382" t="s">
         <v>261</v>
       </c>
       <c r="D382" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E382" t="s">
         <v>388</v>
       </c>
       <c r="F382" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G382" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H382">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I382" t="s">
         <v>721</v>
@@ -13620,16 +13620,16 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B383" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C383" t="s">
         <v>261</v>
       </c>
       <c r="D383" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E383" t="s">
         <v>388</v>
@@ -13638,7 +13638,7 @@
         <v>388</v>
       </c>
       <c r="G383" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H383">
         <v>1</v>
@@ -13649,16 +13649,16 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B384" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C384" t="s">
         <v>261</v>
       </c>
       <c r="D384" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E384" t="s">
         <v>388</v>
@@ -13667,7 +13667,7 @@
         <v>389</v>
       </c>
       <c r="G384" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H384">
         <v>2</v>
@@ -13678,25 +13678,25 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B385" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C385" t="s">
         <v>261</v>
       </c>
       <c r="D385" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E385" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F385" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G385" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H385">
         <v>1</v>
@@ -13707,25 +13707,25 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B386" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C386" t="s">
         <v>261</v>
       </c>
       <c r="D386" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E386" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F386" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G386" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H386">
         <v>2</v>
@@ -13751,13 +13751,13 @@
         <v>387</v>
       </c>
       <c r="F387" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G387" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H387">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I387" t="s">
         <v>721</v>
@@ -13765,28 +13765,28 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B388" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C388" t="s">
         <v>261</v>
       </c>
       <c r="D388" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E388" t="s">
         <v>387</v>
       </c>
       <c r="F388" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G388" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H388">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I388" t="s">
         <v>721</v>
@@ -13794,28 +13794,28 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B389" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C389" t="s">
         <v>261</v>
       </c>
       <c r="D389" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E389" t="s">
         <v>387</v>
       </c>
       <c r="F389" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G389" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H389">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I389" t="s">
         <v>721</v>
@@ -13838,13 +13838,13 @@
         <v>387</v>
       </c>
       <c r="F390" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G390" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="H390">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I390" t="s">
         <v>721</v>
@@ -13852,28 +13852,28 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B391" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C391" t="s">
         <v>261</v>
       </c>
       <c r="D391" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E391" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F391" t="s">
         <v>388</v>
       </c>
       <c r="G391" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="H391">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I391" t="s">
         <v>721</v>
@@ -13881,28 +13881,28 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B392" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C392" t="s">
         <v>261</v>
       </c>
       <c r="D392" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E392" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F392" t="s">
         <v>389</v>
       </c>
       <c r="G392" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H392">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I392" t="s">
         <v>721</v>
@@ -13910,25 +13910,25 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B393" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C393" t="s">
         <v>261</v>
       </c>
       <c r="D393" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E393" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F393" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G393" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H393">
         <v>1</v>
@@ -13939,25 +13939,25 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B394" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C394" t="s">
         <v>261</v>
       </c>
       <c r="D394" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E394" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F394" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G394" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H394">
         <v>2</v>
@@ -13983,13 +13983,13 @@
         <v>387</v>
       </c>
       <c r="F395" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G395" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H395">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I395" t="s">
         <v>721</v>
@@ -13997,28 +13997,28 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B396" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C396" t="s">
         <v>261</v>
       </c>
       <c r="D396" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E396" t="s">
         <v>387</v>
       </c>
       <c r="F396" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G396" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H396">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I396" t="s">
         <v>721</v>
@@ -14026,28 +14026,28 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B397" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C397" t="s">
         <v>261</v>
       </c>
       <c r="D397" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E397" t="s">
         <v>387</v>
       </c>
       <c r="F397" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G397" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H397">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I397" t="s">
         <v>721</v>
@@ -14070,13 +14070,13 @@
         <v>387</v>
       </c>
       <c r="F398" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G398" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H398">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I398" t="s">
         <v>721</v>
@@ -14084,28 +14084,28 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B399" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C399" t="s">
         <v>261</v>
       </c>
       <c r="D399" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E399" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F399" t="s">
         <v>388</v>
       </c>
       <c r="G399" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H399">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I399" t="s">
         <v>721</v>
@@ -14113,28 +14113,28 @@
     </row>
     <row r="400" spans="1:9">
       <c r="A400" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B400" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C400" t="s">
         <v>261</v>
       </c>
       <c r="D400" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E400" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F400" t="s">
         <v>389</v>
       </c>
       <c r="G400" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H400">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I400" t="s">
         <v>721</v>
@@ -14142,16 +14142,16 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B401" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C401" t="s">
         <v>261</v>
       </c>
       <c r="D401" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E401" t="s">
         <v>388</v>
@@ -14160,7 +14160,7 @@
         <v>388</v>
       </c>
       <c r="G401" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H401">
         <v>1</v>
@@ -14171,16 +14171,16 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B402" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C402" t="s">
         <v>261</v>
       </c>
       <c r="D402" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E402" t="s">
         <v>388</v>
@@ -14189,7 +14189,7 @@
         <v>389</v>
       </c>
       <c r="G402" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H402">
         <v>2</v>
@@ -14200,25 +14200,25 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B403" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C403" t="s">
         <v>261</v>
       </c>
       <c r="D403" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E403" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F403" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G403" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H403">
         <v>1</v>
@@ -14229,25 +14229,25 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B404" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C404" t="s">
         <v>261</v>
       </c>
       <c r="D404" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E404" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F404" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G404" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H404">
         <v>2</v>
@@ -14273,13 +14273,13 @@
         <v>387</v>
       </c>
       <c r="F405" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G405" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H405">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I405" t="s">
         <v>721</v>
@@ -14287,28 +14287,28 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B406" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C406" t="s">
         <v>261</v>
       </c>
       <c r="D406" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E406" t="s">
         <v>387</v>
       </c>
       <c r="F406" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G406" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H406">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I406" t="s">
         <v>721</v>
@@ -14316,28 +14316,28 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B407" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C407" t="s">
         <v>261</v>
       </c>
       <c r="D407" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E407" t="s">
         <v>387</v>
       </c>
       <c r="F407" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G407" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H407">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I407" t="s">
         <v>721</v>
@@ -14360,13 +14360,13 @@
         <v>387</v>
       </c>
       <c r="F408" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G408" t="s">
-        <v>590</v>
+        <v>687</v>
       </c>
       <c r="H408">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I408" t="s">
         <v>721</v>
@@ -14374,28 +14374,28 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B409" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C409" t="s">
         <v>261</v>
       </c>
       <c r="D409" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E409" t="s">
         <v>387</v>
       </c>
       <c r="F409" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G409" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H409">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I409" t="s">
         <v>721</v>
@@ -14403,28 +14403,28 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B410" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C410" t="s">
         <v>261</v>
       </c>
       <c r="D410" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E410" t="s">
         <v>387</v>
       </c>
       <c r="F410" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G410" t="s">
-        <v>690</v>
+        <v>590</v>
       </c>
       <c r="H410">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I410" t="s">
         <v>721</v>
@@ -14447,13 +14447,13 @@
         <v>387</v>
       </c>
       <c r="F411" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G411" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H411">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I411" t="s">
         <v>721</v>
@@ -14461,28 +14461,28 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B412" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C412" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D412" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E412" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F412" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G412" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="H412">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I412" t="s">
         <v>721</v>
@@ -14490,28 +14490,28 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B413" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C413" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D413" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E413" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F413" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G413" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H413">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I413" t="s">
         <v>721</v>
@@ -14534,13 +14534,13 @@
         <v>388</v>
       </c>
       <c r="F414" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G414" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H414">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I414" t="s">
         <v>721</v>
@@ -14563,13 +14563,13 @@
         <v>388</v>
       </c>
       <c r="F415" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G415" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H415">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I415" t="s">
         <v>721</v>
@@ -14592,13 +14592,13 @@
         <v>388</v>
       </c>
       <c r="F416" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G416" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="H416">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I416" t="s">
         <v>721</v>
@@ -14621,13 +14621,13 @@
         <v>388</v>
       </c>
       <c r="F417" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G417" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H417">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I417" t="s">
         <v>721</v>
@@ -14653,10 +14653,10 @@
         <v>389</v>
       </c>
       <c r="G418" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H418">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I418" t="s">
         <v>721</v>
@@ -14664,28 +14664,28 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C419" t="s">
         <v>258</v>
       </c>
       <c r="D419" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E419" t="s">
         <v>388</v>
       </c>
       <c r="F419" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G419" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H419">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I419" t="s">
         <v>721</v>
@@ -14693,28 +14693,28 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C420" t="s">
         <v>258</v>
       </c>
       <c r="D420" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E420" t="s">
         <v>388</v>
       </c>
       <c r="F420" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G420" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H420">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I420" t="s">
         <v>721</v>
@@ -14740,10 +14740,10 @@
         <v>392</v>
       </c>
       <c r="G421" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H421">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I421" t="s">
         <v>721</v>
@@ -14769,10 +14769,10 @@
         <v>392</v>
       </c>
       <c r="G422" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="H422">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I422" t="s">
         <v>721</v>
@@ -14798,10 +14798,10 @@
         <v>392</v>
       </c>
       <c r="G423" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H423">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I423" t="s">
         <v>721</v>
@@ -14824,13 +14824,13 @@
         <v>388</v>
       </c>
       <c r="F424" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G424" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H424">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I424" t="s">
         <v>721</v>
@@ -14853,13 +14853,13 @@
         <v>388</v>
       </c>
       <c r="F425" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G425" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H425">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I425" t="s">
         <v>721</v>
@@ -14867,28 +14867,28 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B426" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C426" t="s">
         <v>258</v>
       </c>
       <c r="D426" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E426" t="s">
         <v>388</v>
       </c>
       <c r="F426" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G426" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H426">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I426" t="s">
         <v>721</v>
@@ -14896,28 +14896,28 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B427" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C427" t="s">
         <v>258</v>
       </c>
       <c r="D427" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E427" t="s">
         <v>388</v>
       </c>
       <c r="F427" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G427" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H427">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I427" t="s">
         <v>721</v>
@@ -14940,13 +14940,13 @@
         <v>388</v>
       </c>
       <c r="F428" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G428" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H428">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I428" t="s">
         <v>721</v>
@@ -14954,28 +14954,28 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="B429" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="C429" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D429" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="E429" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F429" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G429" t="s">
-        <v>596</v>
+        <v>707</v>
       </c>
       <c r="H429">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I429" t="s">
         <v>721</v>
@@ -14983,28 +14983,28 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="B430" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="C430" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D430" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
       <c r="E430" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F430" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G430" t="s">
-        <v>597</v>
+        <v>708</v>
       </c>
       <c r="H430">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I430" t="s">
         <v>721</v>
@@ -15024,16 +15024,16 @@
         <v>341</v>
       </c>
       <c r="E431" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F431" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G431" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H431">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I431" t="s">
         <v>721</v>
@@ -15041,28 +15041,28 @@
     </row>
     <row r="432" spans="1:9">
       <c r="A432" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B432" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C432" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D432" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E432" t="s">
         <v>388</v>
       </c>
       <c r="F432" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G432" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H432">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I432" t="s">
         <v>721</v>
@@ -15076,22 +15076,22 @@
         <v>213</v>
       </c>
       <c r="C433" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D433" t="s">
         <v>342</v>
       </c>
       <c r="E433" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F433" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G433" t="s">
-        <v>599</v>
+        <v>428</v>
       </c>
       <c r="H433">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I433" t="s">
         <v>721</v>
@@ -15099,28 +15099,28 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B434" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C434" t="s">
         <v>261</v>
       </c>
       <c r="D434" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E434" t="s">
         <v>387</v>
       </c>
       <c r="F434" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G434" t="s">
-        <v>428</v>
+        <v>598</v>
       </c>
       <c r="H434">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I434" t="s">
         <v>721</v>
@@ -15128,28 +15128,28 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B435" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C435" t="s">
         <v>261</v>
       </c>
       <c r="D435" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E435" t="s">
         <v>387</v>
       </c>
       <c r="F435" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G435" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="H435">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I435" t="s">
         <v>721</v>
@@ -15157,28 +15157,28 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B436" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C436" t="s">
         <v>261</v>
       </c>
       <c r="D436" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E436" t="s">
         <v>387</v>
       </c>
       <c r="F436" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G436" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="H436">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I436" t="s">
         <v>721</v>
@@ -15186,28 +15186,28 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B437" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C437" t="s">
         <v>261</v>
       </c>
       <c r="D437" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E437" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F437" t="s">
         <v>388</v>
       </c>
       <c r="G437" t="s">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="H437">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I437" t="s">
         <v>721</v>
@@ -15215,28 +15215,28 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B438" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C438" t="s">
         <v>261</v>
       </c>
       <c r="D438" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="E438" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F438" t="s">
         <v>389</v>
       </c>
       <c r="G438" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="H438">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I438" t="s">
         <v>721</v>
@@ -15244,25 +15244,25 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B439" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C439" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D439" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="E439" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F439" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G439" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="H439">
         <v>1</v>
@@ -15273,25 +15273,25 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B440" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D440" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="E440" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F440" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G440" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="H440">
         <v>2</v>
@@ -15302,28 +15302,28 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B441" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C441" t="s">
         <v>261</v>
       </c>
       <c r="D441" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E441" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F441" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G441" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="H441">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I441" t="s">
         <v>721</v>
@@ -15331,28 +15331,28 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B442" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C442" t="s">
         <v>261</v>
       </c>
       <c r="D442" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E442" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F442" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G442" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H442">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I442" t="s">
         <v>721</v>
@@ -15360,7 +15360,7 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B443" t="s">
         <v>229</v>
@@ -15375,13 +15375,13 @@
         <v>387</v>
       </c>
       <c r="F443" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G443" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H443">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I443" t="s">
         <v>721</v>
@@ -15389,7 +15389,7 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B444" t="s">
         <v>229</v>
@@ -15404,13 +15404,13 @@
         <v>387</v>
       </c>
       <c r="F444" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G444" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H444">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I444" t="s">
         <v>721</v>
@@ -15418,28 +15418,28 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B445" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C445" t="s">
         <v>261</v>
       </c>
       <c r="D445" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E445" t="s">
         <v>387</v>
       </c>
       <c r="F445" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G445" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H445">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I445" t="s">
         <v>721</v>
@@ -15447,28 +15447,28 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B446" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C446" t="s">
         <v>261</v>
       </c>
       <c r="D446" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E446" t="s">
         <v>387</v>
       </c>
       <c r="F446" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G446" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="H446">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I446" t="s">
         <v>721</v>
@@ -15476,28 +15476,28 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B447" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C447" t="s">
         <v>261</v>
       </c>
       <c r="D447" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E447" t="s">
         <v>387</v>
       </c>
       <c r="F447" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G447" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="H447">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I447" t="s">
         <v>721</v>
@@ -15505,28 +15505,28 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B448" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C448" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D448" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E448" t="s">
         <v>387</v>
       </c>
       <c r="F448" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G448" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="H448">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I448" t="s">
         <v>721</v>
@@ -15534,28 +15534,28 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B449" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C449" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D449" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E449" t="s">
         <v>387</v>
       </c>
       <c r="F449" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G449" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="H449">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I449" t="s">
         <v>721</v>
@@ -15563,28 +15563,28 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B450" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C450" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D450" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E450" t="s">
         <v>387</v>
       </c>
       <c r="F450" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G450" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="H450">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I450" t="s">
         <v>721</v>
@@ -15592,28 +15592,28 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="B451" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="C451" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D451" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="E451" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F451" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G451" t="s">
-        <v>692</v>
+        <v>631</v>
       </c>
       <c r="H451">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I451" t="s">
         <v>721</v>
@@ -15621,28 +15621,28 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B452" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C452" t="s">
         <v>258</v>
       </c>
       <c r="D452" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="E452" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F452" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="G452" t="s">
-        <v>693</v>
+        <v>634</v>
       </c>
       <c r="H452">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I452" t="s">
         <v>721</v>
@@ -15650,28 +15650,28 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B453" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C453" t="s">
         <v>258</v>
       </c>
       <c r="D453" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="E453" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F453" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G453" t="s">
-        <v>694</v>
+        <v>635</v>
       </c>
       <c r="H453">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I453" t="s">
         <v>721</v>
@@ -15679,28 +15679,28 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B454" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="C454" t="s">
         <v>258</v>
       </c>
       <c r="D454" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="E454" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F454" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G454" t="s">
-        <v>695</v>
+        <v>636</v>
       </c>
       <c r="H454">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I454" t="s">
         <v>721</v>
@@ -15723,13 +15723,13 @@
         <v>388</v>
       </c>
       <c r="F455" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G455" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="H455">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I455" t="s">
         <v>721</v>
@@ -15752,13 +15752,13 @@
         <v>388</v>
       </c>
       <c r="F456" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G456" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="H456">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I456" t="s">
         <v>721</v>
@@ -15781,13 +15781,13 @@
         <v>388</v>
       </c>
       <c r="F457" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G457" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="H457">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I457" t="s">
         <v>721</v>
@@ -15795,28 +15795,28 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B458" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C458" t="s">
         <v>258</v>
       </c>
       <c r="D458" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E458" t="s">
         <v>388</v>
       </c>
       <c r="F458" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G458" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="H458">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I458" t="s">
         <v>721</v>
@@ -15824,28 +15824,28 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B459" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C459" t="s">
         <v>258</v>
       </c>
       <c r="D459" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E459" t="s">
         <v>388</v>
       </c>
       <c r="F459" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G459" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="H459">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I459" t="s">
         <v>721</v>
@@ -15853,28 +15853,28 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B460" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C460" t="s">
         <v>258</v>
       </c>
       <c r="D460" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E460" t="s">
         <v>388</v>
       </c>
       <c r="F460" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G460" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="H460">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I460" t="s">
         <v>721</v>
@@ -15882,28 +15882,28 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B461" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C461" t="s">
         <v>258</v>
       </c>
       <c r="D461" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E461" t="s">
         <v>388</v>
       </c>
       <c r="F461" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G461" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="H461">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I461" t="s">
         <v>721</v>
@@ -15929,10 +15929,10 @@
         <v>392</v>
       </c>
       <c r="G462" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="H462">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I462" t="s">
         <v>721</v>
@@ -15955,13 +15955,13 @@
         <v>388</v>
       </c>
       <c r="F463" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G463" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="H463">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I463" t="s">
         <v>721</v>
@@ -15984,13 +15984,13 @@
         <v>388</v>
       </c>
       <c r="F464" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G464" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="H464">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I464" t="s">
         <v>721</v>
@@ -15998,28 +15998,28 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B465" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C465" t="s">
         <v>258</v>
       </c>
       <c r="D465" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E465" t="s">
         <v>388</v>
       </c>
       <c r="F465" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G465" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="H465">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I465" t="s">
         <v>721</v>
@@ -16027,28 +16027,28 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B466" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C466" t="s">
         <v>258</v>
       </c>
       <c r="D466" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E466" t="s">
         <v>388</v>
       </c>
       <c r="F466" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G466" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H466">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I466" t="s">
         <v>721</v>
@@ -16056,30 +16056,146 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B467" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C467" t="s">
         <v>258</v>
       </c>
       <c r="D467" t="s">
+        <v>385</v>
+      </c>
+      <c r="E467" t="s">
+        <v>388</v>
+      </c>
+      <c r="F467" t="s">
+        <v>388</v>
+      </c>
+      <c r="G467" t="s">
+        <v>704</v>
+      </c>
+      <c r="H467">
+        <v>6</v>
+      </c>
+      <c r="I467" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9">
+      <c r="A468" t="s">
+        <v>134</v>
+      </c>
+      <c r="B468" t="s">
+        <v>256</v>
+      </c>
+      <c r="C468" t="s">
+        <v>258</v>
+      </c>
+      <c r="D468" t="s">
+        <v>385</v>
+      </c>
+      <c r="E468" t="s">
+        <v>388</v>
+      </c>
+      <c r="F468" t="s">
+        <v>389</v>
+      </c>
+      <c r="G468" t="s">
+        <v>705</v>
+      </c>
+      <c r="H468">
+        <v>7</v>
+      </c>
+      <c r="I468" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9">
+      <c r="A469" t="s">
+        <v>135</v>
+      </c>
+      <c r="B469" t="s">
+        <v>257</v>
+      </c>
+      <c r="C469" t="s">
+        <v>258</v>
+      </c>
+      <c r="D469" t="s">
         <v>386</v>
       </c>
-      <c r="E467" t="s">
-        <v>388</v>
-      </c>
-      <c r="F467" t="s">
-        <v>389</v>
-      </c>
-      <c r="G467" t="s">
+      <c r="E469" t="s">
+        <v>388</v>
+      </c>
+      <c r="F469" t="s">
+        <v>391</v>
+      </c>
+      <c r="G469" t="s">
+        <v>706</v>
+      </c>
+      <c r="H469">
+        <v>1</v>
+      </c>
+      <c r="I469" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9">
+      <c r="A470" t="s">
+        <v>135</v>
+      </c>
+      <c r="B470" t="s">
+        <v>257</v>
+      </c>
+      <c r="C470" t="s">
+        <v>258</v>
+      </c>
+      <c r="D470" t="s">
+        <v>386</v>
+      </c>
+      <c r="E470" t="s">
+        <v>388</v>
+      </c>
+      <c r="F470" t="s">
+        <v>388</v>
+      </c>
+      <c r="G470" t="s">
+        <v>707</v>
+      </c>
+      <c r="H470">
+        <v>2</v>
+      </c>
+      <c r="I470" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9">
+      <c r="A471" t="s">
+        <v>135</v>
+      </c>
+      <c r="B471" t="s">
+        <v>257</v>
+      </c>
+      <c r="C471" t="s">
+        <v>258</v>
+      </c>
+      <c r="D471" t="s">
+        <v>386</v>
+      </c>
+      <c r="E471" t="s">
+        <v>388</v>
+      </c>
+      <c r="F471" t="s">
+        <v>389</v>
+      </c>
+      <c r="G471" t="s">
         <v>708</v>
       </c>
-      <c r="H467">
+      <c r="H471">
         <v>3</v>
       </c>
-      <c r="I467" t="s">
+      <c r="I471" t="s">
         <v>721</v>
       </c>
     </row>
